--- a/Database/260126_Datenbankdefinition.xlsx
+++ b/Database/260126_Datenbankdefinition.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tgalk\PycharmProjects\SustainabilityOfStructures\Database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonathanbieg/Documents/Master Thesis/1_Code/Python Repository/SDSD_Bieg/Database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{183820BB-F748-4A5F-9675-0F00DC433DA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7000399-25EF-384F-AE9D-829B72397CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="30960" windowHeight="15720" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
+    <workbookView xWindow="1340" yWindow="2200" windowWidth="16760" windowHeight="15840" activeTab="3" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
   </bookViews>
   <sheets>
     <sheet name="products" sheetId="1" r:id="rId1"/>
     <sheet name="material_prop" sheetId="2" r:id="rId2"/>
     <sheet name="floor_struc_prop" sheetId="4" r:id="rId3"/>
+    <sheet name="connector_TCC" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -92,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1881" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="520">
   <si>
     <t>B500B</t>
   </si>
@@ -1648,6 +1649,27 @@
   </si>
   <si>
     <t>ValidEPD</t>
+  </si>
+  <si>
+    <t>DBS_6</t>
+  </si>
+  <si>
+    <t>DBS_8</t>
+  </si>
+  <si>
+    <t>DBS_10</t>
+  </si>
+  <si>
+    <t>DBS_12</t>
+  </si>
+  <si>
+    <t>K_ser [N/m]2</t>
+  </si>
+  <si>
+    <t>d [m]</t>
+  </si>
+  <si>
+    <t>Kerve</t>
   </si>
 </sst>
 </file>
@@ -2215,7 +2237,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="211">
+  <cellXfs count="212">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2683,12 +2705,13 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Standard 2" xfId="1" xr:uid="{FDCFE4BD-E849-456C-8E2E-B78D9BD993F6}"/>
   </cellStyles>
-  <dxfs count="46">
+  <dxfs count="55">
     <dxf>
       <font>
         <b/>
@@ -2708,6 +2731,216 @@
       <fill>
         <patternFill patternType="none">
           <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3770,42 +4003,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}" name="Table2" displayName="Table2" ref="A1:AB132" totalsRowShown="0" headerRowDxfId="45" dataDxfId="44">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}" name="Table2" displayName="Table2" ref="A1:AB132" totalsRowShown="0" headerRowDxfId="54" dataDxfId="53">
   <autoFilter ref="A1:AB132" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}"/>
   <tableColumns count="28">
-    <tableColumn id="9" xr3:uid="{1DBBD25D-72F9-4A81-9CFA-500505E3628D}" name="ID" dataDxfId="43"/>
-    <tableColumn id="14" xr3:uid="{6844A52F-C967-44C0-BF5C-160C47AB6E64}" name="PRO_ID" dataDxfId="42"/>
-    <tableColumn id="12" xr3:uid="{4EDF1E73-4744-474F-8DFE-7F72FB05613C}" name="EPD_ID" dataDxfId="41"/>
-    <tableColumn id="1" xr3:uid="{1CF2E22E-1020-4F35-B31F-6350A15A5DE8}" name="SOURCE" dataDxfId="40"/>
-    <tableColumn id="27" xr3:uid="{07F74D5D-9130-4120-B02C-A11234427F46}" name="KBOB ID-Nr." dataDxfId="39"/>
-    <tableColumn id="11" xr3:uid="{81FE7F31-5F54-40F9-B99E-827E048F7DB5}" name="EPD_DATE" dataDxfId="38"/>
-    <tableColumn id="10" xr3:uid="{54D8BA04-0FEF-4C3B-9B14-59E8F982CD3F}" name="VALID_TO" dataDxfId="37"/>
-    <tableColumn id="22" xr3:uid="{3D6FC370-B8A8-40C3-9FC8-791B178DDFDF}" name="COUNTRY" dataDxfId="36"/>
-    <tableColumn id="4" xr3:uid="{25C7280F-4E3E-4E39-BDBB-DC06DF090C5B}" name="PRODUCT_NAME" dataDxfId="35"/>
-    <tableColumn id="26" xr3:uid="{1053A7DD-B11F-4E75-92EC-BC0F866E90B4}" name="OEKOBAUDAT_ID" dataDxfId="34"/>
-    <tableColumn id="25" xr3:uid="{295F99F8-E318-45C9-833E-F0B45A26471A}" name="MATERIAL_GROUP" dataDxfId="33"/>
-    <tableColumn id="2" xr3:uid="{1326FCEF-D1EE-4F3A-BB8B-77CB4EC72B0C}" name="MATERIAL" dataDxfId="32"/>
-    <tableColumn id="5" xr3:uid="{9B2A7F84-D968-4A00-B61F-23BB0661E7A3}" name="CEMENT" dataDxfId="31"/>
-    <tableColumn id="6" xr3:uid="{2F6E5831-6238-4360-9CFD-ED23A193E761}" name="MECH_PROP" dataDxfId="30"/>
-    <tableColumn id="13" xr3:uid="{50DAB01C-8AF5-4E0C-9904-54F70B81BC55}" name="DENSITY" dataDxfId="29"/>
-    <tableColumn id="18" xr3:uid="{F799A4D4-9543-475F-989E-CFBA47249558}" name="EXPOSITIONSKLASSE" dataDxfId="28"/>
-    <tableColumn id="17" xr3:uid="{ECCBC067-991C-4C60-942D-806BCD77B990}" name="GROESSTKORN" dataDxfId="27"/>
-    <tableColumn id="16" xr3:uid="{05157B85-D5FB-4844-9B53-D8AB09BCE0D9}" name="CHLORIDGEHALT" dataDxfId="26"/>
-    <tableColumn id="15" xr3:uid="{9F53CF50-7148-405A-9295-1F0C3C45645A}" name="KONSISTENZKLASSE" dataDxfId="25"/>
-    <tableColumn id="7" xr3:uid="{E23232F6-E86E-4AD2-8257-F30C0D1F7368}" name="Total_GWP" dataDxfId="24"/>
-    <tableColumn id="20" xr3:uid="{0A9001B4-3AB4-4C58-B125-0B2AA4DB2681}" name="A1toA3_GWP" dataDxfId="23">
+    <tableColumn id="9" xr3:uid="{1DBBD25D-72F9-4A81-9CFA-500505E3628D}" name="ID" dataDxfId="52"/>
+    <tableColumn id="14" xr3:uid="{6844A52F-C967-44C0-BF5C-160C47AB6E64}" name="PRO_ID" dataDxfId="51"/>
+    <tableColumn id="12" xr3:uid="{4EDF1E73-4744-474F-8DFE-7F72FB05613C}" name="EPD_ID" dataDxfId="50"/>
+    <tableColumn id="1" xr3:uid="{1CF2E22E-1020-4F35-B31F-6350A15A5DE8}" name="SOURCE" dataDxfId="49"/>
+    <tableColumn id="27" xr3:uid="{07F74D5D-9130-4120-B02C-A11234427F46}" name="KBOB ID-Nr." dataDxfId="48"/>
+    <tableColumn id="11" xr3:uid="{81FE7F31-5F54-40F9-B99E-827E048F7DB5}" name="EPD_DATE" dataDxfId="47"/>
+    <tableColumn id="10" xr3:uid="{54D8BA04-0FEF-4C3B-9B14-59E8F982CD3F}" name="VALID_TO" dataDxfId="46"/>
+    <tableColumn id="22" xr3:uid="{3D6FC370-B8A8-40C3-9FC8-791B178DDFDF}" name="COUNTRY" dataDxfId="45"/>
+    <tableColumn id="4" xr3:uid="{25C7280F-4E3E-4E39-BDBB-DC06DF090C5B}" name="PRODUCT_NAME" dataDxfId="44"/>
+    <tableColumn id="26" xr3:uid="{1053A7DD-B11F-4E75-92EC-BC0F866E90B4}" name="OEKOBAUDAT_ID" dataDxfId="43"/>
+    <tableColumn id="25" xr3:uid="{295F99F8-E318-45C9-833E-F0B45A26471A}" name="MATERIAL_GROUP" dataDxfId="42"/>
+    <tableColumn id="2" xr3:uid="{1326FCEF-D1EE-4F3A-BB8B-77CB4EC72B0C}" name="MATERIAL" dataDxfId="41"/>
+    <tableColumn id="5" xr3:uid="{9B2A7F84-D968-4A00-B61F-23BB0661E7A3}" name="CEMENT" dataDxfId="40"/>
+    <tableColumn id="6" xr3:uid="{2F6E5831-6238-4360-9CFD-ED23A193E761}" name="MECH_PROP" dataDxfId="39"/>
+    <tableColumn id="13" xr3:uid="{50DAB01C-8AF5-4E0C-9904-54F70B81BC55}" name="DENSITY" dataDxfId="38"/>
+    <tableColumn id="18" xr3:uid="{F799A4D4-9543-475F-989E-CFBA47249558}" name="EXPOSITIONSKLASSE" dataDxfId="37"/>
+    <tableColumn id="17" xr3:uid="{ECCBC067-991C-4C60-942D-806BCD77B990}" name="GROESSTKORN" dataDxfId="36"/>
+    <tableColumn id="16" xr3:uid="{05157B85-D5FB-4844-9B53-D8AB09BCE0D9}" name="CHLORIDGEHALT" dataDxfId="35"/>
+    <tableColumn id="15" xr3:uid="{9F53CF50-7148-405A-9295-1F0C3C45645A}" name="KONSISTENZKLASSE" dataDxfId="34"/>
+    <tableColumn id="7" xr3:uid="{E23232F6-E86E-4AD2-8257-F30C0D1F7368}" name="Total_GWP" dataDxfId="33"/>
+    <tableColumn id="20" xr3:uid="{0A9001B4-3AB4-4C58-B125-0B2AA4DB2681}" name="A1toA3_GWP" dataDxfId="32">
       <calculatedColumnFormula>119+10.9+238</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{2799394A-C481-45CE-B194-AAABAB0AED38}" name="C1toC4_GWP" dataDxfId="22">
+    <tableColumn id="21" xr3:uid="{2799394A-C481-45CE-B194-AAABAB0AED38}" name="C1toC4_GWP" dataDxfId="31">
       <calculatedColumnFormula>51.1+26+2.64+12.6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{70561D70-9D02-4E93-A395-229DA8696DDA}" name="ValidEPD" dataDxfId="21">
+    <tableColumn id="19" xr3:uid="{70561D70-9D02-4E93-A395-229DA8696DDA}" name="ValidEPD" dataDxfId="30">
       <calculatedColumnFormula>IF(OR($D2="Ecoinvent",$D2="Betonsortenrechner",$D2="KBOB",$T2&lt;=0),0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{92D55BC7-F55B-406A-B127-69EC2F0A8B77}" name="noch gültig" dataDxfId="20">
+    <tableColumn id="29" xr3:uid="{92D55BC7-F55B-406A-B127-69EC2F0A8B77}" name="noch gültig" dataDxfId="29">
       <calculatedColumnFormula>IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{DB90AC0A-8933-4040-BADE-E6EE11AC8BD7}" name="Statistik" dataDxfId="19">
+    <tableColumn id="3" xr3:uid="{DB90AC0A-8933-4040-BADE-E6EE11AC8BD7}" name="Statistik" dataDxfId="28">
       <calculatedColumnFormula array="1">IF($W2&lt;&gt;0,
 IF(AND(
                          T2&gt;=_xlfn.PERCENTILE.INC(_xlfn._xlws.FILTER($T$2:$T$148, ($L$2:$L$148=L2)*($W$2:$W$148=1)),0.1),
@@ -3813,27 +4046,40 @@
                ),1,0),
 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{BBA6C134-63F9-4711-8B25-086098EC2CB0}" name="Cost" dataDxfId="18"/>
-    <tableColumn id="24" xr3:uid="{5321A0E1-043C-4E95-A6DA-41830364B2BC}" name="Anmerkung" dataDxfId="17"/>
-    <tableColumn id="23" xr3:uid="{61456234-34E8-4222-B2D6-9DDA8E83B081}" name="Spalte 1" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{BBA6C134-63F9-4711-8B25-086098EC2CB0}" name="Cost" dataDxfId="27"/>
+    <tableColumn id="24" xr3:uid="{5321A0E1-043C-4E95-A6DA-41830364B2BC}" name="Anmerkung" dataDxfId="26"/>
+    <tableColumn id="23" xr3:uid="{61456234-34E8-4222-B2D6-9DDA8E83B081}" name="Spalte 1" dataDxfId="25"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}" name="Tabelle4" displayName="Tabelle4" ref="A1:I8" totalsRowShown="0" headerRowDxfId="15" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12" totalsRowBorderDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}" name="Tabelle4" displayName="Tabelle4" ref="A1:I8" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
   <autoFilter ref="A1:I8" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{AF3C694B-2C8A-40EE-B8BB-2EC9EB81A87A}" name="mat_ID" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{B447FBC2-C455-4332-8F47-150B112A57E0}" name="name" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{BAFC6B47-7268-46CC-A881-892C9A1F4334}" name="strength_comp" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{6FC4C8EB-7581-4E67-81CE-C724161F0838}" name="strength_tens" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{A875970E-61A9-43B5-9361-7616A74C3147}" name="strength_bend" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{EF5B3A69-DD70-420A-88FF-4FE8772A2E14}" name="strength_shea" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{ED461A80-736C-42BD-81BC-C5C0C80FF34C}" name="E_modulus" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{68E47481-7028-4427-B126-2A046FC46737}" name="density_load" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{7AB34570-2BD4-417F-B141-70612577C7D6}" name="burn_rate" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{AF3C694B-2C8A-40EE-B8BB-2EC9EB81A87A}" name="mat_ID" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{B447FBC2-C455-4332-8F47-150B112A57E0}" name="name" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{BAFC6B47-7268-46CC-A881-892C9A1F4334}" name="strength_comp" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{6FC4C8EB-7581-4E67-81CE-C724161F0838}" name="strength_tens" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{A875970E-61A9-43B5-9361-7616A74C3147}" name="strength_bend" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{EF5B3A69-DD70-420A-88FF-4FE8772A2E14}" name="strength_shea" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{ED461A80-736C-42BD-81BC-C5C0C80FF34C}" name="E_modulus" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{68E47481-7028-4427-B126-2A046FC46737}" name="density_load" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{7AB34570-2BD4-417F-B141-70612577C7D6}" name="burn_rate" dataDxfId="11"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1CD264FD-E2C0-E94F-B387-736226CC982D}" name="Tabelle42" displayName="Tabelle42" ref="A1:D6" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" headerRowBorderDxfId="7" tableBorderDxfId="8" totalsRowBorderDxfId="6">
+  <autoFilter ref="A1:D6" xr:uid="{1CD264FD-E2C0-E94F-B387-736226CC982D}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{6590463D-C242-4C4D-AA1F-6FA1F0D35E6F}" name="mat_ID" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{603BAED4-55F2-D040-9D73-1611C1564A84}" name="name" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{D6CC67C0-1ACA-D446-A6F3-00BCC3AC8DAC}" name="d [m]" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{3D62C7FF-3D7F-B245-A874-3A95DF0C49D2}" name="K_ser [N/m]2" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4137,35 +4383,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62619769-F4C0-43FE-B7CF-7C389D172BEA}">
   <dimension ref="A1:AC1048474"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" style="46" customWidth="1"/>
+    <col min="1" max="1" width="6.5" style="46" customWidth="1"/>
     <col min="2" max="2" width="5" style="74" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="24.28515625" customWidth="1"/>
-    <col min="5" max="7" width="10.7109375" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" style="44" customWidth="1"/>
-    <col min="9" max="9" width="19.42578125" customWidth="1"/>
-    <col min="10" max="11" width="10.7109375" customWidth="1"/>
+    <col min="4" max="4" width="24.33203125" customWidth="1"/>
+    <col min="5" max="7" width="10.6640625" customWidth="1"/>
+    <col min="8" max="8" width="10.6640625" style="44" customWidth="1"/>
+    <col min="9" max="9" width="19.5" customWidth="1"/>
+    <col min="10" max="11" width="10.6640625" customWidth="1"/>
     <col min="12" max="12" width="35" style="51" customWidth="1"/>
-    <col min="13" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="6.7109375" customWidth="1"/>
-    <col min="17" max="18" width="6.7109375" style="45" customWidth="1"/>
-    <col min="19" max="19" width="6.7109375" customWidth="1"/>
-    <col min="20" max="20" width="10.28515625" style="91" customWidth="1"/>
-    <col min="21" max="23" width="6.7109375" style="91" customWidth="1"/>
-    <col min="24" max="24" width="8.28515625" style="91" customWidth="1"/>
-    <col min="25" max="25" width="6.7109375" style="91" customWidth="1"/>
-    <col min="26" max="26" width="6.7109375" customWidth="1"/>
+    <col min="13" max="15" width="10.6640625" customWidth="1"/>
+    <col min="16" max="16" width="6.6640625" customWidth="1"/>
+    <col min="17" max="18" width="6.6640625" style="45" customWidth="1"/>
+    <col min="19" max="19" width="6.6640625" customWidth="1"/>
+    <col min="20" max="20" width="10.33203125" style="91" customWidth="1"/>
+    <col min="21" max="23" width="6.6640625" style="91" customWidth="1"/>
+    <col min="24" max="24" width="8.33203125" style="91" customWidth="1"/>
+    <col min="25" max="25" width="6.6640625" style="91" customWidth="1"/>
+    <col min="26" max="26" width="6.6640625" customWidth="1"/>
     <col min="27" max="27" width="71" customWidth="1"/>
-    <col min="28" max="28" width="23.7109375" style="188" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="32" max="58" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="23.6640625" style="188" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="32" max="58" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="15.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="72" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" s="72" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="65" t="s">
         <v>339</v>
       </c>
@@ -4252,7 +4498,7 @@
       </c>
       <c r="AC1" s="71"/>
     </row>
-    <row r="2" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="92" t="s">
         <v>340</v>
       </c>
@@ -4339,7 +4585,7 @@
       <c r="AB2" s="21"/>
       <c r="AC2" s="21"/>
     </row>
-    <row r="3" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="92" t="s">
         <v>341</v>
       </c>
@@ -4426,7 +4672,7 @@
       <c r="AB3" s="21"/>
       <c r="AC3" s="21"/>
     </row>
-    <row r="4" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="92" t="s">
         <v>342</v>
       </c>
@@ -4513,7 +4759,7 @@
       <c r="AB4" s="21"/>
       <c r="AC4" s="21"/>
     </row>
-    <row r="5" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="92" t="s">
         <v>343</v>
       </c>
@@ -4600,7 +4846,7 @@
       <c r="AB5" s="21"/>
       <c r="AC5" s="21"/>
     </row>
-    <row r="6" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="92" t="s">
         <v>344</v>
       </c>
@@ -4687,7 +4933,7 @@
       <c r="AB6" s="21"/>
       <c r="AC6" s="21"/>
     </row>
-    <row r="7" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="92" t="s">
         <v>345</v>
       </c>
@@ -4764,7 +5010,7 @@
       <c r="AB7" s="21"/>
       <c r="AC7" s="21"/>
     </row>
-    <row r="8" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="92" t="s">
         <v>346</v>
       </c>
@@ -4841,7 +5087,7 @@
       <c r="AB8" s="21"/>
       <c r="AC8" s="21"/>
     </row>
-    <row r="9" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="92" t="s">
         <v>347</v>
       </c>
@@ -4918,7 +5164,7 @@
       <c r="AB9" s="21"/>
       <c r="AC9" s="165"/>
     </row>
-    <row r="10" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="92" t="s">
         <v>348</v>
       </c>
@@ -4995,7 +5241,7 @@
       <c r="AB10" s="21"/>
       <c r="AC10" s="165"/>
     </row>
-    <row r="11" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="92" t="s">
         <v>349</v>
       </c>
@@ -5072,7 +5318,7 @@
       <c r="AB11" s="21"/>
       <c r="AC11" s="165"/>
     </row>
-    <row r="12" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="92" t="s">
         <v>350</v>
       </c>
@@ -5159,7 +5405,7 @@
       <c r="AB12" s="21"/>
       <c r="AC12" s="165"/>
     </row>
-    <row r="13" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="94" t="s">
         <v>351</v>
       </c>
@@ -5249,7 +5495,7 @@
       <c r="AB13" s="21"/>
       <c r="AC13" s="165"/>
     </row>
-    <row r="14" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="94" t="s">
         <v>352</v>
       </c>
@@ -5339,7 +5585,7 @@
       <c r="AB14" s="21"/>
       <c r="AC14" s="165"/>
     </row>
-    <row r="15" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="94" t="s">
         <v>353</v>
       </c>
@@ -5429,7 +5675,7 @@
       <c r="AB15" s="21"/>
       <c r="AC15" s="21"/>
     </row>
-    <row r="16" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="94" t="s">
         <v>354</v>
       </c>
@@ -5519,7 +5765,7 @@
       <c r="AB16" s="21"/>
       <c r="AC16"/>
     </row>
-    <row r="17" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="94" t="s">
         <v>355</v>
       </c>
@@ -5609,7 +5855,7 @@
       <c r="AB17" s="21"/>
       <c r="AC17"/>
     </row>
-    <row r="18" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="94" t="s">
         <v>356</v>
       </c>
@@ -5699,7 +5945,7 @@
       <c r="AB18" s="21"/>
       <c r="AC18"/>
     </row>
-    <row r="19" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="94" t="s">
         <v>357</v>
       </c>
@@ -5789,7 +6035,7 @@
       <c r="AB19" s="21"/>
       <c r="AC19"/>
     </row>
-    <row r="20" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="94" t="s">
         <v>358</v>
       </c>
@@ -5879,7 +6125,7 @@
       <c r="AB20" s="21"/>
       <c r="AC20"/>
     </row>
-    <row r="21" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="94" t="s">
         <v>359</v>
       </c>
@@ -5969,7 +6215,7 @@
       <c r="AB21" s="21"/>
       <c r="AC21"/>
     </row>
-    <row r="22" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="94" t="s">
         <v>360</v>
       </c>
@@ -6059,7 +6305,7 @@
       <c r="AB22" s="21"/>
       <c r="AC22"/>
     </row>
-    <row r="23" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="94" t="s">
         <v>361</v>
       </c>
@@ -6149,7 +6395,7 @@
       <c r="AB23" s="21"/>
       <c r="AC23"/>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
         <v>201</v>
       </c>
@@ -6238,7 +6484,7 @@
       <c r="AA24" s="2"/>
       <c r="AB24" s="21"/>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
         <v>202</v>
       </c>
@@ -6327,7 +6573,7 @@
       <c r="AA25" s="2"/>
       <c r="AB25" s="21"/>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
         <v>203</v>
       </c>
@@ -6416,7 +6662,7 @@
       <c r="AA26" s="2"/>
       <c r="AB26" s="21"/>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A27" s="8" t="s">
         <v>204</v>
       </c>
@@ -6505,7 +6751,7 @@
       <c r="AA27" s="2"/>
       <c r="AB27" s="21"/>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A28" s="8" t="s">
         <v>205</v>
       </c>
@@ -6594,7 +6840,7 @@
       <c r="AA28" s="2"/>
       <c r="AB28" s="21"/>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
         <v>206</v>
       </c>
@@ -6683,7 +6929,7 @@
       <c r="AA29" s="2"/>
       <c r="AB29" s="21"/>
     </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
         <v>207</v>
       </c>
@@ -6772,7 +7018,7 @@
       <c r="AA30" s="2"/>
       <c r="AB30" s="21"/>
     </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A31" s="162" t="s">
         <v>486</v>
       </c>
@@ -6843,7 +7089,7 @@
       <c r="AA31" s="2"/>
       <c r="AB31" s="187"/>
     </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A32" s="162" t="s">
         <v>487</v>
       </c>
@@ -6914,7 +7160,7 @@
       <c r="AA32" s="2"/>
       <c r="AB32" s="190"/>
     </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A33" s="162" t="s">
         <v>488</v>
       </c>
@@ -6985,7 +7231,7 @@
       <c r="AA33" s="2"/>
       <c r="AB33" s="190"/>
     </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A34" s="162" t="s">
         <v>489</v>
       </c>
@@ -7056,7 +7302,7 @@
       <c r="AA34" s="2"/>
       <c r="AB34" s="190"/>
     </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A35" s="162" t="s">
         <v>490</v>
       </c>
@@ -7127,7 +7373,7 @@
       <c r="AA35" s="2"/>
       <c r="AB35" s="190"/>
     </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A36" s="162" t="s">
         <v>491</v>
       </c>
@@ -7198,7 +7444,7 @@
       <c r="AA36" s="2"/>
       <c r="AB36" s="190"/>
     </row>
-    <row r="37" spans="1:29" s="15" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:29" s="15" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="179" t="s">
         <v>200</v>
       </c>
@@ -7282,7 +7528,7 @@
       <c r="AB37" s="190"/>
       <c r="AC37"/>
     </row>
-    <row r="38" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="162" t="s">
         <v>198</v>
       </c>
@@ -7365,7 +7611,7 @@
       <c r="AB38" s="190"/>
       <c r="AC38"/>
     </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A39" s="8" t="s">
         <v>199</v>
       </c>
@@ -7454,7 +7700,7 @@
       <c r="AA39" s="2"/>
       <c r="AB39" s="191"/>
     </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A40" s="8" t="s">
         <v>212</v>
       </c>
@@ -7542,7 +7788,7 @@
       <c r="AA40" s="2"/>
       <c r="AB40" s="191"/>
     </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A41" s="8" t="s">
         <v>208</v>
       </c>
@@ -7631,7 +7877,7 @@
       <c r="AA41" s="2"/>
       <c r="AB41" s="191"/>
     </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A42" s="8" t="s">
         <v>219</v>
       </c>
@@ -7720,7 +7966,7 @@
       <c r="AA42" s="2"/>
       <c r="AB42" s="191"/>
     </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A43" s="8" t="s">
         <v>209</v>
       </c>
@@ -7808,7 +8054,7 @@
       <c r="AA43" s="2"/>
       <c r="AB43" s="191"/>
     </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
         <v>210</v>
       </c>
@@ -7897,7 +8143,7 @@
       <c r="AA44" s="2"/>
       <c r="AB44" s="191"/>
     </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A45" s="8" t="s">
         <v>211</v>
       </c>
@@ -7986,7 +8232,7 @@
       <c r="AA45" s="2"/>
       <c r="AB45" s="191"/>
     </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A46" s="8" t="s">
         <v>213</v>
       </c>
@@ -8074,7 +8320,7 @@
       <c r="AA46" s="2"/>
       <c r="AB46" s="191"/>
     </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
         <v>214</v>
       </c>
@@ -8162,7 +8408,7 @@
       <c r="AA47" s="2"/>
       <c r="AB47" s="191"/>
     </row>
-    <row r="48" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A48" s="8" t="s">
         <v>215</v>
       </c>
@@ -8250,7 +8496,7 @@
       <c r="AA48" s="2"/>
       <c r="AB48" s="191"/>
     </row>
-    <row r="49" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A49" s="8" t="s">
         <v>216</v>
       </c>
@@ -8339,7 +8585,7 @@
       <c r="AA49" s="2"/>
       <c r="AB49" s="191"/>
     </row>
-    <row r="50" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
         <v>217</v>
       </c>
@@ -8428,7 +8674,7 @@
       <c r="AA50" s="2"/>
       <c r="AB50" s="191"/>
     </row>
-    <row r="51" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
         <v>222</v>
       </c>
@@ -8517,7 +8763,7 @@
       <c r="AA51" s="2"/>
       <c r="AB51" s="191"/>
     </row>
-    <row r="52" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
         <v>220</v>
       </c>
@@ -8606,7 +8852,7 @@
       <c r="AA52" s="2"/>
       <c r="AB52" s="191"/>
     </row>
-    <row r="53" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A53" s="8" t="s">
         <v>221</v>
       </c>
@@ -8694,7 +8940,7 @@
       <c r="AA53" s="2"/>
       <c r="AB53" s="191"/>
     </row>
-    <row r="54" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A54" s="8" t="s">
         <v>218</v>
       </c>
@@ -8782,7 +9028,7 @@
       <c r="AA54" s="2"/>
       <c r="AB54" s="191"/>
     </row>
-    <row r="55" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A55" s="9" t="s">
         <v>223</v>
       </c>
@@ -8870,7 +9116,7 @@
       <c r="AA55" s="4"/>
       <c r="AB55" s="191"/>
     </row>
-    <row r="56" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A56" s="92" t="s">
         <v>362</v>
       </c>
@@ -8959,7 +9205,7 @@
       <c r="AB56" s="191"/>
       <c r="AC56"/>
     </row>
-    <row r="57" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A57" s="92" t="s">
         <v>363</v>
       </c>
@@ -9048,7 +9294,7 @@
       <c r="AB57" s="191"/>
       <c r="AC57"/>
     </row>
-    <row r="58" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A58" s="92" t="s">
         <v>364</v>
       </c>
@@ -9137,7 +9383,7 @@
       <c r="AB58" s="191"/>
       <c r="AC58"/>
     </row>
-    <row r="59" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A59" s="92" t="s">
         <v>365</v>
       </c>
@@ -9226,7 +9472,7 @@
       <c r="AB59" s="191"/>
       <c r="AC59"/>
     </row>
-    <row r="60" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A60" s="92" t="s">
         <v>366</v>
       </c>
@@ -9315,7 +9561,7 @@
       <c r="AB60" s="191"/>
       <c r="AC60"/>
     </row>
-    <row r="61" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A61" s="92" t="s">
         <v>367</v>
       </c>
@@ -9404,7 +9650,7 @@
       <c r="AB61" s="191"/>
       <c r="AC61"/>
     </row>
-    <row r="62" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A62" s="162" t="s">
         <v>377</v>
       </c>
@@ -9490,7 +9736,7 @@
       <c r="AB62" s="190"/>
       <c r="AC62"/>
     </row>
-    <row r="63" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A63" s="162" t="s">
         <v>230</v>
       </c>
@@ -9573,7 +9819,7 @@
       <c r="AB63" s="190"/>
       <c r="AC63"/>
     </row>
-    <row r="64" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A64" s="162" t="s">
         <v>229</v>
       </c>
@@ -9658,7 +9904,7 @@
       <c r="AB64" s="190"/>
       <c r="AC64"/>
     </row>
-    <row r="65" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A65" s="162" t="s">
         <v>228</v>
       </c>
@@ -9741,7 +9987,7 @@
       <c r="AB65" s="190"/>
       <c r="AC65"/>
     </row>
-    <row r="66" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A66" s="162" t="s">
         <v>227</v>
       </c>
@@ -9824,7 +10070,7 @@
       <c r="AB66" s="190"/>
       <c r="AC66"/>
     </row>
-    <row r="67" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A67" s="8" t="s">
         <v>238</v>
       </c>
@@ -9915,7 +10161,7 @@
       </c>
       <c r="AB67" s="21"/>
     </row>
-    <row r="68" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A68" s="8" t="s">
         <v>237</v>
       </c>
@@ -10006,7 +10252,7 @@
       </c>
       <c r="AB68" s="21"/>
     </row>
-    <row r="69" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A69" s="8" t="s">
         <v>231</v>
       </c>
@@ -10095,7 +10341,7 @@
       <c r="AA69" s="2"/>
       <c r="AB69" s="21"/>
     </row>
-    <row r="70" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A70" s="8" t="s">
         <v>232</v>
       </c>
@@ -10186,7 +10432,7 @@
       </c>
       <c r="AB70" s="21"/>
     </row>
-    <row r="71" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A71" s="8" t="s">
         <v>269</v>
       </c>
@@ -10277,7 +10523,7 @@
       </c>
       <c r="AB71" s="21"/>
     </row>
-    <row r="72" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A72" s="8" t="s">
         <v>233</v>
       </c>
@@ -10368,7 +10614,7 @@
       </c>
       <c r="AB72" s="21"/>
     </row>
-    <row r="73" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A73" s="8" t="s">
         <v>268</v>
       </c>
@@ -10457,7 +10703,7 @@
       <c r="AA73" s="2"/>
       <c r="AB73" s="21"/>
     </row>
-    <row r="74" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="8" t="s">
         <v>368</v>
       </c>
@@ -10550,7 +10796,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="75" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A75" s="8" t="s">
         <v>234</v>
       </c>
@@ -10641,7 +10887,7 @@
       </c>
       <c r="AB75" s="21"/>
     </row>
-    <row r="76" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A76" s="8" t="s">
         <v>235</v>
       </c>
@@ -10732,7 +10978,7 @@
       </c>
       <c r="AB76" s="21"/>
     </row>
-    <row r="77" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A77" s="8" t="s">
         <v>369</v>
       </c>
@@ -10820,7 +11066,7 @@
       <c r="AA77" s="2"/>
       <c r="AB77" s="21"/>
     </row>
-    <row r="78" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A78" s="8" t="s">
         <v>236</v>
       </c>
@@ -10909,7 +11155,7 @@
       <c r="AA78" s="2"/>
       <c r="AB78" s="21"/>
     </row>
-    <row r="79" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A79" s="8" t="s">
         <v>240</v>
       </c>
@@ -11000,7 +11246,7 @@
       </c>
       <c r="AB79" s="21"/>
     </row>
-    <row r="80" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A80" s="8" t="s">
         <v>244</v>
       </c>
@@ -11091,7 +11337,7 @@
       </c>
       <c r="AB80" s="21"/>
     </row>
-    <row r="81" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A81" s="8" t="s">
         <v>250</v>
       </c>
@@ -11184,7 +11430,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="82" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A82" s="8" t="s">
         <v>251</v>
       </c>
@@ -11273,7 +11519,7 @@
       <c r="AA82" s="2"/>
       <c r="AB82" s="21"/>
     </row>
-    <row r="83" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A83" s="8" t="s">
         <v>256</v>
       </c>
@@ -11362,7 +11608,7 @@
       <c r="AA83" s="2"/>
       <c r="AB83" s="21"/>
     </row>
-    <row r="84" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A84" s="8" t="s">
         <v>259</v>
       </c>
@@ -11451,7 +11697,7 @@
       <c r="AA84" s="2"/>
       <c r="AB84" s="21"/>
     </row>
-    <row r="85" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A85" s="8" t="s">
         <v>260</v>
       </c>
@@ -11532,7 +11778,7 @@
       <c r="AA85" s="2"/>
       <c r="AB85" s="21"/>
     </row>
-    <row r="86" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A86" s="8" t="s">
         <v>264</v>
       </c>
@@ -11621,7 +11867,7 @@
       <c r="AA86" s="2"/>
       <c r="AB86" s="21"/>
     </row>
-    <row r="87" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A87" s="8" t="s">
         <v>265</v>
       </c>
@@ -11707,7 +11953,7 @@
       <c r="AA87" s="2"/>
       <c r="AB87" s="21"/>
     </row>
-    <row r="88" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A88" s="8" t="s">
         <v>270</v>
       </c>
@@ -11796,7 +12042,7 @@
       <c r="AA88" s="2"/>
       <c r="AB88" s="21"/>
     </row>
-    <row r="89" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A89" s="8" t="s">
         <v>275</v>
       </c>
@@ -11887,7 +12133,7 @@
       </c>
       <c r="AB89" s="21"/>
     </row>
-    <row r="90" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A90" s="8" t="s">
         <v>277</v>
       </c>
@@ -11977,7 +12223,7 @@
       </c>
       <c r="AB90" s="21"/>
     </row>
-    <row r="91" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A91" s="8" t="s">
         <v>278</v>
       </c>
@@ -12068,7 +12314,7 @@
       </c>
       <c r="AB91" s="21"/>
     </row>
-    <row r="92" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A92" s="8" t="s">
         <v>282</v>
       </c>
@@ -12161,7 +12407,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="93" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A93" s="8" t="s">
         <v>285</v>
       </c>
@@ -12252,7 +12498,7 @@
       </c>
       <c r="AB93" s="21"/>
     </row>
-    <row r="94" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A94" s="8" t="s">
         <v>289</v>
       </c>
@@ -12341,7 +12587,7 @@
       <c r="AA94" s="2"/>
       <c r="AB94" s="21"/>
     </row>
-    <row r="95" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A95" s="8" t="s">
         <v>293</v>
       </c>
@@ -12430,7 +12676,7 @@
       <c r="AA95" s="2"/>
       <c r="AB95" s="21"/>
     </row>
-    <row r="96" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A96" s="8" t="s">
         <v>299</v>
       </c>
@@ -12521,7 +12767,7 @@
       </c>
       <c r="AB96" s="21"/>
     </row>
-    <row r="97" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A97" s="8" t="s">
         <v>305</v>
       </c>
@@ -12612,7 +12858,7 @@
       </c>
       <c r="AB97" s="21"/>
     </row>
-    <row r="98" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A98" s="8" t="s">
         <v>309</v>
       </c>
@@ -12703,7 +12949,7 @@
       </c>
       <c r="AB98" s="21"/>
     </row>
-    <row r="99" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A99" s="8" t="s">
         <v>310</v>
       </c>
@@ -12794,7 +13040,7 @@
       </c>
       <c r="AB99" s="21"/>
     </row>
-    <row r="100" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A100" s="8" t="s">
         <v>314</v>
       </c>
@@ -12885,7 +13131,7 @@
       </c>
       <c r="AB100" s="21"/>
     </row>
-    <row r="101" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A101" s="8" t="s">
         <v>316</v>
       </c>
@@ -12955,11 +13201,11 @@
       </c>
       <c r="W101" s="50">
         <f ca="1">IF(OR($D101="Ecoinvent",$D101="Betonsortenrechner",$D101="KBOB",$T101&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X101" s="207">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y101" s="150" cm="1">
         <f t="array" aca="1" ref="Y101" ca="1">IF($W101&lt;&gt;0,
@@ -12968,7 +13214,7 @@
                          T101&lt;=_xlfn.PERCENTILE.INC(_xlfn._xlws.FILTER($T$2:$T$148, ($K$3:$K$149=K101)*($W$2:$W$148=1)),0.9)
                ),1,0),
 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z101" s="157"/>
       <c r="AA101" s="2" t="s">
@@ -12978,7 +13224,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="102" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A102" s="8" t="s">
         <v>318</v>
       </c>
@@ -13071,7 +13317,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="103" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A103" s="9" t="s">
         <v>466</v>
       </c>
@@ -13162,7 +13408,7 @@
       </c>
       <c r="AB103" s="37"/>
     </row>
-    <row r="104" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A104" s="8" t="s">
         <v>370</v>
       </c>
@@ -13248,7 +13494,7 @@
       <c r="AB104" s="187"/>
       <c r="AC104"/>
     </row>
-    <row r="105" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A105" s="8" t="s">
         <v>371</v>
       </c>
@@ -13335,7 +13581,7 @@
       </c>
       <c r="AB105" s="21"/>
     </row>
-    <row r="106" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A106" s="8" t="s">
         <v>372</v>
       </c>
@@ -13423,7 +13669,7 @@
       </c>
       <c r="AB106" s="21"/>
     </row>
-    <row r="107" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A107" s="8" t="s">
         <v>373</v>
       </c>
@@ -13511,7 +13757,7 @@
       </c>
       <c r="AB107" s="21"/>
     </row>
-    <row r="108" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A108" s="8" t="s">
         <v>374</v>
       </c>
@@ -13599,7 +13845,7 @@
       </c>
       <c r="AB108" s="21"/>
     </row>
-    <row r="109" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A109" s="8" t="s">
         <v>375</v>
       </c>
@@ -13687,7 +13933,7 @@
       </c>
       <c r="AB109" s="21"/>
     </row>
-    <row r="110" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A110" s="8" t="s">
         <v>376</v>
       </c>
@@ -13774,7 +14020,7 @@
       </c>
       <c r="AB110" s="21"/>
     </row>
-    <row r="111" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A111" s="174" t="s">
         <v>441</v>
       </c>
@@ -13863,7 +14109,7 @@
       </c>
       <c r="AB111" s="21"/>
     </row>
-    <row r="112" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A112" s="174" t="s">
         <v>445</v>
       </c>
@@ -13950,7 +14196,7 @@
       </c>
       <c r="AB112" s="21"/>
     </row>
-    <row r="113" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A113" s="174" t="s">
         <v>448</v>
       </c>
@@ -14037,7 +14283,7 @@
       </c>
       <c r="AB113" s="21"/>
     </row>
-    <row r="114" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A114" s="174" t="s">
         <v>449</v>
       </c>
@@ -14126,7 +14372,7 @@
       </c>
       <c r="AB114" s="21"/>
     </row>
-    <row r="115" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A115" s="174" t="s">
         <v>450</v>
       </c>
@@ -14214,7 +14460,7 @@
       </c>
       <c r="AB115" s="21"/>
     </row>
-    <row r="116" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A116" s="174" t="s">
         <v>454</v>
       </c>
@@ -14294,7 +14540,7 @@
                          T116&lt;=_xlfn.PERCENTILE.INC(_xlfn._xlws.FILTER($T$2:$T$148, ($L$2:$L$148=L116)*($W$2:$W$148=1)),0.9)
                ),1,0),
 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z116" s="157"/>
       <c r="AA116" s="2" t="s">
@@ -14302,7 +14548,7 @@
       </c>
       <c r="AB116" s="21"/>
     </row>
-    <row r="117" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A117" s="174" t="s">
         <v>455</v>
       </c>
@@ -14390,7 +14636,7 @@
       </c>
       <c r="AB117" s="21"/>
     </row>
-    <row r="118" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A118" s="174" t="s">
         <v>456</v>
       </c>
@@ -14477,7 +14723,7 @@
       </c>
       <c r="AB118" s="21"/>
     </row>
-    <row r="119" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A119" s="174" t="s">
         <v>457</v>
       </c>
@@ -14544,11 +14790,11 @@
       </c>
       <c r="W119" s="50">
         <f ca="1">IF(OR($D119="Ecoinvent",$D119="Betonsortenrechner",$D119="KBOB",$T119&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X119" s="202">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y119" s="148" cm="1">
         <f t="array" aca="1" ref="Y119" ca="1">IF($W119&lt;&gt;0,
@@ -14565,7 +14811,7 @@
       </c>
       <c r="AB119" s="21"/>
     </row>
-    <row r="120" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A120" s="174" t="s">
         <v>474</v>
       </c>
@@ -14653,7 +14899,7 @@
       </c>
       <c r="AB120" s="21"/>
     </row>
-    <row r="121" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:28" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A121" s="176" t="s">
         <v>477</v>
       </c>
@@ -14742,7 +14988,7 @@
       </c>
       <c r="AB121" s="37"/>
     </row>
-    <row r="122" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A122" s="8" t="s">
         <v>181</v>
       </c>
@@ -14820,7 +15066,7 @@
       </c>
       <c r="AB122" s="21"/>
     </row>
-    <row r="123" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A123" s="8" t="s">
         <v>182</v>
       </c>
@@ -14896,7 +15142,7 @@
       <c r="AA123" s="2"/>
       <c r="AB123" s="21"/>
     </row>
-    <row r="124" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A124" s="8" t="s">
         <v>183</v>
       </c>
@@ -14974,7 +15220,7 @@
       </c>
       <c r="AB124" s="21"/>
     </row>
-    <row r="125" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A125" s="8" t="s">
         <v>184</v>
       </c>
@@ -15053,7 +15299,7 @@
       </c>
       <c r="AB125" s="21"/>
     </row>
-    <row r="126" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A126" s="8" t="s">
         <v>185</v>
       </c>
@@ -15130,7 +15376,7 @@
       <c r="AA126" s="2"/>
       <c r="AB126" s="21"/>
     </row>
-    <row r="127" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A127" s="8" t="s">
         <v>186</v>
       </c>
@@ -15207,7 +15453,7 @@
       <c r="AA127" s="2"/>
       <c r="AB127" s="21"/>
     </row>
-    <row r="128" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A128" s="8" t="s">
         <v>187</v>
       </c>
@@ -15281,7 +15527,7 @@
       <c r="AA128" s="2"/>
       <c r="AB128" s="21"/>
     </row>
-    <row r="129" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A129" s="8" t="s">
         <v>188</v>
       </c>
@@ -15357,7 +15603,7 @@
       <c r="AA129" s="2"/>
       <c r="AB129" s="21"/>
     </row>
-    <row r="130" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:28" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A130" s="9" t="s">
         <v>189</v>
       </c>
@@ -15433,7 +15679,7 @@
       <c r="AA130" s="4"/>
       <c r="AB130" s="21"/>
     </row>
-    <row r="131" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A131" s="8" t="s">
         <v>190</v>
       </c>
@@ -15509,7 +15755,7 @@
       </c>
       <c r="AB131" s="21"/>
     </row>
-    <row r="132" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A132" s="8" t="s">
         <v>191</v>
       </c>
@@ -15585,52 +15831,52 @@
       </c>
       <c r="AB132" s="21"/>
     </row>
-    <row r="133" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:28" x14ac:dyDescent="0.2">
       <c r="E133" s="91"/>
     </row>
-    <row r="1048460" spans="29:29" x14ac:dyDescent="0.25">
+    <row r="1048460" spans="29:29" x14ac:dyDescent="0.2">
       <c r="AC1048460" s="71"/>
     </row>
-    <row r="1048461" spans="29:29" x14ac:dyDescent="0.25">
+    <row r="1048461" spans="29:29" x14ac:dyDescent="0.2">
       <c r="AC1048461" s="21"/>
     </row>
-    <row r="1048462" spans="29:29" x14ac:dyDescent="0.25">
+    <row r="1048462" spans="29:29" x14ac:dyDescent="0.2">
       <c r="AC1048462" s="21"/>
     </row>
-    <row r="1048463" spans="29:29" x14ac:dyDescent="0.25">
+    <row r="1048463" spans="29:29" x14ac:dyDescent="0.2">
       <c r="AC1048463" s="21"/>
     </row>
-    <row r="1048464" spans="29:29" x14ac:dyDescent="0.25">
+    <row r="1048464" spans="29:29" x14ac:dyDescent="0.2">
       <c r="AC1048464" s="21"/>
     </row>
-    <row r="1048465" spans="29:29" x14ac:dyDescent="0.25">
+    <row r="1048465" spans="29:29" x14ac:dyDescent="0.2">
       <c r="AC1048465" s="21"/>
     </row>
-    <row r="1048466" spans="29:29" x14ac:dyDescent="0.25">
+    <row r="1048466" spans="29:29" x14ac:dyDescent="0.2">
       <c r="AC1048466" s="21"/>
     </row>
-    <row r="1048467" spans="29:29" x14ac:dyDescent="0.25">
+    <row r="1048467" spans="29:29" x14ac:dyDescent="0.2">
       <c r="AC1048467" s="21"/>
     </row>
-    <row r="1048468" spans="29:29" x14ac:dyDescent="0.25">
+    <row r="1048468" spans="29:29" x14ac:dyDescent="0.2">
       <c r="AC1048468" s="165"/>
     </row>
-    <row r="1048469" spans="29:29" x14ac:dyDescent="0.25">
+    <row r="1048469" spans="29:29" x14ac:dyDescent="0.2">
       <c r="AC1048469" s="165"/>
     </row>
-    <row r="1048470" spans="29:29" x14ac:dyDescent="0.25">
+    <row r="1048470" spans="29:29" x14ac:dyDescent="0.2">
       <c r="AC1048470" s="165"/>
     </row>
-    <row r="1048471" spans="29:29" x14ac:dyDescent="0.25">
+    <row r="1048471" spans="29:29" x14ac:dyDescent="0.2">
       <c r="AC1048471" s="165"/>
     </row>
-    <row r="1048472" spans="29:29" x14ac:dyDescent="0.25">
+    <row r="1048472" spans="29:29" x14ac:dyDescent="0.2">
       <c r="AC1048472" s="165"/>
     </row>
-    <row r="1048473" spans="29:29" x14ac:dyDescent="0.25">
+    <row r="1048473" spans="29:29" x14ac:dyDescent="0.2">
       <c r="AC1048473" s="165"/>
     </row>
-    <row r="1048474" spans="29:29" x14ac:dyDescent="0.25">
+    <row r="1048474" spans="29:29" x14ac:dyDescent="0.2">
       <c r="AC1048474" s="21"/>
     </row>
   </sheetData>
@@ -15661,19 +15907,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{067AEC17-54D0-422B-913B-12777967F81E}">
   <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" customWidth="1"/>
-    <col min="3" max="3" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="27.28515625" customWidth="1"/>
-    <col min="6" max="6" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.85546875" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" customWidth="1"/>
+    <col min="3" max="3" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="27.33203125" customWidth="1"/>
+    <col min="6" max="6" width="26.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="61" t="s">
         <v>415</v>
       </c>
@@ -15702,7 +15948,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="56">
         <v>1</v>
       </c>
@@ -15725,7 +15971,7 @@
       </c>
       <c r="I2" s="56"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="56">
         <v>2</v>
       </c>
@@ -15748,7 +15994,7 @@
       </c>
       <c r="I3" s="56"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="56">
         <v>3</v>
       </c>
@@ -15771,7 +16017,7 @@
       </c>
       <c r="I4" s="56"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="56">
         <v>4</v>
       </c>
@@ -15792,7 +16038,7 @@
       <c r="H5" s="56"/>
       <c r="I5" s="56"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="56">
         <v>5</v>
       </c>
@@ -15817,7 +16063,7 @@
         <v>6.9999999999999999E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="56">
         <v>6</v>
       </c>
@@ -15842,7 +16088,7 @@
         <v>8.0000000000000004E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="62">
         <v>7</v>
       </c>
@@ -15879,9 +16125,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA60A30-8D92-49EC-964A-A8F2973B4787}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -15904,7 +16150,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="52"/>
       <c r="B2" s="52" t="s">
         <v>400</v>
@@ -15927,7 +16173,7 @@
         <v>1.278688524590164</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="56"/>
       <c r="B3" s="56" t="s">
         <v>401</v>
@@ -15948,7 +16194,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="52"/>
       <c r="B4" s="52" t="s">
         <v>402</v>
@@ -15970,7 +16216,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="56"/>
       <c r="B5" s="56" t="s">
         <v>403</v>
@@ -15991,7 +16237,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>404</v>
       </c>
@@ -16011,7 +16257,7 @@
         <v>0.81599999999999995</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>405</v>
       </c>
@@ -16035,4 +16281,117 @@
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DF23033-31FA-D240-A005-0FD6F443ADB6}">
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" customWidth="1"/>
+    <col min="3" max="3" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="61" t="s">
+        <v>415</v>
+      </c>
+      <c r="B1" s="61" t="s">
+        <v>407</v>
+      </c>
+      <c r="C1" s="61" t="s">
+        <v>518</v>
+      </c>
+      <c r="D1" s="61" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="56">
+        <v>1</v>
+      </c>
+      <c r="B2" s="56" t="s">
+        <v>513</v>
+      </c>
+      <c r="C2" s="56">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="D2" s="56">
+        <v>5830</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="56">
+        <v>2</v>
+      </c>
+      <c r="B3" s="56" t="s">
+        <v>514</v>
+      </c>
+      <c r="C3" s="56">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="D3" s="56">
+        <v>7780</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="56">
+        <v>3</v>
+      </c>
+      <c r="B4" s="56" t="s">
+        <v>515</v>
+      </c>
+      <c r="C4" s="56">
+        <v>0.01</v>
+      </c>
+      <c r="D4" s="56">
+        <v>9700</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="56">
+        <v>4</v>
+      </c>
+      <c r="B5" s="56" t="s">
+        <v>516</v>
+      </c>
+      <c r="C5" s="56">
+        <v>1.2E-2</v>
+      </c>
+      <c r="D5" s="56">
+        <v>11670</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="56">
+        <v>5</v>
+      </c>
+      <c r="B6" s="56" t="s">
+        <v>519</v>
+      </c>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C14" s="211"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C15" s="211"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C16" s="211"/>
+    </row>
+    <row r="17" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C17" s="211"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/Database/260126_Datenbankdefinition.xlsx
+++ b/Database/260126_Datenbankdefinition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonathanbieg/Documents/Master Thesis/1_Code/Python Repository/SDSD_Bieg/Database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7000399-25EF-384F-AE9D-829B72397CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31C98FBF-6703-D746-A4D1-D8677F03FC07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1340" yWindow="2200" windowWidth="16760" windowHeight="15840" activeTab="3" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
+    <workbookView xWindow="14840" yWindow="840" windowWidth="14360" windowHeight="16700" firstSheet="1" activeTab="1" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
   </bookViews>
   <sheets>
     <sheet name="products" sheetId="1" r:id="rId1"/>
@@ -93,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1891" uniqueCount="521">
   <si>
     <t>B500B</t>
   </si>
@@ -1670,6 +1670,9 @@
   </si>
   <si>
     <t>Kerve</t>
+  </si>
+  <si>
+    <t>phi</t>
   </si>
 </sst>
 </file>
@@ -2237,7 +2240,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="212">
+  <cellXfs count="213">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2706,12 +2709,13 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Standard 2" xfId="1" xr:uid="{FDCFE4BD-E849-456C-8E2E-B78D9BD993F6}"/>
   </cellStyles>
-  <dxfs count="55">
+  <dxfs count="56">
     <dxf>
       <font>
         <b/>
@@ -2881,13 +2885,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <top style="thin">
           <color theme="4" tint="0.39997558519241921"/>
         </top>
@@ -2921,6 +2918,13 @@
       </fill>
     </dxf>
     <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -2943,6 +2947,40 @@
           <bgColor theme="4"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -4003,42 +4041,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}" name="Table2" displayName="Table2" ref="A1:AB132" totalsRowShown="0" headerRowDxfId="54" dataDxfId="53">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}" name="Table2" displayName="Table2" ref="A1:AB132" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
   <autoFilter ref="A1:AB132" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}"/>
   <tableColumns count="28">
-    <tableColumn id="9" xr3:uid="{1DBBD25D-72F9-4A81-9CFA-500505E3628D}" name="ID" dataDxfId="52"/>
-    <tableColumn id="14" xr3:uid="{6844A52F-C967-44C0-BF5C-160C47AB6E64}" name="PRO_ID" dataDxfId="51"/>
-    <tableColumn id="12" xr3:uid="{4EDF1E73-4744-474F-8DFE-7F72FB05613C}" name="EPD_ID" dataDxfId="50"/>
-    <tableColumn id="1" xr3:uid="{1CF2E22E-1020-4F35-B31F-6350A15A5DE8}" name="SOURCE" dataDxfId="49"/>
-    <tableColumn id="27" xr3:uid="{07F74D5D-9130-4120-B02C-A11234427F46}" name="KBOB ID-Nr." dataDxfId="48"/>
-    <tableColumn id="11" xr3:uid="{81FE7F31-5F54-40F9-B99E-827E048F7DB5}" name="EPD_DATE" dataDxfId="47"/>
-    <tableColumn id="10" xr3:uid="{54D8BA04-0FEF-4C3B-9B14-59E8F982CD3F}" name="VALID_TO" dataDxfId="46"/>
-    <tableColumn id="22" xr3:uid="{3D6FC370-B8A8-40C3-9FC8-791B178DDFDF}" name="COUNTRY" dataDxfId="45"/>
-    <tableColumn id="4" xr3:uid="{25C7280F-4E3E-4E39-BDBB-DC06DF090C5B}" name="PRODUCT_NAME" dataDxfId="44"/>
-    <tableColumn id="26" xr3:uid="{1053A7DD-B11F-4E75-92EC-BC0F866E90B4}" name="OEKOBAUDAT_ID" dataDxfId="43"/>
-    <tableColumn id="25" xr3:uid="{295F99F8-E318-45C9-833E-F0B45A26471A}" name="MATERIAL_GROUP" dataDxfId="42"/>
-    <tableColumn id="2" xr3:uid="{1326FCEF-D1EE-4F3A-BB8B-77CB4EC72B0C}" name="MATERIAL" dataDxfId="41"/>
-    <tableColumn id="5" xr3:uid="{9B2A7F84-D968-4A00-B61F-23BB0661E7A3}" name="CEMENT" dataDxfId="40"/>
-    <tableColumn id="6" xr3:uid="{2F6E5831-6238-4360-9CFD-ED23A193E761}" name="MECH_PROP" dataDxfId="39"/>
-    <tableColumn id="13" xr3:uid="{50DAB01C-8AF5-4E0C-9904-54F70B81BC55}" name="DENSITY" dataDxfId="38"/>
-    <tableColumn id="18" xr3:uid="{F799A4D4-9543-475F-989E-CFBA47249558}" name="EXPOSITIONSKLASSE" dataDxfId="37"/>
-    <tableColumn id="17" xr3:uid="{ECCBC067-991C-4C60-942D-806BCD77B990}" name="GROESSTKORN" dataDxfId="36"/>
-    <tableColumn id="16" xr3:uid="{05157B85-D5FB-4844-9B53-D8AB09BCE0D9}" name="CHLORIDGEHALT" dataDxfId="35"/>
-    <tableColumn id="15" xr3:uid="{9F53CF50-7148-405A-9295-1F0C3C45645A}" name="KONSISTENZKLASSE" dataDxfId="34"/>
-    <tableColumn id="7" xr3:uid="{E23232F6-E86E-4AD2-8257-F30C0D1F7368}" name="Total_GWP" dataDxfId="33"/>
-    <tableColumn id="20" xr3:uid="{0A9001B4-3AB4-4C58-B125-0B2AA4DB2681}" name="A1toA3_GWP" dataDxfId="32">
+    <tableColumn id="9" xr3:uid="{1DBBD25D-72F9-4A81-9CFA-500505E3628D}" name="ID" dataDxfId="53"/>
+    <tableColumn id="14" xr3:uid="{6844A52F-C967-44C0-BF5C-160C47AB6E64}" name="PRO_ID" dataDxfId="52"/>
+    <tableColumn id="12" xr3:uid="{4EDF1E73-4744-474F-8DFE-7F72FB05613C}" name="EPD_ID" dataDxfId="51"/>
+    <tableColumn id="1" xr3:uid="{1CF2E22E-1020-4F35-B31F-6350A15A5DE8}" name="SOURCE" dataDxfId="50"/>
+    <tableColumn id="27" xr3:uid="{07F74D5D-9130-4120-B02C-A11234427F46}" name="KBOB ID-Nr." dataDxfId="49"/>
+    <tableColumn id="11" xr3:uid="{81FE7F31-5F54-40F9-B99E-827E048F7DB5}" name="EPD_DATE" dataDxfId="48"/>
+    <tableColumn id="10" xr3:uid="{54D8BA04-0FEF-4C3B-9B14-59E8F982CD3F}" name="VALID_TO" dataDxfId="47"/>
+    <tableColumn id="22" xr3:uid="{3D6FC370-B8A8-40C3-9FC8-791B178DDFDF}" name="COUNTRY" dataDxfId="46"/>
+    <tableColumn id="4" xr3:uid="{25C7280F-4E3E-4E39-BDBB-DC06DF090C5B}" name="PRODUCT_NAME" dataDxfId="45"/>
+    <tableColumn id="26" xr3:uid="{1053A7DD-B11F-4E75-92EC-BC0F866E90B4}" name="OEKOBAUDAT_ID" dataDxfId="44"/>
+    <tableColumn id="25" xr3:uid="{295F99F8-E318-45C9-833E-F0B45A26471A}" name="MATERIAL_GROUP" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{1326FCEF-D1EE-4F3A-BB8B-77CB4EC72B0C}" name="MATERIAL" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{9B2A7F84-D968-4A00-B61F-23BB0661E7A3}" name="CEMENT" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{2F6E5831-6238-4360-9CFD-ED23A193E761}" name="MECH_PROP" dataDxfId="40"/>
+    <tableColumn id="13" xr3:uid="{50DAB01C-8AF5-4E0C-9904-54F70B81BC55}" name="DENSITY" dataDxfId="39"/>
+    <tableColumn id="18" xr3:uid="{F799A4D4-9543-475F-989E-CFBA47249558}" name="EXPOSITIONSKLASSE" dataDxfId="38"/>
+    <tableColumn id="17" xr3:uid="{ECCBC067-991C-4C60-942D-806BCD77B990}" name="GROESSTKORN" dataDxfId="37"/>
+    <tableColumn id="16" xr3:uid="{05157B85-D5FB-4844-9B53-D8AB09BCE0D9}" name="CHLORIDGEHALT" dataDxfId="36"/>
+    <tableColumn id="15" xr3:uid="{9F53CF50-7148-405A-9295-1F0C3C45645A}" name="KONSISTENZKLASSE" dataDxfId="35"/>
+    <tableColumn id="7" xr3:uid="{E23232F6-E86E-4AD2-8257-F30C0D1F7368}" name="Total_GWP" dataDxfId="34"/>
+    <tableColumn id="20" xr3:uid="{0A9001B4-3AB4-4C58-B125-0B2AA4DB2681}" name="A1toA3_GWP" dataDxfId="33">
       <calculatedColumnFormula>119+10.9+238</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{2799394A-C481-45CE-B194-AAABAB0AED38}" name="C1toC4_GWP" dataDxfId="31">
+    <tableColumn id="21" xr3:uid="{2799394A-C481-45CE-B194-AAABAB0AED38}" name="C1toC4_GWP" dataDxfId="32">
       <calculatedColumnFormula>51.1+26+2.64+12.6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{70561D70-9D02-4E93-A395-229DA8696DDA}" name="ValidEPD" dataDxfId="30">
+    <tableColumn id="19" xr3:uid="{70561D70-9D02-4E93-A395-229DA8696DDA}" name="ValidEPD" dataDxfId="31">
       <calculatedColumnFormula>IF(OR($D2="Ecoinvent",$D2="Betonsortenrechner",$D2="KBOB",$T2&lt;=0),0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{92D55BC7-F55B-406A-B127-69EC2F0A8B77}" name="noch gültig" dataDxfId="29">
+    <tableColumn id="29" xr3:uid="{92D55BC7-F55B-406A-B127-69EC2F0A8B77}" name="noch gültig" dataDxfId="30">
       <calculatedColumnFormula>IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{DB90AC0A-8933-4040-BADE-E6EE11AC8BD7}" name="Statistik" dataDxfId="28">
+    <tableColumn id="3" xr3:uid="{DB90AC0A-8933-4040-BADE-E6EE11AC8BD7}" name="Statistik" dataDxfId="29">
       <calculatedColumnFormula array="1">IF($W2&lt;&gt;0,
 IF(AND(
                          T2&gt;=_xlfn.PERCENTILE.INC(_xlfn._xlws.FILTER($T$2:$T$148, ($L$2:$L$148=L2)*($W$2:$W$148=1)),0.1),
@@ -4046,34 +4084,35 @@
                ),1,0),
 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{BBA6C134-63F9-4711-8B25-086098EC2CB0}" name="Cost" dataDxfId="27"/>
-    <tableColumn id="24" xr3:uid="{5321A0E1-043C-4E95-A6DA-41830364B2BC}" name="Anmerkung" dataDxfId="26"/>
-    <tableColumn id="23" xr3:uid="{61456234-34E8-4222-B2D6-9DDA8E83B081}" name="Spalte 1" dataDxfId="25"/>
+    <tableColumn id="8" xr3:uid="{BBA6C134-63F9-4711-8B25-086098EC2CB0}" name="Cost" dataDxfId="28"/>
+    <tableColumn id="24" xr3:uid="{5321A0E1-043C-4E95-A6DA-41830364B2BC}" name="Anmerkung" dataDxfId="27"/>
+    <tableColumn id="23" xr3:uid="{61456234-34E8-4222-B2D6-9DDA8E83B081}" name="Spalte 1" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}" name="Tabelle4" displayName="Tabelle4" ref="A1:I8" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
-  <autoFilter ref="A1:I8" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}"/>
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{AF3C694B-2C8A-40EE-B8BB-2EC9EB81A87A}" name="mat_ID" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{B447FBC2-C455-4332-8F47-150B112A57E0}" name="name" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{BAFC6B47-7268-46CC-A881-892C9A1F4334}" name="strength_comp" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{6FC4C8EB-7581-4E67-81CE-C724161F0838}" name="strength_tens" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{A875970E-61A9-43B5-9361-7616A74C3147}" name="strength_bend" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{EF5B3A69-DD70-420A-88FF-4FE8772A2E14}" name="strength_shea" dataDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{ED461A80-736C-42BD-81BC-C5C0C80FF34C}" name="E_modulus" dataDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{68E47481-7028-4427-B126-2A046FC46737}" name="density_load" dataDxfId="12"/>
-    <tableColumn id="9" xr3:uid="{7AB34570-2BD4-417F-B141-70612577C7D6}" name="burn_rate" dataDxfId="11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}" name="Tabelle4" displayName="Tabelle4" ref="A1:J8" totalsRowShown="0" headerRowDxfId="25" dataDxfId="23" headerRowBorderDxfId="24" tableBorderDxfId="22" totalsRowBorderDxfId="21">
+  <autoFilter ref="A1:J8" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{AF3C694B-2C8A-40EE-B8BB-2EC9EB81A87A}" name="mat_ID" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{B447FBC2-C455-4332-8F47-150B112A57E0}" name="name" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{BAFC6B47-7268-46CC-A881-892C9A1F4334}" name="strength_comp" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{6FC4C8EB-7581-4E67-81CE-C724161F0838}" name="strength_tens" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{A875970E-61A9-43B5-9361-7616A74C3147}" name="strength_bend" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{EF5B3A69-DD70-420A-88FF-4FE8772A2E14}" name="strength_shea" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{ED461A80-736C-42BD-81BC-C5C0C80FF34C}" name="E_modulus" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{68E47481-7028-4427-B126-2A046FC46737}" name="density_load" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{7AB34570-2BD4-417F-B141-70612577C7D6}" name="burn_rate" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{69298654-E280-9D4B-9717-7904FADC15B5}" name="phi" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1CD264FD-E2C0-E94F-B387-736226CC982D}" name="Tabelle42" displayName="Tabelle42" ref="A1:D6" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" headerRowBorderDxfId="7" tableBorderDxfId="8" totalsRowBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1CD264FD-E2C0-E94F-B387-736226CC982D}" name="Tabelle42" displayName="Tabelle42" ref="A1:D6" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7" totalsRowBorderDxfId="6">
   <autoFilter ref="A1:D6" xr:uid="{1CD264FD-E2C0-E94F-B387-736226CC982D}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{6590463D-C242-4C4D-AA1F-6FA1F0D35E6F}" name="mat_ID" dataDxfId="5"/>
@@ -15906,7 +15945,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{067AEC17-54D0-422B-913B-12777967F81E}">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.83203125" bestFit="1" customWidth="1"/>
@@ -15919,7 +15958,7 @@
     <col min="9" max="9" width="11.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="61" t="s">
         <v>415</v>
       </c>
@@ -15947,8 +15986,11 @@
       <c r="I1" s="61" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J1" s="61" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="56">
         <v>1</v>
       </c>
@@ -15970,8 +16012,11 @@
         <v>25000</v>
       </c>
       <c r="I2" s="56"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J2" s="212">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="56">
         <v>2</v>
       </c>
@@ -15993,8 +16038,11 @@
         <v>25000</v>
       </c>
       <c r="I3" s="56"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J3" s="56">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="56">
         <v>3</v>
       </c>
@@ -16016,8 +16064,11 @@
         <v>25000</v>
       </c>
       <c r="I4" s="56"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J4" s="56">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="56">
         <v>4</v>
       </c>
@@ -16037,8 +16088,9 @@
       </c>
       <c r="H5" s="56"/>
       <c r="I5" s="56"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J5" s="56"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="56">
         <v>5</v>
       </c>
@@ -16062,8 +16114,11 @@
       <c r="I6" s="56">
         <v>6.9999999999999999E-4</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J6" s="56">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="56">
         <v>6</v>
       </c>
@@ -16087,8 +16142,11 @@
       <c r="I7" s="56">
         <v>8.0000000000000004E-4</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J7" s="56">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="62">
         <v>7</v>
       </c>
@@ -16111,6 +16169,9 @@
       </c>
       <c r="I8" s="62">
         <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="J8" s="62">
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>

--- a/Database/260126_Datenbankdefinition.xlsx
+++ b/Database/260126_Datenbankdefinition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonathanbieg/Documents/Master Thesis/1_Code/Python Repository/SDSD_Bieg/Database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31C98FBF-6703-D746-A4D1-D8677F03FC07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2763DDFA-6CF9-BD46-A06B-41F25BD259C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14840" yWindow="840" windowWidth="14360" windowHeight="16700" firstSheet="1" activeTab="1" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
+    <workbookView xWindow="14840" yWindow="840" windowWidth="14360" windowHeight="16700" activeTab="3" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
   </bookViews>
   <sheets>
     <sheet name="products" sheetId="1" r:id="rId1"/>

--- a/Database/260126_Datenbankdefinition.xlsx
+++ b/Database/260126_Datenbankdefinition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonathanbieg/Documents/Master Thesis/1_Code/Python Repository/SDSD_Bieg/Database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2763DDFA-6CF9-BD46-A06B-41F25BD259C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46CB7A72-0FDC-CB47-B4C6-92AD6D2553C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14840" yWindow="840" windowWidth="14360" windowHeight="16700" activeTab="3" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
+    <workbookView xWindow="14840" yWindow="840" windowWidth="15420" windowHeight="16700" activeTab="1" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
   </bookViews>
   <sheets>
     <sheet name="products" sheetId="1" r:id="rId1"/>
@@ -2770,216 +2770,6 @@
         <bottom style="thin">
           <color theme="4" tint="0.39997558519241921"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -3971,6 +3761,216 @@
       </font>
       <alignment vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -4041,42 +4041,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}" name="Table2" displayName="Table2" ref="A1:AB132" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}" name="Table2" displayName="Table2" ref="A1:AB132" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45">
   <autoFilter ref="A1:AB132" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}"/>
   <tableColumns count="28">
-    <tableColumn id="9" xr3:uid="{1DBBD25D-72F9-4A81-9CFA-500505E3628D}" name="ID" dataDxfId="53"/>
-    <tableColumn id="14" xr3:uid="{6844A52F-C967-44C0-BF5C-160C47AB6E64}" name="PRO_ID" dataDxfId="52"/>
-    <tableColumn id="12" xr3:uid="{4EDF1E73-4744-474F-8DFE-7F72FB05613C}" name="EPD_ID" dataDxfId="51"/>
-    <tableColumn id="1" xr3:uid="{1CF2E22E-1020-4F35-B31F-6350A15A5DE8}" name="SOURCE" dataDxfId="50"/>
-    <tableColumn id="27" xr3:uid="{07F74D5D-9130-4120-B02C-A11234427F46}" name="KBOB ID-Nr." dataDxfId="49"/>
-    <tableColumn id="11" xr3:uid="{81FE7F31-5F54-40F9-B99E-827E048F7DB5}" name="EPD_DATE" dataDxfId="48"/>
-    <tableColumn id="10" xr3:uid="{54D8BA04-0FEF-4C3B-9B14-59E8F982CD3F}" name="VALID_TO" dataDxfId="47"/>
-    <tableColumn id="22" xr3:uid="{3D6FC370-B8A8-40C3-9FC8-791B178DDFDF}" name="COUNTRY" dataDxfId="46"/>
-    <tableColumn id="4" xr3:uid="{25C7280F-4E3E-4E39-BDBB-DC06DF090C5B}" name="PRODUCT_NAME" dataDxfId="45"/>
-    <tableColumn id="26" xr3:uid="{1053A7DD-B11F-4E75-92EC-BC0F866E90B4}" name="OEKOBAUDAT_ID" dataDxfId="44"/>
-    <tableColumn id="25" xr3:uid="{295F99F8-E318-45C9-833E-F0B45A26471A}" name="MATERIAL_GROUP" dataDxfId="43"/>
-    <tableColumn id="2" xr3:uid="{1326FCEF-D1EE-4F3A-BB8B-77CB4EC72B0C}" name="MATERIAL" dataDxfId="42"/>
-    <tableColumn id="5" xr3:uid="{9B2A7F84-D968-4A00-B61F-23BB0661E7A3}" name="CEMENT" dataDxfId="41"/>
-    <tableColumn id="6" xr3:uid="{2F6E5831-6238-4360-9CFD-ED23A193E761}" name="MECH_PROP" dataDxfId="40"/>
-    <tableColumn id="13" xr3:uid="{50DAB01C-8AF5-4E0C-9904-54F70B81BC55}" name="DENSITY" dataDxfId="39"/>
-    <tableColumn id="18" xr3:uid="{F799A4D4-9543-475F-989E-CFBA47249558}" name="EXPOSITIONSKLASSE" dataDxfId="38"/>
-    <tableColumn id="17" xr3:uid="{ECCBC067-991C-4C60-942D-806BCD77B990}" name="GROESSTKORN" dataDxfId="37"/>
-    <tableColumn id="16" xr3:uid="{05157B85-D5FB-4844-9B53-D8AB09BCE0D9}" name="CHLORIDGEHALT" dataDxfId="36"/>
-    <tableColumn id="15" xr3:uid="{9F53CF50-7148-405A-9295-1F0C3C45645A}" name="KONSISTENZKLASSE" dataDxfId="35"/>
-    <tableColumn id="7" xr3:uid="{E23232F6-E86E-4AD2-8257-F30C0D1F7368}" name="Total_GWP" dataDxfId="34"/>
-    <tableColumn id="20" xr3:uid="{0A9001B4-3AB4-4C58-B125-0B2AA4DB2681}" name="A1toA3_GWP" dataDxfId="33">
+    <tableColumn id="9" xr3:uid="{1DBBD25D-72F9-4A81-9CFA-500505E3628D}" name="ID" dataDxfId="44"/>
+    <tableColumn id="14" xr3:uid="{6844A52F-C967-44C0-BF5C-160C47AB6E64}" name="PRO_ID" dataDxfId="43"/>
+    <tableColumn id="12" xr3:uid="{4EDF1E73-4744-474F-8DFE-7F72FB05613C}" name="EPD_ID" dataDxfId="42"/>
+    <tableColumn id="1" xr3:uid="{1CF2E22E-1020-4F35-B31F-6350A15A5DE8}" name="SOURCE" dataDxfId="41"/>
+    <tableColumn id="27" xr3:uid="{07F74D5D-9130-4120-B02C-A11234427F46}" name="KBOB ID-Nr." dataDxfId="40"/>
+    <tableColumn id="11" xr3:uid="{81FE7F31-5F54-40F9-B99E-827E048F7DB5}" name="EPD_DATE" dataDxfId="39"/>
+    <tableColumn id="10" xr3:uid="{54D8BA04-0FEF-4C3B-9B14-59E8F982CD3F}" name="VALID_TO" dataDxfId="38"/>
+    <tableColumn id="22" xr3:uid="{3D6FC370-B8A8-40C3-9FC8-791B178DDFDF}" name="COUNTRY" dataDxfId="37"/>
+    <tableColumn id="4" xr3:uid="{25C7280F-4E3E-4E39-BDBB-DC06DF090C5B}" name="PRODUCT_NAME" dataDxfId="36"/>
+    <tableColumn id="26" xr3:uid="{1053A7DD-B11F-4E75-92EC-BC0F866E90B4}" name="OEKOBAUDAT_ID" dataDxfId="35"/>
+    <tableColumn id="25" xr3:uid="{295F99F8-E318-45C9-833E-F0B45A26471A}" name="MATERIAL_GROUP" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{1326FCEF-D1EE-4F3A-BB8B-77CB4EC72B0C}" name="MATERIAL" dataDxfId="33"/>
+    <tableColumn id="5" xr3:uid="{9B2A7F84-D968-4A00-B61F-23BB0661E7A3}" name="CEMENT" dataDxfId="32"/>
+    <tableColumn id="6" xr3:uid="{2F6E5831-6238-4360-9CFD-ED23A193E761}" name="MECH_PROP" dataDxfId="31"/>
+    <tableColumn id="13" xr3:uid="{50DAB01C-8AF5-4E0C-9904-54F70B81BC55}" name="DENSITY" dataDxfId="30"/>
+    <tableColumn id="18" xr3:uid="{F799A4D4-9543-475F-989E-CFBA47249558}" name="EXPOSITIONSKLASSE" dataDxfId="29"/>
+    <tableColumn id="17" xr3:uid="{ECCBC067-991C-4C60-942D-806BCD77B990}" name="GROESSTKORN" dataDxfId="28"/>
+    <tableColumn id="16" xr3:uid="{05157B85-D5FB-4844-9B53-D8AB09BCE0D9}" name="CHLORIDGEHALT" dataDxfId="27"/>
+    <tableColumn id="15" xr3:uid="{9F53CF50-7148-405A-9295-1F0C3C45645A}" name="KONSISTENZKLASSE" dataDxfId="26"/>
+    <tableColumn id="7" xr3:uid="{E23232F6-E86E-4AD2-8257-F30C0D1F7368}" name="Total_GWP" dataDxfId="25"/>
+    <tableColumn id="20" xr3:uid="{0A9001B4-3AB4-4C58-B125-0B2AA4DB2681}" name="A1toA3_GWP" dataDxfId="24">
       <calculatedColumnFormula>119+10.9+238</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{2799394A-C481-45CE-B194-AAABAB0AED38}" name="C1toC4_GWP" dataDxfId="32">
+    <tableColumn id="21" xr3:uid="{2799394A-C481-45CE-B194-AAABAB0AED38}" name="C1toC4_GWP" dataDxfId="23">
       <calculatedColumnFormula>51.1+26+2.64+12.6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{70561D70-9D02-4E93-A395-229DA8696DDA}" name="ValidEPD" dataDxfId="31">
+    <tableColumn id="19" xr3:uid="{70561D70-9D02-4E93-A395-229DA8696DDA}" name="ValidEPD" dataDxfId="22">
       <calculatedColumnFormula>IF(OR($D2="Ecoinvent",$D2="Betonsortenrechner",$D2="KBOB",$T2&lt;=0),0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{92D55BC7-F55B-406A-B127-69EC2F0A8B77}" name="noch gültig" dataDxfId="30">
+    <tableColumn id="29" xr3:uid="{92D55BC7-F55B-406A-B127-69EC2F0A8B77}" name="noch gültig" dataDxfId="21">
       <calculatedColumnFormula>IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{DB90AC0A-8933-4040-BADE-E6EE11AC8BD7}" name="Statistik" dataDxfId="29">
+    <tableColumn id="3" xr3:uid="{DB90AC0A-8933-4040-BADE-E6EE11AC8BD7}" name="Statistik" dataDxfId="20">
       <calculatedColumnFormula array="1">IF($W2&lt;&gt;0,
 IF(AND(
                          T2&gt;=_xlfn.PERCENTILE.INC(_xlfn._xlws.FILTER($T$2:$T$148, ($L$2:$L$148=L2)*($W$2:$W$148=1)),0.1),
@@ -4084,41 +4084,41 @@
                ),1,0),
 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{BBA6C134-63F9-4711-8B25-086098EC2CB0}" name="Cost" dataDxfId="28"/>
-    <tableColumn id="24" xr3:uid="{5321A0E1-043C-4E95-A6DA-41830364B2BC}" name="Anmerkung" dataDxfId="27"/>
-    <tableColumn id="23" xr3:uid="{61456234-34E8-4222-B2D6-9DDA8E83B081}" name="Spalte 1" dataDxfId="26"/>
+    <tableColumn id="8" xr3:uid="{BBA6C134-63F9-4711-8B25-086098EC2CB0}" name="Cost" dataDxfId="19"/>
+    <tableColumn id="24" xr3:uid="{5321A0E1-043C-4E95-A6DA-41830364B2BC}" name="Anmerkung" dataDxfId="18"/>
+    <tableColumn id="23" xr3:uid="{61456234-34E8-4222-B2D6-9DDA8E83B081}" name="Spalte 1" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}" name="Tabelle4" displayName="Tabelle4" ref="A1:J8" totalsRowShown="0" headerRowDxfId="25" dataDxfId="23" headerRowBorderDxfId="24" tableBorderDxfId="22" totalsRowBorderDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}" name="Tabelle4" displayName="Tabelle4" ref="A1:J8" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13" totalsRowBorderDxfId="12">
   <autoFilter ref="A1:J8" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{AF3C694B-2C8A-40EE-B8BB-2EC9EB81A87A}" name="mat_ID" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{B447FBC2-C455-4332-8F47-150B112A57E0}" name="name" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{BAFC6B47-7268-46CC-A881-892C9A1F4334}" name="strength_comp" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{6FC4C8EB-7581-4E67-81CE-C724161F0838}" name="strength_tens" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{A875970E-61A9-43B5-9361-7616A74C3147}" name="strength_bend" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{EF5B3A69-DD70-420A-88FF-4FE8772A2E14}" name="strength_shea" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{ED461A80-736C-42BD-81BC-C5C0C80FF34C}" name="E_modulus" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{68E47481-7028-4427-B126-2A046FC46737}" name="density_load" dataDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{7AB34570-2BD4-417F-B141-70612577C7D6}" name="burn_rate" dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{69298654-E280-9D4B-9717-7904FADC15B5}" name="phi" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{AF3C694B-2C8A-40EE-B8BB-2EC9EB81A87A}" name="mat_ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{B447FBC2-C455-4332-8F47-150B112A57E0}" name="name" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{BAFC6B47-7268-46CC-A881-892C9A1F4334}" name="strength_comp" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{6FC4C8EB-7581-4E67-81CE-C724161F0838}" name="strength_tens" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{A875970E-61A9-43B5-9361-7616A74C3147}" name="strength_bend" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{EF5B3A69-DD70-420A-88FF-4FE8772A2E14}" name="strength_shea" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{ED461A80-736C-42BD-81BC-C5C0C80FF34C}" name="E_modulus" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{68E47481-7028-4427-B126-2A046FC46737}" name="density_load" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{7AB34570-2BD4-417F-B141-70612577C7D6}" name="burn_rate" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{69298654-E280-9D4B-9717-7904FADC15B5}" name="phi" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1CD264FD-E2C0-E94F-B387-736226CC982D}" name="Tabelle42" displayName="Tabelle42" ref="A1:D6" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7" totalsRowBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1CD264FD-E2C0-E94F-B387-736226CC982D}" name="Tabelle42" displayName="Tabelle42" ref="A1:D6" totalsRowShown="0" headerRowDxfId="55" dataDxfId="53" headerRowBorderDxfId="54" tableBorderDxfId="52" totalsRowBorderDxfId="51">
   <autoFilter ref="A1:D6" xr:uid="{1CD264FD-E2C0-E94F-B387-736226CC982D}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{6590463D-C242-4C4D-AA1F-6FA1F0D35E6F}" name="mat_ID" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{603BAED4-55F2-D040-9D73-1611C1564A84}" name="name" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{D6CC67C0-1ACA-D446-A6F3-00BCC3AC8DAC}" name="d [m]" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{3D62C7FF-3D7F-B245-A874-3A95DF0C49D2}" name="K_ser [N/m]2" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{6590463D-C242-4C4D-AA1F-6FA1F0D35E6F}" name="mat_ID" dataDxfId="50"/>
+    <tableColumn id="2" xr3:uid="{603BAED4-55F2-D040-9D73-1611C1564A84}" name="name" dataDxfId="49"/>
+    <tableColumn id="3" xr3:uid="{D6CC67C0-1ACA-D446-A6F3-00BCC3AC8DAC}" name="d [m]" dataDxfId="48"/>
+    <tableColumn id="4" xr3:uid="{3D62C7FF-3D7F-B245-A874-3A95DF0C49D2}" name="K_ser [N/m]2" dataDxfId="47"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>

--- a/Database/260126_Datenbankdefinition.xlsx
+++ b/Database/260126_Datenbankdefinition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonathanbieg/Documents/Master Thesis/1_Code/Python Repository/SDSD_Bieg/Database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46CB7A72-0FDC-CB47-B4C6-92AD6D2553C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD6F826-6D3D-4644-8BD7-775F45A8B808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14840" yWindow="840" windowWidth="15420" windowHeight="16700" activeTab="1" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
+    <workbookView xWindow="13980" yWindow="840" windowWidth="15420" windowHeight="16700" activeTab="3" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
   </bookViews>
   <sheets>
     <sheet name="products" sheetId="1" r:id="rId1"/>
@@ -1663,16 +1663,16 @@
     <t>DBS_12</t>
   </si>
   <si>
-    <t>K_ser [N/m]2</t>
-  </si>
-  <si>
     <t>d [m]</t>
   </si>
   <si>
-    <t>Kerve</t>
-  </si>
-  <si>
     <t>phi</t>
+  </si>
+  <si>
+    <t>K_ser [N/m]</t>
+  </si>
+  <si>
+    <t>kerve</t>
   </si>
 </sst>
 </file>
@@ -2770,210 +2770,8 @@
         <bottom style="thin">
           <color theme="4" tint="0.39997558519241921"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -3793,8 +3591,210 @@
         <bottom style="thin">
           <color theme="4" tint="0.39997558519241921"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -4041,42 +4041,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}" name="Table2" displayName="Table2" ref="A1:AB132" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}" name="Table2" displayName="Table2" ref="A1:AB132" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39">
   <autoFilter ref="A1:AB132" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}"/>
   <tableColumns count="28">
-    <tableColumn id="9" xr3:uid="{1DBBD25D-72F9-4A81-9CFA-500505E3628D}" name="ID" dataDxfId="44"/>
-    <tableColumn id="14" xr3:uid="{6844A52F-C967-44C0-BF5C-160C47AB6E64}" name="PRO_ID" dataDxfId="43"/>
-    <tableColumn id="12" xr3:uid="{4EDF1E73-4744-474F-8DFE-7F72FB05613C}" name="EPD_ID" dataDxfId="42"/>
-    <tableColumn id="1" xr3:uid="{1CF2E22E-1020-4F35-B31F-6350A15A5DE8}" name="SOURCE" dataDxfId="41"/>
-    <tableColumn id="27" xr3:uid="{07F74D5D-9130-4120-B02C-A11234427F46}" name="KBOB ID-Nr." dataDxfId="40"/>
-    <tableColumn id="11" xr3:uid="{81FE7F31-5F54-40F9-B99E-827E048F7DB5}" name="EPD_DATE" dataDxfId="39"/>
-    <tableColumn id="10" xr3:uid="{54D8BA04-0FEF-4C3B-9B14-59E8F982CD3F}" name="VALID_TO" dataDxfId="38"/>
-    <tableColumn id="22" xr3:uid="{3D6FC370-B8A8-40C3-9FC8-791B178DDFDF}" name="COUNTRY" dataDxfId="37"/>
-    <tableColumn id="4" xr3:uid="{25C7280F-4E3E-4E39-BDBB-DC06DF090C5B}" name="PRODUCT_NAME" dataDxfId="36"/>
-    <tableColumn id="26" xr3:uid="{1053A7DD-B11F-4E75-92EC-BC0F866E90B4}" name="OEKOBAUDAT_ID" dataDxfId="35"/>
-    <tableColumn id="25" xr3:uid="{295F99F8-E318-45C9-833E-F0B45A26471A}" name="MATERIAL_GROUP" dataDxfId="34"/>
-    <tableColumn id="2" xr3:uid="{1326FCEF-D1EE-4F3A-BB8B-77CB4EC72B0C}" name="MATERIAL" dataDxfId="33"/>
-    <tableColumn id="5" xr3:uid="{9B2A7F84-D968-4A00-B61F-23BB0661E7A3}" name="CEMENT" dataDxfId="32"/>
-    <tableColumn id="6" xr3:uid="{2F6E5831-6238-4360-9CFD-ED23A193E761}" name="MECH_PROP" dataDxfId="31"/>
-    <tableColumn id="13" xr3:uid="{50DAB01C-8AF5-4E0C-9904-54F70B81BC55}" name="DENSITY" dataDxfId="30"/>
-    <tableColumn id="18" xr3:uid="{F799A4D4-9543-475F-989E-CFBA47249558}" name="EXPOSITIONSKLASSE" dataDxfId="29"/>
-    <tableColumn id="17" xr3:uid="{ECCBC067-991C-4C60-942D-806BCD77B990}" name="GROESSTKORN" dataDxfId="28"/>
-    <tableColumn id="16" xr3:uid="{05157B85-D5FB-4844-9B53-D8AB09BCE0D9}" name="CHLORIDGEHALT" dataDxfId="27"/>
-    <tableColumn id="15" xr3:uid="{9F53CF50-7148-405A-9295-1F0C3C45645A}" name="KONSISTENZKLASSE" dataDxfId="26"/>
-    <tableColumn id="7" xr3:uid="{E23232F6-E86E-4AD2-8257-F30C0D1F7368}" name="Total_GWP" dataDxfId="25"/>
-    <tableColumn id="20" xr3:uid="{0A9001B4-3AB4-4C58-B125-0B2AA4DB2681}" name="A1toA3_GWP" dataDxfId="24">
+    <tableColumn id="9" xr3:uid="{1DBBD25D-72F9-4A81-9CFA-500505E3628D}" name="ID" dataDxfId="38"/>
+    <tableColumn id="14" xr3:uid="{6844A52F-C967-44C0-BF5C-160C47AB6E64}" name="PRO_ID" dataDxfId="37"/>
+    <tableColumn id="12" xr3:uid="{4EDF1E73-4744-474F-8DFE-7F72FB05613C}" name="EPD_ID" dataDxfId="36"/>
+    <tableColumn id="1" xr3:uid="{1CF2E22E-1020-4F35-B31F-6350A15A5DE8}" name="SOURCE" dataDxfId="35"/>
+    <tableColumn id="27" xr3:uid="{07F74D5D-9130-4120-B02C-A11234427F46}" name="KBOB ID-Nr." dataDxfId="34"/>
+    <tableColumn id="11" xr3:uid="{81FE7F31-5F54-40F9-B99E-827E048F7DB5}" name="EPD_DATE" dataDxfId="33"/>
+    <tableColumn id="10" xr3:uid="{54D8BA04-0FEF-4C3B-9B14-59E8F982CD3F}" name="VALID_TO" dataDxfId="32"/>
+    <tableColumn id="22" xr3:uid="{3D6FC370-B8A8-40C3-9FC8-791B178DDFDF}" name="COUNTRY" dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{25C7280F-4E3E-4E39-BDBB-DC06DF090C5B}" name="PRODUCT_NAME" dataDxfId="30"/>
+    <tableColumn id="26" xr3:uid="{1053A7DD-B11F-4E75-92EC-BC0F866E90B4}" name="OEKOBAUDAT_ID" dataDxfId="29"/>
+    <tableColumn id="25" xr3:uid="{295F99F8-E318-45C9-833E-F0B45A26471A}" name="MATERIAL_GROUP" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{1326FCEF-D1EE-4F3A-BB8B-77CB4EC72B0C}" name="MATERIAL" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{9B2A7F84-D968-4A00-B61F-23BB0661E7A3}" name="CEMENT" dataDxfId="26"/>
+    <tableColumn id="6" xr3:uid="{2F6E5831-6238-4360-9CFD-ED23A193E761}" name="MECH_PROP" dataDxfId="25"/>
+    <tableColumn id="13" xr3:uid="{50DAB01C-8AF5-4E0C-9904-54F70B81BC55}" name="DENSITY" dataDxfId="24"/>
+    <tableColumn id="18" xr3:uid="{F799A4D4-9543-475F-989E-CFBA47249558}" name="EXPOSITIONSKLASSE" dataDxfId="23"/>
+    <tableColumn id="17" xr3:uid="{ECCBC067-991C-4C60-942D-806BCD77B990}" name="GROESSTKORN" dataDxfId="22"/>
+    <tableColumn id="16" xr3:uid="{05157B85-D5FB-4844-9B53-D8AB09BCE0D9}" name="CHLORIDGEHALT" dataDxfId="21"/>
+    <tableColumn id="15" xr3:uid="{9F53CF50-7148-405A-9295-1F0C3C45645A}" name="KONSISTENZKLASSE" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{E23232F6-E86E-4AD2-8257-F30C0D1F7368}" name="Total_GWP" dataDxfId="19"/>
+    <tableColumn id="20" xr3:uid="{0A9001B4-3AB4-4C58-B125-0B2AA4DB2681}" name="A1toA3_GWP" dataDxfId="18">
       <calculatedColumnFormula>119+10.9+238</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{2799394A-C481-45CE-B194-AAABAB0AED38}" name="C1toC4_GWP" dataDxfId="23">
+    <tableColumn id="21" xr3:uid="{2799394A-C481-45CE-B194-AAABAB0AED38}" name="C1toC4_GWP" dataDxfId="17">
       <calculatedColumnFormula>51.1+26+2.64+12.6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{70561D70-9D02-4E93-A395-229DA8696DDA}" name="ValidEPD" dataDxfId="22">
+    <tableColumn id="19" xr3:uid="{70561D70-9D02-4E93-A395-229DA8696DDA}" name="ValidEPD" dataDxfId="16">
       <calculatedColumnFormula>IF(OR($D2="Ecoinvent",$D2="Betonsortenrechner",$D2="KBOB",$T2&lt;=0),0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{92D55BC7-F55B-406A-B127-69EC2F0A8B77}" name="noch gültig" dataDxfId="21">
+    <tableColumn id="29" xr3:uid="{92D55BC7-F55B-406A-B127-69EC2F0A8B77}" name="noch gültig" dataDxfId="15">
       <calculatedColumnFormula>IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{DB90AC0A-8933-4040-BADE-E6EE11AC8BD7}" name="Statistik" dataDxfId="20">
+    <tableColumn id="3" xr3:uid="{DB90AC0A-8933-4040-BADE-E6EE11AC8BD7}" name="Statistik" dataDxfId="14">
       <calculatedColumnFormula array="1">IF($W2&lt;&gt;0,
 IF(AND(
                          T2&gt;=_xlfn.PERCENTILE.INC(_xlfn._xlws.FILTER($T$2:$T$148, ($L$2:$L$148=L2)*($W$2:$W$148=1)),0.1),
@@ -4084,41 +4084,41 @@
                ),1,0),
 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{BBA6C134-63F9-4711-8B25-086098EC2CB0}" name="Cost" dataDxfId="19"/>
-    <tableColumn id="24" xr3:uid="{5321A0E1-043C-4E95-A6DA-41830364B2BC}" name="Anmerkung" dataDxfId="18"/>
-    <tableColumn id="23" xr3:uid="{61456234-34E8-4222-B2D6-9DDA8E83B081}" name="Spalte 1" dataDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{BBA6C134-63F9-4711-8B25-086098EC2CB0}" name="Cost" dataDxfId="13"/>
+    <tableColumn id="24" xr3:uid="{5321A0E1-043C-4E95-A6DA-41830364B2BC}" name="Anmerkung" dataDxfId="12"/>
+    <tableColumn id="23" xr3:uid="{61456234-34E8-4222-B2D6-9DDA8E83B081}" name="Spalte 1" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}" name="Tabelle4" displayName="Tabelle4" ref="A1:J8" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13" totalsRowBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}" name="Tabelle4" displayName="Tabelle4" ref="A1:J8" totalsRowShown="0" headerRowDxfId="55" dataDxfId="53" headerRowBorderDxfId="54" tableBorderDxfId="52" totalsRowBorderDxfId="51">
   <autoFilter ref="A1:J8" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{AF3C694B-2C8A-40EE-B8BB-2EC9EB81A87A}" name="mat_ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{B447FBC2-C455-4332-8F47-150B112A57E0}" name="name" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{BAFC6B47-7268-46CC-A881-892C9A1F4334}" name="strength_comp" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{6FC4C8EB-7581-4E67-81CE-C724161F0838}" name="strength_tens" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{A875970E-61A9-43B5-9361-7616A74C3147}" name="strength_bend" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{EF5B3A69-DD70-420A-88FF-4FE8772A2E14}" name="strength_shea" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{ED461A80-736C-42BD-81BC-C5C0C80FF34C}" name="E_modulus" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{68E47481-7028-4427-B126-2A046FC46737}" name="density_load" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{7AB34570-2BD4-417F-B141-70612577C7D6}" name="burn_rate" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{69298654-E280-9D4B-9717-7904FADC15B5}" name="phi" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{AF3C694B-2C8A-40EE-B8BB-2EC9EB81A87A}" name="mat_ID" dataDxfId="50"/>
+    <tableColumn id="2" xr3:uid="{B447FBC2-C455-4332-8F47-150B112A57E0}" name="name" dataDxfId="49"/>
+    <tableColumn id="3" xr3:uid="{BAFC6B47-7268-46CC-A881-892C9A1F4334}" name="strength_comp" dataDxfId="48"/>
+    <tableColumn id="4" xr3:uid="{6FC4C8EB-7581-4E67-81CE-C724161F0838}" name="strength_tens" dataDxfId="47"/>
+    <tableColumn id="5" xr3:uid="{A875970E-61A9-43B5-9361-7616A74C3147}" name="strength_bend" dataDxfId="46"/>
+    <tableColumn id="6" xr3:uid="{EF5B3A69-DD70-420A-88FF-4FE8772A2E14}" name="strength_shea" dataDxfId="45"/>
+    <tableColumn id="7" xr3:uid="{ED461A80-736C-42BD-81BC-C5C0C80FF34C}" name="E_modulus" dataDxfId="44"/>
+    <tableColumn id="8" xr3:uid="{68E47481-7028-4427-B126-2A046FC46737}" name="density_load" dataDxfId="43"/>
+    <tableColumn id="9" xr3:uid="{7AB34570-2BD4-417F-B141-70612577C7D6}" name="burn_rate" dataDxfId="42"/>
+    <tableColumn id="10" xr3:uid="{69298654-E280-9D4B-9717-7904FADC15B5}" name="phi" dataDxfId="41"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1CD264FD-E2C0-E94F-B387-736226CC982D}" name="Tabelle42" displayName="Tabelle42" ref="A1:D6" totalsRowShown="0" headerRowDxfId="55" dataDxfId="53" headerRowBorderDxfId="54" tableBorderDxfId="52" totalsRowBorderDxfId="51">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1CD264FD-E2C0-E94F-B387-736226CC982D}" name="Tabelle42" displayName="Tabelle42" ref="A1:D6" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7" totalsRowBorderDxfId="6">
   <autoFilter ref="A1:D6" xr:uid="{1CD264FD-E2C0-E94F-B387-736226CC982D}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{6590463D-C242-4C4D-AA1F-6FA1F0D35E6F}" name="mat_ID" dataDxfId="50"/>
-    <tableColumn id="2" xr3:uid="{603BAED4-55F2-D040-9D73-1611C1564A84}" name="name" dataDxfId="49"/>
-    <tableColumn id="3" xr3:uid="{D6CC67C0-1ACA-D446-A6F3-00BCC3AC8DAC}" name="d [m]" dataDxfId="48"/>
-    <tableColumn id="4" xr3:uid="{3D62C7FF-3D7F-B245-A874-3A95DF0C49D2}" name="K_ser [N/m]2" dataDxfId="47"/>
+    <tableColumn id="1" xr3:uid="{6590463D-C242-4C4D-AA1F-6FA1F0D35E6F}" name="mat_ID" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{603BAED4-55F2-D040-9D73-1611C1564A84}" name="name" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{D6CC67C0-1ACA-D446-A6F3-00BCC3AC8DAC}" name="d [m]" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{3D62C7FF-3D7F-B245-A874-3A95DF0C49D2}" name="K_ser [N/m]" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -15987,7 +15987,7 @@
         <v>414</v>
       </c>
       <c r="J1" s="61" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
@@ -16363,10 +16363,10 @@
         <v>407</v>
       </c>
       <c r="C1" s="61" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D1" s="61" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -16430,7 +16430,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="56" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C6" s="56"/>
       <c r="D6" s="56">

--- a/Database/260126_Datenbankdefinition.xlsx
+++ b/Database/260126_Datenbankdefinition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonathanbieg/Documents/Master Thesis/1_Code/Python Repository/SDSD_Bieg/Database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD6F826-6D3D-4644-8BD7-775F45A8B808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{867534AF-8429-4447-B406-3AA3D1D176DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13980" yWindow="840" windowWidth="15420" windowHeight="16700" activeTab="3" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
+    <workbookView xWindow="600" yWindow="840" windowWidth="25180" windowHeight="16700" activeTab="3" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
   </bookViews>
   <sheets>
     <sheet name="products" sheetId="1" r:id="rId1"/>
@@ -1663,16 +1663,16 @@
     <t>DBS_12</t>
   </si>
   <si>
-    <t>d [m]</t>
-  </si>
-  <si>
     <t>phi</t>
   </si>
   <si>
-    <t>K_ser [N/m]</t>
-  </si>
-  <si>
     <t>kerve</t>
+  </si>
+  <si>
+    <t>K_ser</t>
+  </si>
+  <si>
+    <t>d</t>
   </si>
 </sst>
 </file>
@@ -3579,7 +3579,7 @@
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
-          <bgColor auto="1"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
       <border diagonalUp="0" diagonalDown="0">
@@ -3591,6 +3591,8 @@
         <bottom style="thin">
           <color theme="4" tint="0.39997558519241921"/>
         </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -3613,10 +3615,10 @@
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
-          <bgColor auto="1"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
         <top style="thin">
@@ -3625,6 +3627,8 @@
         <bottom style="thin">
           <color theme="4" tint="0.39997558519241921"/>
         </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -4117,8 +4121,8 @@
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{6590463D-C242-4C4D-AA1F-6FA1F0D35E6F}" name="mat_ID" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{603BAED4-55F2-D040-9D73-1611C1564A84}" name="name" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{D6CC67C0-1ACA-D446-A6F3-00BCC3AC8DAC}" name="d [m]" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{3D62C7FF-3D7F-B245-A874-3A95DF0C49D2}" name="K_ser [N/m]" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{D6CC67C0-1ACA-D446-A6F3-00BCC3AC8DAC}" name="d" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{3D62C7FF-3D7F-B245-A874-3A95DF0C49D2}" name="K_ser" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -15987,7 +15991,7 @@
         <v>414</v>
       </c>
       <c r="J1" s="61" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
@@ -16363,7 +16367,7 @@
         <v>407</v>
       </c>
       <c r="C1" s="61" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="D1" s="61" t="s">
         <v>519</v>
@@ -16430,7 +16434,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="56" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C6" s="56"/>
       <c r="D6" s="56">

--- a/Database/260126_Datenbankdefinition.xlsx
+++ b/Database/260126_Datenbankdefinition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonathanbieg/Documents/Master Thesis/1_Code/Python Repository/SDSD_Bieg/Database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{867534AF-8429-4447-B406-3AA3D1D176DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BFD5328-3A24-ED40-B0B1-D0BD7F14B997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="600" yWindow="840" windowWidth="25180" windowHeight="16700" activeTab="3" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
+    <workbookView xWindow="600" yWindow="840" windowWidth="25180" windowHeight="16700" activeTab="2" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
   </bookViews>
   <sheets>
     <sheet name="products" sheetId="1" r:id="rId1"/>
@@ -2758,7 +2758,7 @@
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
-          <bgColor auto="1"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
       <border diagonalUp="0" diagonalDown="0">
@@ -2772,6 +2772,212 @@
         </bottom>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -3579,7 +3785,7 @@
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
+          <bgColor auto="1"/>
         </patternFill>
       </fill>
       <border diagonalUp="0" diagonalDown="0">
@@ -3593,212 +3799,6 @@
         </bottom>
         <vertical/>
         <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -4045,42 +4045,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}" name="Table2" displayName="Table2" ref="A1:AB132" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}" name="Table2" displayName="Table2" ref="A1:AB132" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45">
   <autoFilter ref="A1:AB132" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}"/>
   <tableColumns count="28">
-    <tableColumn id="9" xr3:uid="{1DBBD25D-72F9-4A81-9CFA-500505E3628D}" name="ID" dataDxfId="38"/>
-    <tableColumn id="14" xr3:uid="{6844A52F-C967-44C0-BF5C-160C47AB6E64}" name="PRO_ID" dataDxfId="37"/>
-    <tableColumn id="12" xr3:uid="{4EDF1E73-4744-474F-8DFE-7F72FB05613C}" name="EPD_ID" dataDxfId="36"/>
-    <tableColumn id="1" xr3:uid="{1CF2E22E-1020-4F35-B31F-6350A15A5DE8}" name="SOURCE" dataDxfId="35"/>
-    <tableColumn id="27" xr3:uid="{07F74D5D-9130-4120-B02C-A11234427F46}" name="KBOB ID-Nr." dataDxfId="34"/>
-    <tableColumn id="11" xr3:uid="{81FE7F31-5F54-40F9-B99E-827E048F7DB5}" name="EPD_DATE" dataDxfId="33"/>
-    <tableColumn id="10" xr3:uid="{54D8BA04-0FEF-4C3B-9B14-59E8F982CD3F}" name="VALID_TO" dataDxfId="32"/>
-    <tableColumn id="22" xr3:uid="{3D6FC370-B8A8-40C3-9FC8-791B178DDFDF}" name="COUNTRY" dataDxfId="31"/>
-    <tableColumn id="4" xr3:uid="{25C7280F-4E3E-4E39-BDBB-DC06DF090C5B}" name="PRODUCT_NAME" dataDxfId="30"/>
-    <tableColumn id="26" xr3:uid="{1053A7DD-B11F-4E75-92EC-BC0F866E90B4}" name="OEKOBAUDAT_ID" dataDxfId="29"/>
-    <tableColumn id="25" xr3:uid="{295F99F8-E318-45C9-833E-F0B45A26471A}" name="MATERIAL_GROUP" dataDxfId="28"/>
-    <tableColumn id="2" xr3:uid="{1326FCEF-D1EE-4F3A-BB8B-77CB4EC72B0C}" name="MATERIAL" dataDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{9B2A7F84-D968-4A00-B61F-23BB0661E7A3}" name="CEMENT" dataDxfId="26"/>
-    <tableColumn id="6" xr3:uid="{2F6E5831-6238-4360-9CFD-ED23A193E761}" name="MECH_PROP" dataDxfId="25"/>
-    <tableColumn id="13" xr3:uid="{50DAB01C-8AF5-4E0C-9904-54F70B81BC55}" name="DENSITY" dataDxfId="24"/>
-    <tableColumn id="18" xr3:uid="{F799A4D4-9543-475F-989E-CFBA47249558}" name="EXPOSITIONSKLASSE" dataDxfId="23"/>
-    <tableColumn id="17" xr3:uid="{ECCBC067-991C-4C60-942D-806BCD77B990}" name="GROESSTKORN" dataDxfId="22"/>
-    <tableColumn id="16" xr3:uid="{05157B85-D5FB-4844-9B53-D8AB09BCE0D9}" name="CHLORIDGEHALT" dataDxfId="21"/>
-    <tableColumn id="15" xr3:uid="{9F53CF50-7148-405A-9295-1F0C3C45645A}" name="KONSISTENZKLASSE" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{E23232F6-E86E-4AD2-8257-F30C0D1F7368}" name="Total_GWP" dataDxfId="19"/>
-    <tableColumn id="20" xr3:uid="{0A9001B4-3AB4-4C58-B125-0B2AA4DB2681}" name="A1toA3_GWP" dataDxfId="18">
+    <tableColumn id="9" xr3:uid="{1DBBD25D-72F9-4A81-9CFA-500505E3628D}" name="ID" dataDxfId="44"/>
+    <tableColumn id="14" xr3:uid="{6844A52F-C967-44C0-BF5C-160C47AB6E64}" name="PRO_ID" dataDxfId="43"/>
+    <tableColumn id="12" xr3:uid="{4EDF1E73-4744-474F-8DFE-7F72FB05613C}" name="EPD_ID" dataDxfId="42"/>
+    <tableColumn id="1" xr3:uid="{1CF2E22E-1020-4F35-B31F-6350A15A5DE8}" name="SOURCE" dataDxfId="41"/>
+    <tableColumn id="27" xr3:uid="{07F74D5D-9130-4120-B02C-A11234427F46}" name="KBOB ID-Nr." dataDxfId="40"/>
+    <tableColumn id="11" xr3:uid="{81FE7F31-5F54-40F9-B99E-827E048F7DB5}" name="EPD_DATE" dataDxfId="39"/>
+    <tableColumn id="10" xr3:uid="{54D8BA04-0FEF-4C3B-9B14-59E8F982CD3F}" name="VALID_TO" dataDxfId="38"/>
+    <tableColumn id="22" xr3:uid="{3D6FC370-B8A8-40C3-9FC8-791B178DDFDF}" name="COUNTRY" dataDxfId="37"/>
+    <tableColumn id="4" xr3:uid="{25C7280F-4E3E-4E39-BDBB-DC06DF090C5B}" name="PRODUCT_NAME" dataDxfId="36"/>
+    <tableColumn id="26" xr3:uid="{1053A7DD-B11F-4E75-92EC-BC0F866E90B4}" name="OEKOBAUDAT_ID" dataDxfId="35"/>
+    <tableColumn id="25" xr3:uid="{295F99F8-E318-45C9-833E-F0B45A26471A}" name="MATERIAL_GROUP" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{1326FCEF-D1EE-4F3A-BB8B-77CB4EC72B0C}" name="MATERIAL" dataDxfId="33"/>
+    <tableColumn id="5" xr3:uid="{9B2A7F84-D968-4A00-B61F-23BB0661E7A3}" name="CEMENT" dataDxfId="32"/>
+    <tableColumn id="6" xr3:uid="{2F6E5831-6238-4360-9CFD-ED23A193E761}" name="MECH_PROP" dataDxfId="31"/>
+    <tableColumn id="13" xr3:uid="{50DAB01C-8AF5-4E0C-9904-54F70B81BC55}" name="DENSITY" dataDxfId="30"/>
+    <tableColumn id="18" xr3:uid="{F799A4D4-9543-475F-989E-CFBA47249558}" name="EXPOSITIONSKLASSE" dataDxfId="29"/>
+    <tableColumn id="17" xr3:uid="{ECCBC067-991C-4C60-942D-806BCD77B990}" name="GROESSTKORN" dataDxfId="28"/>
+    <tableColumn id="16" xr3:uid="{05157B85-D5FB-4844-9B53-D8AB09BCE0D9}" name="CHLORIDGEHALT" dataDxfId="27"/>
+    <tableColumn id="15" xr3:uid="{9F53CF50-7148-405A-9295-1F0C3C45645A}" name="KONSISTENZKLASSE" dataDxfId="26"/>
+    <tableColumn id="7" xr3:uid="{E23232F6-E86E-4AD2-8257-F30C0D1F7368}" name="Total_GWP" dataDxfId="25"/>
+    <tableColumn id="20" xr3:uid="{0A9001B4-3AB4-4C58-B125-0B2AA4DB2681}" name="A1toA3_GWP" dataDxfId="24">
       <calculatedColumnFormula>119+10.9+238</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{2799394A-C481-45CE-B194-AAABAB0AED38}" name="C1toC4_GWP" dataDxfId="17">
+    <tableColumn id="21" xr3:uid="{2799394A-C481-45CE-B194-AAABAB0AED38}" name="C1toC4_GWP" dataDxfId="23">
       <calculatedColumnFormula>51.1+26+2.64+12.6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{70561D70-9D02-4E93-A395-229DA8696DDA}" name="ValidEPD" dataDxfId="16">
+    <tableColumn id="19" xr3:uid="{70561D70-9D02-4E93-A395-229DA8696DDA}" name="ValidEPD" dataDxfId="22">
       <calculatedColumnFormula>IF(OR($D2="Ecoinvent",$D2="Betonsortenrechner",$D2="KBOB",$T2&lt;=0),0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{92D55BC7-F55B-406A-B127-69EC2F0A8B77}" name="noch gültig" dataDxfId="15">
+    <tableColumn id="29" xr3:uid="{92D55BC7-F55B-406A-B127-69EC2F0A8B77}" name="noch gültig" dataDxfId="21">
       <calculatedColumnFormula>IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{DB90AC0A-8933-4040-BADE-E6EE11AC8BD7}" name="Statistik" dataDxfId="14">
+    <tableColumn id="3" xr3:uid="{DB90AC0A-8933-4040-BADE-E6EE11AC8BD7}" name="Statistik" dataDxfId="20">
       <calculatedColumnFormula array="1">IF($W2&lt;&gt;0,
 IF(AND(
                          T2&gt;=_xlfn.PERCENTILE.INC(_xlfn._xlws.FILTER($T$2:$T$148, ($L$2:$L$148=L2)*($W$2:$W$148=1)),0.1),
@@ -4088,41 +4088,41 @@
                ),1,0),
 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{BBA6C134-63F9-4711-8B25-086098EC2CB0}" name="Cost" dataDxfId="13"/>
-    <tableColumn id="24" xr3:uid="{5321A0E1-043C-4E95-A6DA-41830364B2BC}" name="Anmerkung" dataDxfId="12"/>
-    <tableColumn id="23" xr3:uid="{61456234-34E8-4222-B2D6-9DDA8E83B081}" name="Spalte 1" dataDxfId="11"/>
+    <tableColumn id="8" xr3:uid="{BBA6C134-63F9-4711-8B25-086098EC2CB0}" name="Cost" dataDxfId="19"/>
+    <tableColumn id="24" xr3:uid="{5321A0E1-043C-4E95-A6DA-41830364B2BC}" name="Anmerkung" dataDxfId="18"/>
+    <tableColumn id="23" xr3:uid="{61456234-34E8-4222-B2D6-9DDA8E83B081}" name="Spalte 1" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}" name="Tabelle4" displayName="Tabelle4" ref="A1:J8" totalsRowShown="0" headerRowDxfId="55" dataDxfId="53" headerRowBorderDxfId="54" tableBorderDxfId="52" totalsRowBorderDxfId="51">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}" name="Tabelle4" displayName="Tabelle4" ref="A1:J8" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13" totalsRowBorderDxfId="12">
   <autoFilter ref="A1:J8" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{AF3C694B-2C8A-40EE-B8BB-2EC9EB81A87A}" name="mat_ID" dataDxfId="50"/>
-    <tableColumn id="2" xr3:uid="{B447FBC2-C455-4332-8F47-150B112A57E0}" name="name" dataDxfId="49"/>
-    <tableColumn id="3" xr3:uid="{BAFC6B47-7268-46CC-A881-892C9A1F4334}" name="strength_comp" dataDxfId="48"/>
-    <tableColumn id="4" xr3:uid="{6FC4C8EB-7581-4E67-81CE-C724161F0838}" name="strength_tens" dataDxfId="47"/>
-    <tableColumn id="5" xr3:uid="{A875970E-61A9-43B5-9361-7616A74C3147}" name="strength_bend" dataDxfId="46"/>
-    <tableColumn id="6" xr3:uid="{EF5B3A69-DD70-420A-88FF-4FE8772A2E14}" name="strength_shea" dataDxfId="45"/>
-    <tableColumn id="7" xr3:uid="{ED461A80-736C-42BD-81BC-C5C0C80FF34C}" name="E_modulus" dataDxfId="44"/>
-    <tableColumn id="8" xr3:uid="{68E47481-7028-4427-B126-2A046FC46737}" name="density_load" dataDxfId="43"/>
-    <tableColumn id="9" xr3:uid="{7AB34570-2BD4-417F-B141-70612577C7D6}" name="burn_rate" dataDxfId="42"/>
-    <tableColumn id="10" xr3:uid="{69298654-E280-9D4B-9717-7904FADC15B5}" name="phi" dataDxfId="41"/>
+    <tableColumn id="1" xr3:uid="{AF3C694B-2C8A-40EE-B8BB-2EC9EB81A87A}" name="mat_ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{B447FBC2-C455-4332-8F47-150B112A57E0}" name="name" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{BAFC6B47-7268-46CC-A881-892C9A1F4334}" name="strength_comp" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{6FC4C8EB-7581-4E67-81CE-C724161F0838}" name="strength_tens" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{A875970E-61A9-43B5-9361-7616A74C3147}" name="strength_bend" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{EF5B3A69-DD70-420A-88FF-4FE8772A2E14}" name="strength_shea" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{ED461A80-736C-42BD-81BC-C5C0C80FF34C}" name="E_modulus" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{68E47481-7028-4427-B126-2A046FC46737}" name="density_load" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{7AB34570-2BD4-417F-B141-70612577C7D6}" name="burn_rate" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{69298654-E280-9D4B-9717-7904FADC15B5}" name="phi" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1CD264FD-E2C0-E94F-B387-736226CC982D}" name="Tabelle42" displayName="Tabelle42" ref="A1:D6" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7" totalsRowBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1CD264FD-E2C0-E94F-B387-736226CC982D}" name="Tabelle42" displayName="Tabelle42" ref="A1:D6" totalsRowShown="0" headerRowDxfId="55" dataDxfId="53" headerRowBorderDxfId="54" tableBorderDxfId="52" totalsRowBorderDxfId="51">
   <autoFilter ref="A1:D6" xr:uid="{1CD264FD-E2C0-E94F-B387-736226CC982D}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{6590463D-C242-4C4D-AA1F-6FA1F0D35E6F}" name="mat_ID" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{603BAED4-55F2-D040-9D73-1611C1564A84}" name="name" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{D6CC67C0-1ACA-D446-A6F3-00BCC3AC8DAC}" name="d" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{3D62C7FF-3D7F-B245-A874-3A95DF0C49D2}" name="K_ser" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{6590463D-C242-4C4D-AA1F-6FA1F0D35E6F}" name="mat_ID" dataDxfId="50"/>
+    <tableColumn id="2" xr3:uid="{603BAED4-55F2-D040-9D73-1611C1564A84}" name="name" dataDxfId="49"/>
+    <tableColumn id="3" xr3:uid="{D6CC67C0-1ACA-D446-A6F3-00BCC3AC8DAC}" name="d" dataDxfId="48"/>
+    <tableColumn id="4" xr3:uid="{3D62C7FF-3D7F-B245-A874-3A95DF0C49D2}" name="K_ser" dataDxfId="47"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -16191,6 +16191,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA60A30-8D92-49EC-964A-A8F2973B4787}">
   <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="33.33203125" customWidth="1"/>
+    <col min="3" max="3" width="19.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">

--- a/Database/260126_Datenbankdefinition.xlsx
+++ b/Database/260126_Datenbankdefinition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonathanbieg/Documents/Master Thesis/1_Code/Python Repository/SDSD_Bieg/Database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BFD5328-3A24-ED40-B0B1-D0BD7F14B997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{451D9134-3CDB-794D-A94C-48E9C3B75C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="600" yWindow="840" windowWidth="25180" windowHeight="16700" activeTab="2" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
+    <workbookView xWindow="600" yWindow="840" windowWidth="25180" windowHeight="16700" activeTab="3" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
   </bookViews>
   <sheets>
     <sheet name="products" sheetId="1" r:id="rId1"/>
@@ -16194,6 +16194,7 @@
   <cols>
     <col min="2" max="2" width="33.33203125" customWidth="1"/>
     <col min="3" max="3" width="19.6640625" customWidth="1"/>
+    <col min="7" max="7" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -16442,7 +16443,7 @@
       </c>
       <c r="C6" s="56"/>
       <c r="D6" s="56">
-        <v>1000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">

--- a/Database/260126_Datenbankdefinition.xlsx
+++ b/Database/260126_Datenbankdefinition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonathanbieg/Documents/Master Thesis/1_Code/Python Repository/SDSD_Bieg/Database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{451D9134-3CDB-794D-A94C-48E9C3B75C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B64A7D-A041-C441-A85B-212128E48FB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="600" yWindow="840" windowWidth="25180" windowHeight="16700" activeTab="3" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
+    <workbookView xWindow="600" yWindow="840" windowWidth="25180" windowHeight="16700" activeTab="2" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
   </bookViews>
   <sheets>
     <sheet name="products" sheetId="1" r:id="rId1"/>
@@ -16194,6 +16194,8 @@
   <cols>
     <col min="2" max="2" width="33.33203125" customWidth="1"/>
     <col min="3" max="3" width="19.6640625" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
   </cols>
   <sheetData>

--- a/Database/260126_Datenbankdefinition.xlsx
+++ b/Database/260126_Datenbankdefinition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonathanbieg/Documents/Master Thesis/1_Code/Python Repository/SDSD_Bieg/Database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B64A7D-A041-C441-A85B-212128E48FB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66093144-EA81-AB49-9E3A-8B056CB4CD5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="600" yWindow="840" windowWidth="25180" windowHeight="16700" activeTab="2" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
+    <workbookView xWindow="600" yWindow="840" windowWidth="25180" windowHeight="16700" activeTab="3" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
   </bookViews>
   <sheets>
     <sheet name="products" sheetId="1" r:id="rId1"/>
@@ -2758,6 +2758,216 @@
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
@@ -3765,216 +3975,6 @@
       </font>
       <alignment vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -4045,42 +4045,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}" name="Table2" displayName="Table2" ref="A1:AB132" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}" name="Table2" displayName="Table2" ref="A1:AB132" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
   <autoFilter ref="A1:AB132" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}"/>
   <tableColumns count="28">
-    <tableColumn id="9" xr3:uid="{1DBBD25D-72F9-4A81-9CFA-500505E3628D}" name="ID" dataDxfId="44"/>
-    <tableColumn id="14" xr3:uid="{6844A52F-C967-44C0-BF5C-160C47AB6E64}" name="PRO_ID" dataDxfId="43"/>
-    <tableColumn id="12" xr3:uid="{4EDF1E73-4744-474F-8DFE-7F72FB05613C}" name="EPD_ID" dataDxfId="42"/>
-    <tableColumn id="1" xr3:uid="{1CF2E22E-1020-4F35-B31F-6350A15A5DE8}" name="SOURCE" dataDxfId="41"/>
-    <tableColumn id="27" xr3:uid="{07F74D5D-9130-4120-B02C-A11234427F46}" name="KBOB ID-Nr." dataDxfId="40"/>
-    <tableColumn id="11" xr3:uid="{81FE7F31-5F54-40F9-B99E-827E048F7DB5}" name="EPD_DATE" dataDxfId="39"/>
-    <tableColumn id="10" xr3:uid="{54D8BA04-0FEF-4C3B-9B14-59E8F982CD3F}" name="VALID_TO" dataDxfId="38"/>
-    <tableColumn id="22" xr3:uid="{3D6FC370-B8A8-40C3-9FC8-791B178DDFDF}" name="COUNTRY" dataDxfId="37"/>
-    <tableColumn id="4" xr3:uid="{25C7280F-4E3E-4E39-BDBB-DC06DF090C5B}" name="PRODUCT_NAME" dataDxfId="36"/>
-    <tableColumn id="26" xr3:uid="{1053A7DD-B11F-4E75-92EC-BC0F866E90B4}" name="OEKOBAUDAT_ID" dataDxfId="35"/>
-    <tableColumn id="25" xr3:uid="{295F99F8-E318-45C9-833E-F0B45A26471A}" name="MATERIAL_GROUP" dataDxfId="34"/>
-    <tableColumn id="2" xr3:uid="{1326FCEF-D1EE-4F3A-BB8B-77CB4EC72B0C}" name="MATERIAL" dataDxfId="33"/>
-    <tableColumn id="5" xr3:uid="{9B2A7F84-D968-4A00-B61F-23BB0661E7A3}" name="CEMENT" dataDxfId="32"/>
-    <tableColumn id="6" xr3:uid="{2F6E5831-6238-4360-9CFD-ED23A193E761}" name="MECH_PROP" dataDxfId="31"/>
-    <tableColumn id="13" xr3:uid="{50DAB01C-8AF5-4E0C-9904-54F70B81BC55}" name="DENSITY" dataDxfId="30"/>
-    <tableColumn id="18" xr3:uid="{F799A4D4-9543-475F-989E-CFBA47249558}" name="EXPOSITIONSKLASSE" dataDxfId="29"/>
-    <tableColumn id="17" xr3:uid="{ECCBC067-991C-4C60-942D-806BCD77B990}" name="GROESSTKORN" dataDxfId="28"/>
-    <tableColumn id="16" xr3:uid="{05157B85-D5FB-4844-9B53-D8AB09BCE0D9}" name="CHLORIDGEHALT" dataDxfId="27"/>
-    <tableColumn id="15" xr3:uid="{9F53CF50-7148-405A-9295-1F0C3C45645A}" name="KONSISTENZKLASSE" dataDxfId="26"/>
-    <tableColumn id="7" xr3:uid="{E23232F6-E86E-4AD2-8257-F30C0D1F7368}" name="Total_GWP" dataDxfId="25"/>
-    <tableColumn id="20" xr3:uid="{0A9001B4-3AB4-4C58-B125-0B2AA4DB2681}" name="A1toA3_GWP" dataDxfId="24">
+    <tableColumn id="9" xr3:uid="{1DBBD25D-72F9-4A81-9CFA-500505E3628D}" name="ID" dataDxfId="53"/>
+    <tableColumn id="14" xr3:uid="{6844A52F-C967-44C0-BF5C-160C47AB6E64}" name="PRO_ID" dataDxfId="52"/>
+    <tableColumn id="12" xr3:uid="{4EDF1E73-4744-474F-8DFE-7F72FB05613C}" name="EPD_ID" dataDxfId="51"/>
+    <tableColumn id="1" xr3:uid="{1CF2E22E-1020-4F35-B31F-6350A15A5DE8}" name="SOURCE" dataDxfId="50"/>
+    <tableColumn id="27" xr3:uid="{07F74D5D-9130-4120-B02C-A11234427F46}" name="KBOB ID-Nr." dataDxfId="49"/>
+    <tableColumn id="11" xr3:uid="{81FE7F31-5F54-40F9-B99E-827E048F7DB5}" name="EPD_DATE" dataDxfId="48"/>
+    <tableColumn id="10" xr3:uid="{54D8BA04-0FEF-4C3B-9B14-59E8F982CD3F}" name="VALID_TO" dataDxfId="47"/>
+    <tableColumn id="22" xr3:uid="{3D6FC370-B8A8-40C3-9FC8-791B178DDFDF}" name="COUNTRY" dataDxfId="46"/>
+    <tableColumn id="4" xr3:uid="{25C7280F-4E3E-4E39-BDBB-DC06DF090C5B}" name="PRODUCT_NAME" dataDxfId="45"/>
+    <tableColumn id="26" xr3:uid="{1053A7DD-B11F-4E75-92EC-BC0F866E90B4}" name="OEKOBAUDAT_ID" dataDxfId="44"/>
+    <tableColumn id="25" xr3:uid="{295F99F8-E318-45C9-833E-F0B45A26471A}" name="MATERIAL_GROUP" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{1326FCEF-D1EE-4F3A-BB8B-77CB4EC72B0C}" name="MATERIAL" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{9B2A7F84-D968-4A00-B61F-23BB0661E7A3}" name="CEMENT" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{2F6E5831-6238-4360-9CFD-ED23A193E761}" name="MECH_PROP" dataDxfId="40"/>
+    <tableColumn id="13" xr3:uid="{50DAB01C-8AF5-4E0C-9904-54F70B81BC55}" name="DENSITY" dataDxfId="39"/>
+    <tableColumn id="18" xr3:uid="{F799A4D4-9543-475F-989E-CFBA47249558}" name="EXPOSITIONSKLASSE" dataDxfId="38"/>
+    <tableColumn id="17" xr3:uid="{ECCBC067-991C-4C60-942D-806BCD77B990}" name="GROESSTKORN" dataDxfId="37"/>
+    <tableColumn id="16" xr3:uid="{05157B85-D5FB-4844-9B53-D8AB09BCE0D9}" name="CHLORIDGEHALT" dataDxfId="36"/>
+    <tableColumn id="15" xr3:uid="{9F53CF50-7148-405A-9295-1F0C3C45645A}" name="KONSISTENZKLASSE" dataDxfId="35"/>
+    <tableColumn id="7" xr3:uid="{E23232F6-E86E-4AD2-8257-F30C0D1F7368}" name="Total_GWP" dataDxfId="34"/>
+    <tableColumn id="20" xr3:uid="{0A9001B4-3AB4-4C58-B125-0B2AA4DB2681}" name="A1toA3_GWP" dataDxfId="33">
       <calculatedColumnFormula>119+10.9+238</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{2799394A-C481-45CE-B194-AAABAB0AED38}" name="C1toC4_GWP" dataDxfId="23">
+    <tableColumn id="21" xr3:uid="{2799394A-C481-45CE-B194-AAABAB0AED38}" name="C1toC4_GWP" dataDxfId="32">
       <calculatedColumnFormula>51.1+26+2.64+12.6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{70561D70-9D02-4E93-A395-229DA8696DDA}" name="ValidEPD" dataDxfId="22">
+    <tableColumn id="19" xr3:uid="{70561D70-9D02-4E93-A395-229DA8696DDA}" name="ValidEPD" dataDxfId="31">
       <calculatedColumnFormula>IF(OR($D2="Ecoinvent",$D2="Betonsortenrechner",$D2="KBOB",$T2&lt;=0),0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{92D55BC7-F55B-406A-B127-69EC2F0A8B77}" name="noch gültig" dataDxfId="21">
+    <tableColumn id="29" xr3:uid="{92D55BC7-F55B-406A-B127-69EC2F0A8B77}" name="noch gültig" dataDxfId="30">
       <calculatedColumnFormula>IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{DB90AC0A-8933-4040-BADE-E6EE11AC8BD7}" name="Statistik" dataDxfId="20">
+    <tableColumn id="3" xr3:uid="{DB90AC0A-8933-4040-BADE-E6EE11AC8BD7}" name="Statistik" dataDxfId="29">
       <calculatedColumnFormula array="1">IF($W2&lt;&gt;0,
 IF(AND(
                          T2&gt;=_xlfn.PERCENTILE.INC(_xlfn._xlws.FILTER($T$2:$T$148, ($L$2:$L$148=L2)*($W$2:$W$148=1)),0.1),
@@ -4088,41 +4088,41 @@
                ),1,0),
 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{BBA6C134-63F9-4711-8B25-086098EC2CB0}" name="Cost" dataDxfId="19"/>
-    <tableColumn id="24" xr3:uid="{5321A0E1-043C-4E95-A6DA-41830364B2BC}" name="Anmerkung" dataDxfId="18"/>
-    <tableColumn id="23" xr3:uid="{61456234-34E8-4222-B2D6-9DDA8E83B081}" name="Spalte 1" dataDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{BBA6C134-63F9-4711-8B25-086098EC2CB0}" name="Cost" dataDxfId="28"/>
+    <tableColumn id="24" xr3:uid="{5321A0E1-043C-4E95-A6DA-41830364B2BC}" name="Anmerkung" dataDxfId="27"/>
+    <tableColumn id="23" xr3:uid="{61456234-34E8-4222-B2D6-9DDA8E83B081}" name="Spalte 1" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}" name="Tabelle4" displayName="Tabelle4" ref="A1:J8" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13" totalsRowBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}" name="Tabelle4" displayName="Tabelle4" ref="A1:J8" totalsRowShown="0" headerRowDxfId="25" dataDxfId="23" headerRowBorderDxfId="24" tableBorderDxfId="22" totalsRowBorderDxfId="21">
   <autoFilter ref="A1:J8" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{AF3C694B-2C8A-40EE-B8BB-2EC9EB81A87A}" name="mat_ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{B447FBC2-C455-4332-8F47-150B112A57E0}" name="name" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{BAFC6B47-7268-46CC-A881-892C9A1F4334}" name="strength_comp" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{6FC4C8EB-7581-4E67-81CE-C724161F0838}" name="strength_tens" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{A875970E-61A9-43B5-9361-7616A74C3147}" name="strength_bend" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{EF5B3A69-DD70-420A-88FF-4FE8772A2E14}" name="strength_shea" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{ED461A80-736C-42BD-81BC-C5C0C80FF34C}" name="E_modulus" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{68E47481-7028-4427-B126-2A046FC46737}" name="density_load" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{7AB34570-2BD4-417F-B141-70612577C7D6}" name="burn_rate" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{69298654-E280-9D4B-9717-7904FADC15B5}" name="phi" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{AF3C694B-2C8A-40EE-B8BB-2EC9EB81A87A}" name="mat_ID" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{B447FBC2-C455-4332-8F47-150B112A57E0}" name="name" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{BAFC6B47-7268-46CC-A881-892C9A1F4334}" name="strength_comp" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{6FC4C8EB-7581-4E67-81CE-C724161F0838}" name="strength_tens" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{A875970E-61A9-43B5-9361-7616A74C3147}" name="strength_bend" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{EF5B3A69-DD70-420A-88FF-4FE8772A2E14}" name="strength_shea" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{ED461A80-736C-42BD-81BC-C5C0C80FF34C}" name="E_modulus" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{68E47481-7028-4427-B126-2A046FC46737}" name="density_load" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{7AB34570-2BD4-417F-B141-70612577C7D6}" name="burn_rate" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{69298654-E280-9D4B-9717-7904FADC15B5}" name="phi" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1CD264FD-E2C0-E94F-B387-736226CC982D}" name="Tabelle42" displayName="Tabelle42" ref="A1:D6" totalsRowShown="0" headerRowDxfId="55" dataDxfId="53" headerRowBorderDxfId="54" tableBorderDxfId="52" totalsRowBorderDxfId="51">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1CD264FD-E2C0-E94F-B387-736226CC982D}" name="Tabelle42" displayName="Tabelle42" ref="A1:D6" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7" totalsRowBorderDxfId="6">
   <autoFilter ref="A1:D6" xr:uid="{1CD264FD-E2C0-E94F-B387-736226CC982D}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{6590463D-C242-4C4D-AA1F-6FA1F0D35E6F}" name="mat_ID" dataDxfId="50"/>
-    <tableColumn id="2" xr3:uid="{603BAED4-55F2-D040-9D73-1611C1564A84}" name="name" dataDxfId="49"/>
-    <tableColumn id="3" xr3:uid="{D6CC67C0-1ACA-D446-A6F3-00BCC3AC8DAC}" name="d" dataDxfId="48"/>
-    <tableColumn id="4" xr3:uid="{3D62C7FF-3D7F-B245-A874-3A95DF0C49D2}" name="K_ser" dataDxfId="47"/>
+    <tableColumn id="1" xr3:uid="{6590463D-C242-4C4D-AA1F-6FA1F0D35E6F}" name="mat_ID" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{603BAED4-55F2-D040-9D73-1611C1564A84}" name="name" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{D6CC67C0-1ACA-D446-A6F3-00BCC3AC8DAC}" name="d" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{3D62C7FF-3D7F-B245-A874-3A95DF0C49D2}" name="K_ser" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8269,7 +8269,7 @@
                          T45&lt;=_xlfn.PERCENTILE.INC(_xlfn._xlws.FILTER($T$2:$T$148, ($L$2:$L$148=L45)*($W$2:$W$148=1)),0.9)
                ),1,0),
 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z45" s="157"/>
       <c r="AA45" s="2"/>
@@ -8800,7 +8800,7 @@
                          T51&lt;=_xlfn.PERCENTILE.INC(_xlfn._xlws.FILTER($T$2:$T$148, ($L$2:$L$148=L51)*($W$2:$W$148=1)),0.9)
                ),1,0),
 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z51" s="157"/>
       <c r="AA51" s="2"/>
@@ -8876,11 +8876,11 @@
       </c>
       <c r="W52" s="50">
         <f ca="1">IF(OR($D52="Ecoinvent",$D52="Betonsortenrechner",$D52="KBOB",$T52&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X52" s="207">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y52" s="150" cm="1">
         <f t="array" aca="1" ref="Y52" ca="1">IF($W52&lt;&gt;0,
@@ -8889,7 +8889,7 @@
                          T52&lt;=_xlfn.PERCENTILE.INC(_xlfn._xlws.FILTER($T$2:$T$148, ($L$2:$L$148=L52)*($W$2:$W$148=1)),0.9)
                ),1,0),
 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z52" s="157"/>
       <c r="AA52" s="2"/>
@@ -12793,7 +12793,7 @@
       </c>
       <c r="X96" s="206">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y96" s="150" cm="1">
         <f t="array" aca="1" ref="Y96" ca="1">IF($W96&lt;&gt;0,
@@ -16391,7 +16391,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="D2" s="56">
-        <v>5830</v>
+        <v>5830000</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -16405,7 +16405,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="D3" s="56">
-        <v>7780</v>
+        <v>7780000</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -16419,7 +16419,7 @@
         <v>0.01</v>
       </c>
       <c r="D4" s="56">
-        <v>9700</v>
+        <v>9700000</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -16433,7 +16433,7 @@
         <v>1.2E-2</v>
       </c>
       <c r="D5" s="56">
-        <v>11670</v>
+        <v>11670000</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -16445,7 +16445,7 @@
       </c>
       <c r="C6" s="56"/>
       <c r="D6" s="56">
-        <v>100000</v>
+        <v>100000000</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">

--- a/Database/260126_Datenbankdefinition.xlsx
+++ b/Database/260126_Datenbankdefinition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonathanbieg/Documents/Master Thesis/1_Code/Python Repository/SDSD_Bieg/Database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66093144-EA81-AB49-9E3A-8B056CB4CD5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{420F4989-3711-8C49-AE0E-7F2378E46135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="600" yWindow="840" windowWidth="25180" windowHeight="16700" activeTab="3" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
+    <workbookView xWindow="-4800" yWindow="-19400" windowWidth="19540" windowHeight="16700" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
   </bookViews>
   <sheets>
     <sheet name="products" sheetId="1" r:id="rId1"/>
@@ -93,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1891" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1894" uniqueCount="524">
   <si>
     <t>B500B</t>
   </si>
@@ -1673,6 +1673,15 @@
   </si>
   <si>
     <t>d</t>
+  </si>
+  <si>
+    <t>Cost [float, CHF/m3]</t>
+  </si>
+  <si>
+    <t>T_construction [h/m2]</t>
+  </si>
+  <si>
+    <t>T_construction</t>
   </si>
 </sst>
 </file>
@@ -1813,12 +1822,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="7" tint="-0.249977111117893"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color rgb="FF7030A0"/>
       <name val="Aptos"/>
@@ -1836,12 +1839,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -1851,6 +1848,16 @@
       <color rgb="FFFF33CC"/>
       <name val="Aptos"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1898,18 +1905,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFAFAFA"/>
+        <fgColor rgb="FFFFCCCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCCCC"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -2208,19 +2215,6 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color theme="4" tint="0.39997558519241921"/>
       </bottom>
@@ -2238,9 +2232,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="213">
+  <cellXfs count="212">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2589,16 +2583,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2607,13 +2591,13 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="4" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="9" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="8" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2621,17 +2605,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="10" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="9" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2647,40 +2631,37 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="22" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="26" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="24" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2695,7 +2676,7 @@
     <xf numFmtId="1" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2707,15 +2688,116 @@
     <xf numFmtId="1" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Standard 2" xfId="1" xr:uid="{FDCFE4BD-E849-456C-8E2E-B78D9BD993F6}"/>
   </cellStyles>
-  <dxfs count="56">
+  <dxfs count="57">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -2735,216 +2817,6 @@
       <fill>
         <patternFill patternType="none">
           <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3363,69 +3235,6 @@
           <bgColor theme="4"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Aptos"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Aptos"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Aptos"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <vertical/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <vertical/>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -3975,6 +3784,216 @@
       </font>
       <alignment vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -4045,42 +4064,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}" name="Table2" displayName="Table2" ref="A1:AB132" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
-  <autoFilter ref="A1:AB132" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}"/>
-  <tableColumns count="28">
-    <tableColumn id="9" xr3:uid="{1DBBD25D-72F9-4A81-9CFA-500505E3628D}" name="ID" dataDxfId="53"/>
-    <tableColumn id="14" xr3:uid="{6844A52F-C967-44C0-BF5C-160C47AB6E64}" name="PRO_ID" dataDxfId="52"/>
-    <tableColumn id="12" xr3:uid="{4EDF1E73-4744-474F-8DFE-7F72FB05613C}" name="EPD_ID" dataDxfId="51"/>
-    <tableColumn id="1" xr3:uid="{1CF2E22E-1020-4F35-B31F-6350A15A5DE8}" name="SOURCE" dataDxfId="50"/>
-    <tableColumn id="27" xr3:uid="{07F74D5D-9130-4120-B02C-A11234427F46}" name="KBOB ID-Nr." dataDxfId="49"/>
-    <tableColumn id="11" xr3:uid="{81FE7F31-5F54-40F9-B99E-827E048F7DB5}" name="EPD_DATE" dataDxfId="48"/>
-    <tableColumn id="10" xr3:uid="{54D8BA04-0FEF-4C3B-9B14-59E8F982CD3F}" name="VALID_TO" dataDxfId="47"/>
-    <tableColumn id="22" xr3:uid="{3D6FC370-B8A8-40C3-9FC8-791B178DDFDF}" name="COUNTRY" dataDxfId="46"/>
-    <tableColumn id="4" xr3:uid="{25C7280F-4E3E-4E39-BDBB-DC06DF090C5B}" name="PRODUCT_NAME" dataDxfId="45"/>
-    <tableColumn id="26" xr3:uid="{1053A7DD-B11F-4E75-92EC-BC0F866E90B4}" name="OEKOBAUDAT_ID" dataDxfId="44"/>
-    <tableColumn id="25" xr3:uid="{295F99F8-E318-45C9-833E-F0B45A26471A}" name="MATERIAL_GROUP" dataDxfId="43"/>
-    <tableColumn id="2" xr3:uid="{1326FCEF-D1EE-4F3A-BB8B-77CB4EC72B0C}" name="MATERIAL" dataDxfId="42"/>
-    <tableColumn id="5" xr3:uid="{9B2A7F84-D968-4A00-B61F-23BB0661E7A3}" name="CEMENT" dataDxfId="41"/>
-    <tableColumn id="6" xr3:uid="{2F6E5831-6238-4360-9CFD-ED23A193E761}" name="MECH_PROP" dataDxfId="40"/>
-    <tableColumn id="13" xr3:uid="{50DAB01C-8AF5-4E0C-9904-54F70B81BC55}" name="DENSITY" dataDxfId="39"/>
-    <tableColumn id="18" xr3:uid="{F799A4D4-9543-475F-989E-CFBA47249558}" name="EXPOSITIONSKLASSE" dataDxfId="38"/>
-    <tableColumn id="17" xr3:uid="{ECCBC067-991C-4C60-942D-806BCD77B990}" name="GROESSTKORN" dataDxfId="37"/>
-    <tableColumn id="16" xr3:uid="{05157B85-D5FB-4844-9B53-D8AB09BCE0D9}" name="CHLORIDGEHALT" dataDxfId="36"/>
-    <tableColumn id="15" xr3:uid="{9F53CF50-7148-405A-9295-1F0C3C45645A}" name="KONSISTENZKLASSE" dataDxfId="35"/>
-    <tableColumn id="7" xr3:uid="{E23232F6-E86E-4AD2-8257-F30C0D1F7368}" name="Total_GWP" dataDxfId="34"/>
-    <tableColumn id="20" xr3:uid="{0A9001B4-3AB4-4C58-B125-0B2AA4DB2681}" name="A1toA3_GWP" dataDxfId="33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}" name="Table2" displayName="Table2" ref="A1:AC132" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46">
+  <autoFilter ref="A1:AC132" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}"/>
+  <tableColumns count="29">
+    <tableColumn id="9" xr3:uid="{1DBBD25D-72F9-4A81-9CFA-500505E3628D}" name="ID" dataDxfId="45"/>
+    <tableColumn id="14" xr3:uid="{6844A52F-C967-44C0-BF5C-160C47AB6E64}" name="PRO_ID" dataDxfId="44"/>
+    <tableColumn id="12" xr3:uid="{4EDF1E73-4744-474F-8DFE-7F72FB05613C}" name="EPD_ID" dataDxfId="43"/>
+    <tableColumn id="1" xr3:uid="{1CF2E22E-1020-4F35-B31F-6350A15A5DE8}" name="SOURCE" dataDxfId="42"/>
+    <tableColumn id="27" xr3:uid="{07F74D5D-9130-4120-B02C-A11234427F46}" name="KBOB ID-Nr." dataDxfId="41"/>
+    <tableColumn id="11" xr3:uid="{81FE7F31-5F54-40F9-B99E-827E048F7DB5}" name="EPD_DATE" dataDxfId="40"/>
+    <tableColumn id="10" xr3:uid="{54D8BA04-0FEF-4C3B-9B14-59E8F982CD3F}" name="VALID_TO" dataDxfId="39"/>
+    <tableColumn id="22" xr3:uid="{3D6FC370-B8A8-40C3-9FC8-791B178DDFDF}" name="COUNTRY" dataDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{25C7280F-4E3E-4E39-BDBB-DC06DF090C5B}" name="PRODUCT_NAME" dataDxfId="37"/>
+    <tableColumn id="26" xr3:uid="{1053A7DD-B11F-4E75-92EC-BC0F866E90B4}" name="OEKOBAUDAT_ID" dataDxfId="36"/>
+    <tableColumn id="25" xr3:uid="{295F99F8-E318-45C9-833E-F0B45A26471A}" name="MATERIAL_GROUP" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{1326FCEF-D1EE-4F3A-BB8B-77CB4EC72B0C}" name="MATERIAL" dataDxfId="34"/>
+    <tableColumn id="5" xr3:uid="{9B2A7F84-D968-4A00-B61F-23BB0661E7A3}" name="CEMENT" dataDxfId="33"/>
+    <tableColumn id="6" xr3:uid="{2F6E5831-6238-4360-9CFD-ED23A193E761}" name="MECH_PROP" dataDxfId="32"/>
+    <tableColumn id="13" xr3:uid="{50DAB01C-8AF5-4E0C-9904-54F70B81BC55}" name="DENSITY" dataDxfId="31"/>
+    <tableColumn id="18" xr3:uid="{F799A4D4-9543-475F-989E-CFBA47249558}" name="EXPOSITIONSKLASSE" dataDxfId="30"/>
+    <tableColumn id="17" xr3:uid="{ECCBC067-991C-4C60-942D-806BCD77B990}" name="GROESSTKORN" dataDxfId="29"/>
+    <tableColumn id="16" xr3:uid="{05157B85-D5FB-4844-9B53-D8AB09BCE0D9}" name="CHLORIDGEHALT" dataDxfId="28"/>
+    <tableColumn id="15" xr3:uid="{9F53CF50-7148-405A-9295-1F0C3C45645A}" name="KONSISTENZKLASSE" dataDxfId="27"/>
+    <tableColumn id="7" xr3:uid="{E23232F6-E86E-4AD2-8257-F30C0D1F7368}" name="Total_GWP" dataDxfId="26"/>
+    <tableColumn id="20" xr3:uid="{0A9001B4-3AB4-4C58-B125-0B2AA4DB2681}" name="A1toA3_GWP" dataDxfId="25">
       <calculatedColumnFormula>119+10.9+238</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{2799394A-C481-45CE-B194-AAABAB0AED38}" name="C1toC4_GWP" dataDxfId="32">
+    <tableColumn id="21" xr3:uid="{2799394A-C481-45CE-B194-AAABAB0AED38}" name="C1toC4_GWP" dataDxfId="24">
       <calculatedColumnFormula>51.1+26+2.64+12.6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{70561D70-9D02-4E93-A395-229DA8696DDA}" name="ValidEPD" dataDxfId="31">
+    <tableColumn id="19" xr3:uid="{70561D70-9D02-4E93-A395-229DA8696DDA}" name="ValidEPD" dataDxfId="23">
       <calculatedColumnFormula>IF(OR($D2="Ecoinvent",$D2="Betonsortenrechner",$D2="KBOB",$T2&lt;=0),0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{92D55BC7-F55B-406A-B127-69EC2F0A8B77}" name="noch gültig" dataDxfId="30">
+    <tableColumn id="29" xr3:uid="{92D55BC7-F55B-406A-B127-69EC2F0A8B77}" name="noch gültig" dataDxfId="22">
       <calculatedColumnFormula>IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{DB90AC0A-8933-4040-BADE-E6EE11AC8BD7}" name="Statistik" dataDxfId="29">
+    <tableColumn id="3" xr3:uid="{DB90AC0A-8933-4040-BADE-E6EE11AC8BD7}" name="Statistik" dataDxfId="4">
       <calculatedColumnFormula array="1">IF($W2&lt;&gt;0,
 IF(AND(
                          T2&gt;=_xlfn.PERCENTILE.INC(_xlfn._xlws.FILTER($T$2:$T$148, ($L$2:$L$148=L2)*($W$2:$W$148=1)),0.1),
@@ -4088,41 +4107,42 @@
                ),1,0),
 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{BBA6C134-63F9-4711-8B25-086098EC2CB0}" name="Cost" dataDxfId="28"/>
-    <tableColumn id="24" xr3:uid="{5321A0E1-043C-4E95-A6DA-41830364B2BC}" name="Anmerkung" dataDxfId="27"/>
-    <tableColumn id="23" xr3:uid="{61456234-34E8-4222-B2D6-9DDA8E83B081}" name="Spalte 1" dataDxfId="26"/>
+    <tableColumn id="8" xr3:uid="{BBA6C134-63F9-4711-8B25-086098EC2CB0}" name="Cost" dataDxfId="2"/>
+    <tableColumn id="24" xr3:uid="{5321A0E1-043C-4E95-A6DA-41830364B2BC}" name="Anmerkung" dataDxfId="3"/>
+    <tableColumn id="23" xr3:uid="{61456234-34E8-4222-B2D6-9DDA8E83B081}" name="Spalte 1" dataDxfId="1"/>
+    <tableColumn id="28" xr3:uid="{D1FC9AF8-A0AE-CE49-8F27-4BB569415BF3}" name="T_construction" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}" name="Tabelle4" displayName="Tabelle4" ref="A1:J8" totalsRowShown="0" headerRowDxfId="25" dataDxfId="23" headerRowBorderDxfId="24" tableBorderDxfId="22" totalsRowBorderDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}" name="Tabelle4" displayName="Tabelle4" ref="A1:J8" totalsRowShown="0" headerRowDxfId="21" dataDxfId="19" headerRowBorderDxfId="20" tableBorderDxfId="18" totalsRowBorderDxfId="17">
   <autoFilter ref="A1:J8" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{AF3C694B-2C8A-40EE-B8BB-2EC9EB81A87A}" name="mat_ID" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{B447FBC2-C455-4332-8F47-150B112A57E0}" name="name" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{BAFC6B47-7268-46CC-A881-892C9A1F4334}" name="strength_comp" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{6FC4C8EB-7581-4E67-81CE-C724161F0838}" name="strength_tens" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{A875970E-61A9-43B5-9361-7616A74C3147}" name="strength_bend" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{EF5B3A69-DD70-420A-88FF-4FE8772A2E14}" name="strength_shea" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{ED461A80-736C-42BD-81BC-C5C0C80FF34C}" name="E_modulus" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{68E47481-7028-4427-B126-2A046FC46737}" name="density_load" dataDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{7AB34570-2BD4-417F-B141-70612577C7D6}" name="burn_rate" dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{69298654-E280-9D4B-9717-7904FADC15B5}" name="phi" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{AF3C694B-2C8A-40EE-B8BB-2EC9EB81A87A}" name="mat_ID" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{B447FBC2-C455-4332-8F47-150B112A57E0}" name="name" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{BAFC6B47-7268-46CC-A881-892C9A1F4334}" name="strength_comp" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{6FC4C8EB-7581-4E67-81CE-C724161F0838}" name="strength_tens" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{A875970E-61A9-43B5-9361-7616A74C3147}" name="strength_bend" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{EF5B3A69-DD70-420A-88FF-4FE8772A2E14}" name="strength_shea" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{ED461A80-736C-42BD-81BC-C5C0C80FF34C}" name="E_modulus" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{68E47481-7028-4427-B126-2A046FC46737}" name="density_load" dataDxfId="9"/>
+    <tableColumn id="9" xr3:uid="{7AB34570-2BD4-417F-B141-70612577C7D6}" name="burn_rate" dataDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{69298654-E280-9D4B-9717-7904FADC15B5}" name="phi" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1CD264FD-E2C0-E94F-B387-736226CC982D}" name="Tabelle42" displayName="Tabelle42" ref="A1:D6" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7" totalsRowBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1CD264FD-E2C0-E94F-B387-736226CC982D}" name="Tabelle42" displayName="Tabelle42" ref="A1:D6" totalsRowShown="0" headerRowDxfId="56" dataDxfId="54" headerRowBorderDxfId="55" tableBorderDxfId="53" totalsRowBorderDxfId="52">
   <autoFilter ref="A1:D6" xr:uid="{1CD264FD-E2C0-E94F-B387-736226CC982D}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{6590463D-C242-4C4D-AA1F-6FA1F0D35E6F}" name="mat_ID" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{603BAED4-55F2-D040-9D73-1611C1564A84}" name="name" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{D6CC67C0-1ACA-D446-A6F3-00BCC3AC8DAC}" name="d" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{3D62C7FF-3D7F-B245-A874-3A95DF0C49D2}" name="K_ser" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{6590463D-C242-4C4D-AA1F-6FA1F0D35E6F}" name="mat_ID" dataDxfId="51"/>
+    <tableColumn id="2" xr3:uid="{603BAED4-55F2-D040-9D73-1611C1564A84}" name="name" dataDxfId="50"/>
+    <tableColumn id="3" xr3:uid="{D6CC67C0-1ACA-D446-A6F3-00BCC3AC8DAC}" name="d" dataDxfId="49"/>
+    <tableColumn id="4" xr3:uid="{3D62C7FF-3D7F-B245-A874-3A95DF0C49D2}" name="K_ser" dataDxfId="48"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4445,9 +4465,9 @@
     <col min="21" max="23" width="6.6640625" style="91" customWidth="1"/>
     <col min="24" max="24" width="8.33203125" style="91" customWidth="1"/>
     <col min="25" max="25" width="6.6640625" style="91" customWidth="1"/>
-    <col min="26" max="26" width="6.6640625" customWidth="1"/>
+    <col min="26" max="26" width="17.33203125" customWidth="1"/>
     <col min="27" max="27" width="71" customWidth="1"/>
-    <col min="28" max="28" width="23.6640625" style="188" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="23.6640625" style="180" bestFit="1" customWidth="1"/>
     <col min="29" max="30" width="23.6640625" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="15.5" bestFit="1" customWidth="1"/>
     <col min="32" max="58" width="23.6640625" bestFit="1" customWidth="1"/>
@@ -4467,7 +4487,7 @@
       <c r="D1" s="67" t="s">
         <v>382</v>
       </c>
-      <c r="E1" s="186" t="s">
+      <c r="E1" s="178" t="s">
         <v>496</v>
       </c>
       <c r="F1" s="68" t="s">
@@ -4524,7 +4544,7 @@
       <c r="W1" s="137" t="s">
         <v>512</v>
       </c>
-      <c r="X1" s="201" t="s">
+      <c r="X1" s="192" t="s">
         <v>510</v>
       </c>
       <c r="Y1" s="138" t="s">
@@ -4536,10 +4556,12 @@
       <c r="AA1" s="109" t="s">
         <v>335</v>
       </c>
-      <c r="AB1" s="192" t="s">
+      <c r="AB1" s="178" t="s">
         <v>497</v>
       </c>
-      <c r="AC1" s="71"/>
+      <c r="AC1" s="206" t="s">
+        <v>523</v>
+      </c>
     </row>
     <row r="2" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="92" t="s">
@@ -4610,7 +4632,7 @@
         <f ca="1">IF(OR($D2="Ecoinvent",$D2="Betonsortenrechner",$D2="KBOB",$T2&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X2" s="202">
+      <c r="X2" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -4623,10 +4645,14 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z2" s="154"/>
+      <c r="Z2" s="207">
+        <v>206</v>
+      </c>
       <c r="AA2" s="11"/>
       <c r="AB2" s="21"/>
-      <c r="AC2" s="21"/>
+      <c r="AC2" s="211">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="3" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="92" t="s">
@@ -4697,7 +4723,7 @@
         <f ca="1">IF(OR($D3="Ecoinvent",$D3="Betonsortenrechner",$D3="KBOB",$T3&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X3" s="202">
+      <c r="X3" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -4710,10 +4736,14 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z3" s="155"/>
+      <c r="Z3" s="207">
+        <v>206</v>
+      </c>
       <c r="AA3" s="11"/>
       <c r="AB3" s="21"/>
-      <c r="AC3" s="21"/>
+      <c r="AC3" s="211">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="4" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="92" t="s">
@@ -4784,7 +4814,7 @@
         <f ca="1">IF(OR($D4="Ecoinvent",$D4="Betonsortenrechner",$D4="KBOB",$T4&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X4" s="202">
+      <c r="X4" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -4797,10 +4827,14 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z4" s="155"/>
+      <c r="Z4" s="207">
+        <v>206</v>
+      </c>
       <c r="AA4" s="11"/>
       <c r="AB4" s="21"/>
-      <c r="AC4" s="21"/>
+      <c r="AC4" s="211">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="5" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="92" t="s">
@@ -4871,7 +4905,7 @@
         <f ca="1">IF(OR($D5="Ecoinvent",$D5="Betonsortenrechner",$D5="KBOB",$T5&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X5" s="202">
+      <c r="X5" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -4884,10 +4918,14 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z5" s="155"/>
+      <c r="Z5" s="207">
+        <v>206</v>
+      </c>
       <c r="AA5" s="11"/>
       <c r="AB5" s="21"/>
-      <c r="AC5" s="21"/>
+      <c r="AC5" s="211">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="6" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="92" t="s">
@@ -4958,7 +4996,7 @@
         <f ca="1">IF(OR($D6="Ecoinvent",$D6="Betonsortenrechner",$D6="KBOB",$T6&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X6" s="202">
+      <c r="X6" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -4971,10 +5009,14 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z6" s="155"/>
+      <c r="Z6" s="207">
+        <v>206</v>
+      </c>
       <c r="AA6" s="11"/>
       <c r="AB6" s="21"/>
-      <c r="AC6" s="21"/>
+      <c r="AC6" s="211">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="7" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="92" t="s">
@@ -5035,7 +5077,7 @@
         <f ca="1">IF(OR($D7="Ecoinvent",$D7="Betonsortenrechner",$D7="KBOB",$T7&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X7" s="202">
+      <c r="X7" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -5048,10 +5090,14 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z7" s="155"/>
+      <c r="Z7" s="207">
+        <v>206</v>
+      </c>
       <c r="AA7" s="11"/>
       <c r="AB7" s="21"/>
-      <c r="AC7" s="21"/>
+      <c r="AC7" s="211">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="8" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="92" t="s">
@@ -5112,7 +5158,7 @@
         <f ca="1">IF(OR($D8="Ecoinvent",$D8="Betonsortenrechner",$D8="KBOB",$T8&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X8" s="202">
+      <c r="X8" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -5125,10 +5171,14 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z8" s="155"/>
+      <c r="Z8" s="207">
+        <v>206</v>
+      </c>
       <c r="AA8" s="11"/>
       <c r="AB8" s="21"/>
-      <c r="AC8" s="21"/>
+      <c r="AC8" s="211">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="9" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="92" t="s">
@@ -5189,7 +5239,7 @@
         <f ca="1">IF(OR($D9="Ecoinvent",$D9="Betonsortenrechner",$D9="KBOB",$T9&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X9" s="202">
+      <c r="X9" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -5202,10 +5252,14 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z9" s="155"/>
+      <c r="Z9" s="207">
+        <v>206</v>
+      </c>
       <c r="AA9" s="11"/>
       <c r="AB9" s="21"/>
-      <c r="AC9" s="165"/>
+      <c r="AC9" s="211">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="10" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="92" t="s">
@@ -5266,7 +5320,7 @@
         <f ca="1">IF(OR($D10="Ecoinvent",$D10="Betonsortenrechner",$D10="KBOB",$T10&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X10" s="202">
+      <c r="X10" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -5279,10 +5333,14 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z10" s="155"/>
+      <c r="Z10" s="207">
+        <v>206</v>
+      </c>
       <c r="AA10" s="11"/>
       <c r="AB10" s="21"/>
-      <c r="AC10" s="165"/>
+      <c r="AC10" s="211">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="11" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="92" t="s">
@@ -5343,7 +5401,7 @@
         <f ca="1">IF(OR($D11="Ecoinvent",$D11="Betonsortenrechner",$D11="KBOB",$T11&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X11" s="202">
+      <c r="X11" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -5356,10 +5414,14 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z11" s="155"/>
+      <c r="Z11" s="207">
+        <v>206</v>
+      </c>
       <c r="AA11" s="11"/>
       <c r="AB11" s="21"/>
-      <c r="AC11" s="165"/>
+      <c r="AC11" s="211">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="12" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="92" t="s">
@@ -5430,7 +5492,7 @@
         <f ca="1">IF(OR($D12="Ecoinvent",$D12="Betonsortenrechner",$D12="KBOB",$T12&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X12" s="202">
+      <c r="X12" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -5443,16 +5505,20 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z12" s="155"/>
+      <c r="Z12" s="207">
+        <v>206</v>
+      </c>
       <c r="AA12" s="11"/>
       <c r="AB12" s="21"/>
-      <c r="AC12" s="165"/>
+      <c r="AC12" s="211">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="13" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="94" t="s">
         <v>351</v>
       </c>
-      <c r="B13" s="183">
+      <c r="B13" s="175">
         <v>12</v>
       </c>
       <c r="C13" s="38" t="s">
@@ -5520,7 +5586,7 @@
         <f ca="1">IF(OR($D13="Ecoinvent",$D13="Betonsortenrechner",$D13="KBOB",$T13&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X13" s="203">
+      <c r="X13" s="194">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -5533,10 +5599,14 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z13" s="156"/>
+      <c r="Z13" s="207">
+        <v>206</v>
+      </c>
       <c r="AA13" s="38"/>
       <c r="AB13" s="21"/>
-      <c r="AC13" s="165"/>
+      <c r="AC13" s="211">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="14" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="94" t="s">
@@ -5610,7 +5680,7 @@
         <f ca="1">IF(OR($D14="Ecoinvent",$D14="Betonsortenrechner",$D14="KBOB",$T14&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X14" s="203">
+      <c r="X14" s="194">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -5623,10 +5693,14 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z14" s="156"/>
+      <c r="Z14" s="207">
+        <v>206</v>
+      </c>
       <c r="AA14" s="38"/>
       <c r="AB14" s="21"/>
-      <c r="AC14" s="165"/>
+      <c r="AC14" s="211">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="15" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="94" t="s">
@@ -5700,7 +5774,7 @@
         <f ca="1">IF(OR($D15="Ecoinvent",$D15="Betonsortenrechner",$D15="KBOB",$T15&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X15" s="203">
+      <c r="X15" s="194">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -5713,10 +5787,14 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z15" s="156"/>
+      <c r="Z15" s="207">
+        <v>206</v>
+      </c>
       <c r="AA15" s="38"/>
       <c r="AB15" s="21"/>
-      <c r="AC15" s="21"/>
+      <c r="AC15" s="211">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="16" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="94" t="s">
@@ -5790,7 +5868,7 @@
         <f ca="1">IF(OR($D16="Ecoinvent",$D16="Betonsortenrechner",$D16="KBOB",$T16&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X16" s="203">
+      <c r="X16" s="194">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -5803,10 +5881,14 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z16" s="156"/>
+      <c r="Z16" s="207">
+        <v>206</v>
+      </c>
       <c r="AA16" s="38"/>
       <c r="AB16" s="21"/>
-      <c r="AC16"/>
+      <c r="AC16" s="211">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="17" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="94" t="s">
@@ -5880,7 +5962,7 @@
         <f ca="1">IF(OR($D17="Ecoinvent",$D17="Betonsortenrechner",$D17="KBOB",$T17&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X17" s="203">
+      <c r="X17" s="194">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -5893,10 +5975,14 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z17" s="156"/>
+      <c r="Z17" s="207">
+        <v>206</v>
+      </c>
       <c r="AA17" s="38"/>
       <c r="AB17" s="21"/>
-      <c r="AC17"/>
+      <c r="AC17" s="211">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="18" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="94" t="s">
@@ -5970,7 +6056,7 @@
         <f ca="1">IF(OR($D18="Ecoinvent",$D18="Betonsortenrechner",$D18="KBOB",$T18&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X18" s="203">
+      <c r="X18" s="194">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -5983,10 +6069,14 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z18" s="156"/>
+      <c r="Z18" s="207">
+        <v>206</v>
+      </c>
       <c r="AA18" s="38"/>
       <c r="AB18" s="21"/>
-      <c r="AC18"/>
+      <c r="AC18" s="211">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="19" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="94" t="s">
@@ -6060,7 +6150,7 @@
         <f ca="1">IF(OR($D19="Ecoinvent",$D19="Betonsortenrechner",$D19="KBOB",$T19&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X19" s="203">
+      <c r="X19" s="194">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -6073,10 +6163,14 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z19" s="156"/>
+      <c r="Z19" s="207">
+        <v>206</v>
+      </c>
       <c r="AA19" s="38"/>
       <c r="AB19" s="21"/>
-      <c r="AC19"/>
+      <c r="AC19" s="211">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="20" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="94" t="s">
@@ -6150,7 +6244,7 @@
         <f ca="1">IF(OR($D20="Ecoinvent",$D20="Betonsortenrechner",$D20="KBOB",$T20&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X20" s="203">
+      <c r="X20" s="194">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -6163,10 +6257,14 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z20" s="156"/>
+      <c r="Z20" s="207">
+        <v>206</v>
+      </c>
       <c r="AA20" s="38"/>
       <c r="AB20" s="21"/>
-      <c r="AC20"/>
+      <c r="AC20" s="211">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="21" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="94" t="s">
@@ -6240,7 +6338,7 @@
         <f ca="1">IF(OR($D21="Ecoinvent",$D21="Betonsortenrechner",$D21="KBOB",$T21&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X21" s="203">
+      <c r="X21" s="194">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -6253,10 +6351,14 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z21" s="156"/>
+      <c r="Z21" s="207">
+        <v>206</v>
+      </c>
       <c r="AA21" s="38"/>
       <c r="AB21" s="21"/>
-      <c r="AC21"/>
+      <c r="AC21" s="211">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="22" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="94" t="s">
@@ -6330,7 +6432,7 @@
         <f ca="1">IF(OR($D22="Ecoinvent",$D22="Betonsortenrechner",$D22="KBOB",$T22&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X22" s="203">
+      <c r="X22" s="194">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -6343,10 +6445,14 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z22" s="156"/>
+      <c r="Z22" s="207">
+        <v>206</v>
+      </c>
       <c r="AA22" s="38"/>
       <c r="AB22" s="21"/>
-      <c r="AC22"/>
+      <c r="AC22" s="211">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="23" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="94" t="s">
@@ -6420,7 +6526,7 @@
         <f ca="1">IF(OR($D23="Ecoinvent",$D23="Betonsortenrechner",$D23="KBOB",$T23&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X23" s="203">
+      <c r="X23" s="194">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -6433,10 +6539,14 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z23" s="156"/>
+      <c r="Z23" s="207">
+        <v>206</v>
+      </c>
       <c r="AA23" s="38"/>
       <c r="AB23" s="21"/>
-      <c r="AC23"/>
+      <c r="AC23" s="211">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
@@ -6510,7 +6620,7 @@
         <f ca="1">IF(OR($D24="Ecoinvent",$D24="Betonsortenrechner",$D24="KBOB",$T24&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X24" s="207">
+      <c r="X24" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -6523,9 +6633,14 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z24" s="157"/>
+      <c r="Z24" s="207">
+        <v>206</v>
+      </c>
       <c r="AA24" s="2"/>
       <c r="AB24" s="21"/>
+      <c r="AC24" s="211">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
@@ -6599,7 +6714,7 @@
         <f ca="1">IF(OR($D25="Ecoinvent",$D25="Betonsortenrechner",$D25="KBOB",$T25&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X25" s="207">
+      <c r="X25" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -6612,9 +6727,14 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z25" s="157"/>
+      <c r="Z25" s="207">
+        <v>206</v>
+      </c>
       <c r="AA25" s="2"/>
       <c r="AB25" s="21"/>
+      <c r="AC25" s="211">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
@@ -6688,7 +6808,7 @@
         <f ca="1">IF(OR($D26="Ecoinvent",$D26="Betonsortenrechner",$D26="KBOB",$T26&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X26" s="207">
+      <c r="X26" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -6701,9 +6821,14 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z26" s="157"/>
+      <c r="Z26" s="207">
+        <v>206</v>
+      </c>
       <c r="AA26" s="2"/>
       <c r="AB26" s="21"/>
+      <c r="AC26" s="211">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A27" s="8" t="s">
@@ -6777,7 +6902,7 @@
         <f ca="1">IF(OR($D27="Ecoinvent",$D27="Betonsortenrechner",$D27="KBOB",$T27&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X27" s="207">
+      <c r="X27" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -6790,9 +6915,14 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z27" s="157"/>
+      <c r="Z27" s="207">
+        <v>206</v>
+      </c>
       <c r="AA27" s="2"/>
       <c r="AB27" s="21"/>
+      <c r="AC27" s="211">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A28" s="8" t="s">
@@ -6866,7 +6996,7 @@
         <f ca="1">IF(OR($D28="Ecoinvent",$D28="Betonsortenrechner",$D28="KBOB",$T28&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X28" s="207">
+      <c r="X28" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -6879,9 +7009,14 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z28" s="157"/>
+      <c r="Z28" s="207">
+        <v>206</v>
+      </c>
       <c r="AA28" s="2"/>
       <c r="AB28" s="21"/>
+      <c r="AC28" s="211">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
@@ -6955,7 +7090,7 @@
         <f ca="1">IF(OR($D29="Ecoinvent",$D29="Betonsortenrechner",$D29="KBOB",$T29&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X29" s="207">
+      <c r="X29" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -6968,9 +7103,14 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z29" s="157"/>
+      <c r="Z29" s="207">
+        <v>206</v>
+      </c>
       <c r="AA29" s="2"/>
       <c r="AB29" s="21"/>
+      <c r="AC29" s="211">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="30" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
@@ -7044,7 +7184,7 @@
         <f ca="1">IF(OR($D30="Ecoinvent",$D30="Betonsortenrechner",$D30="KBOB",$T30&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X30" s="207">
+      <c r="X30" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -7057,22 +7197,27 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z30" s="157"/>
+      <c r="Z30" s="207">
+        <v>206</v>
+      </c>
       <c r="AA30" s="2"/>
       <c r="AB30" s="21"/>
+      <c r="AC30" s="211">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="31" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A31" s="162" t="s">
+      <c r="A31" s="154" t="s">
         <v>486</v>
       </c>
-      <c r="B31" s="163">
+      <c r="B31" s="155">
         <v>30</v>
       </c>
       <c r="C31" s="16"/>
       <c r="D31" s="17" t="s">
         <v>479</v>
       </c>
-      <c r="E31" s="189" t="s">
+      <c r="E31" s="181" t="s">
         <v>500</v>
       </c>
       <c r="F31" s="36"/>
@@ -7081,7 +7226,7 @@
       <c r="I31" s="16" t="s">
         <v>478</v>
       </c>
-      <c r="J31" s="177" t="s">
+      <c r="J31" s="169" t="s">
         <v>332</v>
       </c>
       <c r="K31" s="16" t="s">
@@ -7115,11 +7260,11 @@
         <f ca="1">IF(OR($D31="Ecoinvent",$D31="Betonsortenrechner",$D31="KBOB",$T31&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X31" s="204">
+      <c r="X31" s="195">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
-      <c r="Y31" s="164" cm="1">
+      <c r="Y31" s="156" cm="1">
         <f t="array" aca="1" ref="Y31" ca="1">IF($W31&lt;&gt;0,
 IF(AND(
                          T31&gt;=_xlfn.PERCENTILE.INC(_xlfn._xlws.FILTER($T$2:$T$148, ($L$2:$L$148=L31)*($W$2:$W$148=1)),0.1),
@@ -7128,22 +7273,27 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z31" s="161"/>
+      <c r="Z31" s="207">
+        <v>206</v>
+      </c>
       <c r="AA31" s="2"/>
-      <c r="AB31" s="187"/>
+      <c r="AB31" s="179"/>
+      <c r="AC31" s="211">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A32" s="162" t="s">
+      <c r="A32" s="154" t="s">
         <v>487</v>
       </c>
-      <c r="B32" s="163">
+      <c r="B32" s="155">
         <v>31</v>
       </c>
       <c r="C32" s="16"/>
       <c r="D32" s="17" t="s">
         <v>479</v>
       </c>
-      <c r="E32" s="189" t="s">
+      <c r="E32" s="181" t="s">
         <v>501</v>
       </c>
       <c r="F32" s="36"/>
@@ -7152,7 +7302,7 @@
       <c r="I32" s="107" t="s">
         <v>480</v>
       </c>
-      <c r="J32" s="177" t="s">
+      <c r="J32" s="169" t="s">
         <v>332</v>
       </c>
       <c r="K32" s="16" t="s">
@@ -7186,11 +7336,11 @@
         <f ca="1">IF(OR($D32="Ecoinvent",$D32="Betonsortenrechner",$D32="KBOB",$T32&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X32" s="204">
+      <c r="X32" s="195">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
-      <c r="Y32" s="164" cm="1">
+      <c r="Y32" s="156" cm="1">
         <f t="array" aca="1" ref="Y32" ca="1">IF($W32&lt;&gt;0,
 IF(AND(
                          T32&gt;=_xlfn.PERCENTILE.INC(_xlfn._xlws.FILTER($T$2:$T$148, ($L$2:$L$148=L32)*($W$2:$W$148=1)),0.1),
@@ -7199,22 +7349,27 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z32" s="161"/>
+      <c r="Z32" s="207">
+        <v>206</v>
+      </c>
       <c r="AA32" s="2"/>
-      <c r="AB32" s="190"/>
+      <c r="AB32" s="182"/>
+      <c r="AC32" s="211">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="33" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A33" s="162" t="s">
+      <c r="A33" s="154" t="s">
         <v>488</v>
       </c>
-      <c r="B33" s="163">
+      <c r="B33" s="155">
         <v>32</v>
       </c>
       <c r="C33" s="16"/>
       <c r="D33" s="17" t="s">
         <v>479</v>
       </c>
-      <c r="E33" s="194" t="s">
+      <c r="E33" s="185" t="s">
         <v>502</v>
       </c>
       <c r="F33" s="36"/>
@@ -7223,7 +7378,7 @@
       <c r="I33" s="107" t="s">
         <v>481</v>
       </c>
-      <c r="J33" s="177" t="s">
+      <c r="J33" s="169" t="s">
         <v>332</v>
       </c>
       <c r="K33" s="16" t="s">
@@ -7257,11 +7412,11 @@
         <f ca="1">IF(OR($D33="Ecoinvent",$D33="Betonsortenrechner",$D33="KBOB",$T33&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X33" s="204">
+      <c r="X33" s="195">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
-      <c r="Y33" s="164" cm="1">
+      <c r="Y33" s="156" cm="1">
         <f t="array" aca="1" ref="Y33" ca="1">IF($W33&lt;&gt;0,
 IF(AND(
                          T33&gt;=_xlfn.PERCENTILE.INC(_xlfn._xlws.FILTER($T$2:$T$148, ($L$2:$L$148=L33)*($W$2:$W$148=1)),0.1),
@@ -7270,22 +7425,27 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z33" s="161"/>
+      <c r="Z33" s="207">
+        <v>206</v>
+      </c>
       <c r="AA33" s="2"/>
-      <c r="AB33" s="190"/>
+      <c r="AB33" s="182"/>
+      <c r="AC33" s="211">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="34" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A34" s="162" t="s">
+      <c r="A34" s="154" t="s">
         <v>489</v>
       </c>
-      <c r="B34" s="163">
+      <c r="B34" s="155">
         <v>33</v>
       </c>
       <c r="C34" s="16"/>
       <c r="D34" s="17" t="s">
         <v>479</v>
       </c>
-      <c r="E34" s="194" t="s">
+      <c r="E34" s="185" t="s">
         <v>503</v>
       </c>
       <c r="F34" s="36"/>
@@ -7294,7 +7454,7 @@
       <c r="I34" s="107" t="s">
         <v>482</v>
       </c>
-      <c r="J34" s="177" t="s">
+      <c r="J34" s="169" t="s">
         <v>332</v>
       </c>
       <c r="K34" s="16" t="s">
@@ -7328,11 +7488,11 @@
         <f ca="1">IF(OR($D34="Ecoinvent",$D34="Betonsortenrechner",$D34="KBOB",$T34&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X34" s="204">
+      <c r="X34" s="195">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
-      <c r="Y34" s="164" cm="1">
+      <c r="Y34" s="156" cm="1">
         <f t="array" aca="1" ref="Y34" ca="1">IF($W34&lt;&gt;0,
 IF(AND(
                          T34&gt;=_xlfn.PERCENTILE.INC(_xlfn._xlws.FILTER($T$2:$T$148, ($L$2:$L$148=L34)*($W$2:$W$148=1)),0.1),
@@ -7341,22 +7501,27 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z34" s="161"/>
+      <c r="Z34" s="207">
+        <v>206</v>
+      </c>
       <c r="AA34" s="2"/>
-      <c r="AB34" s="190"/>
+      <c r="AB34" s="182"/>
+      <c r="AC34" s="211">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="35" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A35" s="162" t="s">
+      <c r="A35" s="154" t="s">
         <v>490</v>
       </c>
-      <c r="B35" s="178">
+      <c r="B35" s="170">
         <v>34</v>
       </c>
       <c r="C35" s="16"/>
       <c r="D35" s="17" t="s">
         <v>479</v>
       </c>
-      <c r="E35" s="194" t="s">
+      <c r="E35" s="185" t="s">
         <v>504</v>
       </c>
       <c r="F35" s="36"/>
@@ -7365,7 +7530,7 @@
       <c r="I35" s="107" t="s">
         <v>483</v>
       </c>
-      <c r="J35" s="177" t="s">
+      <c r="J35" s="169" t="s">
         <v>332</v>
       </c>
       <c r="K35" s="16" t="s">
@@ -7399,11 +7564,11 @@
         <f ca="1">IF(OR($D35="Ecoinvent",$D35="Betonsortenrechner",$D35="KBOB",$T35&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X35" s="204">
+      <c r="X35" s="195">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
-      <c r="Y35" s="164" cm="1">
+      <c r="Y35" s="156" cm="1">
         <f t="array" aca="1" ref="Y35" ca="1">IF($W35&lt;&gt;0,
 IF(AND(
                          T35&gt;=_xlfn.PERCENTILE.INC(_xlfn._xlws.FILTER($T$2:$T$148, ($L$2:$L$148=L35)*($W$2:$W$148=1)),0.1),
@@ -7412,22 +7577,27 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z35" s="161"/>
+      <c r="Z35" s="207">
+        <v>206</v>
+      </c>
       <c r="AA35" s="2"/>
-      <c r="AB35" s="190"/>
+      <c r="AB35" s="182"/>
+      <c r="AC35" s="211">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="36" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A36" s="162" t="s">
+      <c r="A36" s="154" t="s">
         <v>491</v>
       </c>
-      <c r="B36" s="163">
+      <c r="B36" s="155">
         <v>35</v>
       </c>
       <c r="C36" s="16"/>
       <c r="D36" s="17" t="s">
         <v>479</v>
       </c>
-      <c r="E36" s="194" t="s">
+      <c r="E36" s="185" t="s">
         <v>505</v>
       </c>
       <c r="F36" s="36"/>
@@ -7436,7 +7606,7 @@
       <c r="I36" s="107" t="s">
         <v>484</v>
       </c>
-      <c r="J36" s="177" t="s">
+      <c r="J36" s="169" t="s">
         <v>332</v>
       </c>
       <c r="K36" s="16" t="s">
@@ -7470,11 +7640,11 @@
         <f ca="1">IF(OR($D36="Ecoinvent",$D36="Betonsortenrechner",$D36="KBOB",$T36&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X36" s="204">
+      <c r="X36" s="195">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
-      <c r="Y36" s="164" cm="1">
+      <c r="Y36" s="156" cm="1">
         <f t="array" aca="1" ref="Y36" ca="1">IF($W36&lt;&gt;0,
 IF(AND(
                          T36&gt;=_xlfn.PERCENTILE.INC(_xlfn._xlws.FILTER($T$2:$T$148, ($L$2:$L$148=L36)*($W$2:$W$148=1)),0.1),
@@ -7483,22 +7653,27 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z36" s="161"/>
+      <c r="Z36" s="207">
+        <v>206</v>
+      </c>
       <c r="AA36" s="2"/>
-      <c r="AB36" s="190"/>
+      <c r="AB36" s="182"/>
+      <c r="AC36" s="211">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="37" spans="1:29" s="15" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="179" t="s">
+      <c r="A37" s="171" t="s">
         <v>200</v>
       </c>
-      <c r="B37" s="180">
+      <c r="B37" s="172">
         <v>36</v>
       </c>
       <c r="C37" s="13"/>
       <c r="D37" s="14" t="s">
         <v>479</v>
       </c>
-      <c r="E37" s="195" t="s">
+      <c r="E37" s="186" t="s">
         <v>506</v>
       </c>
       <c r="F37" s="14"/>
@@ -7515,7 +7690,7 @@
       <c r="K37" s="13" t="s">
         <v>324</v>
       </c>
-      <c r="L37" s="181" t="s">
+      <c r="L37" s="173" t="s">
         <v>325</v>
       </c>
       <c r="M37" s="111" t="s">
@@ -7553,11 +7728,11 @@
         <f ca="1">IF(OR($D37="Ecoinvent",$D37="Betonsortenrechner",$D37="KBOB",$T37&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X37" s="205">
+      <c r="X37" s="196">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
-      <c r="Y37" s="182" cm="1">
+      <c r="Y37" s="174" cm="1">
         <f t="array" aca="1" ref="Y37" ca="1">IF($W37&lt;&gt;0,
 IF(AND(
                          T37&gt;=_xlfn.PERCENTILE.INC(_xlfn._xlws.FILTER($T$2:$T$148, ($L$2:$L$148=L37)*($W$2:$W$148=1)),0.1),
@@ -7566,23 +7741,27 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z37" s="158"/>
+      <c r="Z37" s="207">
+        <v>206</v>
+      </c>
       <c r="AA37" s="13"/>
-      <c r="AB37" s="190"/>
-      <c r="AC37"/>
+      <c r="AB37" s="182"/>
+      <c r="AC37" s="211">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
     <row r="38" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="162" t="s">
+      <c r="A38" s="154" t="s">
         <v>198</v>
       </c>
-      <c r="B38" s="163">
+      <c r="B38" s="155">
         <v>37</v>
       </c>
       <c r="C38" s="16"/>
       <c r="D38" s="17" t="s">
         <v>479</v>
       </c>
-      <c r="E38" s="196">
+      <c r="E38" s="187">
         <v>6.0030000000000001</v>
       </c>
       <c r="F38" s="17"/>
@@ -7636,11 +7815,11 @@
         <f ca="1">IF(OR($D38="Ecoinvent",$D38="Betonsortenrechner",$D38="KBOB",$T38&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X38" s="204">
+      <c r="X38" s="195">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
-      <c r="Y38" s="164" cm="1">
+      <c r="Y38" s="156" cm="1">
         <f t="array" aca="1" ref="Y38" ca="1">IF($W38&lt;&gt;0,
 IF(AND(
                          T38&gt;=_xlfn.PERCENTILE.INC(_xlfn._xlws.FILTER($T$2:$T$148, ($L$2:$L$148=L38)*($W$2:$W$148=1)),0.1),
@@ -7649,10 +7828,16 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z38" s="159"/>
+      <c r="Z38" s="208">
+        <f>2.01*Table2[[#This Row],[DENSITY]]</f>
+        <v>15778.499999999998</v>
+      </c>
       <c r="AA38" s="16"/>
-      <c r="AB38" s="190"/>
-      <c r="AC38"/>
+      <c r="AB38" s="182"/>
+      <c r="AC38" s="211">
+        <f>0.009*Table2[[#This Row],[DENSITY]]</f>
+        <v>70.649999999999991</v>
+      </c>
     </row>
     <row r="39" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A39" s="8" t="s">
@@ -7726,7 +7911,7 @@
         <f ca="1">IF(OR($D39="Ecoinvent",$D39="Betonsortenrechner",$D39="KBOB",$T39&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X39" s="207">
+      <c r="X39" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -7739,9 +7924,16 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z39" s="157"/>
+      <c r="Z39" s="208">
+        <f>2.01*Table2[[#This Row],[DENSITY]]</f>
+        <v>15778.499999999998</v>
+      </c>
       <c r="AA39" s="2"/>
-      <c r="AB39" s="191"/>
+      <c r="AB39" s="183"/>
+      <c r="AC39" s="211">
+        <f>0.009*Table2[[#This Row],[DENSITY]]</f>
+        <v>70.649999999999991</v>
+      </c>
     </row>
     <row r="40" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A40" s="8" t="s">
@@ -7814,7 +8006,7 @@
         <f ca="1">IF(OR($D40="Ecoinvent",$D40="Betonsortenrechner",$D40="KBOB",$T40&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X40" s="207">
+      <c r="X40" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -7827,9 +8019,16 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z40" s="157"/>
+      <c r="Z40" s="208">
+        <f>2.01*Table2[[#This Row],[DENSITY]]</f>
+        <v>15778.499999999998</v>
+      </c>
       <c r="AA40" s="2"/>
-      <c r="AB40" s="191"/>
+      <c r="AB40" s="183"/>
+      <c r="AC40" s="211">
+        <f>0.009*Table2[[#This Row],[DENSITY]]</f>
+        <v>70.649999999999991</v>
+      </c>
     </row>
     <row r="41" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A41" s="8" t="s">
@@ -7903,7 +8102,7 @@
         <f ca="1">IF(OR($D41="Ecoinvent",$D41="Betonsortenrechner",$D41="KBOB",$T41&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X41" s="207">
+      <c r="X41" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
@@ -7916,9 +8115,16 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z41" s="157"/>
+      <c r="Z41" s="208">
+        <f>2.01*Table2[[#This Row],[DENSITY]]</f>
+        <v>15778.499999999998</v>
+      </c>
       <c r="AA41" s="2"/>
-      <c r="AB41" s="191"/>
+      <c r="AB41" s="183"/>
+      <c r="AC41" s="211">
+        <f>0.009*Table2[[#This Row],[DENSITY]]</f>
+        <v>70.649999999999991</v>
+      </c>
     </row>
     <row r="42" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A42" s="8" t="s">
@@ -7992,7 +8198,7 @@
         <f ca="1">IF(OR($D42="Ecoinvent",$D42="Betonsortenrechner",$D42="KBOB",$T42&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X42" s="207">
+      <c r="X42" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
@@ -8005,9 +8211,16 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z42" s="157"/>
+      <c r="Z42" s="208">
+        <f>2.01*Table2[[#This Row],[DENSITY]]</f>
+        <v>15778.499999999998</v>
+      </c>
       <c r="AA42" s="2"/>
-      <c r="AB42" s="191"/>
+      <c r="AB42" s="183"/>
+      <c r="AC42" s="211">
+        <f>0.009*Table2[[#This Row],[DENSITY]]</f>
+        <v>70.649999999999991</v>
+      </c>
     </row>
     <row r="43" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A43" s="8" t="s">
@@ -8080,7 +8293,7 @@
         <f ca="1">IF(OR($D43="Ecoinvent",$D43="Betonsortenrechner",$D43="KBOB",$T43&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X43" s="207">
+      <c r="X43" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -8093,9 +8306,16 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z43" s="157"/>
+      <c r="Z43" s="208">
+        <f>2.01*Table2[[#This Row],[DENSITY]]</f>
+        <v>15778.499999999998</v>
+      </c>
       <c r="AA43" s="2"/>
-      <c r="AB43" s="191"/>
+      <c r="AB43" s="183"/>
+      <c r="AC43" s="211">
+        <f>0.009*Table2[[#This Row],[DENSITY]]</f>
+        <v>70.649999999999991</v>
+      </c>
     </row>
     <row r="44" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
@@ -8169,7 +8389,7 @@
         <f ca="1">IF(OR($D44="Ecoinvent",$D44="Betonsortenrechner",$D44="KBOB",$T44&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X44" s="207">
+      <c r="X44" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
@@ -8182,9 +8402,16 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z44" s="157"/>
+      <c r="Z44" s="208">
+        <f>2.01*Table2[[#This Row],[DENSITY]]</f>
+        <v>15778.499999999998</v>
+      </c>
       <c r="AA44" s="2"/>
-      <c r="AB44" s="191"/>
+      <c r="AB44" s="183"/>
+      <c r="AC44" s="211">
+        <f>0.009*Table2[[#This Row],[DENSITY]]</f>
+        <v>70.649999999999991</v>
+      </c>
     </row>
     <row r="45" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A45" s="8" t="s">
@@ -8258,7 +8485,7 @@
         <f ca="1">IF(OR($D45="Ecoinvent",$D45="Betonsortenrechner",$D45="KBOB",$T45&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X45" s="207">
+      <c r="X45" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -8271,9 +8498,16 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z45" s="157"/>
+      <c r="Z45" s="208">
+        <f>2.01*Table2[[#This Row],[DENSITY]]</f>
+        <v>15778.499999999998</v>
+      </c>
       <c r="AA45" s="2"/>
-      <c r="AB45" s="191"/>
+      <c r="AB45" s="183"/>
+      <c r="AC45" s="211">
+        <f>0.009*Table2[[#This Row],[DENSITY]]</f>
+        <v>70.649999999999991</v>
+      </c>
     </row>
     <row r="46" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A46" s="8" t="s">
@@ -8346,7 +8580,7 @@
         <f ca="1">IF(OR($D46="Ecoinvent",$D46="Betonsortenrechner",$D46="KBOB",$T46&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X46" s="207">
+      <c r="X46" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
@@ -8359,9 +8593,16 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z46" s="157"/>
+      <c r="Z46" s="208">
+        <f>2.01*Table2[[#This Row],[DENSITY]]</f>
+        <v>15778.499999999998</v>
+      </c>
       <c r="AA46" s="2"/>
-      <c r="AB46" s="191"/>
+      <c r="AB46" s="183"/>
+      <c r="AC46" s="211">
+        <f>0.009*Table2[[#This Row],[DENSITY]]</f>
+        <v>70.649999999999991</v>
+      </c>
     </row>
     <row r="47" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
@@ -8434,7 +8675,7 @@
         <f ca="1">IF(OR($D47="Ecoinvent",$D47="Betonsortenrechner",$D47="KBOB",$T47&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X47" s="207">
+      <c r="X47" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -8447,9 +8688,16 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z47" s="157"/>
+      <c r="Z47" s="208">
+        <f>2.01*Table2[[#This Row],[DENSITY]]</f>
+        <v>15778.499999999998</v>
+      </c>
       <c r="AA47" s="2"/>
-      <c r="AB47" s="191"/>
+      <c r="AB47" s="183"/>
+      <c r="AC47" s="211">
+        <f>0.009*Table2[[#This Row],[DENSITY]]</f>
+        <v>70.649999999999991</v>
+      </c>
     </row>
     <row r="48" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A48" s="8" t="s">
@@ -8522,7 +8770,7 @@
         <f ca="1">IF(OR($D48="Ecoinvent",$D48="Betonsortenrechner",$D48="KBOB",$T48&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X48" s="207">
+      <c r="X48" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -8535,9 +8783,16 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z48" s="157"/>
+      <c r="Z48" s="208">
+        <f>2.01*Table2[[#This Row],[DENSITY]]</f>
+        <v>15778.499999999998</v>
+      </c>
       <c r="AA48" s="2"/>
-      <c r="AB48" s="191"/>
+      <c r="AB48" s="183"/>
+      <c r="AC48" s="211">
+        <f>0.009*Table2[[#This Row],[DENSITY]]</f>
+        <v>70.649999999999991</v>
+      </c>
     </row>
     <row r="49" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A49" s="8" t="s">
@@ -8611,7 +8866,7 @@
         <f ca="1">IF(OR($D49="Ecoinvent",$D49="Betonsortenrechner",$D49="KBOB",$T49&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X49" s="207">
+      <c r="X49" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -8624,9 +8879,16 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z49" s="157"/>
+      <c r="Z49" s="208">
+        <f>2.01*Table2[[#This Row],[DENSITY]]</f>
+        <v>15778.499999999998</v>
+      </c>
       <c r="AA49" s="2"/>
-      <c r="AB49" s="191"/>
+      <c r="AB49" s="183"/>
+      <c r="AC49" s="211">
+        <f>0.009*Table2[[#This Row],[DENSITY]]</f>
+        <v>70.649999999999991</v>
+      </c>
     </row>
     <row r="50" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
@@ -8700,7 +8962,7 @@
         <f ca="1">IF(OR($D50="Ecoinvent",$D50="Betonsortenrechner",$D50="KBOB",$T50&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X50" s="207">
+      <c r="X50" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -8713,9 +8975,16 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z50" s="157"/>
+      <c r="Z50" s="208">
+        <f>2.01*Table2[[#This Row],[DENSITY]]</f>
+        <v>15778.499999999998</v>
+      </c>
       <c r="AA50" s="2"/>
-      <c r="AB50" s="191"/>
+      <c r="AB50" s="183"/>
+      <c r="AC50" s="211">
+        <f>0.009*Table2[[#This Row],[DENSITY]]</f>
+        <v>70.649999999999991</v>
+      </c>
     </row>
     <row r="51" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
@@ -8789,7 +9058,7 @@
         <f ca="1">IF(OR($D51="Ecoinvent",$D51="Betonsortenrechner",$D51="KBOB",$T51&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X51" s="207">
+      <c r="X51" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -8802,9 +9071,16 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z51" s="157"/>
+      <c r="Z51" s="208">
+        <f>2.01*Table2[[#This Row],[DENSITY]]</f>
+        <v>15778.499999999998</v>
+      </c>
       <c r="AA51" s="2"/>
-      <c r="AB51" s="191"/>
+      <c r="AB51" s="183"/>
+      <c r="AC51" s="211">
+        <f>0.009*Table2[[#This Row],[DENSITY]]</f>
+        <v>70.649999999999991</v>
+      </c>
     </row>
     <row r="52" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
@@ -8878,7 +9154,7 @@
         <f ca="1">IF(OR($D52="Ecoinvent",$D52="Betonsortenrechner",$D52="KBOB",$T52&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X52" s="207">
+      <c r="X52" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
@@ -8891,9 +9167,16 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z52" s="157"/>
+      <c r="Z52" s="208">
+        <f>2.01*Table2[[#This Row],[DENSITY]]</f>
+        <v>15778.499999999998</v>
+      </c>
       <c r="AA52" s="2"/>
-      <c r="AB52" s="191"/>
+      <c r="AB52" s="183"/>
+      <c r="AC52" s="211">
+        <f>0.009*Table2[[#This Row],[DENSITY]]</f>
+        <v>70.649999999999991</v>
+      </c>
     </row>
     <row r="53" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A53" s="8" t="s">
@@ -8966,7 +9249,7 @@
         <f ca="1">IF(OR($D53="Ecoinvent",$D53="Betonsortenrechner",$D53="KBOB",$T53&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X53" s="207">
+      <c r="X53" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -8979,9 +9262,16 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z53" s="157"/>
+      <c r="Z53" s="208">
+        <f>2.01*Table2[[#This Row],[DENSITY]]</f>
+        <v>15778.499999999998</v>
+      </c>
       <c r="AA53" s="2"/>
-      <c r="AB53" s="191"/>
+      <c r="AB53" s="183"/>
+      <c r="AC53" s="211">
+        <f>0.009*Table2[[#This Row],[DENSITY]]</f>
+        <v>70.649999999999991</v>
+      </c>
     </row>
     <row r="54" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A54" s="8" t="s">
@@ -9054,7 +9344,7 @@
         <f ca="1">IF(OR($D54="Ecoinvent",$D54="Betonsortenrechner",$D54="KBOB",$T54&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X54" s="207">
+      <c r="X54" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -9067,9 +9357,16 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z54" s="157"/>
+      <c r="Z54" s="208">
+        <f>2.01*Table2[[#This Row],[DENSITY]]</f>
+        <v>15778.499999999998</v>
+      </c>
       <c r="AA54" s="2"/>
-      <c r="AB54" s="191"/>
+      <c r="AB54" s="183"/>
+      <c r="AC54" s="211">
+        <f>0.009*Table2[[#This Row],[DENSITY]]</f>
+        <v>70.649999999999991</v>
+      </c>
     </row>
     <row r="55" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A55" s="9" t="s">
@@ -9142,7 +9439,7 @@
         <f ca="1">IF(OR($D55="Ecoinvent",$D55="Betonsortenrechner",$D55="KBOB",$T55&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X55" s="208">
+      <c r="X55" s="199">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
@@ -9155,9 +9452,16 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z55" s="160"/>
+      <c r="Z55" s="208">
+        <f>2.01*Table2[[#This Row],[DENSITY]]</f>
+        <v>15778.499999999998</v>
+      </c>
       <c r="AA55" s="4"/>
-      <c r="AB55" s="191"/>
+      <c r="AB55" s="183"/>
+      <c r="AC55" s="211">
+        <f>0.009*Table2[[#This Row],[DENSITY]]</f>
+        <v>70.649999999999991</v>
+      </c>
     </row>
     <row r="56" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A56" s="92" t="s">
@@ -9230,7 +9534,7 @@
         <f ca="1">IF(OR($D56="Ecoinvent",$D56="Betonsortenrechner",$D56="KBOB",$T56&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X56" s="202">
+      <c r="X56" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -9243,10 +9547,16 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z56" s="155"/>
+      <c r="Z56" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA56" s="11"/>
-      <c r="AB56" s="191"/>
-      <c r="AC56"/>
+      <c r="AB56" s="183"/>
+      <c r="AC56" s="211">
+        <f>1.2</f>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="57" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A57" s="92" t="s">
@@ -9319,7 +9629,7 @@
         <f ca="1">IF(OR($D57="Ecoinvent",$D57="Betonsortenrechner",$D57="KBOB",$T57&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X57" s="202">
+      <c r="X57" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -9332,10 +9642,16 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z57" s="155"/>
+      <c r="Z57" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA57" s="11"/>
-      <c r="AB57" s="191"/>
-      <c r="AC57"/>
+      <c r="AB57" s="183"/>
+      <c r="AC57" s="211">
+        <f t="shared" ref="AC57:AC120" si="1">1.2</f>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="58" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A58" s="92" t="s">
@@ -9408,7 +9724,7 @@
         <f ca="1">IF(OR($D58="Ecoinvent",$D58="Betonsortenrechner",$D58="KBOB",$T58&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X58" s="202">
+      <c r="X58" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -9421,10 +9737,16 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z58" s="155"/>
+      <c r="Z58" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA58" s="11"/>
-      <c r="AB58" s="191"/>
-      <c r="AC58"/>
+      <c r="AB58" s="183"/>
+      <c r="AC58" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="59" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A59" s="92" t="s">
@@ -9497,7 +9819,7 @@
         <f ca="1">IF(OR($D59="Ecoinvent",$D59="Betonsortenrechner",$D59="KBOB",$T59&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X59" s="202">
+      <c r="X59" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -9510,10 +9832,16 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z59" s="155"/>
+      <c r="Z59" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA59" s="11"/>
-      <c r="AB59" s="191"/>
-      <c r="AC59"/>
+      <c r="AB59" s="183"/>
+      <c r="AC59" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="60" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A60" s="92" t="s">
@@ -9586,7 +9914,7 @@
         <f ca="1">IF(OR($D60="Ecoinvent",$D60="Betonsortenrechner",$D60="KBOB",$T60&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X60" s="202">
+      <c r="X60" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -9599,10 +9927,16 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z60" s="155"/>
+      <c r="Z60" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1100</v>
+      </c>
       <c r="AA60" s="11"/>
-      <c r="AB60" s="191"/>
-      <c r="AC60"/>
+      <c r="AB60" s="183"/>
+      <c r="AC60" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="61" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A61" s="92" t="s">
@@ -9675,7 +10009,7 @@
         <f ca="1">IF(OR($D61="Ecoinvent",$D61="Betonsortenrechner",$D61="KBOB",$T61&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X61" s="202">
+      <c r="X61" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -9688,16 +10022,22 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z61" s="155"/>
+      <c r="Z61" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1100</v>
+      </c>
       <c r="AA61" s="11"/>
-      <c r="AB61" s="191"/>
-      <c r="AC61"/>
+      <c r="AB61" s="183"/>
+      <c r="AC61" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="62" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="162" t="s">
+      <c r="A62" s="154" t="s">
         <v>377</v>
       </c>
-      <c r="B62" s="163">
+      <c r="B62" s="155">
         <v>61</v>
       </c>
       <c r="C62" s="20" t="s">
@@ -9706,7 +10046,7 @@
       <c r="D62" s="17" t="s">
         <v>479</v>
       </c>
-      <c r="E62" s="193" t="s">
+      <c r="E62" s="184" t="s">
         <v>498</v>
       </c>
       <c r="F62" s="17"/>
@@ -9761,11 +10101,11 @@
         <f ca="1">IF(OR($D62="Ecoinvent",$D62="Betonsortenrechner",$D62="KBOB",$T62&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X62" s="204">
+      <c r="X62" s="195">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
-      <c r="Y62" s="164" cm="1">
+      <c r="Y62" s="156" cm="1">
         <f t="array" aca="1" ref="Y62" ca="1">IF($W62&lt;&gt;0,
 IF(AND(
                          T62&gt;=_xlfn.PERCENTILE.INC(_xlfn._xlws.FILTER($T$2:$T$148, ($K$2:$K$148=K62)*($W$2:$W$148=1)),0.1),
@@ -9774,16 +10114,22 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z62" s="161"/>
+      <c r="Z62" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA62" s="16"/>
-      <c r="AB62" s="190"/>
-      <c r="AC62"/>
+      <c r="AB62" s="182"/>
+      <c r="AC62" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="63" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="162" t="s">
+      <c r="A63" s="154" t="s">
         <v>230</v>
       </c>
-      <c r="B63" s="163">
+      <c r="B63" s="155">
         <v>62</v>
       </c>
       <c r="C63" s="20" t="s">
@@ -9792,7 +10138,7 @@
       <c r="D63" s="17" t="s">
         <v>479</v>
       </c>
-      <c r="E63" s="196">
+      <c r="E63" s="187">
         <v>7.0030000000000001</v>
       </c>
       <c r="F63" s="17"/>
@@ -9844,11 +10190,11 @@
         <f ca="1">IF(OR($D63="Ecoinvent",$D63="Betonsortenrechner",$D63="KBOB",$T63&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X63" s="204">
+      <c r="X63" s="195">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
-      <c r="Y63" s="164" cm="1">
+      <c r="Y63" s="156" cm="1">
         <f t="array" aca="1" ref="Y63" ca="1">IF($W63&lt;&gt;0,
 IF(AND(
                          T63&gt;=_xlfn.PERCENTILE.INC(_xlfn._xlws.FILTER($T$2:$T$148, ($K$2:$K$148=K63)*($W$2:$W$148=1)),0.1),
@@ -9857,16 +10203,22 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z63" s="161"/>
+      <c r="Z63" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA63" s="16"/>
-      <c r="AB63" s="190"/>
-      <c r="AC63"/>
+      <c r="AB63" s="182"/>
+      <c r="AC63" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="64" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="162" t="s">
+      <c r="A64" s="154" t="s">
         <v>229</v>
       </c>
-      <c r="B64" s="163">
+      <c r="B64" s="155">
         <v>63</v>
       </c>
       <c r="C64" s="20" t="s">
@@ -9875,7 +10227,7 @@
       <c r="D64" s="17" t="s">
         <v>479</v>
       </c>
-      <c r="E64" s="193" t="s">
+      <c r="E64" s="184" t="s">
         <v>498</v>
       </c>
       <c r="F64" s="17"/>
@@ -9929,11 +10281,11 @@
         <f ca="1">IF(OR($D64="Ecoinvent",$D64="Betonsortenrechner",$D64="KBOB",$T64&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X64" s="204">
+      <c r="X64" s="195">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
-      <c r="Y64" s="164" cm="1">
+      <c r="Y64" s="156" cm="1">
         <f t="array" aca="1" ref="Y64" ca="1">IF($W64&lt;&gt;0,
 IF(AND(
                          T64&gt;=_xlfn.PERCENTILE.INC(_xlfn._xlws.FILTER($T$2:$T$148, ($K$2:$K$148=K64)*($W$2:$W$148=1)),0.1),
@@ -9942,16 +10294,22 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z64" s="161"/>
+      <c r="Z64" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA64" s="16"/>
-      <c r="AB64" s="190"/>
-      <c r="AC64"/>
+      <c r="AB64" s="182"/>
+      <c r="AC64" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="65" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="162" t="s">
+      <c r="A65" s="154" t="s">
         <v>228</v>
       </c>
-      <c r="B65" s="163">
+      <c r="B65" s="155">
         <v>64</v>
       </c>
       <c r="C65" s="20" t="s">
@@ -9960,7 +10318,7 @@
       <c r="D65" s="17" t="s">
         <v>479</v>
       </c>
-      <c r="E65" s="196">
+      <c r="E65" s="187">
         <v>7.02</v>
       </c>
       <c r="F65" s="17"/>
@@ -10012,11 +10370,11 @@
         <f ca="1">IF(OR($D65="Ecoinvent",$D65="Betonsortenrechner",$D65="KBOB",$T65&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X65" s="204">
+      <c r="X65" s="195">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
-      <c r="Y65" s="164" cm="1">
+      <c r="Y65" s="156" cm="1">
         <f t="array" aca="1" ref="Y65" ca="1">IF($W65&lt;&gt;0,
 IF(AND(
                          T65&gt;=_xlfn.PERCENTILE.INC(_xlfn._xlws.FILTER($T$2:$T$148, ($K$2:$K$148=K65)*($W$2:$W$148=1)),0.1),
@@ -10025,25 +10383,31 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z65" s="161"/>
+      <c r="Z65" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA65" s="16"/>
-      <c r="AB65" s="190"/>
-      <c r="AC65"/>
+      <c r="AB65" s="182"/>
+      <c r="AC65" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="66" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="162" t="s">
+      <c r="A66" s="154" t="s">
         <v>227</v>
       </c>
-      <c r="B66" s="163">
+      <c r="B66" s="155">
         <v>65</v>
       </c>
       <c r="C66" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="D66" s="189" t="s">
+      <c r="D66" s="181" t="s">
         <v>479</v>
       </c>
-      <c r="E66" s="193" t="s">
+      <c r="E66" s="184" t="s">
         <v>499</v>
       </c>
       <c r="F66" s="17"/>
@@ -10095,11 +10459,11 @@
         <f ca="1">IF(OR($D66="Ecoinvent",$D66="Betonsortenrechner",$D66="KBOB",$T66&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X66" s="204">
+      <c r="X66" s="195">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
-      <c r="Y66" s="164" cm="1">
+      <c r="Y66" s="156" cm="1">
         <f t="array" aca="1" ref="Y66" ca="1">IF($W66&lt;&gt;0,
 IF(AND(
                          T66&gt;=_xlfn.PERCENTILE.INC(_xlfn._xlws.FILTER($T$2:$T$148, ($K$2:$K$148=K66)*($W$2:$W$148=1)),0.1),
@@ -10108,10 +10472,16 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z66" s="161"/>
+      <c r="Z66" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1100</v>
+      </c>
       <c r="AA66" s="16"/>
-      <c r="AB66" s="190"/>
-      <c r="AC66"/>
+      <c r="AB66" s="182"/>
+      <c r="AC66" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="67" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A67" s="8" t="s">
@@ -10130,7 +10500,7 @@
       <c r="F67" s="33">
         <v>43248</v>
       </c>
-      <c r="G67" s="198">
+      <c r="G67" s="189">
         <v>45439</v>
       </c>
       <c r="H67" s="26" t="s">
@@ -10185,7 +10555,7 @@
         <f ca="1">IF(OR($D67="Ecoinvent",$D67="Betonsortenrechner",$D67="KBOB",$T67&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X67" s="207">
+      <c r="X67" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
@@ -10198,11 +10568,18 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z67" s="157"/>
+      <c r="Z67" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA67" s="2" t="s">
         <v>428</v>
       </c>
       <c r="AB67" s="21"/>
+      <c r="AC67" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="68" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A68" s="8" t="s">
@@ -10242,7 +10619,7 @@
       <c r="M68" s="110" t="s">
         <v>167</v>
       </c>
-      <c r="N68" s="197" t="s">
+      <c r="N68" s="188" t="s">
         <v>1</v>
       </c>
       <c r="O68" s="26">
@@ -10276,7 +10653,7 @@
         <f ca="1">IF(OR($D68="Ecoinvent",$D68="Betonsortenrechner",$D68="KBOB",$T68&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X68" s="207">
+      <c r="X68" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -10289,11 +10666,18 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z68" s="157"/>
+      <c r="Z68" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA68" s="2" t="s">
         <v>429</v>
       </c>
       <c r="AB68" s="21"/>
+      <c r="AC68" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="69" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A69" s="8" t="s">
@@ -10367,7 +10751,7 @@
         <f ca="1">IF(OR($D69="Ecoinvent",$D69="Betonsortenrechner",$D69="KBOB",$T69&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X69" s="207">
+      <c r="X69" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
@@ -10380,9 +10764,16 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z69" s="157"/>
+      <c r="Z69" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA69" s="2"/>
       <c r="AB69" s="21"/>
+      <c r="AC69" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="70" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A70" s="8" t="s">
@@ -10456,7 +10847,7 @@
         <f ca="1">IF(OR($D70="Ecoinvent",$D70="Betonsortenrechner",$D70="KBOB",$T70&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X70" s="207">
+      <c r="X70" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -10469,11 +10860,18 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z70" s="157"/>
+      <c r="Z70" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA70" s="2" t="s">
         <v>431</v>
       </c>
       <c r="AB70" s="21"/>
+      <c r="AC70" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="71" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A71" s="8" t="s">
@@ -10547,7 +10945,7 @@
         <f ca="1">IF(OR($D71="Ecoinvent",$D71="Betonsortenrechner",$D71="KBOB",$T71&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X71" s="207">
+      <c r="X71" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -10560,11 +10958,18 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z71" s="157"/>
+      <c r="Z71" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA71" s="2" t="s">
         <v>430</v>
       </c>
       <c r="AB71" s="21"/>
+      <c r="AC71" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="72" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A72" s="8" t="s">
@@ -10638,7 +11043,7 @@
         <f ca="1">IF(OR($D72="Ecoinvent",$D72="Betonsortenrechner",$D72="KBOB",$T72&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X72" s="207">
+      <c r="X72" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -10651,11 +11056,18 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z72" s="157"/>
+      <c r="Z72" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA72" s="2" t="s">
         <v>431</v>
       </c>
       <c r="AB72" s="21"/>
+      <c r="AC72" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="73" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A73" s="8" t="s">
@@ -10729,7 +11141,7 @@
         <f ca="1">IF(OR($D73="Ecoinvent",$D73="Betonsortenrechner",$D73="KBOB",$T73&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X73" s="207">
+      <c r="X73" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
@@ -10742,9 +11154,16 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z73" s="157"/>
+      <c r="Z73" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA73" s="2"/>
       <c r="AB73" s="21"/>
+      <c r="AC73" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="74" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="8" t="s">
@@ -10772,13 +11191,13 @@
       <c r="I74" s="105" t="s">
         <v>114</v>
       </c>
-      <c r="J74" s="199" t="s">
+      <c r="J74" s="190" t="s">
         <v>337</v>
       </c>
       <c r="K74" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="L74" s="200" t="s">
+      <c r="L74" s="191" t="s">
         <v>330</v>
       </c>
       <c r="M74" s="110" t="s">
@@ -10818,7 +11237,7 @@
         <f ca="1">IF(OR($D74="Ecoinvent",$D74="Betonsortenrechner",$D74="KBOB",$T74&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X74" s="207">
+      <c r="X74" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -10831,12 +11250,19 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z74" s="157"/>
+      <c r="Z74" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1100</v>
+      </c>
       <c r="AA74" s="63" t="s">
         <v>416</v>
       </c>
       <c r="AB74" s="21" t="s">
         <v>419</v>
+      </c>
+      <c r="AC74" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
       </c>
     </row>
     <row r="75" spans="1:29" x14ac:dyDescent="0.2">
@@ -10911,7 +11337,7 @@
         <f ca="1">IF(OR($D75="Ecoinvent",$D75="Betonsortenrechner",$D75="KBOB",$T75&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X75" s="207">
+      <c r="X75" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -10924,11 +11350,18 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z75" s="157"/>
+      <c r="Z75" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA75" s="2" t="s">
         <v>433</v>
       </c>
       <c r="AB75" s="21"/>
+      <c r="AC75" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="76" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A76" s="8" t="s">
@@ -11002,7 +11435,7 @@
         <f ca="1">IF(OR($D76="Ecoinvent",$D76="Betonsortenrechner",$D76="KBOB",$T76&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X76" s="207">
+      <c r="X76" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -11015,11 +11448,18 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z76" s="157"/>
+      <c r="Z76" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA76" s="2" t="s">
         <v>433</v>
       </c>
       <c r="AB76" s="21"/>
+      <c r="AC76" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="77" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A77" s="8" t="s">
@@ -11028,17 +11468,17 @@
       <c r="B77" s="98">
         <v>76</v>
       </c>
-      <c r="C77" s="169" t="s">
+      <c r="C77" s="161" t="s">
         <v>123</v>
       </c>
-      <c r="D77" s="170" t="s">
+      <c r="D77" s="162" t="s">
         <v>121</v>
       </c>
-      <c r="E77" s="170"/>
-      <c r="F77" s="171" t="s">
+      <c r="E77" s="162"/>
+      <c r="F77" s="163" t="s">
         <v>123</v>
       </c>
-      <c r="G77" s="171" t="s">
+      <c r="G77" s="163" t="s">
         <v>123</v>
       </c>
       <c r="H77" s="26" t="s">
@@ -11077,22 +11517,22 @@
       <c r="S77" s="132" t="s">
         <v>427</v>
       </c>
-      <c r="T77" s="166">
+      <c r="T77" s="158">
         <f>SUM(Table2[[#This Row],[A1toA3_GWP]:[C1toC4_GWP]])</f>
         <v>3056.7816091954023</v>
       </c>
-      <c r="U77" s="172">
+      <c r="U77" s="164">
         <f>(-1220-1400+3250)/Table2[[#This Row],[DENSITY]]*1000</f>
         <v>1448.2758620689656</v>
       </c>
-      <c r="V77" s="168">
+      <c r="V77" s="160">
         <f>(0.7+699)/Table2[[#This Row],[DENSITY]]*1000</f>
         <v>1608.5057471264367</v>
       </c>
       <c r="W77" s="50">
         <v>0</v>
       </c>
-      <c r="X77" s="206">
+      <c r="X77" s="197">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -11105,9 +11545,16 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z77" s="157"/>
+      <c r="Z77" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA77" s="2"/>
       <c r="AB77" s="21"/>
+      <c r="AC77" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="78" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A78" s="8" t="s">
@@ -11181,7 +11628,7 @@
         <f ca="1">IF(OR($D78="Ecoinvent",$D78="Betonsortenrechner",$D78="KBOB",$T78&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X78" s="207">
+      <c r="X78" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -11194,9 +11641,16 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z78" s="157"/>
+      <c r="Z78" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA78" s="2"/>
       <c r="AB78" s="21"/>
+      <c r="AC78" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="79" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A79" s="8" t="s">
@@ -11270,7 +11724,7 @@
         <f ca="1">IF(OR($D79="Ecoinvent",$D79="Betonsortenrechner",$D79="KBOB",$T79&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X79" s="207">
+      <c r="X79" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
@@ -11283,11 +11737,18 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z79" s="157"/>
+      <c r="Z79" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA79" s="2" t="s">
         <v>438</v>
       </c>
       <c r="AB79" s="21"/>
+      <c r="AC79" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="80" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A80" s="8" t="s">
@@ -11345,15 +11806,15 @@
       <c r="S80" s="132" t="s">
         <v>427</v>
       </c>
-      <c r="T80" s="166">
+      <c r="T80" s="158">
         <f>SUM(Table2[[#This Row],[A1toA3_GWP]:[C1toC4_GWP]])</f>
         <v>-66.186046511627865</v>
       </c>
-      <c r="U80" s="167">
+      <c r="U80" s="159">
         <f>-780/Table2[[#This Row],[DENSITY]]*1000</f>
         <v>-1813.9534883720928</v>
       </c>
-      <c r="V80" s="168">
+      <c r="V80" s="160">
         <f>(0.24+1.3+750)/Table2[[#This Row],[DENSITY]]*1000</f>
         <v>1747.7674418604649</v>
       </c>
@@ -11361,7 +11822,7 @@
         <f ca="1">IF(OR($D80="Ecoinvent",$D80="Betonsortenrechner",$D80="KBOB",$T80&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X80" s="206">
+      <c r="X80" s="197">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -11374,13 +11835,20 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z80" s="157"/>
+      <c r="Z80" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA80" s="2" t="s">
         <v>439</v>
       </c>
       <c r="AB80" s="21"/>
+      <c r="AC80" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
-    <row r="81" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A81" s="8" t="s">
         <v>250</v>
       </c>
@@ -11452,7 +11920,7 @@
         <f ca="1">IF(OR($D81="Ecoinvent",$D81="Betonsortenrechner",$D81="KBOB",$T81&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X81" s="207">
+      <c r="X81" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -11465,15 +11933,22 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z81" s="157"/>
+      <c r="Z81" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA81" s="2" t="s">
         <v>440</v>
       </c>
       <c r="AB81" s="21" t="s">
         <v>423</v>
       </c>
+      <c r="AC81" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
-    <row r="82" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A82" s="8" t="s">
         <v>251</v>
       </c>
@@ -11545,7 +12020,7 @@
         <f ca="1">IF(OR($D82="Ecoinvent",$D82="Betonsortenrechner",$D82="KBOB",$T82&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X82" s="207">
+      <c r="X82" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
@@ -11558,11 +12033,18 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z82" s="157"/>
+      <c r="Z82" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA82" s="2"/>
       <c r="AB82" s="21"/>
+      <c r="AC82" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
-    <row r="83" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A83" s="8" t="s">
         <v>256</v>
       </c>
@@ -11634,7 +12116,7 @@
         <f ca="1">IF(OR($D83="Ecoinvent",$D83="Betonsortenrechner",$D83="KBOB",$T83&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X83" s="207">
+      <c r="X83" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -11647,11 +12129,18 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z83" s="157"/>
+      <c r="Z83" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA83" s="2"/>
       <c r="AB83" s="21"/>
+      <c r="AC83" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
-    <row r="84" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A84" s="8" t="s">
         <v>259</v>
       </c>
@@ -11723,7 +12212,7 @@
         <f ca="1">IF(OR($D84="Ecoinvent",$D84="Betonsortenrechner",$D84="KBOB",$T84&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X84" s="207">
+      <c r="X84" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -11736,11 +12225,18 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z84" s="157"/>
+      <c r="Z84" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA84" s="2"/>
       <c r="AB84" s="21"/>
+      <c r="AC84" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
-    <row r="85" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A85" s="8" t="s">
         <v>260</v>
       </c>
@@ -11804,7 +12300,7 @@
         <f ca="1">IF(OR($D85="Ecoinvent",$D85="Betonsortenrechner",$D85="KBOB",$T85&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X85" s="207">
+      <c r="X85" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
@@ -11817,11 +12313,18 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z85" s="157"/>
+      <c r="Z85" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA85" s="2"/>
       <c r="AB85" s="21"/>
+      <c r="AC85" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
-    <row r="86" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A86" s="8" t="s">
         <v>264</v>
       </c>
@@ -11893,7 +12396,7 @@
         <f ca="1">IF(OR($D86="Ecoinvent",$D86="Betonsortenrechner",$D86="KBOB",$T86&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X86" s="207">
+      <c r="X86" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
@@ -11906,11 +12409,18 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z86" s="157"/>
+      <c r="Z86" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA86" s="2"/>
       <c r="AB86" s="21"/>
+      <c r="AC86" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
-    <row r="87" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A87" s="8" t="s">
         <v>265</v>
       </c>
@@ -11979,7 +12489,7 @@
         <f ca="1">IF(OR($D87="Ecoinvent",$D87="Betonsortenrechner",$D87="KBOB",$T87&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X87" s="207">
+      <c r="X87" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
@@ -11992,11 +12502,18 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z87" s="157"/>
+      <c r="Z87" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA87" s="2"/>
       <c r="AB87" s="21"/>
+      <c r="AC87" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
-    <row r="88" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A88" s="8" t="s">
         <v>270</v>
       </c>
@@ -12068,7 +12585,7 @@
         <f ca="1">IF(OR($D88="Ecoinvent",$D88="Betonsortenrechner",$D88="KBOB",$T88&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X88" s="207">
+      <c r="X88" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -12081,11 +12598,18 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z88" s="157"/>
+      <c r="Z88" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA88" s="2"/>
       <c r="AB88" s="21"/>
+      <c r="AC88" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
-    <row r="89" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A89" s="8" t="s">
         <v>275</v>
       </c>
@@ -12157,7 +12681,7 @@
         <f ca="1">IF(OR($D89="Ecoinvent",$D89="Betonsortenrechner",$D89="KBOB",$T89&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X89" s="207">
+      <c r="X89" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -12170,13 +12694,20 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z89" s="157"/>
+      <c r="Z89" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA89" s="2" t="s">
         <v>434</v>
       </c>
       <c r="AB89" s="21"/>
+      <c r="AC89" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
-    <row r="90" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A90" s="8" t="s">
         <v>277</v>
       </c>
@@ -12232,22 +12763,22 @@
       <c r="S90" s="132" t="s">
         <v>427</v>
       </c>
-      <c r="T90" s="166">
+      <c r="T90" s="158">
         <f>SUM(Table2[[#This Row],[A1toA3_GWP]:[C1toC4_GWP]])</f>
         <v>-1534.8837209302326</v>
       </c>
-      <c r="U90" s="167">
+      <c r="U90" s="159">
         <f>(-660)/Table2[[#This Row],[DENSITY]]*1000</f>
         <v>-1534.8837209302326</v>
       </c>
-      <c r="V90" s="168" t="s">
+      <c r="V90" s="160" t="s">
         <v>167</v>
       </c>
       <c r="W90" s="50">
         <f ca="1">IF(OR($D90="Ecoinvent",$D90="Betonsortenrechner",$D90="KBOB",$T90&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X90" s="206">
+      <c r="X90" s="197">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
@@ -12260,13 +12791,20 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z90" s="157"/>
+      <c r="Z90" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA90" s="2" t="s">
         <v>432</v>
       </c>
       <c r="AB90" s="21"/>
+      <c r="AC90" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
-    <row r="91" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A91" s="8" t="s">
         <v>278</v>
       </c>
@@ -12338,7 +12876,7 @@
         <f ca="1">IF(OR($D91="Ecoinvent",$D91="Betonsortenrechner",$D91="KBOB",$T91&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X91" s="207">
+      <c r="X91" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -12351,13 +12889,20 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z91" s="157"/>
+      <c r="Z91" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA91" s="2" t="s">
         <v>435</v>
       </c>
       <c r="AB91" s="21"/>
+      <c r="AC91" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
-    <row r="92" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A92" s="8" t="s">
         <v>282</v>
       </c>
@@ -12429,7 +12974,7 @@
         <f ca="1">IF(OR($D92="Ecoinvent",$D92="Betonsortenrechner",$D92="KBOB",$T92&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X92" s="207">
+      <c r="X92" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -12442,15 +12987,22 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z92" s="157"/>
+      <c r="Z92" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA92" s="2" t="s">
         <v>437</v>
       </c>
       <c r="AB92" s="21" t="s">
         <v>436</v>
       </c>
+      <c r="AC92" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
-    <row r="93" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A93" s="8" t="s">
         <v>285</v>
       </c>
@@ -12522,7 +13074,7 @@
         <f ca="1">IF(OR($D93="Ecoinvent",$D93="Betonsortenrechner",$D93="KBOB",$T93&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X93" s="207">
+      <c r="X93" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -12535,13 +13087,20 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z93" s="157"/>
+      <c r="Z93" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA93" s="2" t="s">
         <v>434</v>
       </c>
       <c r="AB93" s="21"/>
+      <c r="AC93" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
-    <row r="94" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A94" s="8" t="s">
         <v>289</v>
       </c>
@@ -12613,7 +13172,7 @@
         <f ca="1">IF(OR($D94="Ecoinvent",$D94="Betonsortenrechner",$D94="KBOB",$T94&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X94" s="207">
+      <c r="X94" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
@@ -12626,11 +13185,18 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z94" s="157"/>
+      <c r="Z94" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA94" s="2"/>
       <c r="AB94" s="21"/>
+      <c r="AC94" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
-    <row r="95" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A95" s="8" t="s">
         <v>293</v>
       </c>
@@ -12702,7 +13268,7 @@
         <f ca="1">IF(OR($D95="Ecoinvent",$D95="Betonsortenrechner",$D95="KBOB",$T95&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X95" s="207">
+      <c r="X95" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
@@ -12715,11 +13281,18 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z95" s="157"/>
+      <c r="Z95" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA95" s="2"/>
       <c r="AB95" s="21"/>
+      <c r="AC95" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
-    <row r="96" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A96" s="8" t="s">
         <v>299</v>
       </c>
@@ -12775,15 +13348,15 @@
       <c r="S96" s="132" t="s">
         <v>427</v>
       </c>
-      <c r="T96" s="166">
+      <c r="T96" s="158">
         <f>SUM(Table2[[#This Row],[A1toA3_GWP]:[C1toC4_GWP]])</f>
         <v>-220.42826552462543</v>
       </c>
-      <c r="U96" s="167">
+      <c r="U96" s="159">
         <f>(-814)/Table2[[#This Row],[DENSITY]]*1000</f>
         <v>-1743.0406852248395</v>
       </c>
-      <c r="V96" s="168">
+      <c r="V96" s="160">
         <f>(1.57+6.49+703)/Table2[[#This Row],[DENSITY]]*1000</f>
         <v>1522.6124197002141</v>
       </c>
@@ -12791,7 +13364,7 @@
         <f ca="1">IF(OR($D96="Ecoinvent",$D96="Betonsortenrechner",$D96="KBOB",$T96&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X96" s="206">
+      <c r="X96" s="197">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
@@ -12804,11 +13377,18 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z96" s="157"/>
+      <c r="Z96" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA96" s="2" t="s">
         <v>438</v>
       </c>
       <c r="AB96" s="21"/>
+      <c r="AC96" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="97" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A97" s="8" t="s">
@@ -12848,7 +13428,7 @@
       <c r="M97" s="110" t="s">
         <v>167</v>
       </c>
-      <c r="N97" s="197" t="s">
+      <c r="N97" s="188" t="s">
         <v>119</v>
       </c>
       <c r="O97" s="26">
@@ -12882,7 +13462,7 @@
         <f ca="1">IF(OR($D97="Ecoinvent",$D97="Betonsortenrechner",$D97="KBOB",$T97&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X97" s="207">
+      <c r="X97" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
@@ -12895,11 +13475,18 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z97" s="157"/>
+      <c r="Z97" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1100</v>
+      </c>
       <c r="AA97" s="2" t="s">
         <v>418</v>
       </c>
       <c r="AB97" s="21"/>
+      <c r="AC97" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="98" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A98" s="8" t="s">
@@ -12973,7 +13560,7 @@
         <f ca="1">IF(OR($D98="Ecoinvent",$D98="Betonsortenrechner",$D98="KBOB",$T98&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X98" s="207">
+      <c r="X98" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
@@ -12986,11 +13573,18 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z98" s="157"/>
+      <c r="Z98" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1100</v>
+      </c>
       <c r="AA98" s="2" t="s">
         <v>417</v>
       </c>
       <c r="AB98" s="21"/>
+      <c r="AC98" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="99" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A99" s="8" t="s">
@@ -13064,7 +13658,7 @@
         <f ca="1">IF(OR($D99="Ecoinvent",$D99="Betonsortenrechner",$D99="KBOB",$T99&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X99" s="207">
+      <c r="X99" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -13077,11 +13671,18 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z99" s="157"/>
+      <c r="Z99" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1100</v>
+      </c>
       <c r="AA99" s="2" t="s">
         <v>420</v>
       </c>
       <c r="AB99" s="21"/>
+      <c r="AC99" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="100" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A100" s="8" t="s">
@@ -13155,7 +13756,7 @@
         <f ca="1">IF(OR($D100="Ecoinvent",$D100="Betonsortenrechner",$D100="KBOB",$T100&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X100" s="207">
+      <c r="X100" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -13168,11 +13769,18 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z100" s="157"/>
+      <c r="Z100" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1100</v>
+      </c>
       <c r="AA100" s="2" t="s">
         <v>421</v>
       </c>
       <c r="AB100" s="21"/>
+      <c r="AC100" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="101" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A101" s="8" t="s">
@@ -13246,7 +13854,7 @@
         <f ca="1">IF(OR($D101="Ecoinvent",$D101="Betonsortenrechner",$D101="KBOB",$T101&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X101" s="207">
+      <c r="X101" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
@@ -13259,12 +13867,19 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z101" s="157"/>
+      <c r="Z101" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1100</v>
+      </c>
       <c r="AA101" s="2" t="s">
         <v>422</v>
       </c>
       <c r="AB101" s="21" t="s">
         <v>424</v>
+      </c>
+      <c r="AC101" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
       </c>
     </row>
     <row r="102" spans="1:29" x14ac:dyDescent="0.2">
@@ -13339,7 +13954,7 @@
         <f ca="1">IF(OR($D102="Ecoinvent",$D102="Betonsortenrechner",$D102="KBOB",$T102&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X102" s="207">
+      <c r="X102" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -13352,12 +13967,19 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z102" s="157"/>
+      <c r="Z102" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1100</v>
+      </c>
       <c r="AA102" s="2" t="s">
         <v>426</v>
       </c>
       <c r="AB102" s="21" t="s">
         <v>425</v>
+      </c>
+      <c r="AC102" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
       </c>
     </row>
     <row r="103" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
@@ -13432,11 +14054,11 @@
         <f ca="1">IF(OR($D103="Ecoinvent",$D103="Betonsortenrechner",$D103="KBOB",$T103&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X103" s="207">
+      <c r="X103" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
-      <c r="Y103" s="175" cm="1">
+      <c r="Y103" s="167" cm="1">
         <f t="array" aca="1" ref="Y103" ca="1">IF($W103&lt;&gt;0,
 IF(AND(
                          T103&gt;=_xlfn.PERCENTILE.INC(_xlfn._xlws.FILTER($T$2:$T$148, ($L$2:$L$148=L103)*($W$2:$W$148=1)),0.1),
@@ -13445,11 +14067,18 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z103" s="160"/>
+      <c r="Z103" s="207">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
+        <v>1800</v>
+      </c>
       <c r="AA103" s="4" t="s">
         <v>467</v>
       </c>
       <c r="AB103" s="37"/>
+      <c r="AC103" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="104" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A104" s="8" t="s">
@@ -13459,10 +14088,10 @@
         <v>103</v>
       </c>
       <c r="C104" s="16"/>
-      <c r="D104" s="189" t="s">
+      <c r="D104" s="181" t="s">
         <v>479</v>
       </c>
-      <c r="E104" s="196">
+      <c r="E104" s="187">
         <v>6.0119999999999996</v>
       </c>
       <c r="F104" s="36"/>
@@ -13517,7 +14146,7 @@
         <f ca="1">IF(OR($D104="Ecoinvent",$D104="Betonsortenrechner",$D104="KBOB",$T104&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X104" s="202">
+      <c r="X104" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
@@ -13530,12 +14159,18 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z104" s="161"/>
-      <c r="AA104" s="184" t="s">
+      <c r="Z104" s="209">
+        <f>17*Table2[[#This Row],[DENSITY]]</f>
+        <v>133450</v>
+      </c>
+      <c r="AA104" s="176" t="s">
         <v>493</v>
       </c>
-      <c r="AB104" s="187"/>
-      <c r="AC104"/>
+      <c r="AB104" s="179"/>
+      <c r="AC104" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="105" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A105" s="8" t="s">
@@ -13605,7 +14240,7 @@
         <f ca="1">IF(OR($D105="Ecoinvent",$D105="Betonsortenrechner",$D105="KBOB",$T105&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X105" s="202">
+      <c r="X105" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
@@ -13618,11 +14253,18 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z105" s="157"/>
-      <c r="AA105" s="185" t="s">
+      <c r="Z105" s="209">
+        <f>17*Table2[[#This Row],[DENSITY]]</f>
+        <v>133450</v>
+      </c>
+      <c r="AA105" s="177" t="s">
         <v>493</v>
       </c>
       <c r="AB105" s="21"/>
+      <c r="AC105" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="106" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A106" s="8" t="s">
@@ -13693,7 +14335,7 @@
         <f ca="1">IF(OR($D106="Ecoinvent",$D106="Betonsortenrechner",$D106="KBOB",$T106&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X106" s="202">
+      <c r="X106" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
@@ -13706,11 +14348,18 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z106" s="157"/>
-      <c r="AA106" s="185" t="s">
+      <c r="Z106" s="209">
+        <f>17*Table2[[#This Row],[DENSITY]]</f>
+        <v>133450</v>
+      </c>
+      <c r="AA106" s="177" t="s">
         <v>493</v>
       </c>
       <c r="AB106" s="21"/>
+      <c r="AC106" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="107" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A107" s="8" t="s">
@@ -13781,7 +14430,7 @@
         <f ca="1">IF(OR($D107="Ecoinvent",$D107="Betonsortenrechner",$D107="KBOB",$T107&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X107" s="202">
+      <c r="X107" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -13794,11 +14443,18 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z107" s="157"/>
-      <c r="AA107" s="185" t="s">
+      <c r="Z107" s="209">
+        <f>17*Table2[[#This Row],[DENSITY]]</f>
+        <v>133450</v>
+      </c>
+      <c r="AA107" s="177" t="s">
         <v>493</v>
       </c>
       <c r="AB107" s="21"/>
+      <c r="AC107" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="108" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A108" s="8" t="s">
@@ -13869,7 +14525,7 @@
         <f ca="1">IF(OR($D108="Ecoinvent",$D108="Betonsortenrechner",$D108="KBOB",$T108&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X108" s="202">
+      <c r="X108" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -13882,11 +14538,18 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z108" s="157"/>
-      <c r="AA108" s="185" t="s">
+      <c r="Z108" s="209">
+        <f>17*Table2[[#This Row],[DENSITY]]</f>
+        <v>133450</v>
+      </c>
+      <c r="AA108" s="177" t="s">
         <v>493</v>
       </c>
       <c r="AB108" s="21"/>
+      <c r="AC108" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="109" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A109" s="8" t="s">
@@ -13957,7 +14620,7 @@
         <f ca="1">IF(OR($D109="Ecoinvent",$D109="Betonsortenrechner",$D109="KBOB",$T109&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X109" s="202">
+      <c r="X109" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -13970,11 +14633,18 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z109" s="157"/>
-      <c r="AA109" s="185" t="s">
+      <c r="Z109" s="209">
+        <f>17*Table2[[#This Row],[DENSITY]]</f>
+        <v>133450</v>
+      </c>
+      <c r="AA109" s="177" t="s">
         <v>493</v>
       </c>
       <c r="AB109" s="21"/>
+      <c r="AC109" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="110" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A110" s="8" t="s">
@@ -14044,7 +14714,7 @@
         <f ca="1">IF(OR($D110="Ecoinvent",$D110="Betonsortenrechner",$D110="KBOB",$T110&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X110" s="202">
+      <c r="X110" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
@@ -14057,14 +14727,21 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z110" s="157"/>
-      <c r="AA110" s="185" t="s">
+      <c r="Z110" s="209">
+        <f>17*Table2[[#This Row],[DENSITY]]</f>
+        <v>133450</v>
+      </c>
+      <c r="AA110" s="177" t="s">
         <v>493</v>
       </c>
       <c r="AB110" s="21"/>
+      <c r="AC110" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="111" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A111" s="174" t="s">
+      <c r="A111" s="166" t="s">
         <v>441</v>
       </c>
       <c r="B111" s="98">
@@ -14133,7 +14810,7 @@
         <f ca="1">IF(OR($D111="Ecoinvent",$D111="Betonsortenrechner",$D111="KBOB",$T111&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X111" s="202">
+      <c r="X111" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -14146,14 +14823,21 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z111" s="157"/>
-      <c r="AA111" s="185" t="s">
+      <c r="Z111" s="209">
+        <f>17*Table2[[#This Row],[DENSITY]]</f>
+        <v>133450</v>
+      </c>
+      <c r="AA111" s="177" t="s">
         <v>493</v>
       </c>
       <c r="AB111" s="21"/>
+      <c r="AC111" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="112" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A112" s="174" t="s">
+      <c r="A112" s="166" t="s">
         <v>445</v>
       </c>
       <c r="B112" s="98">
@@ -14220,7 +14904,7 @@
         <f ca="1">IF(OR($D112="Ecoinvent",$D112="Betonsortenrechner",$D112="KBOB",$T112&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X112" s="202">
+      <c r="X112" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -14233,14 +14917,21 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z112" s="157"/>
-      <c r="AA112" s="185" t="s">
+      <c r="Z112" s="209">
+        <f>17*Table2[[#This Row],[DENSITY]]</f>
+        <v>133450</v>
+      </c>
+      <c r="AA112" s="177" t="s">
         <v>493</v>
       </c>
       <c r="AB112" s="21"/>
+      <c r="AC112" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
-    <row r="113" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A113" s="174" t="s">
+    <row r="113" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A113" s="166" t="s">
         <v>448</v>
       </c>
       <c r="B113" s="98">
@@ -14307,7 +14998,7 @@
         <f ca="1">IF(OR($D113="Ecoinvent",$D113="Betonsortenrechner",$D113="KBOB",$T113&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X113" s="202">
+      <c r="X113" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
@@ -14320,14 +15011,21 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z113" s="157"/>
-      <c r="AA113" s="185" t="s">
+      <c r="Z113" s="209">
+        <f>17*Table2[[#This Row],[DENSITY]]</f>
+        <v>133450</v>
+      </c>
+      <c r="AA113" s="177" t="s">
         <v>493</v>
       </c>
       <c r="AB113" s="21"/>
+      <c r="AC113" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
-    <row r="114" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A114" s="174" t="s">
+    <row r="114" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A114" s="166" t="s">
         <v>449</v>
       </c>
       <c r="B114" s="98">
@@ -14396,7 +15094,7 @@
         <f ca="1">IF(OR($D114="Ecoinvent",$D114="Betonsortenrechner",$D114="KBOB",$T114&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X114" s="202">
+      <c r="X114" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -14409,14 +15107,21 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z114" s="157"/>
-      <c r="AA114" s="185" t="s">
+      <c r="Z114" s="209">
+        <f>17*Table2[[#This Row],[DENSITY]]</f>
+        <v>133450</v>
+      </c>
+      <c r="AA114" s="177" t="s">
         <v>493</v>
       </c>
       <c r="AB114" s="21"/>
+      <c r="AC114" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
-    <row r="115" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A115" s="174" t="s">
+    <row r="115" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A115" s="166" t="s">
         <v>450</v>
       </c>
       <c r="B115" s="98">
@@ -14484,7 +15189,7 @@
         <f ca="1">IF(OR($D115="Ecoinvent",$D115="Betonsortenrechner",$D115="KBOB",$T115&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X115" s="202">
+      <c r="X115" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -14497,14 +15202,21 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z115" s="157"/>
+      <c r="Z115" s="209">
+        <f>17*Table2[[#This Row],[DENSITY]]</f>
+        <v>133450</v>
+      </c>
       <c r="AA115" s="2" t="s">
         <v>493</v>
       </c>
       <c r="AB115" s="21"/>
+      <c r="AC115" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
-    <row r="116" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A116" s="174" t="s">
+    <row r="116" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A116" s="166" t="s">
         <v>454</v>
       </c>
       <c r="B116" s="98">
@@ -14572,7 +15284,7 @@
         <f ca="1">IF(OR($D116="Ecoinvent",$D116="Betonsortenrechner",$D116="KBOB",$T116&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X116" s="202">
+      <c r="X116" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -14585,14 +15297,21 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z116" s="157"/>
+      <c r="Z116" s="209">
+        <f>17*Table2[[#This Row],[DENSITY]]</f>
+        <v>133450</v>
+      </c>
       <c r="AA116" s="2" t="s">
         <v>493</v>
       </c>
       <c r="AB116" s="21"/>
+      <c r="AC116" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
-    <row r="117" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A117" s="174" t="s">
+    <row r="117" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A117" s="166" t="s">
         <v>455</v>
       </c>
       <c r="B117" s="98">
@@ -14660,7 +15379,7 @@
         <f ca="1">IF(OR($D117="Ecoinvent",$D117="Betonsortenrechner",$D117="KBOB",$T117&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X117" s="202">
+      <c r="X117" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -14673,14 +15392,21 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z117" s="157"/>
+      <c r="Z117" s="209">
+        <f>17*Table2[[#This Row],[DENSITY]]</f>
+        <v>133450</v>
+      </c>
       <c r="AA117" s="2" t="s">
         <v>494</v>
       </c>
       <c r="AB117" s="21"/>
+      <c r="AC117" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
-    <row r="118" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A118" s="174" t="s">
+    <row r="118" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A118" s="166" t="s">
         <v>456</v>
       </c>
       <c r="B118" s="98">
@@ -14744,10 +15470,10 @@
         <f>1.1+9.68+26.7</f>
         <v>37.479999999999997</v>
       </c>
-      <c r="W118" s="166">
-        <v>0</v>
-      </c>
-      <c r="X118" s="202">
+      <c r="W118" s="158">
+        <v>0</v>
+      </c>
+      <c r="X118" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -14760,14 +15486,21 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z118" s="157"/>
-      <c r="AA118" s="210" t="s">
+      <c r="Z118" s="209">
+        <f>17*Table2[[#This Row],[DENSITY]]</f>
+        <v>133450</v>
+      </c>
+      <c r="AA118" s="201" t="s">
         <v>511</v>
       </c>
       <c r="AB118" s="21"/>
+      <c r="AC118" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
-    <row r="119" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A119" s="174" t="s">
+    <row r="119" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A119" s="166" t="s">
         <v>457</v>
       </c>
       <c r="B119" s="98">
@@ -14835,7 +15568,7 @@
         <f ca="1">IF(OR($D119="Ecoinvent",$D119="Betonsortenrechner",$D119="KBOB",$T119&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X119" s="202">
+      <c r="X119" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
@@ -14848,14 +15581,21 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z119" s="157"/>
+      <c r="Z119" s="209">
+        <f>17*Table2[[#This Row],[DENSITY]]</f>
+        <v>133450</v>
+      </c>
       <c r="AA119" s="2" t="s">
         <v>493</v>
       </c>
       <c r="AB119" s="21"/>
+      <c r="AC119" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
-    <row r="120" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A120" s="174" t="s">
+    <row r="120" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A120" s="166" t="s">
         <v>474</v>
       </c>
       <c r="B120" s="98">
@@ -14923,7 +15663,7 @@
         <f ca="1">IF(OR($D120="Ecoinvent",$D120="Betonsortenrechner",$D120="KBOB",$T120&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X120" s="202">
+      <c r="X120" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -14936,14 +15676,21 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z120" s="157"/>
+      <c r="Z120" s="209">
+        <f>17*Table2[[#This Row],[DENSITY]]</f>
+        <v>133450</v>
+      </c>
       <c r="AA120" s="2" t="s">
         <v>493</v>
       </c>
       <c r="AB120" s="21"/>
+      <c r="AC120" s="211">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
     </row>
-    <row r="121" spans="1:28" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="176" t="s">
+    <row r="121" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="168" t="s">
         <v>477</v>
       </c>
       <c r="B121" s="99">
@@ -15012,11 +15759,11 @@
         <f ca="1">IF(OR($D121="Ecoinvent",$D121="Betonsortenrechner",$D121="KBOB",$T121&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X121" s="209">
+      <c r="X121" s="200">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
-      <c r="Y121" s="173" cm="1">
+      <c r="Y121" s="165" cm="1">
         <f t="array" aca="1" ref="Y121" ca="1">IF($W121&lt;&gt;0,
 IF(AND(
                          T121&gt;=_xlfn.PERCENTILE.INC(_xlfn._xlws.FILTER($T$2:$T$148, ($L$2:$L$148=L121)*($W$2:$W$148=1)),0.1),
@@ -15025,13 +15772,20 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z121" s="160"/>
+      <c r="Z121" s="209">
+        <f>17*Table2[[#This Row],[DENSITY]]</f>
+        <v>133450</v>
+      </c>
       <c r="AA121" s="4" t="s">
         <v>493</v>
       </c>
       <c r="AB121" s="37"/>
+      <c r="AC121" s="211">
+        <f t="shared" ref="AC121" si="2">1.2</f>
+        <v>1.2</v>
+      </c>
     </row>
-    <row r="122" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A122" s="8" t="s">
         <v>181</v>
       </c>
@@ -15090,7 +15844,7 @@
         <f ca="1">IF(OR($D122="Ecoinvent",$D122="Betonsortenrechner",$D122="KBOB",$T122&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X122" s="202">
+      <c r="X122" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -15103,13 +15857,20 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z122" s="157"/>
+      <c r="Z122" s="210">
+        <f>10*7850</f>
+        <v>78500</v>
+      </c>
       <c r="AA122" s="2" t="s">
         <v>171</v>
       </c>
       <c r="AB122" s="21"/>
+      <c r="AC122" s="211">
+        <f>7850*0.02</f>
+        <v>157</v>
+      </c>
     </row>
-    <row r="123" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A123" s="8" t="s">
         <v>182</v>
       </c>
@@ -15168,7 +15929,7 @@
         <f ca="1">IF(OR($D123="Ecoinvent",$D123="Betonsortenrechner",$D123="KBOB",$T123&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X123" s="202">
+      <c r="X123" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -15181,11 +15942,18 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z123" s="157"/>
+      <c r="Z123" s="210">
+        <f t="shared" ref="Z123:Z130" si="3">10*7850</f>
+        <v>78500</v>
+      </c>
       <c r="AA123" s="2"/>
       <c r="AB123" s="21"/>
+      <c r="AC123" s="211">
+        <f t="shared" ref="AC123:AC130" si="4">7850*0.02</f>
+        <v>157</v>
+      </c>
     </row>
-    <row r="124" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A124" s="8" t="s">
         <v>183</v>
       </c>
@@ -15244,7 +16012,7 @@
         <f ca="1">IF(OR($D124="Ecoinvent",$D124="Betonsortenrechner",$D124="KBOB",$T124&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X124" s="202">
+      <c r="X124" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
@@ -15257,13 +16025,20 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z124" s="157"/>
+      <c r="Z124" s="210">
+        <f t="shared" si="3"/>
+        <v>78500</v>
+      </c>
       <c r="AA124" s="2" t="s">
         <v>170</v>
       </c>
       <c r="AB124" s="21"/>
+      <c r="AC124" s="211">
+        <f t="shared" si="4"/>
+        <v>157</v>
+      </c>
     </row>
-    <row r="125" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A125" s="8" t="s">
         <v>184</v>
       </c>
@@ -15323,7 +16098,7 @@
         <f ca="1">IF(OR($D125="Ecoinvent",$D125="Betonsortenrechner",$D125="KBOB",$T125&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X125" s="202">
+      <c r="X125" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -15336,13 +16111,20 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z125" s="157"/>
+      <c r="Z125" s="210">
+        <f t="shared" si="3"/>
+        <v>78500</v>
+      </c>
       <c r="AA125" s="2" t="s">
         <v>170</v>
       </c>
       <c r="AB125" s="21"/>
+      <c r="AC125" s="211">
+        <f t="shared" si="4"/>
+        <v>157</v>
+      </c>
     </row>
-    <row r="126" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A126" s="8" t="s">
         <v>185</v>
       </c>
@@ -15402,7 +16184,7 @@
         <f ca="1">IF(OR($D126="Ecoinvent",$D126="Betonsortenrechner",$D126="KBOB",$T126&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X126" s="202">
+      <c r="X126" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
@@ -15415,11 +16197,18 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z126" s="157"/>
+      <c r="Z126" s="210">
+        <f t="shared" si="3"/>
+        <v>78500</v>
+      </c>
       <c r="AA126" s="2"/>
       <c r="AB126" s="21"/>
+      <c r="AC126" s="211">
+        <f t="shared" si="4"/>
+        <v>157</v>
+      </c>
     </row>
-    <row r="127" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A127" s="8" t="s">
         <v>186</v>
       </c>
@@ -15479,7 +16268,7 @@
         <f ca="1">IF(OR($D127="Ecoinvent",$D127="Betonsortenrechner",$D127="KBOB",$T127&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X127" s="202">
+      <c r="X127" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
@@ -15492,11 +16281,18 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z127" s="157"/>
+      <c r="Z127" s="210">
+        <f t="shared" si="3"/>
+        <v>78500</v>
+      </c>
       <c r="AA127" s="2"/>
       <c r="AB127" s="21"/>
+      <c r="AC127" s="211">
+        <f t="shared" si="4"/>
+        <v>157</v>
+      </c>
     </row>
-    <row r="128" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A128" s="8" t="s">
         <v>187</v>
       </c>
@@ -15553,7 +16349,7 @@
         <f ca="1">IF(OR($D128="Ecoinvent",$D128="Betonsortenrechner",$D128="KBOB",$T128&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X128" s="202">
+      <c r="X128" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
@@ -15566,11 +16362,18 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z128" s="157"/>
+      <c r="Z128" s="210">
+        <f t="shared" si="3"/>
+        <v>78500</v>
+      </c>
       <c r="AA128" s="2"/>
       <c r="AB128" s="21"/>
+      <c r="AC128" s="211">
+        <f t="shared" si="4"/>
+        <v>157</v>
+      </c>
     </row>
-    <row r="129" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A129" s="8" t="s">
         <v>188</v>
       </c>
@@ -15629,7 +16432,7 @@
         <f ca="1">IF(OR($D129="Ecoinvent",$D129="Betonsortenrechner",$D129="KBOB",$T129&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X129" s="202">
+      <c r="X129" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -15642,11 +16445,18 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z129" s="157"/>
+      <c r="Z129" s="210">
+        <f t="shared" si="3"/>
+        <v>78500</v>
+      </c>
       <c r="AA129" s="2"/>
       <c r="AB129" s="21"/>
+      <c r="AC129" s="211">
+        <f t="shared" si="4"/>
+        <v>157</v>
+      </c>
     </row>
-    <row r="130" spans="1:28" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A130" s="9" t="s">
         <v>189</v>
       </c>
@@ -15705,7 +16515,7 @@
         <f ca="1">IF(OR($D130="Ecoinvent",$D130="Betonsortenrechner",$D130="KBOB",$T130&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
-      <c r="X130" s="209">
+      <c r="X130" s="200">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>1</v>
       </c>
@@ -15718,11 +16528,18 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z130" s="160"/>
+      <c r="Z130" s="210">
+        <f t="shared" si="3"/>
+        <v>78500</v>
+      </c>
       <c r="AA130" s="4"/>
       <c r="AB130" s="21"/>
+      <c r="AC130" s="211">
+        <f t="shared" si="4"/>
+        <v>157</v>
+      </c>
     </row>
-    <row r="131" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A131" s="8" t="s">
         <v>190</v>
       </c>
@@ -15779,7 +16596,7 @@
         <f ca="1">IF(OR($D131="Ecoinvent",$D131="Betonsortenrechner",$D131="KBOB",$T131&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X131" s="202">
+      <c r="X131" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
@@ -15792,13 +16609,14 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z131" s="157"/>
+      <c r="Z131" s="210"/>
       <c r="AA131" s="2" t="s">
         <v>193</v>
       </c>
       <c r="AB131" s="21"/>
+      <c r="AC131" s="211"/>
     </row>
-    <row r="132" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A132" s="8" t="s">
         <v>191</v>
       </c>
@@ -15855,7 +16673,7 @@
         <f ca="1">IF(OR($D132="Ecoinvent",$D132="Betonsortenrechner",$D132="KBOB",$T132&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X132" s="202">
+      <c r="X132" s="193">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
@@ -15868,13 +16686,14 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z132" s="157"/>
+      <c r="Z132" s="210"/>
       <c r="AA132" s="2" t="s">
         <v>194</v>
       </c>
       <c r="AB132" s="21"/>
+      <c r="AC132" s="211"/>
     </row>
-    <row r="133" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:29" x14ac:dyDescent="0.2">
       <c r="E133" s="91"/>
     </row>
     <row r="1048460" spans="29:29" x14ac:dyDescent="0.2">
@@ -15902,22 +16721,22 @@
       <c r="AC1048467" s="21"/>
     </row>
     <row r="1048468" spans="29:29" x14ac:dyDescent="0.2">
-      <c r="AC1048468" s="165"/>
+      <c r="AC1048468" s="157"/>
     </row>
     <row r="1048469" spans="29:29" x14ac:dyDescent="0.2">
-      <c r="AC1048469" s="165"/>
+      <c r="AC1048469" s="157"/>
     </row>
     <row r="1048470" spans="29:29" x14ac:dyDescent="0.2">
-      <c r="AC1048470" s="165"/>
+      <c r="AC1048470" s="157"/>
     </row>
     <row r="1048471" spans="29:29" x14ac:dyDescent="0.2">
-      <c r="AC1048471" s="165"/>
+      <c r="AC1048471" s="157"/>
     </row>
     <row r="1048472" spans="29:29" x14ac:dyDescent="0.2">
-      <c r="AC1048472" s="165"/>
+      <c r="AC1048472" s="157"/>
     </row>
     <row r="1048473" spans="29:29" x14ac:dyDescent="0.2">
-      <c r="AC1048473" s="165"/>
+      <c r="AC1048473" s="157"/>
     </row>
     <row r="1048474" spans="29:29" x14ac:dyDescent="0.2">
       <c r="AC1048474" s="21"/>
@@ -15925,12 +16744,12 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="Y1:Y121">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y122:Y1048576">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16016,7 +16835,7 @@
         <v>25000</v>
       </c>
       <c r="I2" s="56"/>
-      <c r="J2" s="212">
+      <c r="J2" s="203">
         <v>2.5</v>
       </c>
     </row>
@@ -16189,17 +17008,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA60A30-8D92-49EC-964A-A8F2973B4787}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="33.33203125" customWidth="1"/>
     <col min="3" max="3" width="19.6640625" customWidth="1"/>
     <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="5" max="5" width="28.6640625" customWidth="1"/>
+    <col min="6" max="6" width="21.5" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
+    <col min="8" max="8" width="17.33203125" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -16221,8 +17043,14 @@
       <c r="G1" s="1" t="s">
         <v>399</v>
       </c>
+      <c r="H1" s="204" t="s">
+        <v>521</v>
+      </c>
+      <c r="I1" s="204" t="s">
+        <v>522</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="52"/>
       <c r="B2" s="52" t="s">
         <v>400</v>
@@ -16244,8 +17072,14 @@
         <f>7.8/C2/(E2)</f>
         <v>1.278688524590164</v>
       </c>
+      <c r="H2">
+        <v>9626</v>
+      </c>
+      <c r="I2">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="56"/>
       <c r="B3" s="56" t="s">
         <v>401</v>
@@ -16265,8 +17099,14 @@
       <c r="G3" s="59">
         <v>0.12</v>
       </c>
+      <c r="H3">
+        <v>391</v>
+      </c>
+      <c r="I3">
+        <v>0.55000000000000004</v>
+      </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="52"/>
       <c r="B4" s="52" t="s">
         <v>402</v>
@@ -16287,8 +17127,14 @@
         <f>1.1</f>
         <v>1.1000000000000001</v>
       </c>
+      <c r="H4">
+        <v>335</v>
+      </c>
+      <c r="I4">
+        <v>0.2</v>
+      </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="56"/>
       <c r="B5" s="56" t="s">
         <v>403</v>
@@ -16308,8 +17154,14 @@
       <c r="G5" s="56">
         <v>1.7999999999999999E-2</v>
       </c>
+      <c r="H5" s="205">
+        <v>253</v>
+      </c>
+      <c r="I5" s="205">
+        <v>0.2</v>
+      </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>404</v>
       </c>
@@ -16328,8 +17180,14 @@
       <c r="G6">
         <v>0.81599999999999995</v>
       </c>
+      <c r="H6" s="205">
+        <v>335</v>
+      </c>
+      <c r="I6" s="205">
+        <v>0.2</v>
+      </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>405</v>
       </c>
@@ -16347,10 +17205,17 @@
       </c>
       <c r="G7">
         <v>0.55200000000000005</v>
+      </c>
+      <c r="H7" s="205">
+        <v>335</v>
+      </c>
+      <c r="I7" s="205">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -16449,16 +17314,16 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C14" s="211"/>
+      <c r="C14" s="202"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C15" s="211"/>
+      <c r="C15" s="202"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C16" s="211"/>
+      <c r="C16" s="202"/>
     </row>
     <row r="17" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C17" s="211"/>
+      <c r="C17" s="202"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Database/260126_Datenbankdefinition.xlsx
+++ b/Database/260126_Datenbankdefinition.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonathanbieg/Documents/Master Thesis/1_Code/Python Repository/SDSD_Bieg/Database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{420F4989-3711-8C49-AE0E-7F2378E46135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE5C075-267A-B846-9C98-652A93E0D557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-4800" yWindow="-19400" windowWidth="19540" windowHeight="16700" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
   </bookViews>

--- a/Database/260126_Datenbankdefinition.xlsx
+++ b/Database/260126_Datenbankdefinition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonathanbieg/Documents/Master Thesis/1_Code/Python Repository/SDSD_Bieg/Database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE5C075-267A-B846-9C98-652A93E0D557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4C1A30B-1D3E-D941-812A-1EB5684C6013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4800" yWindow="-19400" windowWidth="19540" windowHeight="16700" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
+    <workbookView xWindow="-3400" yWindow="-20280" windowWidth="32160" windowHeight="19140" activeTab="3" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
   </bookViews>
   <sheets>
     <sheet name="products" sheetId="1" r:id="rId1"/>
@@ -93,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1894" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1896" uniqueCount="524">
   <si>
     <t>B500B</t>
   </si>
@@ -2234,7 +2234,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="212">
+  <cellXfs count="214">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2691,8 +2691,7 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2701,70 +2700,47 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Standard 2" xfId="1" xr:uid="{FDCFE4BD-E849-456C-8E2E-B78D9BD993F6}"/>
   </cellStyles>
-  <dxfs count="57">
+  <dxfs count="59">
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="9"/>
+        <sz val="11"/>
         <color theme="1"/>
-        <name val="Aptos"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill patternType="none">
           <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor auto="1"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Aptos"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Aptos"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -2778,24 +2754,27 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="9"/>
+        <sz val="11"/>
         <color theme="1"/>
-        <name val="Aptos"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -2817,6 +2796,216 @@
       <fill>
         <patternFill patternType="none">
           <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3235,6 +3424,97 @@
           <bgColor theme="4"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -3784,216 +4064,6 @@
       </font>
       <alignment vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -4064,42 +4134,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}" name="Table2" displayName="Table2" ref="A1:AC132" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}" name="Table2" displayName="Table2" ref="A1:AC132" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57">
   <autoFilter ref="A1:AC132" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}"/>
   <tableColumns count="29">
-    <tableColumn id="9" xr3:uid="{1DBBD25D-72F9-4A81-9CFA-500505E3628D}" name="ID" dataDxfId="45"/>
-    <tableColumn id="14" xr3:uid="{6844A52F-C967-44C0-BF5C-160C47AB6E64}" name="PRO_ID" dataDxfId="44"/>
-    <tableColumn id="12" xr3:uid="{4EDF1E73-4744-474F-8DFE-7F72FB05613C}" name="EPD_ID" dataDxfId="43"/>
-    <tableColumn id="1" xr3:uid="{1CF2E22E-1020-4F35-B31F-6350A15A5DE8}" name="SOURCE" dataDxfId="42"/>
-    <tableColumn id="27" xr3:uid="{07F74D5D-9130-4120-B02C-A11234427F46}" name="KBOB ID-Nr." dataDxfId="41"/>
-    <tableColumn id="11" xr3:uid="{81FE7F31-5F54-40F9-B99E-827E048F7DB5}" name="EPD_DATE" dataDxfId="40"/>
-    <tableColumn id="10" xr3:uid="{54D8BA04-0FEF-4C3B-9B14-59E8F982CD3F}" name="VALID_TO" dataDxfId="39"/>
-    <tableColumn id="22" xr3:uid="{3D6FC370-B8A8-40C3-9FC8-791B178DDFDF}" name="COUNTRY" dataDxfId="38"/>
-    <tableColumn id="4" xr3:uid="{25C7280F-4E3E-4E39-BDBB-DC06DF090C5B}" name="PRODUCT_NAME" dataDxfId="37"/>
-    <tableColumn id="26" xr3:uid="{1053A7DD-B11F-4E75-92EC-BC0F866E90B4}" name="OEKOBAUDAT_ID" dataDxfId="36"/>
-    <tableColumn id="25" xr3:uid="{295F99F8-E318-45C9-833E-F0B45A26471A}" name="MATERIAL_GROUP" dataDxfId="35"/>
-    <tableColumn id="2" xr3:uid="{1326FCEF-D1EE-4F3A-BB8B-77CB4EC72B0C}" name="MATERIAL" dataDxfId="34"/>
-    <tableColumn id="5" xr3:uid="{9B2A7F84-D968-4A00-B61F-23BB0661E7A3}" name="CEMENT" dataDxfId="33"/>
-    <tableColumn id="6" xr3:uid="{2F6E5831-6238-4360-9CFD-ED23A193E761}" name="MECH_PROP" dataDxfId="32"/>
-    <tableColumn id="13" xr3:uid="{50DAB01C-8AF5-4E0C-9904-54F70B81BC55}" name="DENSITY" dataDxfId="31"/>
-    <tableColumn id="18" xr3:uid="{F799A4D4-9543-475F-989E-CFBA47249558}" name="EXPOSITIONSKLASSE" dataDxfId="30"/>
-    <tableColumn id="17" xr3:uid="{ECCBC067-991C-4C60-942D-806BCD77B990}" name="GROESSTKORN" dataDxfId="29"/>
-    <tableColumn id="16" xr3:uid="{05157B85-D5FB-4844-9B53-D8AB09BCE0D9}" name="CHLORIDGEHALT" dataDxfId="28"/>
-    <tableColumn id="15" xr3:uid="{9F53CF50-7148-405A-9295-1F0C3C45645A}" name="KONSISTENZKLASSE" dataDxfId="27"/>
-    <tableColumn id="7" xr3:uid="{E23232F6-E86E-4AD2-8257-F30C0D1F7368}" name="Total_GWP" dataDxfId="26"/>
-    <tableColumn id="20" xr3:uid="{0A9001B4-3AB4-4C58-B125-0B2AA4DB2681}" name="A1toA3_GWP" dataDxfId="25">
+    <tableColumn id="9" xr3:uid="{1DBBD25D-72F9-4A81-9CFA-500505E3628D}" name="ID" dataDxfId="56"/>
+    <tableColumn id="14" xr3:uid="{6844A52F-C967-44C0-BF5C-160C47AB6E64}" name="PRO_ID" dataDxfId="55"/>
+    <tableColumn id="12" xr3:uid="{4EDF1E73-4744-474F-8DFE-7F72FB05613C}" name="EPD_ID" dataDxfId="54"/>
+    <tableColumn id="1" xr3:uid="{1CF2E22E-1020-4F35-B31F-6350A15A5DE8}" name="SOURCE" dataDxfId="53"/>
+    <tableColumn id="27" xr3:uid="{07F74D5D-9130-4120-B02C-A11234427F46}" name="KBOB ID-Nr." dataDxfId="52"/>
+    <tableColumn id="11" xr3:uid="{81FE7F31-5F54-40F9-B99E-827E048F7DB5}" name="EPD_DATE" dataDxfId="51"/>
+    <tableColumn id="10" xr3:uid="{54D8BA04-0FEF-4C3B-9B14-59E8F982CD3F}" name="VALID_TO" dataDxfId="50"/>
+    <tableColumn id="22" xr3:uid="{3D6FC370-B8A8-40C3-9FC8-791B178DDFDF}" name="COUNTRY" dataDxfId="49"/>
+    <tableColumn id="4" xr3:uid="{25C7280F-4E3E-4E39-BDBB-DC06DF090C5B}" name="PRODUCT_NAME" dataDxfId="48"/>
+    <tableColumn id="26" xr3:uid="{1053A7DD-B11F-4E75-92EC-BC0F866E90B4}" name="OEKOBAUDAT_ID" dataDxfId="47"/>
+    <tableColumn id="25" xr3:uid="{295F99F8-E318-45C9-833E-F0B45A26471A}" name="MATERIAL_GROUP" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{1326FCEF-D1EE-4F3A-BB8B-77CB4EC72B0C}" name="MATERIAL" dataDxfId="45"/>
+    <tableColumn id="5" xr3:uid="{9B2A7F84-D968-4A00-B61F-23BB0661E7A3}" name="CEMENT" dataDxfId="44"/>
+    <tableColumn id="6" xr3:uid="{2F6E5831-6238-4360-9CFD-ED23A193E761}" name="MECH_PROP" dataDxfId="43"/>
+    <tableColumn id="13" xr3:uid="{50DAB01C-8AF5-4E0C-9904-54F70B81BC55}" name="DENSITY" dataDxfId="42"/>
+    <tableColumn id="18" xr3:uid="{F799A4D4-9543-475F-989E-CFBA47249558}" name="EXPOSITIONSKLASSE" dataDxfId="41"/>
+    <tableColumn id="17" xr3:uid="{ECCBC067-991C-4C60-942D-806BCD77B990}" name="GROESSTKORN" dataDxfId="40"/>
+    <tableColumn id="16" xr3:uid="{05157B85-D5FB-4844-9B53-D8AB09BCE0D9}" name="CHLORIDGEHALT" dataDxfId="39"/>
+    <tableColumn id="15" xr3:uid="{9F53CF50-7148-405A-9295-1F0C3C45645A}" name="KONSISTENZKLASSE" dataDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{E23232F6-E86E-4AD2-8257-F30C0D1F7368}" name="Total_GWP" dataDxfId="37"/>
+    <tableColumn id="20" xr3:uid="{0A9001B4-3AB4-4C58-B125-0B2AA4DB2681}" name="A1toA3_GWP" dataDxfId="36">
       <calculatedColumnFormula>119+10.9+238</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{2799394A-C481-45CE-B194-AAABAB0AED38}" name="C1toC4_GWP" dataDxfId="24">
+    <tableColumn id="21" xr3:uid="{2799394A-C481-45CE-B194-AAABAB0AED38}" name="C1toC4_GWP" dataDxfId="35">
       <calculatedColumnFormula>51.1+26+2.64+12.6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{70561D70-9D02-4E93-A395-229DA8696DDA}" name="ValidEPD" dataDxfId="23">
+    <tableColumn id="19" xr3:uid="{70561D70-9D02-4E93-A395-229DA8696DDA}" name="ValidEPD" dataDxfId="34">
       <calculatedColumnFormula>IF(OR($D2="Ecoinvent",$D2="Betonsortenrechner",$D2="KBOB",$T2&lt;=0),0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{92D55BC7-F55B-406A-B127-69EC2F0A8B77}" name="noch gültig" dataDxfId="22">
+    <tableColumn id="29" xr3:uid="{92D55BC7-F55B-406A-B127-69EC2F0A8B77}" name="noch gültig" dataDxfId="33">
       <calculatedColumnFormula>IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{DB90AC0A-8933-4040-BADE-E6EE11AC8BD7}" name="Statistik" dataDxfId="4">
+    <tableColumn id="3" xr3:uid="{DB90AC0A-8933-4040-BADE-E6EE11AC8BD7}" name="Statistik" dataDxfId="32">
       <calculatedColumnFormula array="1">IF($W2&lt;&gt;0,
 IF(AND(
                          T2&gt;=_xlfn.PERCENTILE.INC(_xlfn._xlws.FILTER($T$2:$T$148, ($L$2:$L$148=L2)*($W$2:$W$148=1)),0.1),
@@ -4107,42 +4177,44 @@
                ),1,0),
 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{BBA6C134-63F9-4711-8B25-086098EC2CB0}" name="Cost" dataDxfId="2"/>
-    <tableColumn id="24" xr3:uid="{5321A0E1-043C-4E95-A6DA-41830364B2BC}" name="Anmerkung" dataDxfId="3"/>
-    <tableColumn id="23" xr3:uid="{61456234-34E8-4222-B2D6-9DDA8E83B081}" name="Spalte 1" dataDxfId="1"/>
-    <tableColumn id="28" xr3:uid="{D1FC9AF8-A0AE-CE49-8F27-4BB569415BF3}" name="T_construction" dataDxfId="0"/>
+    <tableColumn id="8" xr3:uid="{BBA6C134-63F9-4711-8B25-086098EC2CB0}" name="Cost" dataDxfId="31"/>
+    <tableColumn id="24" xr3:uid="{5321A0E1-043C-4E95-A6DA-41830364B2BC}" name="Anmerkung" dataDxfId="30"/>
+    <tableColumn id="23" xr3:uid="{61456234-34E8-4222-B2D6-9DDA8E83B081}" name="Spalte 1" dataDxfId="29"/>
+    <tableColumn id="28" xr3:uid="{D1FC9AF8-A0AE-CE49-8F27-4BB569415BF3}" name="T_construction" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}" name="Tabelle4" displayName="Tabelle4" ref="A1:J8" totalsRowShown="0" headerRowDxfId="21" dataDxfId="19" headerRowBorderDxfId="20" tableBorderDxfId="18" totalsRowBorderDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}" name="Tabelle4" displayName="Tabelle4" ref="A1:J8" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
   <autoFilter ref="A1:J8" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{AF3C694B-2C8A-40EE-B8BB-2EC9EB81A87A}" name="mat_ID" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{B447FBC2-C455-4332-8F47-150B112A57E0}" name="name" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{BAFC6B47-7268-46CC-A881-892C9A1F4334}" name="strength_comp" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{6FC4C8EB-7581-4E67-81CE-C724161F0838}" name="strength_tens" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{A875970E-61A9-43B5-9361-7616A74C3147}" name="strength_bend" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{EF5B3A69-DD70-420A-88FF-4FE8772A2E14}" name="strength_shea" dataDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{ED461A80-736C-42BD-81BC-C5C0C80FF34C}" name="E_modulus" dataDxfId="10"/>
-    <tableColumn id="8" xr3:uid="{68E47481-7028-4427-B126-2A046FC46737}" name="density_load" dataDxfId="9"/>
-    <tableColumn id="9" xr3:uid="{7AB34570-2BD4-417F-B141-70612577C7D6}" name="burn_rate" dataDxfId="8"/>
-    <tableColumn id="10" xr3:uid="{69298654-E280-9D4B-9717-7904FADC15B5}" name="phi" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{AF3C694B-2C8A-40EE-B8BB-2EC9EB81A87A}" name="mat_ID" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{B447FBC2-C455-4332-8F47-150B112A57E0}" name="name" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{BAFC6B47-7268-46CC-A881-892C9A1F4334}" name="strength_comp" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{6FC4C8EB-7581-4E67-81CE-C724161F0838}" name="strength_tens" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{A875970E-61A9-43B5-9361-7616A74C3147}" name="strength_bend" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{EF5B3A69-DD70-420A-88FF-4FE8772A2E14}" name="strength_shea" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{ED461A80-736C-42BD-81BC-C5C0C80FF34C}" name="E_modulus" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{68E47481-7028-4427-B126-2A046FC46737}" name="density_load" dataDxfId="15"/>
+    <tableColumn id="9" xr3:uid="{7AB34570-2BD4-417F-B141-70612577C7D6}" name="burn_rate" dataDxfId="14"/>
+    <tableColumn id="10" xr3:uid="{69298654-E280-9D4B-9717-7904FADC15B5}" name="phi" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1CD264FD-E2C0-E94F-B387-736226CC982D}" name="Tabelle42" displayName="Tabelle42" ref="A1:D6" totalsRowShown="0" headerRowDxfId="56" dataDxfId="54" headerRowBorderDxfId="55" tableBorderDxfId="53" totalsRowBorderDxfId="52">
-  <autoFilter ref="A1:D6" xr:uid="{1CD264FD-E2C0-E94F-B387-736226CC982D}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{6590463D-C242-4C4D-AA1F-6FA1F0D35E6F}" name="mat_ID" dataDxfId="51"/>
-    <tableColumn id="2" xr3:uid="{603BAED4-55F2-D040-9D73-1611C1564A84}" name="name" dataDxfId="50"/>
-    <tableColumn id="3" xr3:uid="{D6CC67C0-1ACA-D446-A6F3-00BCC3AC8DAC}" name="d" dataDxfId="49"/>
-    <tableColumn id="4" xr3:uid="{3D62C7FF-3D7F-B245-A874-3A95DF0C49D2}" name="K_ser" dataDxfId="48"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1CD264FD-E2C0-E94F-B387-736226CC982D}" name="Tabelle42" displayName="Tabelle42" ref="A1:F6" totalsRowShown="0" headerRowDxfId="12" dataDxfId="10" headerRowBorderDxfId="11" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A1:F6" xr:uid="{1CD264FD-E2C0-E94F-B387-736226CC982D}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{6590463D-C242-4C4D-AA1F-6FA1F0D35E6F}" name="mat_ID" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{603BAED4-55F2-D040-9D73-1611C1564A84}" name="name" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{D6CC67C0-1ACA-D446-A6F3-00BCC3AC8DAC}" name="d" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{3D62C7FF-3D7F-B245-A874-3A95DF0C49D2}" name="K_ser" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{0C35052C-7630-EC48-BB52-4928EDE8D2AC}" name="Cost" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{5101DCF1-1E94-3949-9F50-D0C3653EA4AB}" name="T_construction" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4559,7 +4631,7 @@
       <c r="AB1" s="178" t="s">
         <v>497</v>
       </c>
-      <c r="AC1" s="206" t="s">
+      <c r="AC1" s="205" t="s">
         <v>523</v>
       </c>
     </row>
@@ -4645,12 +4717,12 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z2" s="207">
+      <c r="Z2" s="206">
         <v>206</v>
       </c>
       <c r="AA2" s="11"/>
       <c r="AB2" s="21"/>
-      <c r="AC2" s="211">
+      <c r="AC2" s="210">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -4736,12 +4808,12 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z3" s="207">
+      <c r="Z3" s="206">
         <v>206</v>
       </c>
       <c r="AA3" s="11"/>
       <c r="AB3" s="21"/>
-      <c r="AC3" s="211">
+      <c r="AC3" s="210">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -4827,12 +4899,12 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z4" s="207">
+      <c r="Z4" s="206">
         <v>206</v>
       </c>
       <c r="AA4" s="11"/>
       <c r="AB4" s="21"/>
-      <c r="AC4" s="211">
+      <c r="AC4" s="210">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -4918,12 +4990,12 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z5" s="207">
+      <c r="Z5" s="206">
         <v>206</v>
       </c>
       <c r="AA5" s="11"/>
       <c r="AB5" s="21"/>
-      <c r="AC5" s="211">
+      <c r="AC5" s="210">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -5009,12 +5081,12 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z6" s="207">
+      <c r="Z6" s="206">
         <v>206</v>
       </c>
       <c r="AA6" s="11"/>
       <c r="AB6" s="21"/>
-      <c r="AC6" s="211">
+      <c r="AC6" s="210">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -5090,12 +5162,12 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z7" s="207">
+      <c r="Z7" s="206">
         <v>206</v>
       </c>
       <c r="AA7" s="11"/>
       <c r="AB7" s="21"/>
-      <c r="AC7" s="211">
+      <c r="AC7" s="210">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -5171,12 +5243,12 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z8" s="207">
+      <c r="Z8" s="206">
         <v>206</v>
       </c>
       <c r="AA8" s="11"/>
       <c r="AB8" s="21"/>
-      <c r="AC8" s="211">
+      <c r="AC8" s="210">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -5252,12 +5324,12 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z9" s="207">
+      <c r="Z9" s="206">
         <v>206</v>
       </c>
       <c r="AA9" s="11"/>
       <c r="AB9" s="21"/>
-      <c r="AC9" s="211">
+      <c r="AC9" s="210">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -5333,12 +5405,12 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z10" s="207">
+      <c r="Z10" s="206">
         <v>206</v>
       </c>
       <c r="AA10" s="11"/>
       <c r="AB10" s="21"/>
-      <c r="AC10" s="211">
+      <c r="AC10" s="210">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -5414,12 +5486,12 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z11" s="207">
+      <c r="Z11" s="206">
         <v>206</v>
       </c>
       <c r="AA11" s="11"/>
       <c r="AB11" s="21"/>
-      <c r="AC11" s="211">
+      <c r="AC11" s="210">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -5505,12 +5577,12 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z12" s="207">
+      <c r="Z12" s="206">
         <v>206</v>
       </c>
       <c r="AA12" s="11"/>
       <c r="AB12" s="21"/>
-      <c r="AC12" s="211">
+      <c r="AC12" s="210">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -5599,12 +5671,12 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z13" s="207">
+      <c r="Z13" s="206">
         <v>206</v>
       </c>
       <c r="AA13" s="38"/>
       <c r="AB13" s="21"/>
-      <c r="AC13" s="211">
+      <c r="AC13" s="210">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -5693,12 +5765,12 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z14" s="207">
+      <c r="Z14" s="206">
         <v>206</v>
       </c>
       <c r="AA14" s="38"/>
       <c r="AB14" s="21"/>
-      <c r="AC14" s="211">
+      <c r="AC14" s="210">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -5787,12 +5859,12 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z15" s="207">
+      <c r="Z15" s="206">
         <v>206</v>
       </c>
       <c r="AA15" s="38"/>
       <c r="AB15" s="21"/>
-      <c r="AC15" s="211">
+      <c r="AC15" s="210">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -5881,12 +5953,12 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z16" s="207">
+      <c r="Z16" s="206">
         <v>206</v>
       </c>
       <c r="AA16" s="38"/>
       <c r="AB16" s="21"/>
-      <c r="AC16" s="211">
+      <c r="AC16" s="210">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -5975,12 +6047,12 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z17" s="207">
+      <c r="Z17" s="206">
         <v>206</v>
       </c>
       <c r="AA17" s="38"/>
       <c r="AB17" s="21"/>
-      <c r="AC17" s="211">
+      <c r="AC17" s="210">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -6069,12 +6141,12 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z18" s="207">
+      <c r="Z18" s="206">
         <v>206</v>
       </c>
       <c r="AA18" s="38"/>
       <c r="AB18" s="21"/>
-      <c r="AC18" s="211">
+      <c r="AC18" s="210">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -6163,12 +6235,12 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z19" s="207">
+      <c r="Z19" s="206">
         <v>206</v>
       </c>
       <c r="AA19" s="38"/>
       <c r="AB19" s="21"/>
-      <c r="AC19" s="211">
+      <c r="AC19" s="210">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -6257,12 +6329,12 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z20" s="207">
+      <c r="Z20" s="206">
         <v>206</v>
       </c>
       <c r="AA20" s="38"/>
       <c r="AB20" s="21"/>
-      <c r="AC20" s="211">
+      <c r="AC20" s="210">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -6351,12 +6423,12 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z21" s="207">
+      <c r="Z21" s="206">
         <v>206</v>
       </c>
       <c r="AA21" s="38"/>
       <c r="AB21" s="21"/>
-      <c r="AC21" s="211">
+      <c r="AC21" s="210">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -6445,12 +6517,12 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z22" s="207">
+      <c r="Z22" s="206">
         <v>206</v>
       </c>
       <c r="AA22" s="38"/>
       <c r="AB22" s="21"/>
-      <c r="AC22" s="211">
+      <c r="AC22" s="210">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -6539,12 +6611,12 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z23" s="207">
+      <c r="Z23" s="206">
         <v>206</v>
       </c>
       <c r="AA23" s="38"/>
       <c r="AB23" s="21"/>
-      <c r="AC23" s="211">
+      <c r="AC23" s="210">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -6633,12 +6705,12 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z24" s="207">
+      <c r="Z24" s="206">
         <v>206</v>
       </c>
       <c r="AA24" s="2"/>
       <c r="AB24" s="21"/>
-      <c r="AC24" s="211">
+      <c r="AC24" s="210">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -6727,12 +6799,12 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z25" s="207">
+      <c r="Z25" s="206">
         <v>206</v>
       </c>
       <c r="AA25" s="2"/>
       <c r="AB25" s="21"/>
-      <c r="AC25" s="211">
+      <c r="AC25" s="210">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -6821,12 +6893,12 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z26" s="207">
+      <c r="Z26" s="206">
         <v>206</v>
       </c>
       <c r="AA26" s="2"/>
       <c r="AB26" s="21"/>
-      <c r="AC26" s="211">
+      <c r="AC26" s="210">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -6915,12 +6987,12 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z27" s="207">
+      <c r="Z27" s="206">
         <v>206</v>
       </c>
       <c r="AA27" s="2"/>
       <c r="AB27" s="21"/>
-      <c r="AC27" s="211">
+      <c r="AC27" s="210">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -7009,12 +7081,12 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z28" s="207">
+      <c r="Z28" s="206">
         <v>206</v>
       </c>
       <c r="AA28" s="2"/>
       <c r="AB28" s="21"/>
-      <c r="AC28" s="211">
+      <c r="AC28" s="210">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -7103,12 +7175,12 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z29" s="207">
+      <c r="Z29" s="206">
         <v>206</v>
       </c>
       <c r="AA29" s="2"/>
       <c r="AB29" s="21"/>
-      <c r="AC29" s="211">
+      <c r="AC29" s="210">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -7197,12 +7269,12 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z30" s="207">
+      <c r="Z30" s="206">
         <v>206</v>
       </c>
       <c r="AA30" s="2"/>
       <c r="AB30" s="21"/>
-      <c r="AC30" s="211">
+      <c r="AC30" s="210">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -7273,12 +7345,12 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z31" s="207">
+      <c r="Z31" s="206">
         <v>206</v>
       </c>
       <c r="AA31" s="2"/>
       <c r="AB31" s="179"/>
-      <c r="AC31" s="211">
+      <c r="AC31" s="210">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -7349,12 +7421,12 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z32" s="207">
+      <c r="Z32" s="206">
         <v>206</v>
       </c>
       <c r="AA32" s="2"/>
       <c r="AB32" s="182"/>
-      <c r="AC32" s="211">
+      <c r="AC32" s="210">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -7425,12 +7497,12 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z33" s="207">
+      <c r="Z33" s="206">
         <v>206</v>
       </c>
       <c r="AA33" s="2"/>
       <c r="AB33" s="182"/>
-      <c r="AC33" s="211">
+      <c r="AC33" s="210">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -7501,12 +7573,12 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z34" s="207">
+      <c r="Z34" s="206">
         <v>206</v>
       </c>
       <c r="AA34" s="2"/>
       <c r="AB34" s="182"/>
-      <c r="AC34" s="211">
+      <c r="AC34" s="210">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -7577,12 +7649,12 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z35" s="207">
+      <c r="Z35" s="206">
         <v>206</v>
       </c>
       <c r="AA35" s="2"/>
       <c r="AB35" s="182"/>
-      <c r="AC35" s="211">
+      <c r="AC35" s="210">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -7653,12 +7725,12 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z36" s="207">
+      <c r="Z36" s="206">
         <v>206</v>
       </c>
       <c r="AA36" s="2"/>
       <c r="AB36" s="182"/>
-      <c r="AC36" s="211">
+      <c r="AC36" s="210">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -7741,12 +7813,12 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z37" s="207">
+      <c r="Z37" s="206">
         <v>206</v>
       </c>
       <c r="AA37" s="13"/>
       <c r="AB37" s="182"/>
-      <c r="AC37" s="211">
+      <c r="AC37" s="210">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -7828,13 +7900,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z38" s="208">
+      <c r="Z38" s="207">
         <f>2.01*Table2[[#This Row],[DENSITY]]</f>
         <v>15778.499999999998</v>
       </c>
       <c r="AA38" s="16"/>
       <c r="AB38" s="182"/>
-      <c r="AC38" s="211">
+      <c r="AC38" s="210">
         <f>0.009*Table2[[#This Row],[DENSITY]]</f>
         <v>70.649999999999991</v>
       </c>
@@ -7924,13 +7996,13 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z39" s="208">
+      <c r="Z39" s="207">
         <f>2.01*Table2[[#This Row],[DENSITY]]</f>
         <v>15778.499999999998</v>
       </c>
       <c r="AA39" s="2"/>
       <c r="AB39" s="183"/>
-      <c r="AC39" s="211">
+      <c r="AC39" s="210">
         <f>0.009*Table2[[#This Row],[DENSITY]]</f>
         <v>70.649999999999991</v>
       </c>
@@ -8019,13 +8091,13 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z40" s="208">
+      <c r="Z40" s="207">
         <f>2.01*Table2[[#This Row],[DENSITY]]</f>
         <v>15778.499999999998</v>
       </c>
       <c r="AA40" s="2"/>
       <c r="AB40" s="183"/>
-      <c r="AC40" s="211">
+      <c r="AC40" s="210">
         <f>0.009*Table2[[#This Row],[DENSITY]]</f>
         <v>70.649999999999991</v>
       </c>
@@ -8115,13 +8187,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z41" s="208">
+      <c r="Z41" s="207">
         <f>2.01*Table2[[#This Row],[DENSITY]]</f>
         <v>15778.499999999998</v>
       </c>
       <c r="AA41" s="2"/>
       <c r="AB41" s="183"/>
-      <c r="AC41" s="211">
+      <c r="AC41" s="210">
         <f>0.009*Table2[[#This Row],[DENSITY]]</f>
         <v>70.649999999999991</v>
       </c>
@@ -8211,13 +8283,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z42" s="208">
+      <c r="Z42" s="207">
         <f>2.01*Table2[[#This Row],[DENSITY]]</f>
         <v>15778.499999999998</v>
       </c>
       <c r="AA42" s="2"/>
       <c r="AB42" s="183"/>
-      <c r="AC42" s="211">
+      <c r="AC42" s="210">
         <f>0.009*Table2[[#This Row],[DENSITY]]</f>
         <v>70.649999999999991</v>
       </c>
@@ -8306,13 +8378,13 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z43" s="208">
+      <c r="Z43" s="207">
         <f>2.01*Table2[[#This Row],[DENSITY]]</f>
         <v>15778.499999999998</v>
       </c>
       <c r="AA43" s="2"/>
       <c r="AB43" s="183"/>
-      <c r="AC43" s="211">
+      <c r="AC43" s="210">
         <f>0.009*Table2[[#This Row],[DENSITY]]</f>
         <v>70.649999999999991</v>
       </c>
@@ -8402,13 +8474,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z44" s="208">
+      <c r="Z44" s="207">
         <f>2.01*Table2[[#This Row],[DENSITY]]</f>
         <v>15778.499999999998</v>
       </c>
       <c r="AA44" s="2"/>
       <c r="AB44" s="183"/>
-      <c r="AC44" s="211">
+      <c r="AC44" s="210">
         <f>0.009*Table2[[#This Row],[DENSITY]]</f>
         <v>70.649999999999991</v>
       </c>
@@ -8498,13 +8570,13 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z45" s="208">
+      <c r="Z45" s="207">
         <f>2.01*Table2[[#This Row],[DENSITY]]</f>
         <v>15778.499999999998</v>
       </c>
       <c r="AA45" s="2"/>
       <c r="AB45" s="183"/>
-      <c r="AC45" s="211">
+      <c r="AC45" s="210">
         <f>0.009*Table2[[#This Row],[DENSITY]]</f>
         <v>70.649999999999991</v>
       </c>
@@ -8593,13 +8665,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z46" s="208">
+      <c r="Z46" s="207">
         <f>2.01*Table2[[#This Row],[DENSITY]]</f>
         <v>15778.499999999998</v>
       </c>
       <c r="AA46" s="2"/>
       <c r="AB46" s="183"/>
-      <c r="AC46" s="211">
+      <c r="AC46" s="210">
         <f>0.009*Table2[[#This Row],[DENSITY]]</f>
         <v>70.649999999999991</v>
       </c>
@@ -8688,13 +8760,13 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z47" s="208">
+      <c r="Z47" s="207">
         <f>2.01*Table2[[#This Row],[DENSITY]]</f>
         <v>15778.499999999998</v>
       </c>
       <c r="AA47" s="2"/>
       <c r="AB47" s="183"/>
-      <c r="AC47" s="211">
+      <c r="AC47" s="210">
         <f>0.009*Table2[[#This Row],[DENSITY]]</f>
         <v>70.649999999999991</v>
       </c>
@@ -8783,13 +8855,13 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z48" s="208">
+      <c r="Z48" s="207">
         <f>2.01*Table2[[#This Row],[DENSITY]]</f>
         <v>15778.499999999998</v>
       </c>
       <c r="AA48" s="2"/>
       <c r="AB48" s="183"/>
-      <c r="AC48" s="211">
+      <c r="AC48" s="210">
         <f>0.009*Table2[[#This Row],[DENSITY]]</f>
         <v>70.649999999999991</v>
       </c>
@@ -8879,13 +8951,13 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z49" s="208">
+      <c r="Z49" s="207">
         <f>2.01*Table2[[#This Row],[DENSITY]]</f>
         <v>15778.499999999998</v>
       </c>
       <c r="AA49" s="2"/>
       <c r="AB49" s="183"/>
-      <c r="AC49" s="211">
+      <c r="AC49" s="210">
         <f>0.009*Table2[[#This Row],[DENSITY]]</f>
         <v>70.649999999999991</v>
       </c>
@@ -8975,13 +9047,13 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z50" s="208">
+      <c r="Z50" s="207">
         <f>2.01*Table2[[#This Row],[DENSITY]]</f>
         <v>15778.499999999998</v>
       </c>
       <c r="AA50" s="2"/>
       <c r="AB50" s="183"/>
-      <c r="AC50" s="211">
+      <c r="AC50" s="210">
         <f>0.009*Table2[[#This Row],[DENSITY]]</f>
         <v>70.649999999999991</v>
       </c>
@@ -9071,13 +9143,13 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z51" s="208">
+      <c r="Z51" s="207">
         <f>2.01*Table2[[#This Row],[DENSITY]]</f>
         <v>15778.499999999998</v>
       </c>
       <c r="AA51" s="2"/>
       <c r="AB51" s="183"/>
-      <c r="AC51" s="211">
+      <c r="AC51" s="210">
         <f>0.009*Table2[[#This Row],[DENSITY]]</f>
         <v>70.649999999999991</v>
       </c>
@@ -9167,13 +9239,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z52" s="208">
+      <c r="Z52" s="207">
         <f>2.01*Table2[[#This Row],[DENSITY]]</f>
         <v>15778.499999999998</v>
       </c>
       <c r="AA52" s="2"/>
       <c r="AB52" s="183"/>
-      <c r="AC52" s="211">
+      <c r="AC52" s="210">
         <f>0.009*Table2[[#This Row],[DENSITY]]</f>
         <v>70.649999999999991</v>
       </c>
@@ -9262,13 +9334,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z53" s="208">
+      <c r="Z53" s="207">
         <f>2.01*Table2[[#This Row],[DENSITY]]</f>
         <v>15778.499999999998</v>
       </c>
       <c r="AA53" s="2"/>
       <c r="AB53" s="183"/>
-      <c r="AC53" s="211">
+      <c r="AC53" s="210">
         <f>0.009*Table2[[#This Row],[DENSITY]]</f>
         <v>70.649999999999991</v>
       </c>
@@ -9357,13 +9429,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z54" s="208">
+      <c r="Z54" s="207">
         <f>2.01*Table2[[#This Row],[DENSITY]]</f>
         <v>15778.499999999998</v>
       </c>
       <c r="AA54" s="2"/>
       <c r="AB54" s="183"/>
-      <c r="AC54" s="211">
+      <c r="AC54" s="210">
         <f>0.009*Table2[[#This Row],[DENSITY]]</f>
         <v>70.649999999999991</v>
       </c>
@@ -9452,13 +9524,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z55" s="208">
+      <c r="Z55" s="207">
         <f>2.01*Table2[[#This Row],[DENSITY]]</f>
         <v>15778.499999999998</v>
       </c>
       <c r="AA55" s="4"/>
       <c r="AB55" s="183"/>
-      <c r="AC55" s="211">
+      <c r="AC55" s="210">
         <f>0.009*Table2[[#This Row],[DENSITY]]</f>
         <v>70.649999999999991</v>
       </c>
@@ -9547,13 +9619,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z56" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z56" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA56" s="11"/>
       <c r="AB56" s="183"/>
-      <c r="AC56" s="211">
+      <c r="AC56" s="210">
         <f>1.2</f>
         <v>1.2</v>
       </c>
@@ -9642,13 +9714,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z57" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z57" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA57" s="11"/>
       <c r="AB57" s="183"/>
-      <c r="AC57" s="211">
+      <c r="AC57" s="210">
         <f t="shared" ref="AC57:AC120" si="1">1.2</f>
         <v>1.2</v>
       </c>
@@ -9737,13 +9809,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z58" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z58" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA58" s="11"/>
       <c r="AB58" s="183"/>
-      <c r="AC58" s="211">
+      <c r="AC58" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -9832,13 +9904,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z59" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z59" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA59" s="11"/>
       <c r="AB59" s="183"/>
-      <c r="AC59" s="211">
+      <c r="AC59" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -9927,13 +9999,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z60" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1100</v>
+      <c r="Z60" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>1500</v>
       </c>
       <c r="AA60" s="11"/>
       <c r="AB60" s="183"/>
-      <c r="AC60" s="211">
+      <c r="AC60" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -10022,13 +10094,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z61" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1100</v>
+      <c r="Z61" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>1500</v>
       </c>
       <c r="AA61" s="11"/>
       <c r="AB61" s="183"/>
-      <c r="AC61" s="211">
+      <c r="AC61" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -10114,13 +10186,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z62" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z62" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA62" s="16"/>
       <c r="AB62" s="182"/>
-      <c r="AC62" s="211">
+      <c r="AC62" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -10203,13 +10275,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z63" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z63" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA63" s="16"/>
       <c r="AB63" s="182"/>
-      <c r="AC63" s="211">
+      <c r="AC63" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -10294,13 +10366,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z64" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z64" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA64" s="16"/>
       <c r="AB64" s="182"/>
-      <c r="AC64" s="211">
+      <c r="AC64" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -10383,13 +10455,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z65" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z65" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA65" s="16"/>
       <c r="AB65" s="182"/>
-      <c r="AC65" s="211">
+      <c r="AC65" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -10472,13 +10544,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z66" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1100</v>
+      <c r="Z66" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>1500</v>
       </c>
       <c r="AA66" s="16"/>
       <c r="AB66" s="182"/>
-      <c r="AC66" s="211">
+      <c r="AC66" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -10568,15 +10640,15 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z67" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z67" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA67" s="2" t="s">
         <v>428</v>
       </c>
       <c r="AB67" s="21"/>
-      <c r="AC67" s="211">
+      <c r="AC67" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -10666,15 +10738,15 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z68" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z68" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA68" s="2" t="s">
         <v>429</v>
       </c>
       <c r="AB68" s="21"/>
-      <c r="AC68" s="211">
+      <c r="AC68" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -10764,13 +10836,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z69" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z69" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA69" s="2"/>
       <c r="AB69" s="21"/>
-      <c r="AC69" s="211">
+      <c r="AC69" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -10860,15 +10932,15 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z70" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z70" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA70" s="2" t="s">
         <v>431</v>
       </c>
       <c r="AB70" s="21"/>
-      <c r="AC70" s="211">
+      <c r="AC70" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -10958,15 +11030,15 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z71" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z71" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA71" s="2" t="s">
         <v>430</v>
       </c>
       <c r="AB71" s="21"/>
-      <c r="AC71" s="211">
+      <c r="AC71" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -11056,15 +11128,15 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z72" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z72" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA72" s="2" t="s">
         <v>431</v>
       </c>
       <c r="AB72" s="21"/>
-      <c r="AC72" s="211">
+      <c r="AC72" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -11154,13 +11226,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z73" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z73" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA73" s="2"/>
       <c r="AB73" s="21"/>
-      <c r="AC73" s="211">
+      <c r="AC73" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -11250,9 +11322,9 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z74" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1100</v>
+      <c r="Z74" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>1500</v>
       </c>
       <c r="AA74" s="63" t="s">
         <v>416</v>
@@ -11260,7 +11332,7 @@
       <c r="AB74" s="21" t="s">
         <v>419</v>
       </c>
-      <c r="AC74" s="211">
+      <c r="AC74" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -11350,15 +11422,15 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z75" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z75" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA75" s="2" t="s">
         <v>433</v>
       </c>
       <c r="AB75" s="21"/>
-      <c r="AC75" s="211">
+      <c r="AC75" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -11448,15 +11520,15 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z76" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z76" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA76" s="2" t="s">
         <v>433</v>
       </c>
       <c r="AB76" s="21"/>
-      <c r="AC76" s="211">
+      <c r="AC76" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -11545,13 +11617,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z77" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z77" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA77" s="2"/>
       <c r="AB77" s="21"/>
-      <c r="AC77" s="211">
+      <c r="AC77" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -11641,13 +11713,13 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z78" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z78" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA78" s="2"/>
       <c r="AB78" s="21"/>
-      <c r="AC78" s="211">
+      <c r="AC78" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -11737,15 +11809,15 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z79" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z79" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA79" s="2" t="s">
         <v>438</v>
       </c>
       <c r="AB79" s="21"/>
-      <c r="AC79" s="211">
+      <c r="AC79" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -11835,15 +11907,15 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z80" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z80" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA80" s="2" t="s">
         <v>439</v>
       </c>
       <c r="AB80" s="21"/>
-      <c r="AC80" s="211">
+      <c r="AC80" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -11933,9 +12005,9 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z81" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z81" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA81" s="2" t="s">
         <v>440</v>
@@ -11943,7 +12015,7 @@
       <c r="AB81" s="21" t="s">
         <v>423</v>
       </c>
-      <c r="AC81" s="211">
+      <c r="AC81" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -12033,13 +12105,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z82" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z82" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA82" s="2"/>
       <c r="AB82" s="21"/>
-      <c r="AC82" s="211">
+      <c r="AC82" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -12129,13 +12201,13 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z83" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z83" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA83" s="2"/>
       <c r="AB83" s="21"/>
-      <c r="AC83" s="211">
+      <c r="AC83" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -12225,13 +12297,13 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z84" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z84" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA84" s="2"/>
       <c r="AB84" s="21"/>
-      <c r="AC84" s="211">
+      <c r="AC84" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -12313,13 +12385,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z85" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z85" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA85" s="2"/>
       <c r="AB85" s="21"/>
-      <c r="AC85" s="211">
+      <c r="AC85" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -12409,13 +12481,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z86" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z86" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA86" s="2"/>
       <c r="AB86" s="21"/>
-      <c r="AC86" s="211">
+      <c r="AC86" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -12502,13 +12574,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z87" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z87" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA87" s="2"/>
       <c r="AB87" s="21"/>
-      <c r="AC87" s="211">
+      <c r="AC87" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -12598,13 +12670,13 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z88" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z88" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA88" s="2"/>
       <c r="AB88" s="21"/>
-      <c r="AC88" s="211">
+      <c r="AC88" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -12694,15 +12766,15 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z89" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z89" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA89" s="2" t="s">
         <v>434</v>
       </c>
       <c r="AB89" s="21"/>
-      <c r="AC89" s="211">
+      <c r="AC89" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -12791,15 +12863,15 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z90" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z90" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA90" s="2" t="s">
         <v>432</v>
       </c>
       <c r="AB90" s="21"/>
-      <c r="AC90" s="211">
+      <c r="AC90" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -12889,15 +12961,15 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z91" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z91" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA91" s="2" t="s">
         <v>435</v>
       </c>
       <c r="AB91" s="21"/>
-      <c r="AC91" s="211">
+      <c r="AC91" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -12987,9 +13059,9 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z92" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z92" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA92" s="2" t="s">
         <v>437</v>
@@ -12997,7 +13069,7 @@
       <c r="AB92" s="21" t="s">
         <v>436</v>
       </c>
-      <c r="AC92" s="211">
+      <c r="AC92" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -13087,15 +13159,15 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z93" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z93" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA93" s="2" t="s">
         <v>434</v>
       </c>
       <c r="AB93" s="21"/>
-      <c r="AC93" s="211">
+      <c r="AC93" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -13185,13 +13257,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z94" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z94" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA94" s="2"/>
       <c r="AB94" s="21"/>
-      <c r="AC94" s="211">
+      <c r="AC94" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -13281,13 +13353,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z95" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z95" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA95" s="2"/>
       <c r="AB95" s="21"/>
-      <c r="AC95" s="211">
+      <c r="AC95" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -13377,15 +13449,15 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z96" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z96" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA96" s="2" t="s">
         <v>438</v>
       </c>
       <c r="AB96" s="21"/>
-      <c r="AC96" s="211">
+      <c r="AC96" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -13475,15 +13547,15 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z97" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1100</v>
+      <c r="Z97" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>1500</v>
       </c>
       <c r="AA97" s="2" t="s">
         <v>418</v>
       </c>
       <c r="AB97" s="21"/>
-      <c r="AC97" s="211">
+      <c r="AC97" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -13573,15 +13645,15 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z98" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1100</v>
+      <c r="Z98" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>1500</v>
       </c>
       <c r="AA98" s="2" t="s">
         <v>417</v>
       </c>
       <c r="AB98" s="21"/>
-      <c r="AC98" s="211">
+      <c r="AC98" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -13669,17 +13741,17 @@
                          T99&lt;=_xlfn.PERCENTILE.INC(_xlfn._xlws.FILTER($T$2:$T$148, ($K$3:$K$149=K99)*($W$2:$W$148=1)),0.9)
                ),1,0),
 0)</f>
-        <v>1</v>
-      </c>
-      <c r="Z99" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1100</v>
+        <v>0</v>
+      </c>
+      <c r="Z99" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>1500</v>
       </c>
       <c r="AA99" s="2" t="s">
         <v>420</v>
       </c>
       <c r="AB99" s="21"/>
-      <c r="AC99" s="211">
+      <c r="AC99" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -13769,15 +13841,15 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z100" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1100</v>
+      <c r="Z100" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>1500</v>
       </c>
       <c r="AA100" s="2" t="s">
         <v>421</v>
       </c>
       <c r="AB100" s="21"/>
-      <c r="AC100" s="211">
+      <c r="AC100" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -13867,9 +13939,9 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z101" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1100</v>
+      <c r="Z101" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>1500</v>
       </c>
       <c r="AA101" s="2" t="s">
         <v>422</v>
@@ -13877,7 +13949,7 @@
       <c r="AB101" s="21" t="s">
         <v>424</v>
       </c>
-      <c r="AC101" s="211">
+      <c r="AC101" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -13967,9 +14039,9 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z102" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1100</v>
+      <c r="Z102" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>1500</v>
       </c>
       <c r="AA102" s="2" t="s">
         <v>426</v>
@@ -13977,7 +14049,7 @@
       <c r="AB102" s="21" t="s">
         <v>425</v>
       </c>
-      <c r="AC102" s="211">
+      <c r="AC102" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -14052,11 +14124,11 @@
       </c>
       <c r="W103" s="50">
         <f ca="1">IF(OR($D103="Ecoinvent",$D103="Betonsortenrechner",$D103="KBOB",$T103&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X103" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y103" s="167" cm="1">
         <f t="array" aca="1" ref="Y103" ca="1">IF($W103&lt;&gt;0,
@@ -14067,15 +14139,15 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z103" s="207">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1100,1800)</f>
-        <v>1800</v>
+      <c r="Z103" s="206">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <v>2200</v>
       </c>
       <c r="AA103" s="4" t="s">
         <v>467</v>
       </c>
       <c r="AB103" s="37"/>
-      <c r="AC103" s="211">
+      <c r="AC103" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -14159,7 +14231,7 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z104" s="209">
+      <c r="Z104" s="208">
         <f>17*Table2[[#This Row],[DENSITY]]</f>
         <v>133450</v>
       </c>
@@ -14167,7 +14239,7 @@
         <v>493</v>
       </c>
       <c r="AB104" s="179"/>
-      <c r="AC104" s="211">
+      <c r="AC104" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -14253,7 +14325,7 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z105" s="209">
+      <c r="Z105" s="208">
         <f>17*Table2[[#This Row],[DENSITY]]</f>
         <v>133450</v>
       </c>
@@ -14261,7 +14333,7 @@
         <v>493</v>
       </c>
       <c r="AB105" s="21"/>
-      <c r="AC105" s="211">
+      <c r="AC105" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -14348,7 +14420,7 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z106" s="209">
+      <c r="Z106" s="208">
         <f>17*Table2[[#This Row],[DENSITY]]</f>
         <v>133450</v>
       </c>
@@ -14356,7 +14428,7 @@
         <v>493</v>
       </c>
       <c r="AB106" s="21"/>
-      <c r="AC106" s="211">
+      <c r="AC106" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -14443,7 +14515,7 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z107" s="209">
+      <c r="Z107" s="208">
         <f>17*Table2[[#This Row],[DENSITY]]</f>
         <v>133450</v>
       </c>
@@ -14451,7 +14523,7 @@
         <v>493</v>
       </c>
       <c r="AB107" s="21"/>
-      <c r="AC107" s="211">
+      <c r="AC107" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -14538,7 +14610,7 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z108" s="209">
+      <c r="Z108" s="208">
         <f>17*Table2[[#This Row],[DENSITY]]</f>
         <v>133450</v>
       </c>
@@ -14546,7 +14618,7 @@
         <v>493</v>
       </c>
       <c r="AB108" s="21"/>
-      <c r="AC108" s="211">
+      <c r="AC108" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -14633,7 +14705,7 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z109" s="209">
+      <c r="Z109" s="208">
         <f>17*Table2[[#This Row],[DENSITY]]</f>
         <v>133450</v>
       </c>
@@ -14641,7 +14713,7 @@
         <v>493</v>
       </c>
       <c r="AB109" s="21"/>
-      <c r="AC109" s="211">
+      <c r="AC109" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -14727,7 +14799,7 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z110" s="209">
+      <c r="Z110" s="208">
         <f>17*Table2[[#This Row],[DENSITY]]</f>
         <v>133450</v>
       </c>
@@ -14735,7 +14807,7 @@
         <v>493</v>
       </c>
       <c r="AB110" s="21"/>
-      <c r="AC110" s="211">
+      <c r="AC110" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -14823,7 +14895,7 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z111" s="209">
+      <c r="Z111" s="208">
         <f>17*Table2[[#This Row],[DENSITY]]</f>
         <v>133450</v>
       </c>
@@ -14831,7 +14903,7 @@
         <v>493</v>
       </c>
       <c r="AB111" s="21"/>
-      <c r="AC111" s="211">
+      <c r="AC111" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -14917,7 +14989,7 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z112" s="209">
+      <c r="Z112" s="208">
         <f>17*Table2[[#This Row],[DENSITY]]</f>
         <v>133450</v>
       </c>
@@ -14925,7 +14997,7 @@
         <v>493</v>
       </c>
       <c r="AB112" s="21"/>
-      <c r="AC112" s="211">
+      <c r="AC112" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -15011,7 +15083,7 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z113" s="209">
+      <c r="Z113" s="208">
         <f>17*Table2[[#This Row],[DENSITY]]</f>
         <v>133450</v>
       </c>
@@ -15019,7 +15091,7 @@
         <v>493</v>
       </c>
       <c r="AB113" s="21"/>
-      <c r="AC113" s="211">
+      <c r="AC113" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -15107,7 +15179,7 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z114" s="209">
+      <c r="Z114" s="208">
         <f>17*Table2[[#This Row],[DENSITY]]</f>
         <v>133450</v>
       </c>
@@ -15115,7 +15187,7 @@
         <v>493</v>
       </c>
       <c r="AB114" s="21"/>
-      <c r="AC114" s="211">
+      <c r="AC114" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -15202,7 +15274,7 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z115" s="209">
+      <c r="Z115" s="208">
         <f>17*Table2[[#This Row],[DENSITY]]</f>
         <v>133450</v>
       </c>
@@ -15210,7 +15282,7 @@
         <v>493</v>
       </c>
       <c r="AB115" s="21"/>
-      <c r="AC115" s="211">
+      <c r="AC115" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -15297,7 +15369,7 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z116" s="209">
+      <c r="Z116" s="208">
         <f>17*Table2[[#This Row],[DENSITY]]</f>
         <v>133450</v>
       </c>
@@ -15305,7 +15377,7 @@
         <v>493</v>
       </c>
       <c r="AB116" s="21"/>
-      <c r="AC116" s="211">
+      <c r="AC116" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -15392,7 +15464,7 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z117" s="209">
+      <c r="Z117" s="208">
         <f>17*Table2[[#This Row],[DENSITY]]</f>
         <v>133450</v>
       </c>
@@ -15400,7 +15472,7 @@
         <v>494</v>
       </c>
       <c r="AB117" s="21"/>
-      <c r="AC117" s="211">
+      <c r="AC117" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -15486,7 +15558,7 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z118" s="209">
+      <c r="Z118" s="208">
         <f>17*Table2[[#This Row],[DENSITY]]</f>
         <v>133450</v>
       </c>
@@ -15494,7 +15566,7 @@
         <v>511</v>
       </c>
       <c r="AB118" s="21"/>
-      <c r="AC118" s="211">
+      <c r="AC118" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -15581,7 +15653,7 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z119" s="209">
+      <c r="Z119" s="208">
         <f>17*Table2[[#This Row],[DENSITY]]</f>
         <v>133450</v>
       </c>
@@ -15589,7 +15661,7 @@
         <v>493</v>
       </c>
       <c r="AB119" s="21"/>
-      <c r="AC119" s="211">
+      <c r="AC119" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -15676,7 +15748,7 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z120" s="209">
+      <c r="Z120" s="208">
         <f>17*Table2[[#This Row],[DENSITY]]</f>
         <v>133450</v>
       </c>
@@ -15684,7 +15756,7 @@
         <v>493</v>
       </c>
       <c r="AB120" s="21"/>
-      <c r="AC120" s="211">
+      <c r="AC120" s="210">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
@@ -15772,7 +15844,7 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z121" s="209">
+      <c r="Z121" s="208">
         <f>17*Table2[[#This Row],[DENSITY]]</f>
         <v>133450</v>
       </c>
@@ -15780,7 +15852,7 @@
         <v>493</v>
       </c>
       <c r="AB121" s="37"/>
-      <c r="AC121" s="211">
+      <c r="AC121" s="210">
         <f t="shared" ref="AC121" si="2">1.2</f>
         <v>1.2</v>
       </c>
@@ -15857,7 +15929,7 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z122" s="210">
+      <c r="Z122" s="209">
         <f>10*7850</f>
         <v>78500</v>
       </c>
@@ -15865,7 +15937,7 @@
         <v>171</v>
       </c>
       <c r="AB122" s="21"/>
-      <c r="AC122" s="211">
+      <c r="AC122" s="210">
         <f>7850*0.02</f>
         <v>157</v>
       </c>
@@ -15942,13 +16014,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z123" s="210">
+      <c r="Z123" s="209">
         <f t="shared" ref="Z123:Z130" si="3">10*7850</f>
         <v>78500</v>
       </c>
       <c r="AA123" s="2"/>
       <c r="AB123" s="21"/>
-      <c r="AC123" s="211">
+      <c r="AC123" s="210">
         <f t="shared" ref="AC123:AC130" si="4">7850*0.02</f>
         <v>157</v>
       </c>
@@ -16025,7 +16097,7 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z124" s="210">
+      <c r="Z124" s="209">
         <f t="shared" si="3"/>
         <v>78500</v>
       </c>
@@ -16033,7 +16105,7 @@
         <v>170</v>
       </c>
       <c r="AB124" s="21"/>
-      <c r="AC124" s="211">
+      <c r="AC124" s="210">
         <f t="shared" si="4"/>
         <v>157</v>
       </c>
@@ -16111,7 +16183,7 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z125" s="210">
+      <c r="Z125" s="209">
         <f t="shared" si="3"/>
         <v>78500</v>
       </c>
@@ -16119,7 +16191,7 @@
         <v>170</v>
       </c>
       <c r="AB125" s="21"/>
-      <c r="AC125" s="211">
+      <c r="AC125" s="210">
         <f t="shared" si="4"/>
         <v>157</v>
       </c>
@@ -16197,13 +16269,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z126" s="210">
+      <c r="Z126" s="209">
         <f t="shared" si="3"/>
         <v>78500</v>
       </c>
       <c r="AA126" s="2"/>
       <c r="AB126" s="21"/>
-      <c r="AC126" s="211">
+      <c r="AC126" s="210">
         <f t="shared" si="4"/>
         <v>157</v>
       </c>
@@ -16281,13 +16353,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z127" s="210">
+      <c r="Z127" s="209">
         <f t="shared" si="3"/>
         <v>78500</v>
       </c>
       <c r="AA127" s="2"/>
       <c r="AB127" s="21"/>
-      <c r="AC127" s="211">
+      <c r="AC127" s="210">
         <f t="shared" si="4"/>
         <v>157</v>
       </c>
@@ -16362,13 +16434,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z128" s="210">
+      <c r="Z128" s="209">
         <f t="shared" si="3"/>
         <v>78500</v>
       </c>
       <c r="AA128" s="2"/>
       <c r="AB128" s="21"/>
-      <c r="AC128" s="211">
+      <c r="AC128" s="210">
         <f t="shared" si="4"/>
         <v>157</v>
       </c>
@@ -16445,13 +16517,13 @@
 0)</f>
         <v>1</v>
       </c>
-      <c r="Z129" s="210">
+      <c r="Z129" s="209">
         <f t="shared" si="3"/>
         <v>78500</v>
       </c>
       <c r="AA129" s="2"/>
       <c r="AB129" s="21"/>
-      <c r="AC129" s="211">
+      <c r="AC129" s="210">
         <f t="shared" si="4"/>
         <v>157</v>
       </c>
@@ -16528,13 +16600,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z130" s="210">
+      <c r="Z130" s="209">
         <f t="shared" si="3"/>
         <v>78500</v>
       </c>
       <c r="AA130" s="4"/>
       <c r="AB130" s="21"/>
-      <c r="AC130" s="211">
+      <c r="AC130" s="210">
         <f t="shared" si="4"/>
         <v>157</v>
       </c>
@@ -16609,12 +16681,12 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z131" s="210"/>
+      <c r="Z131" s="209"/>
       <c r="AA131" s="2" t="s">
         <v>193</v>
       </c>
       <c r="AB131" s="21"/>
-      <c r="AC131" s="211"/>
+      <c r="AC131" s="210"/>
     </row>
     <row r="132" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A132" s="8" t="s">
@@ -16686,12 +16758,12 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z132" s="210"/>
+      <c r="Z132" s="209"/>
       <c r="AA132" s="2" t="s">
         <v>194</v>
       </c>
       <c r="AB132" s="21"/>
-      <c r="AC132" s="211"/>
+      <c r="AC132" s="210"/>
     </row>
     <row r="133" spans="1:29" x14ac:dyDescent="0.2">
       <c r="E133" s="91"/>
@@ -16744,12 +16816,12 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="Y1:Y121">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y122:Y1048576">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17154,10 +17226,10 @@
       <c r="G5" s="56">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="H5" s="205">
+      <c r="H5">
         <v>253</v>
       </c>
-      <c r="I5" s="205">
+      <c r="I5">
         <v>0.2</v>
       </c>
     </row>
@@ -17180,10 +17252,10 @@
       <c r="G6">
         <v>0.81599999999999995</v>
       </c>
-      <c r="H6" s="205">
+      <c r="H6">
         <v>335</v>
       </c>
-      <c r="I6" s="205">
+      <c r="I6">
         <v>0.2</v>
       </c>
     </row>
@@ -17206,10 +17278,10 @@
       <c r="G7">
         <v>0.55200000000000005</v>
       </c>
-      <c r="H7" s="205">
+      <c r="H7">
         <v>335</v>
       </c>
-      <c r="I7" s="205">
+      <c r="I7">
         <v>0.2</v>
       </c>
     </row>
@@ -17222,7 +17294,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DF23033-31FA-D240-A005-0FD6F443ADB6}">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.83203125" bestFit="1" customWidth="1"/>
@@ -17231,7 +17303,7 @@
     <col min="4" max="4" width="27.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="61" t="s">
         <v>415</v>
       </c>
@@ -17244,8 +17316,14 @@
       <c r="D1" s="61" t="s">
         <v>519</v>
       </c>
+      <c r="E1" s="61" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1" s="61" t="s">
+        <v>523</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="56">
         <v>1</v>
       </c>
@@ -17258,8 +17336,14 @@
       <c r="D2" s="56">
         <v>5830000</v>
       </c>
+      <c r="E2" s="212">
+        <v>8</v>
+      </c>
+      <c r="F2" s="212">
+        <v>0.02</v>
+      </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="56">
         <v>2</v>
       </c>
@@ -17272,8 +17356,14 @@
       <c r="D3" s="56">
         <v>7780000</v>
       </c>
+      <c r="E3" s="211">
+        <v>9</v>
+      </c>
+      <c r="F3" s="211">
+        <v>0.02</v>
+      </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="56">
         <v>3</v>
       </c>
@@ -17286,8 +17376,14 @@
       <c r="D4" s="56">
         <v>9700000</v>
       </c>
+      <c r="E4" s="211">
+        <v>10</v>
+      </c>
+      <c r="F4" s="211">
+        <v>2.5000000000000001E-2</v>
+      </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="56">
         <v>4</v>
       </c>
@@ -17300,8 +17396,14 @@
       <c r="D5" s="56">
         <v>11670000</v>
       </c>
+      <c r="E5" s="211">
+        <v>11</v>
+      </c>
+      <c r="F5" s="211">
+        <v>2.5000000000000001E-2</v>
+      </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="56">
         <v>5</v>
       </c>
@@ -17312,14 +17414,20 @@
       <c r="D6" s="56">
         <v>100000000</v>
       </c>
+      <c r="E6" s="213">
+        <v>30</v>
+      </c>
+      <c r="F6" s="213">
+        <v>0.01</v>
+      </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C14" s="202"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C15" s="202"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C16" s="202"/>
     </row>
     <row r="17" spans="3:3" x14ac:dyDescent="0.2">

--- a/Database/260126_Datenbankdefinition.xlsx
+++ b/Database/260126_Datenbankdefinition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonathanbieg/Documents/Master Thesis/1_Code/Python Repository/SDSD_Bieg/Database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4C1A30B-1D3E-D941-812A-1EB5684C6013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBFDFAE5-7CDD-FB4D-ADAE-035C47EACC7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3400" yWindow="-20280" windowWidth="32160" windowHeight="19140" activeTab="3" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17160" activeTab="3" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
   </bookViews>
   <sheets>
     <sheet name="products" sheetId="1" r:id="rId1"/>
@@ -2234,7 +2234,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="214">
+  <cellXfs count="211">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2700,15 +2700,34 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Standard 2" xfId="1" xr:uid="{FDCFE4BD-E849-456C-8E2E-B78D9BD993F6}"/>
   </cellStyles>
   <dxfs count="59">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2776,28 +2795,6 @@
           <color theme="4" tint="0.39997558519241921"/>
         </bottom>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -4213,8 +4210,8 @@
     <tableColumn id="2" xr3:uid="{603BAED4-55F2-D040-9D73-1611C1564A84}" name="name" dataDxfId="6"/>
     <tableColumn id="3" xr3:uid="{D6CC67C0-1ACA-D446-A6F3-00BCC3AC8DAC}" name="d" dataDxfId="5"/>
     <tableColumn id="4" xr3:uid="{3D62C7FF-3D7F-B245-A874-3A95DF0C49D2}" name="K_ser" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{0C35052C-7630-EC48-BB52-4928EDE8D2AC}" name="Cost" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{5101DCF1-1E94-3949-9F50-D0C3653EA4AB}" name="T_construction" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{0C35052C-7630-EC48-BB52-4928EDE8D2AC}" name="Cost" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{5101DCF1-1E94-3949-9F50-D0C3653EA4AB}" name="T_construction" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9620,14 +9617,13 @@
         <v>0</v>
       </c>
       <c r="Z56" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA56" s="11"/>
       <c r="AB56" s="183"/>
       <c r="AC56" s="210">
-        <f>1.2</f>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
@@ -9715,14 +9711,13 @@
         <v>0</v>
       </c>
       <c r="Z57" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA57" s="11"/>
       <c r="AB57" s="183"/>
       <c r="AC57" s="210">
-        <f t="shared" ref="AC57:AC120" si="1">1.2</f>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
@@ -9810,14 +9805,13 @@
         <v>0</v>
       </c>
       <c r="Z58" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA58" s="11"/>
       <c r="AB58" s="183"/>
       <c r="AC58" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
@@ -9905,14 +9899,13 @@
         <v>0</v>
       </c>
       <c r="Z59" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA59" s="11"/>
       <c r="AB59" s="183"/>
       <c r="AC59" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
@@ -10000,14 +9993,13 @@
         <v>0</v>
       </c>
       <c r="Z60" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
-        <v>1500</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
+        <v>1700</v>
       </c>
       <c r="AA60" s="11"/>
       <c r="AB60" s="183"/>
       <c r="AC60" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
@@ -10095,14 +10087,13 @@
         <v>0</v>
       </c>
       <c r="Z61" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
-        <v>1500</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
+        <v>1700</v>
       </c>
       <c r="AA61" s="11"/>
       <c r="AB61" s="183"/>
       <c r="AC61" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.2">
@@ -10187,14 +10178,13 @@
         <v>0</v>
       </c>
       <c r="Z62" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA62" s="16"/>
       <c r="AB62" s="182"/>
       <c r="AC62" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.2">
@@ -10276,14 +10266,13 @@
         <v>0</v>
       </c>
       <c r="Z63" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA63" s="16"/>
       <c r="AB63" s="182"/>
       <c r="AC63" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.2">
@@ -10367,14 +10356,13 @@
         <v>0</v>
       </c>
       <c r="Z64" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA64" s="16"/>
       <c r="AB64" s="182"/>
       <c r="AC64" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.2">
@@ -10456,14 +10444,13 @@
         <v>0</v>
       </c>
       <c r="Z65" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA65" s="16"/>
       <c r="AB65" s="182"/>
       <c r="AC65" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.2">
@@ -10545,14 +10532,13 @@
         <v>0</v>
       </c>
       <c r="Z66" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
-        <v>1500</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
+        <v>1700</v>
       </c>
       <c r="AA66" s="16"/>
       <c r="AB66" s="182"/>
       <c r="AC66" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:29" x14ac:dyDescent="0.2">
@@ -10641,7 +10627,7 @@
         <v>0</v>
       </c>
       <c r="Z67" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA67" s="2" t="s">
@@ -10649,8 +10635,7 @@
       </c>
       <c r="AB67" s="21"/>
       <c r="AC67" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:29" x14ac:dyDescent="0.2">
@@ -10739,7 +10724,7 @@
         <v>1</v>
       </c>
       <c r="Z68" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA68" s="2" t="s">
@@ -10747,8 +10732,7 @@
       </c>
       <c r="AB68" s="21"/>
       <c r="AC68" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:29" x14ac:dyDescent="0.2">
@@ -10837,14 +10821,13 @@
         <v>0</v>
       </c>
       <c r="Z69" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA69" s="2"/>
       <c r="AB69" s="21"/>
       <c r="AC69" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:29" x14ac:dyDescent="0.2">
@@ -10933,7 +10916,7 @@
         <v>1</v>
       </c>
       <c r="Z70" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA70" s="2" t="s">
@@ -10941,8 +10924,7 @@
       </c>
       <c r="AB70" s="21"/>
       <c r="AC70" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:29" x14ac:dyDescent="0.2">
@@ -11031,7 +11013,7 @@
         <v>1</v>
       </c>
       <c r="Z71" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA71" s="2" t="s">
@@ -11039,8 +11021,7 @@
       </c>
       <c r="AB71" s="21"/>
       <c r="AC71" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:29" x14ac:dyDescent="0.2">
@@ -11129,7 +11110,7 @@
         <v>1</v>
       </c>
       <c r="Z72" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA72" s="2" t="s">
@@ -11137,8 +11118,7 @@
       </c>
       <c r="AB72" s="21"/>
       <c r="AC72" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:29" x14ac:dyDescent="0.2">
@@ -11227,14 +11207,13 @@
         <v>0</v>
       </c>
       <c r="Z73" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA73" s="2"/>
       <c r="AB73" s="21"/>
       <c r="AC73" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11323,8 +11302,8 @@
         <v>1</v>
       </c>
       <c r="Z74" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
-        <v>1500</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
+        <v>1700</v>
       </c>
       <c r="AA74" s="63" t="s">
         <v>416</v>
@@ -11333,8 +11312,7 @@
         <v>419</v>
       </c>
       <c r="AC74" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:29" x14ac:dyDescent="0.2">
@@ -11423,7 +11401,7 @@
         <v>0</v>
       </c>
       <c r="Z75" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA75" s="2" t="s">
@@ -11431,8 +11409,7 @@
       </c>
       <c r="AB75" s="21"/>
       <c r="AC75" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:29" x14ac:dyDescent="0.2">
@@ -11521,7 +11498,7 @@
         <v>0</v>
       </c>
       <c r="Z76" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA76" s="2" t="s">
@@ -11529,8 +11506,7 @@
       </c>
       <c r="AB76" s="21"/>
       <c r="AC76" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:29" x14ac:dyDescent="0.2">
@@ -11618,14 +11594,13 @@
         <v>0</v>
       </c>
       <c r="Z77" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA77" s="2"/>
       <c r="AB77" s="21"/>
       <c r="AC77" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:29" x14ac:dyDescent="0.2">
@@ -11714,14 +11689,13 @@
         <v>1</v>
       </c>
       <c r="Z78" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA78" s="2"/>
       <c r="AB78" s="21"/>
       <c r="AC78" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:29" x14ac:dyDescent="0.2">
@@ -11810,7 +11784,7 @@
         <v>0</v>
       </c>
       <c r="Z79" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA79" s="2" t="s">
@@ -11818,8 +11792,7 @@
       </c>
       <c r="AB79" s="21"/>
       <c r="AC79" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:29" x14ac:dyDescent="0.2">
@@ -11908,7 +11881,7 @@
         <v>0</v>
       </c>
       <c r="Z80" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA80" s="2" t="s">
@@ -11916,8 +11889,7 @@
       </c>
       <c r="AB80" s="21"/>
       <c r="AC80" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:29" x14ac:dyDescent="0.2">
@@ -12006,7 +11978,7 @@
         <v>1</v>
       </c>
       <c r="Z81" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA81" s="2" t="s">
@@ -12016,8 +11988,7 @@
         <v>423</v>
       </c>
       <c r="AC81" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:29" x14ac:dyDescent="0.2">
@@ -12106,14 +12077,13 @@
         <v>0</v>
       </c>
       <c r="Z82" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA82" s="2"/>
       <c r="AB82" s="21"/>
       <c r="AC82" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:29" x14ac:dyDescent="0.2">
@@ -12202,14 +12172,13 @@
         <v>1</v>
       </c>
       <c r="Z83" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA83" s="2"/>
       <c r="AB83" s="21"/>
       <c r="AC83" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:29" x14ac:dyDescent="0.2">
@@ -12298,14 +12267,13 @@
         <v>1</v>
       </c>
       <c r="Z84" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA84" s="2"/>
       <c r="AB84" s="21"/>
       <c r="AC84" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:29" x14ac:dyDescent="0.2">
@@ -12386,14 +12354,13 @@
         <v>0</v>
       </c>
       <c r="Z85" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA85" s="2"/>
       <c r="AB85" s="21"/>
       <c r="AC85" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:29" x14ac:dyDescent="0.2">
@@ -12482,14 +12449,13 @@
         <v>0</v>
       </c>
       <c r="Z86" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA86" s="2"/>
       <c r="AB86" s="21"/>
       <c r="AC86" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:29" x14ac:dyDescent="0.2">
@@ -12575,14 +12541,13 @@
         <v>0</v>
       </c>
       <c r="Z87" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA87" s="2"/>
       <c r="AB87" s="21"/>
       <c r="AC87" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:29" x14ac:dyDescent="0.2">
@@ -12671,14 +12636,13 @@
         <v>1</v>
       </c>
       <c r="Z88" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA88" s="2"/>
       <c r="AB88" s="21"/>
       <c r="AC88" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:29" x14ac:dyDescent="0.2">
@@ -12767,7 +12731,7 @@
         <v>1</v>
       </c>
       <c r="Z89" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA89" s="2" t="s">
@@ -12775,8 +12739,7 @@
       </c>
       <c r="AB89" s="21"/>
       <c r="AC89" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:29" x14ac:dyDescent="0.2">
@@ -12864,7 +12827,7 @@
         <v>0</v>
       </c>
       <c r="Z90" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA90" s="2" t="s">
@@ -12872,8 +12835,7 @@
       </c>
       <c r="AB90" s="21"/>
       <c r="AC90" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:29" x14ac:dyDescent="0.2">
@@ -12962,7 +12924,7 @@
         <v>1</v>
       </c>
       <c r="Z91" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA91" s="2" t="s">
@@ -12970,8 +12932,7 @@
       </c>
       <c r="AB91" s="21"/>
       <c r="AC91" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:29" x14ac:dyDescent="0.2">
@@ -13060,7 +13021,7 @@
         <v>1</v>
       </c>
       <c r="Z92" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA92" s="2" t="s">
@@ -13070,8 +13031,7 @@
         <v>436</v>
       </c>
       <c r="AC92" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:29" x14ac:dyDescent="0.2">
@@ -13160,7 +13120,7 @@
         <v>1</v>
       </c>
       <c r="Z93" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA93" s="2" t="s">
@@ -13168,8 +13128,7 @@
       </c>
       <c r="AB93" s="21"/>
       <c r="AC93" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:29" x14ac:dyDescent="0.2">
@@ -13258,14 +13217,13 @@
         <v>0</v>
       </c>
       <c r="Z94" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA94" s="2"/>
       <c r="AB94" s="21"/>
       <c r="AC94" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:29" x14ac:dyDescent="0.2">
@@ -13354,14 +13312,13 @@
         <v>0</v>
       </c>
       <c r="Z95" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA95" s="2"/>
       <c r="AB95" s="21"/>
       <c r="AC95" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:29" x14ac:dyDescent="0.2">
@@ -13450,7 +13407,7 @@
         <v>0</v>
       </c>
       <c r="Z96" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA96" s="2" t="s">
@@ -13458,8 +13415,7 @@
       </c>
       <c r="AB96" s="21"/>
       <c r="AC96" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:29" x14ac:dyDescent="0.2">
@@ -13548,16 +13504,15 @@
         <v>0</v>
       </c>
       <c r="Z97" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
-        <v>1500</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
+        <v>1700</v>
       </c>
       <c r="AA97" s="2" t="s">
         <v>418</v>
       </c>
       <c r="AB97" s="21"/>
       <c r="AC97" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:29" x14ac:dyDescent="0.2">
@@ -13646,16 +13601,15 @@
         <v>0</v>
       </c>
       <c r="Z98" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
-        <v>1500</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
+        <v>1700</v>
       </c>
       <c r="AA98" s="2" t="s">
         <v>417</v>
       </c>
       <c r="AB98" s="21"/>
       <c r="AC98" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:29" x14ac:dyDescent="0.2">
@@ -13744,16 +13698,15 @@
         <v>0</v>
       </c>
       <c r="Z99" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
-        <v>1500</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
+        <v>1700</v>
       </c>
       <c r="AA99" s="2" t="s">
         <v>420</v>
       </c>
       <c r="AB99" s="21"/>
       <c r="AC99" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:29" x14ac:dyDescent="0.2">
@@ -13842,16 +13795,15 @@
         <v>1</v>
       </c>
       <c r="Z100" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
-        <v>1500</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
+        <v>1700</v>
       </c>
       <c r="AA100" s="2" t="s">
         <v>421</v>
       </c>
       <c r="AB100" s="21"/>
       <c r="AC100" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:29" x14ac:dyDescent="0.2">
@@ -13940,8 +13892,8 @@
         <v>0</v>
       </c>
       <c r="Z101" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
-        <v>1500</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
+        <v>1700</v>
       </c>
       <c r="AA101" s="2" t="s">
         <v>422</v>
@@ -13950,8 +13902,7 @@
         <v>424</v>
       </c>
       <c r="AC101" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:29" x14ac:dyDescent="0.2">
@@ -14040,8 +13991,8 @@
         <v>0</v>
       </c>
       <c r="Z102" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
-        <v>1500</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
+        <v>1700</v>
       </c>
       <c r="AA102" s="2" t="s">
         <v>426</v>
@@ -14050,8 +14001,7 @@
         <v>425</v>
       </c>
       <c r="AC102" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
@@ -14140,7 +14090,7 @@
         <v>0</v>
       </c>
       <c r="Z103" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1500,2200)</f>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
         <v>2200</v>
       </c>
       <c r="AA103" s="4" t="s">
@@ -14148,8 +14098,7 @@
       </c>
       <c r="AB103" s="37"/>
       <c r="AC103" s="210">
-        <f t="shared" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.2">
@@ -14240,7 +14189,6 @@
       </c>
       <c r="AB104" s="179"/>
       <c r="AC104" s="210">
-        <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
     </row>
@@ -14334,7 +14282,7 @@
       </c>
       <c r="AB105" s="21"/>
       <c r="AC105" s="210">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="AC105:AC120" si="1">1.2</f>
         <v>1.2</v>
       </c>
     </row>
@@ -16816,12 +16764,12 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="Y1:Y121">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y122:Y1048576">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17336,10 +17284,10 @@
       <c r="D2" s="56">
         <v>5830000</v>
       </c>
-      <c r="E2" s="212">
+      <c r="E2" s="203">
         <v>8</v>
       </c>
-      <c r="F2" s="212">
+      <c r="F2" s="203">
         <v>0.02</v>
       </c>
     </row>
@@ -17356,10 +17304,10 @@
       <c r="D3" s="56">
         <v>7780000</v>
       </c>
-      <c r="E3" s="211">
+      <c r="E3" s="56">
         <v>9</v>
       </c>
-      <c r="F3" s="211">
+      <c r="F3" s="56">
         <v>0.02</v>
       </c>
     </row>
@@ -17376,10 +17324,10 @@
       <c r="D4" s="56">
         <v>9700000</v>
       </c>
-      <c r="E4" s="211">
+      <c r="E4" s="56">
         <v>10</v>
       </c>
-      <c r="F4" s="211">
+      <c r="F4" s="56">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
@@ -17396,10 +17344,10 @@
       <c r="D5" s="56">
         <v>11670000</v>
       </c>
-      <c r="E5" s="211">
+      <c r="E5" s="56">
         <v>11</v>
       </c>
-      <c r="F5" s="211">
+      <c r="F5" s="56">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
@@ -17414,10 +17362,10 @@
       <c r="D6" s="56">
         <v>100000000</v>
       </c>
-      <c r="E6" s="213">
+      <c r="E6" s="62">
         <v>30</v>
       </c>
-      <c r="F6" s="213">
+      <c r="F6" s="62">
         <v>0.01</v>
       </c>
     </row>

--- a/Database/260126_Datenbankdefinition.xlsx
+++ b/Database/260126_Datenbankdefinition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonathanbieg/Documents/Master Thesis/1_Code/Python Repository/SDSD_Bieg/Database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBFDFAE5-7CDD-FB4D-ADAE-035C47EACC7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A0D5814-88E2-FF43-84D8-35F857464BF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17160" activeTab="3" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17160" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
   </bookViews>
   <sheets>
     <sheet name="products" sheetId="1" r:id="rId1"/>
@@ -93,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1896" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1906" uniqueCount="525">
   <si>
     <t>B500B</t>
   </si>
@@ -1682,6 +1682,9 @@
   </si>
   <si>
     <t>T_construction</t>
+  </si>
+  <si>
+    <t>Y1860</t>
   </si>
 </sst>
 </file>
@@ -2234,7 +2237,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="211">
+  <cellXfs count="212">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2700,6 +2703,7 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2830,422 +2834,6 @@
         </bottom>
         <vertical/>
         <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -4061,6 +3649,422 @@
       </font>
       <alignment vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -4131,42 +4135,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}" name="Table2" displayName="Table2" ref="A1:AC132" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}" name="Table2" displayName="Table2" ref="A1:AC132" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42">
   <autoFilter ref="A1:AC132" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}"/>
   <tableColumns count="29">
-    <tableColumn id="9" xr3:uid="{1DBBD25D-72F9-4A81-9CFA-500505E3628D}" name="ID" dataDxfId="56"/>
-    <tableColumn id="14" xr3:uid="{6844A52F-C967-44C0-BF5C-160C47AB6E64}" name="PRO_ID" dataDxfId="55"/>
-    <tableColumn id="12" xr3:uid="{4EDF1E73-4744-474F-8DFE-7F72FB05613C}" name="EPD_ID" dataDxfId="54"/>
-    <tableColumn id="1" xr3:uid="{1CF2E22E-1020-4F35-B31F-6350A15A5DE8}" name="SOURCE" dataDxfId="53"/>
-    <tableColumn id="27" xr3:uid="{07F74D5D-9130-4120-B02C-A11234427F46}" name="KBOB ID-Nr." dataDxfId="52"/>
-    <tableColumn id="11" xr3:uid="{81FE7F31-5F54-40F9-B99E-827E048F7DB5}" name="EPD_DATE" dataDxfId="51"/>
-    <tableColumn id="10" xr3:uid="{54D8BA04-0FEF-4C3B-9B14-59E8F982CD3F}" name="VALID_TO" dataDxfId="50"/>
-    <tableColumn id="22" xr3:uid="{3D6FC370-B8A8-40C3-9FC8-791B178DDFDF}" name="COUNTRY" dataDxfId="49"/>
-    <tableColumn id="4" xr3:uid="{25C7280F-4E3E-4E39-BDBB-DC06DF090C5B}" name="PRODUCT_NAME" dataDxfId="48"/>
-    <tableColumn id="26" xr3:uid="{1053A7DD-B11F-4E75-92EC-BC0F866E90B4}" name="OEKOBAUDAT_ID" dataDxfId="47"/>
-    <tableColumn id="25" xr3:uid="{295F99F8-E318-45C9-833E-F0B45A26471A}" name="MATERIAL_GROUP" dataDxfId="46"/>
-    <tableColumn id="2" xr3:uid="{1326FCEF-D1EE-4F3A-BB8B-77CB4EC72B0C}" name="MATERIAL" dataDxfId="45"/>
-    <tableColumn id="5" xr3:uid="{9B2A7F84-D968-4A00-B61F-23BB0661E7A3}" name="CEMENT" dataDxfId="44"/>
-    <tableColumn id="6" xr3:uid="{2F6E5831-6238-4360-9CFD-ED23A193E761}" name="MECH_PROP" dataDxfId="43"/>
-    <tableColumn id="13" xr3:uid="{50DAB01C-8AF5-4E0C-9904-54F70B81BC55}" name="DENSITY" dataDxfId="42"/>
-    <tableColumn id="18" xr3:uid="{F799A4D4-9543-475F-989E-CFBA47249558}" name="EXPOSITIONSKLASSE" dataDxfId="41"/>
-    <tableColumn id="17" xr3:uid="{ECCBC067-991C-4C60-942D-806BCD77B990}" name="GROESSTKORN" dataDxfId="40"/>
-    <tableColumn id="16" xr3:uid="{05157B85-D5FB-4844-9B53-D8AB09BCE0D9}" name="CHLORIDGEHALT" dataDxfId="39"/>
-    <tableColumn id="15" xr3:uid="{9F53CF50-7148-405A-9295-1F0C3C45645A}" name="KONSISTENZKLASSE" dataDxfId="38"/>
-    <tableColumn id="7" xr3:uid="{E23232F6-E86E-4AD2-8257-F30C0D1F7368}" name="Total_GWP" dataDxfId="37"/>
-    <tableColumn id="20" xr3:uid="{0A9001B4-3AB4-4C58-B125-0B2AA4DB2681}" name="A1toA3_GWP" dataDxfId="36">
+    <tableColumn id="9" xr3:uid="{1DBBD25D-72F9-4A81-9CFA-500505E3628D}" name="ID" dataDxfId="41"/>
+    <tableColumn id="14" xr3:uid="{6844A52F-C967-44C0-BF5C-160C47AB6E64}" name="PRO_ID" dataDxfId="40"/>
+    <tableColumn id="12" xr3:uid="{4EDF1E73-4744-474F-8DFE-7F72FB05613C}" name="EPD_ID" dataDxfId="39"/>
+    <tableColumn id="1" xr3:uid="{1CF2E22E-1020-4F35-B31F-6350A15A5DE8}" name="SOURCE" dataDxfId="38"/>
+    <tableColumn id="27" xr3:uid="{07F74D5D-9130-4120-B02C-A11234427F46}" name="KBOB ID-Nr." dataDxfId="37"/>
+    <tableColumn id="11" xr3:uid="{81FE7F31-5F54-40F9-B99E-827E048F7DB5}" name="EPD_DATE" dataDxfId="36"/>
+    <tableColumn id="10" xr3:uid="{54D8BA04-0FEF-4C3B-9B14-59E8F982CD3F}" name="VALID_TO" dataDxfId="35"/>
+    <tableColumn id="22" xr3:uid="{3D6FC370-B8A8-40C3-9FC8-791B178DDFDF}" name="COUNTRY" dataDxfId="34"/>
+    <tableColumn id="4" xr3:uid="{25C7280F-4E3E-4E39-BDBB-DC06DF090C5B}" name="PRODUCT_NAME" dataDxfId="33"/>
+    <tableColumn id="26" xr3:uid="{1053A7DD-B11F-4E75-92EC-BC0F866E90B4}" name="OEKOBAUDAT_ID" dataDxfId="32"/>
+    <tableColumn id="25" xr3:uid="{295F99F8-E318-45C9-833E-F0B45A26471A}" name="MATERIAL_GROUP" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{1326FCEF-D1EE-4F3A-BB8B-77CB4EC72B0C}" name="MATERIAL" dataDxfId="30"/>
+    <tableColumn id="5" xr3:uid="{9B2A7F84-D968-4A00-B61F-23BB0661E7A3}" name="CEMENT" dataDxfId="29"/>
+    <tableColumn id="6" xr3:uid="{2F6E5831-6238-4360-9CFD-ED23A193E761}" name="MECH_PROP" dataDxfId="28"/>
+    <tableColumn id="13" xr3:uid="{50DAB01C-8AF5-4E0C-9904-54F70B81BC55}" name="DENSITY" dataDxfId="27"/>
+    <tableColumn id="18" xr3:uid="{F799A4D4-9543-475F-989E-CFBA47249558}" name="EXPOSITIONSKLASSE" dataDxfId="26"/>
+    <tableColumn id="17" xr3:uid="{ECCBC067-991C-4C60-942D-806BCD77B990}" name="GROESSTKORN" dataDxfId="25"/>
+    <tableColumn id="16" xr3:uid="{05157B85-D5FB-4844-9B53-D8AB09BCE0D9}" name="CHLORIDGEHALT" dataDxfId="24"/>
+    <tableColumn id="15" xr3:uid="{9F53CF50-7148-405A-9295-1F0C3C45645A}" name="KONSISTENZKLASSE" dataDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{E23232F6-E86E-4AD2-8257-F30C0D1F7368}" name="Total_GWP" dataDxfId="22"/>
+    <tableColumn id="20" xr3:uid="{0A9001B4-3AB4-4C58-B125-0B2AA4DB2681}" name="A1toA3_GWP" dataDxfId="21">
       <calculatedColumnFormula>119+10.9+238</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{2799394A-C481-45CE-B194-AAABAB0AED38}" name="C1toC4_GWP" dataDxfId="35">
+    <tableColumn id="21" xr3:uid="{2799394A-C481-45CE-B194-AAABAB0AED38}" name="C1toC4_GWP" dataDxfId="20">
       <calculatedColumnFormula>51.1+26+2.64+12.6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{70561D70-9D02-4E93-A395-229DA8696DDA}" name="ValidEPD" dataDxfId="34">
+    <tableColumn id="19" xr3:uid="{70561D70-9D02-4E93-A395-229DA8696DDA}" name="ValidEPD" dataDxfId="19">
       <calculatedColumnFormula>IF(OR($D2="Ecoinvent",$D2="Betonsortenrechner",$D2="KBOB",$T2&lt;=0),0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{92D55BC7-F55B-406A-B127-69EC2F0A8B77}" name="noch gültig" dataDxfId="33">
+    <tableColumn id="29" xr3:uid="{92D55BC7-F55B-406A-B127-69EC2F0A8B77}" name="noch gültig" dataDxfId="18">
       <calculatedColumnFormula>IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{DB90AC0A-8933-4040-BADE-E6EE11AC8BD7}" name="Statistik" dataDxfId="32">
+    <tableColumn id="3" xr3:uid="{DB90AC0A-8933-4040-BADE-E6EE11AC8BD7}" name="Statistik" dataDxfId="17">
       <calculatedColumnFormula array="1">IF($W2&lt;&gt;0,
 IF(AND(
                          T2&gt;=_xlfn.PERCENTILE.INC(_xlfn._xlws.FILTER($T$2:$T$148, ($L$2:$L$148=L2)*($W$2:$W$148=1)),0.1),
@@ -4174,29 +4178,29 @@
                ),1,0),
 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{BBA6C134-63F9-4711-8B25-086098EC2CB0}" name="Cost" dataDxfId="31"/>
-    <tableColumn id="24" xr3:uid="{5321A0E1-043C-4E95-A6DA-41830364B2BC}" name="Anmerkung" dataDxfId="30"/>
-    <tableColumn id="23" xr3:uid="{61456234-34E8-4222-B2D6-9DDA8E83B081}" name="Spalte 1" dataDxfId="29"/>
-    <tableColumn id="28" xr3:uid="{D1FC9AF8-A0AE-CE49-8F27-4BB569415BF3}" name="T_construction" dataDxfId="28"/>
+    <tableColumn id="8" xr3:uid="{BBA6C134-63F9-4711-8B25-086098EC2CB0}" name="Cost" dataDxfId="16"/>
+    <tableColumn id="24" xr3:uid="{5321A0E1-043C-4E95-A6DA-41830364B2BC}" name="Anmerkung" dataDxfId="15"/>
+    <tableColumn id="23" xr3:uid="{61456234-34E8-4222-B2D6-9DDA8E83B081}" name="Spalte 1" dataDxfId="14"/>
+    <tableColumn id="28" xr3:uid="{D1FC9AF8-A0AE-CE49-8F27-4BB569415BF3}" name="T_construction" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}" name="Tabelle4" displayName="Tabelle4" ref="A1:J8" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
-  <autoFilter ref="A1:J8" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}" name="Tabelle4" displayName="Tabelle4" ref="A1:J9" totalsRowShown="0" headerRowDxfId="58" dataDxfId="56" headerRowBorderDxfId="57" tableBorderDxfId="55" totalsRowBorderDxfId="54">
+  <autoFilter ref="A1:J9" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{AF3C694B-2C8A-40EE-B8BB-2EC9EB81A87A}" name="mat_ID" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{B447FBC2-C455-4332-8F47-150B112A57E0}" name="name" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{BAFC6B47-7268-46CC-A881-892C9A1F4334}" name="strength_comp" dataDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{6FC4C8EB-7581-4E67-81CE-C724161F0838}" name="strength_tens" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{A875970E-61A9-43B5-9361-7616A74C3147}" name="strength_bend" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{EF5B3A69-DD70-420A-88FF-4FE8772A2E14}" name="strength_shea" dataDxfId="17"/>
-    <tableColumn id="7" xr3:uid="{ED461A80-736C-42BD-81BC-C5C0C80FF34C}" name="E_modulus" dataDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{68E47481-7028-4427-B126-2A046FC46737}" name="density_load" dataDxfId="15"/>
-    <tableColumn id="9" xr3:uid="{7AB34570-2BD4-417F-B141-70612577C7D6}" name="burn_rate" dataDxfId="14"/>
-    <tableColumn id="10" xr3:uid="{69298654-E280-9D4B-9717-7904FADC15B5}" name="phi" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{AF3C694B-2C8A-40EE-B8BB-2EC9EB81A87A}" name="mat_ID" dataDxfId="53"/>
+    <tableColumn id="2" xr3:uid="{B447FBC2-C455-4332-8F47-150B112A57E0}" name="name" dataDxfId="52"/>
+    <tableColumn id="3" xr3:uid="{BAFC6B47-7268-46CC-A881-892C9A1F4334}" name="strength_comp" dataDxfId="51"/>
+    <tableColumn id="4" xr3:uid="{6FC4C8EB-7581-4E67-81CE-C724161F0838}" name="strength_tens" dataDxfId="50"/>
+    <tableColumn id="5" xr3:uid="{A875970E-61A9-43B5-9361-7616A74C3147}" name="strength_bend" dataDxfId="49"/>
+    <tableColumn id="6" xr3:uid="{EF5B3A69-DD70-420A-88FF-4FE8772A2E14}" name="strength_shea" dataDxfId="48"/>
+    <tableColumn id="7" xr3:uid="{ED461A80-736C-42BD-81BC-C5C0C80FF34C}" name="E_modulus" dataDxfId="47"/>
+    <tableColumn id="8" xr3:uid="{68E47481-7028-4427-B126-2A046FC46737}" name="density_load" dataDxfId="46"/>
+    <tableColumn id="9" xr3:uid="{7AB34570-2BD4-417F-B141-70612577C7D6}" name="burn_rate" dataDxfId="45"/>
+    <tableColumn id="10" xr3:uid="{69298654-E280-9D4B-9717-7904FADC15B5}" name="phi" dataDxfId="44"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -15843,7 +15847,9 @@
       <c r="M122" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="N122" s="26"/>
+      <c r="N122" s="26" t="s">
+        <v>524</v>
+      </c>
       <c r="O122" s="26"/>
       <c r="P122" s="3"/>
       <c r="Q122" s="3"/>
@@ -15928,7 +15934,9 @@
       <c r="M123" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="N123" s="26"/>
+      <c r="N123" s="26" t="s">
+        <v>524</v>
+      </c>
       <c r="O123" s="26"/>
       <c r="P123" s="3"/>
       <c r="Q123" s="3"/>
@@ -16011,7 +16019,9 @@
       <c r="M124" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="N124" s="26"/>
+      <c r="N124" s="26" t="s">
+        <v>524</v>
+      </c>
       <c r="O124" s="26"/>
       <c r="P124" s="3"/>
       <c r="Q124" s="3"/>
@@ -16096,7 +16106,9 @@
       <c r="M125" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="N125" s="26"/>
+      <c r="N125" s="26" t="s">
+        <v>524</v>
+      </c>
       <c r="O125" s="26"/>
       <c r="P125" s="3"/>
       <c r="Q125" s="3"/>
@@ -16182,7 +16194,9 @@
       <c r="M126" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="N126" s="26"/>
+      <c r="N126" s="26" t="s">
+        <v>524</v>
+      </c>
       <c r="O126" s="26"/>
       <c r="P126" s="3"/>
       <c r="Q126" s="3"/>
@@ -16266,7 +16280,9 @@
       <c r="M127" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="N127" s="26"/>
+      <c r="N127" s="26" t="s">
+        <v>524</v>
+      </c>
       <c r="O127" s="26"/>
       <c r="P127" s="3"/>
       <c r="Q127" s="3"/>
@@ -16348,7 +16364,9 @@
       <c r="M128" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="N128" s="26"/>
+      <c r="N128" s="26" t="s">
+        <v>524</v>
+      </c>
       <c r="O128" s="26"/>
       <c r="P128" s="3"/>
       <c r="Q128" s="3"/>
@@ -16431,7 +16449,9 @@
       <c r="M129" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="N129" s="26"/>
+      <c r="N129" s="26" t="s">
+        <v>524</v>
+      </c>
       <c r="O129" s="26"/>
       <c r="P129" s="3"/>
       <c r="Q129" s="3"/>
@@ -16514,7 +16534,9 @@
       <c r="M130" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="N130" s="29"/>
+      <c r="N130" s="29" t="s">
+        <v>524</v>
+      </c>
       <c r="O130" s="29"/>
       <c r="P130" s="5"/>
       <c r="Q130" s="5"/>
@@ -16788,7 +16810,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{067AEC17-54D0-422B-913B-12777967F81E}">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.83203125" bestFit="1" customWidth="1"/>
@@ -17016,6 +17038,26 @@
       <c r="J8" s="62">
         <v>0.6</v>
       </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="62">
+        <v>8</v>
+      </c>
+      <c r="B9" s="62" t="s">
+        <v>524</v>
+      </c>
+      <c r="C9" s="62"/>
+      <c r="D9" s="62">
+        <v>1600000000</v>
+      </c>
+      <c r="E9" s="62"/>
+      <c r="F9" s="62"/>
+      <c r="G9" s="211">
+        <v>195000000000</v>
+      </c>
+      <c r="H9" s="62"/>
+      <c r="I9" s="62"/>
+      <c r="J9" s="62"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Database/260126_Datenbankdefinition.xlsx
+++ b/Database/260126_Datenbankdefinition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonathanbieg/Documents/Master Thesis/1_Code/Python Repository/SDSD_Bieg/Database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A0D5814-88E2-FF43-84D8-35F857464BF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D943D0A5-A188-A14A-B5BD-62BE563A0ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17160" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17160" activeTab="1" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
   </bookViews>
   <sheets>
     <sheet name="products" sheetId="1" r:id="rId1"/>
@@ -3012,6 +3012,422 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -3649,422 +4065,6 @@
       </font>
       <alignment vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -4135,42 +4135,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}" name="Table2" displayName="Table2" ref="A1:AC132" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}" name="Table2" displayName="Table2" ref="A1:AC132" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57">
   <autoFilter ref="A1:AC132" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}"/>
   <tableColumns count="29">
-    <tableColumn id="9" xr3:uid="{1DBBD25D-72F9-4A81-9CFA-500505E3628D}" name="ID" dataDxfId="41"/>
-    <tableColumn id="14" xr3:uid="{6844A52F-C967-44C0-BF5C-160C47AB6E64}" name="PRO_ID" dataDxfId="40"/>
-    <tableColumn id="12" xr3:uid="{4EDF1E73-4744-474F-8DFE-7F72FB05613C}" name="EPD_ID" dataDxfId="39"/>
-    <tableColumn id="1" xr3:uid="{1CF2E22E-1020-4F35-B31F-6350A15A5DE8}" name="SOURCE" dataDxfId="38"/>
-    <tableColumn id="27" xr3:uid="{07F74D5D-9130-4120-B02C-A11234427F46}" name="KBOB ID-Nr." dataDxfId="37"/>
-    <tableColumn id="11" xr3:uid="{81FE7F31-5F54-40F9-B99E-827E048F7DB5}" name="EPD_DATE" dataDxfId="36"/>
-    <tableColumn id="10" xr3:uid="{54D8BA04-0FEF-4C3B-9B14-59E8F982CD3F}" name="VALID_TO" dataDxfId="35"/>
-    <tableColumn id="22" xr3:uid="{3D6FC370-B8A8-40C3-9FC8-791B178DDFDF}" name="COUNTRY" dataDxfId="34"/>
-    <tableColumn id="4" xr3:uid="{25C7280F-4E3E-4E39-BDBB-DC06DF090C5B}" name="PRODUCT_NAME" dataDxfId="33"/>
-    <tableColumn id="26" xr3:uid="{1053A7DD-B11F-4E75-92EC-BC0F866E90B4}" name="OEKOBAUDAT_ID" dataDxfId="32"/>
-    <tableColumn id="25" xr3:uid="{295F99F8-E318-45C9-833E-F0B45A26471A}" name="MATERIAL_GROUP" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{1326FCEF-D1EE-4F3A-BB8B-77CB4EC72B0C}" name="MATERIAL" dataDxfId="30"/>
-    <tableColumn id="5" xr3:uid="{9B2A7F84-D968-4A00-B61F-23BB0661E7A3}" name="CEMENT" dataDxfId="29"/>
-    <tableColumn id="6" xr3:uid="{2F6E5831-6238-4360-9CFD-ED23A193E761}" name="MECH_PROP" dataDxfId="28"/>
-    <tableColumn id="13" xr3:uid="{50DAB01C-8AF5-4E0C-9904-54F70B81BC55}" name="DENSITY" dataDxfId="27"/>
-    <tableColumn id="18" xr3:uid="{F799A4D4-9543-475F-989E-CFBA47249558}" name="EXPOSITIONSKLASSE" dataDxfId="26"/>
-    <tableColumn id="17" xr3:uid="{ECCBC067-991C-4C60-942D-806BCD77B990}" name="GROESSTKORN" dataDxfId="25"/>
-    <tableColumn id="16" xr3:uid="{05157B85-D5FB-4844-9B53-D8AB09BCE0D9}" name="CHLORIDGEHALT" dataDxfId="24"/>
-    <tableColumn id="15" xr3:uid="{9F53CF50-7148-405A-9295-1F0C3C45645A}" name="KONSISTENZKLASSE" dataDxfId="23"/>
-    <tableColumn id="7" xr3:uid="{E23232F6-E86E-4AD2-8257-F30C0D1F7368}" name="Total_GWP" dataDxfId="22"/>
-    <tableColumn id="20" xr3:uid="{0A9001B4-3AB4-4C58-B125-0B2AA4DB2681}" name="A1toA3_GWP" dataDxfId="21">
+    <tableColumn id="9" xr3:uid="{1DBBD25D-72F9-4A81-9CFA-500505E3628D}" name="ID" dataDxfId="56"/>
+    <tableColumn id="14" xr3:uid="{6844A52F-C967-44C0-BF5C-160C47AB6E64}" name="PRO_ID" dataDxfId="55"/>
+    <tableColumn id="12" xr3:uid="{4EDF1E73-4744-474F-8DFE-7F72FB05613C}" name="EPD_ID" dataDxfId="54"/>
+    <tableColumn id="1" xr3:uid="{1CF2E22E-1020-4F35-B31F-6350A15A5DE8}" name="SOURCE" dataDxfId="53"/>
+    <tableColumn id="27" xr3:uid="{07F74D5D-9130-4120-B02C-A11234427F46}" name="KBOB ID-Nr." dataDxfId="52"/>
+    <tableColumn id="11" xr3:uid="{81FE7F31-5F54-40F9-B99E-827E048F7DB5}" name="EPD_DATE" dataDxfId="51"/>
+    <tableColumn id="10" xr3:uid="{54D8BA04-0FEF-4C3B-9B14-59E8F982CD3F}" name="VALID_TO" dataDxfId="50"/>
+    <tableColumn id="22" xr3:uid="{3D6FC370-B8A8-40C3-9FC8-791B178DDFDF}" name="COUNTRY" dataDxfId="49"/>
+    <tableColumn id="4" xr3:uid="{25C7280F-4E3E-4E39-BDBB-DC06DF090C5B}" name="PRODUCT_NAME" dataDxfId="48"/>
+    <tableColumn id="26" xr3:uid="{1053A7DD-B11F-4E75-92EC-BC0F866E90B4}" name="OEKOBAUDAT_ID" dataDxfId="47"/>
+    <tableColumn id="25" xr3:uid="{295F99F8-E318-45C9-833E-F0B45A26471A}" name="MATERIAL_GROUP" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{1326FCEF-D1EE-4F3A-BB8B-77CB4EC72B0C}" name="MATERIAL" dataDxfId="45"/>
+    <tableColumn id="5" xr3:uid="{9B2A7F84-D968-4A00-B61F-23BB0661E7A3}" name="CEMENT" dataDxfId="44"/>
+    <tableColumn id="6" xr3:uid="{2F6E5831-6238-4360-9CFD-ED23A193E761}" name="MECH_PROP" dataDxfId="43"/>
+    <tableColumn id="13" xr3:uid="{50DAB01C-8AF5-4E0C-9904-54F70B81BC55}" name="DENSITY" dataDxfId="42"/>
+    <tableColumn id="18" xr3:uid="{F799A4D4-9543-475F-989E-CFBA47249558}" name="EXPOSITIONSKLASSE" dataDxfId="41"/>
+    <tableColumn id="17" xr3:uid="{ECCBC067-991C-4C60-942D-806BCD77B990}" name="GROESSTKORN" dataDxfId="40"/>
+    <tableColumn id="16" xr3:uid="{05157B85-D5FB-4844-9B53-D8AB09BCE0D9}" name="CHLORIDGEHALT" dataDxfId="39"/>
+    <tableColumn id="15" xr3:uid="{9F53CF50-7148-405A-9295-1F0C3C45645A}" name="KONSISTENZKLASSE" dataDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{E23232F6-E86E-4AD2-8257-F30C0D1F7368}" name="Total_GWP" dataDxfId="37"/>
+    <tableColumn id="20" xr3:uid="{0A9001B4-3AB4-4C58-B125-0B2AA4DB2681}" name="A1toA3_GWP" dataDxfId="36">
       <calculatedColumnFormula>119+10.9+238</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{2799394A-C481-45CE-B194-AAABAB0AED38}" name="C1toC4_GWP" dataDxfId="20">
+    <tableColumn id="21" xr3:uid="{2799394A-C481-45CE-B194-AAABAB0AED38}" name="C1toC4_GWP" dataDxfId="35">
       <calculatedColumnFormula>51.1+26+2.64+12.6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{70561D70-9D02-4E93-A395-229DA8696DDA}" name="ValidEPD" dataDxfId="19">
+    <tableColumn id="19" xr3:uid="{70561D70-9D02-4E93-A395-229DA8696DDA}" name="ValidEPD" dataDxfId="34">
       <calculatedColumnFormula>IF(OR($D2="Ecoinvent",$D2="Betonsortenrechner",$D2="KBOB",$T2&lt;=0),0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{92D55BC7-F55B-406A-B127-69EC2F0A8B77}" name="noch gültig" dataDxfId="18">
+    <tableColumn id="29" xr3:uid="{92D55BC7-F55B-406A-B127-69EC2F0A8B77}" name="noch gültig" dataDxfId="33">
       <calculatedColumnFormula>IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{DB90AC0A-8933-4040-BADE-E6EE11AC8BD7}" name="Statistik" dataDxfId="17">
+    <tableColumn id="3" xr3:uid="{DB90AC0A-8933-4040-BADE-E6EE11AC8BD7}" name="Statistik" dataDxfId="32">
       <calculatedColumnFormula array="1">IF($W2&lt;&gt;0,
 IF(AND(
                          T2&gt;=_xlfn.PERCENTILE.INC(_xlfn._xlws.FILTER($T$2:$T$148, ($L$2:$L$148=L2)*($W$2:$W$148=1)),0.1),
@@ -4178,29 +4178,29 @@
                ),1,0),
 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{BBA6C134-63F9-4711-8B25-086098EC2CB0}" name="Cost" dataDxfId="16"/>
-    <tableColumn id="24" xr3:uid="{5321A0E1-043C-4E95-A6DA-41830364B2BC}" name="Anmerkung" dataDxfId="15"/>
-    <tableColumn id="23" xr3:uid="{61456234-34E8-4222-B2D6-9DDA8E83B081}" name="Spalte 1" dataDxfId="14"/>
-    <tableColumn id="28" xr3:uid="{D1FC9AF8-A0AE-CE49-8F27-4BB569415BF3}" name="T_construction" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{BBA6C134-63F9-4711-8B25-086098EC2CB0}" name="Cost" dataDxfId="31"/>
+    <tableColumn id="24" xr3:uid="{5321A0E1-043C-4E95-A6DA-41830364B2BC}" name="Anmerkung" dataDxfId="30"/>
+    <tableColumn id="23" xr3:uid="{61456234-34E8-4222-B2D6-9DDA8E83B081}" name="Spalte 1" dataDxfId="29"/>
+    <tableColumn id="28" xr3:uid="{D1FC9AF8-A0AE-CE49-8F27-4BB569415BF3}" name="T_construction" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}" name="Tabelle4" displayName="Tabelle4" ref="A1:J9" totalsRowShown="0" headerRowDxfId="58" dataDxfId="56" headerRowBorderDxfId="57" tableBorderDxfId="55" totalsRowBorderDxfId="54">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}" name="Tabelle4" displayName="Tabelle4" ref="A1:J9" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
   <autoFilter ref="A1:J9" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{AF3C694B-2C8A-40EE-B8BB-2EC9EB81A87A}" name="mat_ID" dataDxfId="53"/>
-    <tableColumn id="2" xr3:uid="{B447FBC2-C455-4332-8F47-150B112A57E0}" name="name" dataDxfId="52"/>
-    <tableColumn id="3" xr3:uid="{BAFC6B47-7268-46CC-A881-892C9A1F4334}" name="strength_comp" dataDxfId="51"/>
-    <tableColumn id="4" xr3:uid="{6FC4C8EB-7581-4E67-81CE-C724161F0838}" name="strength_tens" dataDxfId="50"/>
-    <tableColumn id="5" xr3:uid="{A875970E-61A9-43B5-9361-7616A74C3147}" name="strength_bend" dataDxfId="49"/>
-    <tableColumn id="6" xr3:uid="{EF5B3A69-DD70-420A-88FF-4FE8772A2E14}" name="strength_shea" dataDxfId="48"/>
-    <tableColumn id="7" xr3:uid="{ED461A80-736C-42BD-81BC-C5C0C80FF34C}" name="E_modulus" dataDxfId="47"/>
-    <tableColumn id="8" xr3:uid="{68E47481-7028-4427-B126-2A046FC46737}" name="density_load" dataDxfId="46"/>
-    <tableColumn id="9" xr3:uid="{7AB34570-2BD4-417F-B141-70612577C7D6}" name="burn_rate" dataDxfId="45"/>
-    <tableColumn id="10" xr3:uid="{69298654-E280-9D4B-9717-7904FADC15B5}" name="phi" dataDxfId="44"/>
+    <tableColumn id="1" xr3:uid="{AF3C694B-2C8A-40EE-B8BB-2EC9EB81A87A}" name="mat_ID" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{B447FBC2-C455-4332-8F47-150B112A57E0}" name="name" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{BAFC6B47-7268-46CC-A881-892C9A1F4334}" name="strength_comp" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{6FC4C8EB-7581-4E67-81CE-C724161F0838}" name="strength_tens" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{A875970E-61A9-43B5-9361-7616A74C3147}" name="strength_bend" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{EF5B3A69-DD70-420A-88FF-4FE8772A2E14}" name="strength_shea" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{ED461A80-736C-42BD-81BC-C5C0C80FF34C}" name="E_modulus" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{68E47481-7028-4427-B126-2A046FC46737}" name="density_load" dataDxfId="15"/>
+    <tableColumn id="9" xr3:uid="{7AB34570-2BD4-417F-B141-70612577C7D6}" name="burn_rate" dataDxfId="14"/>
+    <tableColumn id="10" xr3:uid="{69298654-E280-9D4B-9717-7904FADC15B5}" name="phi" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -17048,7 +17048,7 @@
       </c>
       <c r="C9" s="62"/>
       <c r="D9" s="62">
-        <v>1600000000</v>
+        <v>1860000000</v>
       </c>
       <c r="E9" s="62"/>
       <c r="F9" s="62"/>

--- a/Database/260126_Datenbankdefinition.xlsx
+++ b/Database/260126_Datenbankdefinition.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -3012,422 +3012,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -4065,6 +3649,422 @@
       </font>
       <alignment vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -4135,42 +4135,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}" name="Table2" displayName="Table2" ref="A1:AC132" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}" name="Table2" displayName="Table2" ref="A1:AC132" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42">
   <autoFilter ref="A1:AC132" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}"/>
   <tableColumns count="29">
-    <tableColumn id="9" xr3:uid="{1DBBD25D-72F9-4A81-9CFA-500505E3628D}" name="ID" dataDxfId="56"/>
-    <tableColumn id="14" xr3:uid="{6844A52F-C967-44C0-BF5C-160C47AB6E64}" name="PRO_ID" dataDxfId="55"/>
-    <tableColumn id="12" xr3:uid="{4EDF1E73-4744-474F-8DFE-7F72FB05613C}" name="EPD_ID" dataDxfId="54"/>
-    <tableColumn id="1" xr3:uid="{1CF2E22E-1020-4F35-B31F-6350A15A5DE8}" name="SOURCE" dataDxfId="53"/>
-    <tableColumn id="27" xr3:uid="{07F74D5D-9130-4120-B02C-A11234427F46}" name="KBOB ID-Nr." dataDxfId="52"/>
-    <tableColumn id="11" xr3:uid="{81FE7F31-5F54-40F9-B99E-827E048F7DB5}" name="EPD_DATE" dataDxfId="51"/>
-    <tableColumn id="10" xr3:uid="{54D8BA04-0FEF-4C3B-9B14-59E8F982CD3F}" name="VALID_TO" dataDxfId="50"/>
-    <tableColumn id="22" xr3:uid="{3D6FC370-B8A8-40C3-9FC8-791B178DDFDF}" name="COUNTRY" dataDxfId="49"/>
-    <tableColumn id="4" xr3:uid="{25C7280F-4E3E-4E39-BDBB-DC06DF090C5B}" name="PRODUCT_NAME" dataDxfId="48"/>
-    <tableColumn id="26" xr3:uid="{1053A7DD-B11F-4E75-92EC-BC0F866E90B4}" name="OEKOBAUDAT_ID" dataDxfId="47"/>
-    <tableColumn id="25" xr3:uid="{295F99F8-E318-45C9-833E-F0B45A26471A}" name="MATERIAL_GROUP" dataDxfId="46"/>
-    <tableColumn id="2" xr3:uid="{1326FCEF-D1EE-4F3A-BB8B-77CB4EC72B0C}" name="MATERIAL" dataDxfId="45"/>
-    <tableColumn id="5" xr3:uid="{9B2A7F84-D968-4A00-B61F-23BB0661E7A3}" name="CEMENT" dataDxfId="44"/>
-    <tableColumn id="6" xr3:uid="{2F6E5831-6238-4360-9CFD-ED23A193E761}" name="MECH_PROP" dataDxfId="43"/>
-    <tableColumn id="13" xr3:uid="{50DAB01C-8AF5-4E0C-9904-54F70B81BC55}" name="DENSITY" dataDxfId="42"/>
-    <tableColumn id="18" xr3:uid="{F799A4D4-9543-475F-989E-CFBA47249558}" name="EXPOSITIONSKLASSE" dataDxfId="41"/>
-    <tableColumn id="17" xr3:uid="{ECCBC067-991C-4C60-942D-806BCD77B990}" name="GROESSTKORN" dataDxfId="40"/>
-    <tableColumn id="16" xr3:uid="{05157B85-D5FB-4844-9B53-D8AB09BCE0D9}" name="CHLORIDGEHALT" dataDxfId="39"/>
-    <tableColumn id="15" xr3:uid="{9F53CF50-7148-405A-9295-1F0C3C45645A}" name="KONSISTENZKLASSE" dataDxfId="38"/>
-    <tableColumn id="7" xr3:uid="{E23232F6-E86E-4AD2-8257-F30C0D1F7368}" name="Total_GWP" dataDxfId="37"/>
-    <tableColumn id="20" xr3:uid="{0A9001B4-3AB4-4C58-B125-0B2AA4DB2681}" name="A1toA3_GWP" dataDxfId="36">
+    <tableColumn id="9" xr3:uid="{1DBBD25D-72F9-4A81-9CFA-500505E3628D}" name="ID" dataDxfId="41"/>
+    <tableColumn id="14" xr3:uid="{6844A52F-C967-44C0-BF5C-160C47AB6E64}" name="PRO_ID" dataDxfId="40"/>
+    <tableColumn id="12" xr3:uid="{4EDF1E73-4744-474F-8DFE-7F72FB05613C}" name="EPD_ID" dataDxfId="39"/>
+    <tableColumn id="1" xr3:uid="{1CF2E22E-1020-4F35-B31F-6350A15A5DE8}" name="SOURCE" dataDxfId="38"/>
+    <tableColumn id="27" xr3:uid="{07F74D5D-9130-4120-B02C-A11234427F46}" name="KBOB ID-Nr." dataDxfId="37"/>
+    <tableColumn id="11" xr3:uid="{81FE7F31-5F54-40F9-B99E-827E048F7DB5}" name="EPD_DATE" dataDxfId="36"/>
+    <tableColumn id="10" xr3:uid="{54D8BA04-0FEF-4C3B-9B14-59E8F982CD3F}" name="VALID_TO" dataDxfId="35"/>
+    <tableColumn id="22" xr3:uid="{3D6FC370-B8A8-40C3-9FC8-791B178DDFDF}" name="COUNTRY" dataDxfId="34"/>
+    <tableColumn id="4" xr3:uid="{25C7280F-4E3E-4E39-BDBB-DC06DF090C5B}" name="PRODUCT_NAME" dataDxfId="33"/>
+    <tableColumn id="26" xr3:uid="{1053A7DD-B11F-4E75-92EC-BC0F866E90B4}" name="OEKOBAUDAT_ID" dataDxfId="32"/>
+    <tableColumn id="25" xr3:uid="{295F99F8-E318-45C9-833E-F0B45A26471A}" name="MATERIAL_GROUP" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{1326FCEF-D1EE-4F3A-BB8B-77CB4EC72B0C}" name="MATERIAL" dataDxfId="30"/>
+    <tableColumn id="5" xr3:uid="{9B2A7F84-D968-4A00-B61F-23BB0661E7A3}" name="CEMENT" dataDxfId="29"/>
+    <tableColumn id="6" xr3:uid="{2F6E5831-6238-4360-9CFD-ED23A193E761}" name="MECH_PROP" dataDxfId="28"/>
+    <tableColumn id="13" xr3:uid="{50DAB01C-8AF5-4E0C-9904-54F70B81BC55}" name="DENSITY" dataDxfId="27"/>
+    <tableColumn id="18" xr3:uid="{F799A4D4-9543-475F-989E-CFBA47249558}" name="EXPOSITIONSKLASSE" dataDxfId="26"/>
+    <tableColumn id="17" xr3:uid="{ECCBC067-991C-4C60-942D-806BCD77B990}" name="GROESSTKORN" dataDxfId="25"/>
+    <tableColumn id="16" xr3:uid="{05157B85-D5FB-4844-9B53-D8AB09BCE0D9}" name="CHLORIDGEHALT" dataDxfId="24"/>
+    <tableColumn id="15" xr3:uid="{9F53CF50-7148-405A-9295-1F0C3C45645A}" name="KONSISTENZKLASSE" dataDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{E23232F6-E86E-4AD2-8257-F30C0D1F7368}" name="Total_GWP" dataDxfId="22"/>
+    <tableColumn id="20" xr3:uid="{0A9001B4-3AB4-4C58-B125-0B2AA4DB2681}" name="A1toA3_GWP" dataDxfId="21">
       <calculatedColumnFormula>119+10.9+238</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{2799394A-C481-45CE-B194-AAABAB0AED38}" name="C1toC4_GWP" dataDxfId="35">
+    <tableColumn id="21" xr3:uid="{2799394A-C481-45CE-B194-AAABAB0AED38}" name="C1toC4_GWP" dataDxfId="20">
       <calculatedColumnFormula>51.1+26+2.64+12.6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{70561D70-9D02-4E93-A395-229DA8696DDA}" name="ValidEPD" dataDxfId="34">
+    <tableColumn id="19" xr3:uid="{70561D70-9D02-4E93-A395-229DA8696DDA}" name="ValidEPD" dataDxfId="19">
       <calculatedColumnFormula>IF(OR($D2="Ecoinvent",$D2="Betonsortenrechner",$D2="KBOB",$T2&lt;=0),0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{92D55BC7-F55B-406A-B127-69EC2F0A8B77}" name="noch gültig" dataDxfId="33">
+    <tableColumn id="29" xr3:uid="{92D55BC7-F55B-406A-B127-69EC2F0A8B77}" name="noch gültig" dataDxfId="18">
       <calculatedColumnFormula>IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{DB90AC0A-8933-4040-BADE-E6EE11AC8BD7}" name="Statistik" dataDxfId="32">
+    <tableColumn id="3" xr3:uid="{DB90AC0A-8933-4040-BADE-E6EE11AC8BD7}" name="Statistik" dataDxfId="17">
       <calculatedColumnFormula array="1">IF($W2&lt;&gt;0,
 IF(AND(
                          T2&gt;=_xlfn.PERCENTILE.INC(_xlfn._xlws.FILTER($T$2:$T$148, ($L$2:$L$148=L2)*($W$2:$W$148=1)),0.1),
@@ -4178,29 +4178,29 @@
                ),1,0),
 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{BBA6C134-63F9-4711-8B25-086098EC2CB0}" name="Cost" dataDxfId="31"/>
-    <tableColumn id="24" xr3:uid="{5321A0E1-043C-4E95-A6DA-41830364B2BC}" name="Anmerkung" dataDxfId="30"/>
-    <tableColumn id="23" xr3:uid="{61456234-34E8-4222-B2D6-9DDA8E83B081}" name="Spalte 1" dataDxfId="29"/>
-    <tableColumn id="28" xr3:uid="{D1FC9AF8-A0AE-CE49-8F27-4BB569415BF3}" name="T_construction" dataDxfId="28"/>
+    <tableColumn id="8" xr3:uid="{BBA6C134-63F9-4711-8B25-086098EC2CB0}" name="Cost" dataDxfId="16"/>
+    <tableColumn id="24" xr3:uid="{5321A0E1-043C-4E95-A6DA-41830364B2BC}" name="Anmerkung" dataDxfId="15"/>
+    <tableColumn id="23" xr3:uid="{61456234-34E8-4222-B2D6-9DDA8E83B081}" name="Spalte 1" dataDxfId="14"/>
+    <tableColumn id="28" xr3:uid="{D1FC9AF8-A0AE-CE49-8F27-4BB569415BF3}" name="T_construction" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}" name="Tabelle4" displayName="Tabelle4" ref="A1:J9" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}" name="Tabelle4" displayName="Tabelle4" ref="A1:J9" totalsRowShown="0" headerRowDxfId="58" dataDxfId="56" headerRowBorderDxfId="57" tableBorderDxfId="55" totalsRowBorderDxfId="54">
   <autoFilter ref="A1:J9" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{AF3C694B-2C8A-40EE-B8BB-2EC9EB81A87A}" name="mat_ID" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{B447FBC2-C455-4332-8F47-150B112A57E0}" name="name" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{BAFC6B47-7268-46CC-A881-892C9A1F4334}" name="strength_comp" dataDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{6FC4C8EB-7581-4E67-81CE-C724161F0838}" name="strength_tens" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{A875970E-61A9-43B5-9361-7616A74C3147}" name="strength_bend" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{EF5B3A69-DD70-420A-88FF-4FE8772A2E14}" name="strength_shea" dataDxfId="17"/>
-    <tableColumn id="7" xr3:uid="{ED461A80-736C-42BD-81BC-C5C0C80FF34C}" name="E_modulus" dataDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{68E47481-7028-4427-B126-2A046FC46737}" name="density_load" dataDxfId="15"/>
-    <tableColumn id="9" xr3:uid="{7AB34570-2BD4-417F-B141-70612577C7D6}" name="burn_rate" dataDxfId="14"/>
-    <tableColumn id="10" xr3:uid="{69298654-E280-9D4B-9717-7904FADC15B5}" name="phi" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{AF3C694B-2C8A-40EE-B8BB-2EC9EB81A87A}" name="mat_ID" dataDxfId="53"/>
+    <tableColumn id="2" xr3:uid="{B447FBC2-C455-4332-8F47-150B112A57E0}" name="name" dataDxfId="52"/>
+    <tableColumn id="3" xr3:uid="{BAFC6B47-7268-46CC-A881-892C9A1F4334}" name="strength_comp" dataDxfId="51"/>
+    <tableColumn id="4" xr3:uid="{6FC4C8EB-7581-4E67-81CE-C724161F0838}" name="strength_tens" dataDxfId="50"/>
+    <tableColumn id="5" xr3:uid="{A875970E-61A9-43B5-9361-7616A74C3147}" name="strength_bend" dataDxfId="49"/>
+    <tableColumn id="6" xr3:uid="{EF5B3A69-DD70-420A-88FF-4FE8772A2E14}" name="strength_shea" dataDxfId="48"/>
+    <tableColumn id="7" xr3:uid="{ED461A80-736C-42BD-81BC-C5C0C80FF34C}" name="E_modulus" dataDxfId="47"/>
+    <tableColumn id="8" xr3:uid="{68E47481-7028-4427-B126-2A046FC46737}" name="density_load" dataDxfId="46"/>
+    <tableColumn id="9" xr3:uid="{7AB34570-2BD4-417F-B141-70612577C7D6}" name="burn_rate" dataDxfId="45"/>
+    <tableColumn id="10" xr3:uid="{69298654-E280-9D4B-9717-7904FADC15B5}" name="phi" dataDxfId="44"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8569,7 +8569,7 @@
                          T45&lt;=_xlfn.PERCENTILE.INC(_xlfn._xlws.FILTER($T$2:$T$148, ($L$2:$L$148=L45)*($W$2:$W$148=1)),0.9)
                ),1,0),
 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z45" s="207">
         <f>2.01*Table2[[#This Row],[DENSITY]]</f>
@@ -9142,7 +9142,7 @@
                          T51&lt;=_xlfn.PERCENTILE.INC(_xlfn._xlws.FILTER($T$2:$T$148, ($L$2:$L$148=L51)*($W$2:$W$148=1)),0.9)
                ),1,0),
 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z51" s="207">
         <f>2.01*Table2[[#This Row],[DENSITY]]</f>
@@ -9320,11 +9320,11 @@
       </c>
       <c r="W53" s="50">
         <f ca="1">IF(OR($D53="Ecoinvent",$D53="Betonsortenrechner",$D53="KBOB",$T53&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X53" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y53" s="150" cm="1">
         <f t="array" aca="1" ref="Y53" ca="1">IF($W53&lt;&gt;0,
@@ -9415,11 +9415,11 @@
       </c>
       <c r="W54" s="50">
         <f ca="1">IF(OR($D54="Ecoinvent",$D54="Betonsortenrechner",$D54="KBOB",$T54&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X54" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y54" s="150" cm="1">
         <f t="array" aca="1" ref="Y54" ca="1">IF($W54&lt;&gt;0,
@@ -13783,11 +13783,11 @@
       </c>
       <c r="W100" s="50">
         <f ca="1">IF(OR($D100="Ecoinvent",$D100="Betonsortenrechner",$D100="KBOB",$T100&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X100" s="198">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y100" s="150" cm="1">
         <f t="array" aca="1" ref="Y100" ca="1">IF($W100&lt;&gt;0,
@@ -13796,7 +13796,7 @@
                          T100&lt;=_xlfn.PERCENTILE.INC(_xlfn._xlws.FILTER($T$2:$T$148, ($K$3:$K$149=K100)*($W$2:$W$148=1)),0.9)
                ),1,0),
 0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z100" s="206">
         <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>

--- a/Database/260126_Datenbankdefinition.xlsx
+++ b/Database/260126_Datenbankdefinition.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonathanbieg/Documents/Master Thesis/1_Code/Python Repository/SDSD_Bieg/Database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D943D0A5-A188-A14A-B5BD-62BE563A0ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03CE3E68-0469-A74A-BDA0-BB8187620FEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17160" activeTab="1" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
   </bookViews>
@@ -16951,7 +16951,9 @@
       <c r="G5" s="56">
         <v>205000000000</v>
       </c>
-      <c r="H5" s="56"/>
+      <c r="H5" s="56">
+        <v>78500</v>
+      </c>
       <c r="I5" s="56"/>
       <c r="J5" s="56"/>
     </row>
@@ -17055,7 +17057,9 @@
       <c r="G9" s="211">
         <v>195000000000</v>
       </c>
-      <c r="H9" s="62"/>
+      <c r="H9" s="62">
+        <v>78500</v>
+      </c>
       <c r="I9" s="62"/>
       <c r="J9" s="62"/>
     </row>

--- a/Database/260126_Datenbankdefinition.xlsx
+++ b/Database/260126_Datenbankdefinition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonathanbieg/Documents/Master Thesis/1_Code/Python Repository/SDSD_Bieg/Database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03CE3E68-0469-A74A-BDA0-BB8187620FEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1594CA47-2175-8149-86C5-8BB35061CC53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17160" activeTab="1" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17160" activeTab="2" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
   </bookViews>
   <sheets>
     <sheet name="products" sheetId="1" r:id="rId1"/>
@@ -93,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1906" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1904" uniqueCount="525">
   <si>
     <t>B500B</t>
   </si>
@@ -17177,11 +17177,11 @@
       <c r="B4" s="52" t="s">
         <v>402</v>
       </c>
-      <c r="C4" s="52" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="52" t="s">
-        <v>7</v>
+      <c r="C4" s="52">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="D4" s="52">
+        <v>6000</v>
       </c>
       <c r="E4" s="53">
         <v>80</v>

--- a/Database/260126_Datenbankdefinition.xlsx
+++ b/Database/260126_Datenbankdefinition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonathanbieg/Documents/Master Thesis/1_Code/Python Repository/SDSD_Bieg/Database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1594CA47-2175-8149-86C5-8BB35061CC53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3773198-9B14-1F43-8E20-3F9D5FEFC04D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17160" activeTab="2" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
+    <workbookView xWindow="-20" yWindow="660" windowWidth="29400" windowHeight="17160" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
   </bookViews>
   <sheets>
     <sheet name="products" sheetId="1" r:id="rId1"/>
@@ -2752,10 +2752,82 @@
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
         <top style="thin">
@@ -2789,7 +2861,7 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
         <top style="thin">
@@ -2823,7 +2895,7 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
         <top style="thin">
@@ -2832,8 +2904,74 @@
         <bottom style="thin">
           <color theme="4" tint="0.39997558519241921"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -3669,82 +3807,10 @@
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
+          <bgColor auto="1"/>
         </patternFill>
       </fill>
       <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
         <top style="thin">
@@ -3778,7 +3844,7 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
         <top style="thin">
@@ -3812,7 +3878,7 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
         <top style="thin">
@@ -3821,74 +3887,8 @@
         <bottom style="thin">
           <color theme="4" tint="0.39997558519241921"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -4135,42 +4135,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}" name="Table2" displayName="Table2" ref="A1:AC132" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}" name="Table2" displayName="Table2" ref="A1:AC132" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46">
   <autoFilter ref="A1:AC132" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}"/>
   <tableColumns count="29">
-    <tableColumn id="9" xr3:uid="{1DBBD25D-72F9-4A81-9CFA-500505E3628D}" name="ID" dataDxfId="41"/>
-    <tableColumn id="14" xr3:uid="{6844A52F-C967-44C0-BF5C-160C47AB6E64}" name="PRO_ID" dataDxfId="40"/>
-    <tableColumn id="12" xr3:uid="{4EDF1E73-4744-474F-8DFE-7F72FB05613C}" name="EPD_ID" dataDxfId="39"/>
-    <tableColumn id="1" xr3:uid="{1CF2E22E-1020-4F35-B31F-6350A15A5DE8}" name="SOURCE" dataDxfId="38"/>
-    <tableColumn id="27" xr3:uid="{07F74D5D-9130-4120-B02C-A11234427F46}" name="KBOB ID-Nr." dataDxfId="37"/>
-    <tableColumn id="11" xr3:uid="{81FE7F31-5F54-40F9-B99E-827E048F7DB5}" name="EPD_DATE" dataDxfId="36"/>
-    <tableColumn id="10" xr3:uid="{54D8BA04-0FEF-4C3B-9B14-59E8F982CD3F}" name="VALID_TO" dataDxfId="35"/>
-    <tableColumn id="22" xr3:uid="{3D6FC370-B8A8-40C3-9FC8-791B178DDFDF}" name="COUNTRY" dataDxfId="34"/>
-    <tableColumn id="4" xr3:uid="{25C7280F-4E3E-4E39-BDBB-DC06DF090C5B}" name="PRODUCT_NAME" dataDxfId="33"/>
-    <tableColumn id="26" xr3:uid="{1053A7DD-B11F-4E75-92EC-BC0F866E90B4}" name="OEKOBAUDAT_ID" dataDxfId="32"/>
-    <tableColumn id="25" xr3:uid="{295F99F8-E318-45C9-833E-F0B45A26471A}" name="MATERIAL_GROUP" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{1326FCEF-D1EE-4F3A-BB8B-77CB4EC72B0C}" name="MATERIAL" dataDxfId="30"/>
-    <tableColumn id="5" xr3:uid="{9B2A7F84-D968-4A00-B61F-23BB0661E7A3}" name="CEMENT" dataDxfId="29"/>
-    <tableColumn id="6" xr3:uid="{2F6E5831-6238-4360-9CFD-ED23A193E761}" name="MECH_PROP" dataDxfId="28"/>
-    <tableColumn id="13" xr3:uid="{50DAB01C-8AF5-4E0C-9904-54F70B81BC55}" name="DENSITY" dataDxfId="27"/>
-    <tableColumn id="18" xr3:uid="{F799A4D4-9543-475F-989E-CFBA47249558}" name="EXPOSITIONSKLASSE" dataDxfId="26"/>
-    <tableColumn id="17" xr3:uid="{ECCBC067-991C-4C60-942D-806BCD77B990}" name="GROESSTKORN" dataDxfId="25"/>
-    <tableColumn id="16" xr3:uid="{05157B85-D5FB-4844-9B53-D8AB09BCE0D9}" name="CHLORIDGEHALT" dataDxfId="24"/>
-    <tableColumn id="15" xr3:uid="{9F53CF50-7148-405A-9295-1F0C3C45645A}" name="KONSISTENZKLASSE" dataDxfId="23"/>
-    <tableColumn id="7" xr3:uid="{E23232F6-E86E-4AD2-8257-F30C0D1F7368}" name="Total_GWP" dataDxfId="22"/>
-    <tableColumn id="20" xr3:uid="{0A9001B4-3AB4-4C58-B125-0B2AA4DB2681}" name="A1toA3_GWP" dataDxfId="21">
+    <tableColumn id="9" xr3:uid="{1DBBD25D-72F9-4A81-9CFA-500505E3628D}" name="ID" dataDxfId="45"/>
+    <tableColumn id="14" xr3:uid="{6844A52F-C967-44C0-BF5C-160C47AB6E64}" name="PRO_ID" dataDxfId="44"/>
+    <tableColumn id="12" xr3:uid="{4EDF1E73-4744-474F-8DFE-7F72FB05613C}" name="EPD_ID" dataDxfId="43"/>
+    <tableColumn id="1" xr3:uid="{1CF2E22E-1020-4F35-B31F-6350A15A5DE8}" name="SOURCE" dataDxfId="42"/>
+    <tableColumn id="27" xr3:uid="{07F74D5D-9130-4120-B02C-A11234427F46}" name="KBOB ID-Nr." dataDxfId="41"/>
+    <tableColumn id="11" xr3:uid="{81FE7F31-5F54-40F9-B99E-827E048F7DB5}" name="EPD_DATE" dataDxfId="40"/>
+    <tableColumn id="10" xr3:uid="{54D8BA04-0FEF-4C3B-9B14-59E8F982CD3F}" name="VALID_TO" dataDxfId="39"/>
+    <tableColumn id="22" xr3:uid="{3D6FC370-B8A8-40C3-9FC8-791B178DDFDF}" name="COUNTRY" dataDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{25C7280F-4E3E-4E39-BDBB-DC06DF090C5B}" name="PRODUCT_NAME" dataDxfId="37"/>
+    <tableColumn id="26" xr3:uid="{1053A7DD-B11F-4E75-92EC-BC0F866E90B4}" name="OEKOBAUDAT_ID" dataDxfId="36"/>
+    <tableColumn id="25" xr3:uid="{295F99F8-E318-45C9-833E-F0B45A26471A}" name="MATERIAL_GROUP" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{1326FCEF-D1EE-4F3A-BB8B-77CB4EC72B0C}" name="MATERIAL" dataDxfId="34"/>
+    <tableColumn id="5" xr3:uid="{9B2A7F84-D968-4A00-B61F-23BB0661E7A3}" name="CEMENT" dataDxfId="33"/>
+    <tableColumn id="6" xr3:uid="{2F6E5831-6238-4360-9CFD-ED23A193E761}" name="MECH_PROP" dataDxfId="32"/>
+    <tableColumn id="13" xr3:uid="{50DAB01C-8AF5-4E0C-9904-54F70B81BC55}" name="DENSITY" dataDxfId="31"/>
+    <tableColumn id="18" xr3:uid="{F799A4D4-9543-475F-989E-CFBA47249558}" name="EXPOSITIONSKLASSE" dataDxfId="30"/>
+    <tableColumn id="17" xr3:uid="{ECCBC067-991C-4C60-942D-806BCD77B990}" name="GROESSTKORN" dataDxfId="29"/>
+    <tableColumn id="16" xr3:uid="{05157B85-D5FB-4844-9B53-D8AB09BCE0D9}" name="CHLORIDGEHALT" dataDxfId="28"/>
+    <tableColumn id="15" xr3:uid="{9F53CF50-7148-405A-9295-1F0C3C45645A}" name="KONSISTENZKLASSE" dataDxfId="27"/>
+    <tableColumn id="7" xr3:uid="{E23232F6-E86E-4AD2-8257-F30C0D1F7368}" name="Total_GWP" dataDxfId="26"/>
+    <tableColumn id="20" xr3:uid="{0A9001B4-3AB4-4C58-B125-0B2AA4DB2681}" name="A1toA3_GWP" dataDxfId="25">
       <calculatedColumnFormula>119+10.9+238</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{2799394A-C481-45CE-B194-AAABAB0AED38}" name="C1toC4_GWP" dataDxfId="20">
+    <tableColumn id="21" xr3:uid="{2799394A-C481-45CE-B194-AAABAB0AED38}" name="C1toC4_GWP" dataDxfId="24">
       <calculatedColumnFormula>51.1+26+2.64+12.6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{70561D70-9D02-4E93-A395-229DA8696DDA}" name="ValidEPD" dataDxfId="19">
+    <tableColumn id="19" xr3:uid="{70561D70-9D02-4E93-A395-229DA8696DDA}" name="ValidEPD" dataDxfId="23">
       <calculatedColumnFormula>IF(OR($D2="Ecoinvent",$D2="Betonsortenrechner",$D2="KBOB",$T2&lt;=0),0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{92D55BC7-F55B-406A-B127-69EC2F0A8B77}" name="noch gültig" dataDxfId="18">
+    <tableColumn id="29" xr3:uid="{92D55BC7-F55B-406A-B127-69EC2F0A8B77}" name="noch gültig" dataDxfId="22">
       <calculatedColumnFormula>IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{DB90AC0A-8933-4040-BADE-E6EE11AC8BD7}" name="Statistik" dataDxfId="17">
+    <tableColumn id="3" xr3:uid="{DB90AC0A-8933-4040-BADE-E6EE11AC8BD7}" name="Statistik" dataDxfId="21">
       <calculatedColumnFormula array="1">IF($W2&lt;&gt;0,
 IF(AND(
                          T2&gt;=_xlfn.PERCENTILE.INC(_xlfn._xlws.FILTER($T$2:$T$148, ($L$2:$L$148=L2)*($W$2:$W$148=1)),0.1),
@@ -4178,44 +4178,44 @@
                ),1,0),
 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{BBA6C134-63F9-4711-8B25-086098EC2CB0}" name="Cost" dataDxfId="16"/>
-    <tableColumn id="24" xr3:uid="{5321A0E1-043C-4E95-A6DA-41830364B2BC}" name="Anmerkung" dataDxfId="15"/>
-    <tableColumn id="23" xr3:uid="{61456234-34E8-4222-B2D6-9DDA8E83B081}" name="Spalte 1" dataDxfId="14"/>
-    <tableColumn id="28" xr3:uid="{D1FC9AF8-A0AE-CE49-8F27-4BB569415BF3}" name="T_construction" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{BBA6C134-63F9-4711-8B25-086098EC2CB0}" name="Cost" dataDxfId="20"/>
+    <tableColumn id="24" xr3:uid="{5321A0E1-043C-4E95-A6DA-41830364B2BC}" name="Anmerkung" dataDxfId="19"/>
+    <tableColumn id="23" xr3:uid="{61456234-34E8-4222-B2D6-9DDA8E83B081}" name="Spalte 1" dataDxfId="18"/>
+    <tableColumn id="28" xr3:uid="{D1FC9AF8-A0AE-CE49-8F27-4BB569415BF3}" name="T_construction" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}" name="Tabelle4" displayName="Tabelle4" ref="A1:J9" totalsRowShown="0" headerRowDxfId="58" dataDxfId="56" headerRowBorderDxfId="57" tableBorderDxfId="55" totalsRowBorderDxfId="54">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}" name="Tabelle4" displayName="Tabelle4" ref="A1:J9" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13" totalsRowBorderDxfId="12">
   <autoFilter ref="A1:J9" xr:uid="{188FAA96-3B75-4826-B66B-A81D5BCFC670}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{AF3C694B-2C8A-40EE-B8BB-2EC9EB81A87A}" name="mat_ID" dataDxfId="53"/>
-    <tableColumn id="2" xr3:uid="{B447FBC2-C455-4332-8F47-150B112A57E0}" name="name" dataDxfId="52"/>
-    <tableColumn id="3" xr3:uid="{BAFC6B47-7268-46CC-A881-892C9A1F4334}" name="strength_comp" dataDxfId="51"/>
-    <tableColumn id="4" xr3:uid="{6FC4C8EB-7581-4E67-81CE-C724161F0838}" name="strength_tens" dataDxfId="50"/>
-    <tableColumn id="5" xr3:uid="{A875970E-61A9-43B5-9361-7616A74C3147}" name="strength_bend" dataDxfId="49"/>
-    <tableColumn id="6" xr3:uid="{EF5B3A69-DD70-420A-88FF-4FE8772A2E14}" name="strength_shea" dataDxfId="48"/>
-    <tableColumn id="7" xr3:uid="{ED461A80-736C-42BD-81BC-C5C0C80FF34C}" name="E_modulus" dataDxfId="47"/>
-    <tableColumn id="8" xr3:uid="{68E47481-7028-4427-B126-2A046FC46737}" name="density_load" dataDxfId="46"/>
-    <tableColumn id="9" xr3:uid="{7AB34570-2BD4-417F-B141-70612577C7D6}" name="burn_rate" dataDxfId="45"/>
-    <tableColumn id="10" xr3:uid="{69298654-E280-9D4B-9717-7904FADC15B5}" name="phi" dataDxfId="44"/>
+    <tableColumn id="1" xr3:uid="{AF3C694B-2C8A-40EE-B8BB-2EC9EB81A87A}" name="mat_ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{B447FBC2-C455-4332-8F47-150B112A57E0}" name="name" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{BAFC6B47-7268-46CC-A881-892C9A1F4334}" name="strength_comp" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{6FC4C8EB-7581-4E67-81CE-C724161F0838}" name="strength_tens" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{A875970E-61A9-43B5-9361-7616A74C3147}" name="strength_bend" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{EF5B3A69-DD70-420A-88FF-4FE8772A2E14}" name="strength_shea" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{ED461A80-736C-42BD-81BC-C5C0C80FF34C}" name="E_modulus" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{68E47481-7028-4427-B126-2A046FC46737}" name="density_load" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{7AB34570-2BD4-417F-B141-70612577C7D6}" name="burn_rate" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{69298654-E280-9D4B-9717-7904FADC15B5}" name="phi" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1CD264FD-E2C0-E94F-B387-736226CC982D}" name="Tabelle42" displayName="Tabelle42" ref="A1:F6" totalsRowShown="0" headerRowDxfId="12" dataDxfId="10" headerRowBorderDxfId="11" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1CD264FD-E2C0-E94F-B387-736226CC982D}" name="Tabelle42" displayName="Tabelle42" ref="A1:F6" totalsRowShown="0" headerRowDxfId="58" dataDxfId="56" headerRowBorderDxfId="57" tableBorderDxfId="55" totalsRowBorderDxfId="54">
   <autoFilter ref="A1:F6" xr:uid="{1CD264FD-E2C0-E94F-B387-736226CC982D}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{6590463D-C242-4C4D-AA1F-6FA1F0D35E6F}" name="mat_ID" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{603BAED4-55F2-D040-9D73-1611C1564A84}" name="name" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{D6CC67C0-1ACA-D446-A6F3-00BCC3AC8DAC}" name="d" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{3D62C7FF-3D7F-B245-A874-3A95DF0C49D2}" name="K_ser" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{0C35052C-7630-EC48-BB52-4928EDE8D2AC}" name="Cost" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{5101DCF1-1E94-3949-9F50-D0C3653EA4AB}" name="T_construction" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{6590463D-C242-4C4D-AA1F-6FA1F0D35E6F}" name="mat_ID" dataDxfId="53"/>
+    <tableColumn id="2" xr3:uid="{603BAED4-55F2-D040-9D73-1611C1564A84}" name="name" dataDxfId="52"/>
+    <tableColumn id="3" xr3:uid="{D6CC67C0-1ACA-D446-A6F3-00BCC3AC8DAC}" name="d" dataDxfId="51"/>
+    <tableColumn id="4" xr3:uid="{3D62C7FF-3D7F-B245-A874-3A95DF0C49D2}" name="K_ser" dataDxfId="50"/>
+    <tableColumn id="5" xr3:uid="{0C35052C-7630-EC48-BB52-4928EDE8D2AC}" name="Cost" dataDxfId="49"/>
+    <tableColumn id="6" xr3:uid="{5101DCF1-1E94-3949-9F50-D0C3653EA4AB}" name="T_construction" dataDxfId="48"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4528,9 +4528,12 @@
     <col min="5" max="7" width="10.6640625" customWidth="1"/>
     <col min="8" max="8" width="10.6640625" style="44" customWidth="1"/>
     <col min="9" max="9" width="19.5" customWidth="1"/>
-    <col min="10" max="11" width="10.6640625" customWidth="1"/>
+    <col min="10" max="10" width="10.6640625" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
     <col min="12" max="12" width="35" style="51" customWidth="1"/>
-    <col min="13" max="15" width="10.6640625" customWidth="1"/>
+    <col min="13" max="13" width="10.6640625" customWidth="1"/>
+    <col min="14" max="14" width="21.83203125" customWidth="1"/>
+    <col min="15" max="15" width="10.6640625" customWidth="1"/>
     <col min="16" max="16" width="6.6640625" customWidth="1"/>
     <col min="17" max="18" width="6.6640625" style="45" customWidth="1"/>
     <col min="19" max="19" width="6.6640625" customWidth="1"/>
@@ -17406,7 +17409,7 @@
       </c>
       <c r="C6" s="56"/>
       <c r="D6" s="56">
-        <v>100000000</v>
+        <v>1000000000</v>
       </c>
       <c r="E6" s="62">
         <v>30</v>

--- a/Database/260126_Datenbankdefinition.xlsx
+++ b/Database/260126_Datenbankdefinition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonathanbieg/Documents/Master Thesis/1_Code/Python Repository/SDSD_Bieg/Database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3773198-9B14-1F43-8E20-3F9D5FEFC04D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB516A97-A7B2-5F49-9546-9C6F9CD423EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="660" windowWidth="29400" windowHeight="17160" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17160" activeTab="3" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
   </bookViews>
   <sheets>
     <sheet name="products" sheetId="1" r:id="rId1"/>
@@ -93,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1904" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1905" uniqueCount="526">
   <si>
     <t>B500B</t>
   </si>
@@ -1666,9 +1666,6 @@
     <t>phi</t>
   </si>
   <si>
-    <t>kerve</t>
-  </si>
-  <si>
     <t>K_ser</t>
   </si>
   <si>
@@ -1685,6 +1682,12 @@
   </si>
   <si>
     <t>Y1860</t>
+  </si>
+  <si>
+    <t>kerve_30</t>
+  </si>
+  <si>
+    <t>kerve_20</t>
   </si>
 </sst>
 </file>
@@ -1919,7 +1922,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -2232,12 +2235,49 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="212">
+  <cellXfs count="221">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2704,6 +2744,21 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="8" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4207,8 +4262,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1CD264FD-E2C0-E94F-B387-736226CC982D}" name="Tabelle42" displayName="Tabelle42" ref="A1:F6" totalsRowShown="0" headerRowDxfId="58" dataDxfId="56" headerRowBorderDxfId="57" tableBorderDxfId="55" totalsRowBorderDxfId="54">
-  <autoFilter ref="A1:F6" xr:uid="{1CD264FD-E2C0-E94F-B387-736226CC982D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1CD264FD-E2C0-E94F-B387-736226CC982D}" name="Tabelle42" displayName="Tabelle42" ref="A1:F7" totalsRowShown="0" headerRowDxfId="58" dataDxfId="56" headerRowBorderDxfId="57" tableBorderDxfId="55" totalsRowBorderDxfId="54">
+  <autoFilter ref="A1:F7" xr:uid="{1CD264FD-E2C0-E94F-B387-736226CC982D}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{6590463D-C242-4C4D-AA1F-6FA1F0D35E6F}" name="mat_ID" dataDxfId="53"/>
     <tableColumn id="2" xr3:uid="{603BAED4-55F2-D040-9D73-1611C1564A84}" name="name" dataDxfId="52"/>
@@ -4636,7 +4691,7 @@
         <v>497</v>
       </c>
       <c r="AC1" s="205" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="2" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
@@ -4727,7 +4782,7 @@
       <c r="AA2" s="11"/>
       <c r="AB2" s="21"/>
       <c r="AC2" s="210">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="3" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
@@ -4818,7 +4873,7 @@
       <c r="AA3" s="11"/>
       <c r="AB3" s="21"/>
       <c r="AC3" s="210">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="4" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
@@ -4909,7 +4964,7 @@
       <c r="AA4" s="11"/>
       <c r="AB4" s="21"/>
       <c r="AC4" s="210">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="5" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
@@ -5000,7 +5055,7 @@
       <c r="AA5" s="11"/>
       <c r="AB5" s="21"/>
       <c r="AC5" s="210">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="6" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
@@ -5091,7 +5146,7 @@
       <c r="AA6" s="11"/>
       <c r="AB6" s="21"/>
       <c r="AC6" s="210">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="7" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
@@ -5172,7 +5227,7 @@
       <c r="AA7" s="11"/>
       <c r="AB7" s="21"/>
       <c r="AC7" s="210">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="8" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
@@ -5253,7 +5308,7 @@
       <c r="AA8" s="11"/>
       <c r="AB8" s="21"/>
       <c r="AC8" s="210">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="9" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
@@ -5334,7 +5389,7 @@
       <c r="AA9" s="11"/>
       <c r="AB9" s="21"/>
       <c r="AC9" s="210">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="10" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
@@ -5415,7 +5470,7 @@
       <c r="AA10" s="11"/>
       <c r="AB10" s="21"/>
       <c r="AC10" s="210">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="11" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
@@ -5496,7 +5551,7 @@
       <c r="AA11" s="11"/>
       <c r="AB11" s="21"/>
       <c r="AC11" s="210">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="12" spans="1:29" s="10" customFormat="1" x14ac:dyDescent="0.2">
@@ -5587,7 +5642,7 @@
       <c r="AA12" s="11"/>
       <c r="AB12" s="21"/>
       <c r="AC12" s="210">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="13" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.2">
@@ -5681,7 +5736,7 @@
       <c r="AA13" s="38"/>
       <c r="AB13" s="21"/>
       <c r="AC13" s="210">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="14" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.2">
@@ -5775,7 +5830,7 @@
       <c r="AA14" s="38"/>
       <c r="AB14" s="21"/>
       <c r="AC14" s="210">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="15" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.2">
@@ -5869,7 +5924,7 @@
       <c r="AA15" s="38"/>
       <c r="AB15" s="21"/>
       <c r="AC15" s="210">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="16" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.2">
@@ -5963,7 +6018,7 @@
       <c r="AA16" s="38"/>
       <c r="AB16" s="21"/>
       <c r="AC16" s="210">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="17" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.2">
@@ -6057,7 +6112,7 @@
       <c r="AA17" s="38"/>
       <c r="AB17" s="21"/>
       <c r="AC17" s="210">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="18" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.2">
@@ -6151,7 +6206,7 @@
       <c r="AA18" s="38"/>
       <c r="AB18" s="21"/>
       <c r="AC18" s="210">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="19" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.2">
@@ -6245,7 +6300,7 @@
       <c r="AA19" s="38"/>
       <c r="AB19" s="21"/>
       <c r="AC19" s="210">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="20" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.2">
@@ -6339,7 +6394,7 @@
       <c r="AA20" s="38"/>
       <c r="AB20" s="21"/>
       <c r="AC20" s="210">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="21" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.2">
@@ -6433,7 +6488,7 @@
       <c r="AA21" s="38"/>
       <c r="AB21" s="21"/>
       <c r="AC21" s="210">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="22" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.2">
@@ -6527,7 +6582,7 @@
       <c r="AA22" s="38"/>
       <c r="AB22" s="21"/>
       <c r="AC22" s="210">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="23" spans="1:29" s="41" customFormat="1" x14ac:dyDescent="0.2">
@@ -6621,7 +6676,7 @@
       <c r="AA23" s="38"/>
       <c r="AB23" s="21"/>
       <c r="AC23" s="210">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.2">
@@ -6715,7 +6770,7 @@
       <c r="AA24" s="2"/>
       <c r="AB24" s="21"/>
       <c r="AC24" s="210">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.2">
@@ -6809,7 +6864,7 @@
       <c r="AA25" s="2"/>
       <c r="AB25" s="21"/>
       <c r="AC25" s="210">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.2">
@@ -6903,7 +6958,7 @@
       <c r="AA26" s="2"/>
       <c r="AB26" s="21"/>
       <c r="AC26" s="210">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.2">
@@ -6997,7 +7052,7 @@
       <c r="AA27" s="2"/>
       <c r="AB27" s="21"/>
       <c r="AC27" s="210">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.2">
@@ -7091,7 +7146,7 @@
       <c r="AA28" s="2"/>
       <c r="AB28" s="21"/>
       <c r="AC28" s="210">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.2">
@@ -7185,7 +7240,7 @@
       <c r="AA29" s="2"/>
       <c r="AB29" s="21"/>
       <c r="AC29" s="210">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="30" spans="1:29" x14ac:dyDescent="0.2">
@@ -7279,7 +7334,7 @@
       <c r="AA30" s="2"/>
       <c r="AB30" s="21"/>
       <c r="AC30" s="210">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="31" spans="1:29" x14ac:dyDescent="0.2">
@@ -7355,7 +7410,7 @@
       <c r="AA31" s="2"/>
       <c r="AB31" s="179"/>
       <c r="AC31" s="210">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.2">
@@ -7431,7 +7486,7 @@
       <c r="AA32" s="2"/>
       <c r="AB32" s="182"/>
       <c r="AC32" s="210">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="33" spans="1:29" x14ac:dyDescent="0.2">
@@ -7507,7 +7562,7 @@
       <c r="AA33" s="2"/>
       <c r="AB33" s="182"/>
       <c r="AC33" s="210">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="34" spans="1:29" x14ac:dyDescent="0.2">
@@ -7583,7 +7638,7 @@
       <c r="AA34" s="2"/>
       <c r="AB34" s="182"/>
       <c r="AC34" s="210">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="35" spans="1:29" x14ac:dyDescent="0.2">
@@ -7659,7 +7714,7 @@
       <c r="AA35" s="2"/>
       <c r="AB35" s="182"/>
       <c r="AC35" s="210">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="36" spans="1:29" x14ac:dyDescent="0.2">
@@ -7735,7 +7790,7 @@
       <c r="AA36" s="2"/>
       <c r="AB36" s="182"/>
       <c r="AC36" s="210">
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="37" spans="1:29" s="15" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
@@ -7800,7 +7855,7 @@
       <c r="V37" s="142">
         <v>13</v>
       </c>
-      <c r="W37" s="50">
+      <c r="W37" s="212">
         <f ca="1">IF(OR($D37="Ecoinvent",$D37="Betonsortenrechner",$D37="KBOB",$T37&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
@@ -7817,13 +7872,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z37" s="206">
+      <c r="Z37" s="213">
         <v>206</v>
       </c>
       <c r="AA37" s="13"/>
-      <c r="AB37" s="182"/>
-      <c r="AC37" s="210">
-        <v>0.55000000000000004</v>
+      <c r="AB37" s="214"/>
+      <c r="AC37" s="215">
+        <v>0.4</v>
       </c>
     </row>
     <row r="38" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.2">
@@ -9511,7 +9566,7 @@
       <c r="V55" s="144" t="s">
         <v>167</v>
       </c>
-      <c r="W55" s="50">
+      <c r="W55" s="212">
         <f ca="1">IF(OR($D55="Ecoinvent",$D55="Betonsortenrechner",$D55="KBOB",$T55&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
@@ -9528,13 +9583,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z55" s="207">
+      <c r="Z55" s="216">
         <f>2.01*Table2[[#This Row],[DENSITY]]</f>
         <v>15778.499999999998</v>
       </c>
       <c r="AA55" s="4"/>
-      <c r="AB55" s="183"/>
-      <c r="AC55" s="210">
+      <c r="AB55" s="217"/>
+      <c r="AC55" s="215">
         <f>0.009*Table2[[#This Row],[DENSITY]]</f>
         <v>70.649999999999991</v>
       </c>
@@ -9624,8 +9679,8 @@
         <v>0</v>
       </c>
       <c r="Z56" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA56" s="11"/>
       <c r="AB56" s="183"/>
@@ -9718,8 +9773,8 @@
         <v>0</v>
       </c>
       <c r="Z57" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA57" s="11"/>
       <c r="AB57" s="183"/>
@@ -9812,8 +9867,8 @@
         <v>0</v>
       </c>
       <c r="Z58" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA58" s="11"/>
       <c r="AB58" s="183"/>
@@ -9906,8 +9961,8 @@
         <v>0</v>
       </c>
       <c r="Z59" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA59" s="11"/>
       <c r="AB59" s="183"/>
@@ -10000,8 +10055,8 @@
         <v>0</v>
       </c>
       <c r="Z60" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>1700</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1250</v>
       </c>
       <c r="AA60" s="11"/>
       <c r="AB60" s="183"/>
@@ -10094,8 +10149,8 @@
         <v>0</v>
       </c>
       <c r="Z61" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>1700</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1250</v>
       </c>
       <c r="AA61" s="11"/>
       <c r="AB61" s="183"/>
@@ -10185,8 +10240,8 @@
         <v>0</v>
       </c>
       <c r="Z62" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA62" s="16"/>
       <c r="AB62" s="182"/>
@@ -10273,8 +10328,8 @@
         <v>0</v>
       </c>
       <c r="Z63" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA63" s="16"/>
       <c r="AB63" s="182"/>
@@ -10363,8 +10418,8 @@
         <v>0</v>
       </c>
       <c r="Z64" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA64" s="16"/>
       <c r="AB64" s="182"/>
@@ -10451,8 +10506,8 @@
         <v>0</v>
       </c>
       <c r="Z65" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA65" s="16"/>
       <c r="AB65" s="182"/>
@@ -10539,8 +10594,8 @@
         <v>0</v>
       </c>
       <c r="Z66" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>1700</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1250</v>
       </c>
       <c r="AA66" s="16"/>
       <c r="AB66" s="182"/>
@@ -10634,8 +10689,8 @@
         <v>0</v>
       </c>
       <c r="Z67" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA67" s="2" t="s">
         <v>428</v>
@@ -10731,8 +10786,8 @@
         <v>1</v>
       </c>
       <c r="Z68" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA68" s="2" t="s">
         <v>429</v>
@@ -10828,8 +10883,8 @@
         <v>0</v>
       </c>
       <c r="Z69" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA69" s="2"/>
       <c r="AB69" s="21"/>
@@ -10923,8 +10978,8 @@
         <v>1</v>
       </c>
       <c r="Z70" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA70" s="2" t="s">
         <v>431</v>
@@ -11020,8 +11075,8 @@
         <v>1</v>
       </c>
       <c r="Z71" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA71" s="2" t="s">
         <v>430</v>
@@ -11117,8 +11172,8 @@
         <v>1</v>
       </c>
       <c r="Z72" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA72" s="2" t="s">
         <v>431</v>
@@ -11214,8 +11269,8 @@
         <v>0</v>
       </c>
       <c r="Z73" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA73" s="2"/>
       <c r="AB73" s="21"/>
@@ -11309,8 +11364,8 @@
         <v>1</v>
       </c>
       <c r="Z74" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>1700</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1250</v>
       </c>
       <c r="AA74" s="63" t="s">
         <v>416</v>
@@ -11408,8 +11463,8 @@
         <v>0</v>
       </c>
       <c r="Z75" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA75" s="2" t="s">
         <v>433</v>
@@ -11505,8 +11560,8 @@
         <v>0</v>
       </c>
       <c r="Z76" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA76" s="2" t="s">
         <v>433</v>
@@ -11601,8 +11656,8 @@
         <v>0</v>
       </c>
       <c r="Z77" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA77" s="2"/>
       <c r="AB77" s="21"/>
@@ -11696,8 +11751,8 @@
         <v>1</v>
       </c>
       <c r="Z78" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA78" s="2"/>
       <c r="AB78" s="21"/>
@@ -11791,8 +11846,8 @@
         <v>0</v>
       </c>
       <c r="Z79" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA79" s="2" t="s">
         <v>438</v>
@@ -11888,8 +11943,8 @@
         <v>0</v>
       </c>
       <c r="Z80" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA80" s="2" t="s">
         <v>439</v>
@@ -11985,8 +12040,8 @@
         <v>1</v>
       </c>
       <c r="Z81" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA81" s="2" t="s">
         <v>440</v>
@@ -12084,8 +12139,8 @@
         <v>0</v>
       </c>
       <c r="Z82" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA82" s="2"/>
       <c r="AB82" s="21"/>
@@ -12179,8 +12234,8 @@
         <v>1</v>
       </c>
       <c r="Z83" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA83" s="2"/>
       <c r="AB83" s="21"/>
@@ -12274,8 +12329,8 @@
         <v>1</v>
       </c>
       <c r="Z84" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA84" s="2"/>
       <c r="AB84" s="21"/>
@@ -12361,8 +12416,8 @@
         <v>0</v>
       </c>
       <c r="Z85" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA85" s="2"/>
       <c r="AB85" s="21"/>
@@ -12456,8 +12511,8 @@
         <v>0</v>
       </c>
       <c r="Z86" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA86" s="2"/>
       <c r="AB86" s="21"/>
@@ -12548,8 +12603,8 @@
         <v>0</v>
       </c>
       <c r="Z87" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA87" s="2"/>
       <c r="AB87" s="21"/>
@@ -12643,8 +12698,8 @@
         <v>1</v>
       </c>
       <c r="Z88" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA88" s="2"/>
       <c r="AB88" s="21"/>
@@ -12738,8 +12793,8 @@
         <v>1</v>
       </c>
       <c r="Z89" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA89" s="2" t="s">
         <v>434</v>
@@ -12834,8 +12889,8 @@
         <v>0</v>
       </c>
       <c r="Z90" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA90" s="2" t="s">
         <v>432</v>
@@ -12931,8 +12986,8 @@
         <v>1</v>
       </c>
       <c r="Z91" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA91" s="2" t="s">
         <v>435</v>
@@ -13028,8 +13083,8 @@
         <v>1</v>
       </c>
       <c r="Z92" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA92" s="2" t="s">
         <v>437</v>
@@ -13127,8 +13182,8 @@
         <v>1</v>
       </c>
       <c r="Z93" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA93" s="2" t="s">
         <v>434</v>
@@ -13224,8 +13279,8 @@
         <v>0</v>
       </c>
       <c r="Z94" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA94" s="2"/>
       <c r="AB94" s="21"/>
@@ -13319,8 +13374,8 @@
         <v>0</v>
       </c>
       <c r="Z95" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA95" s="2"/>
       <c r="AB95" s="21"/>
@@ -13414,8 +13469,8 @@
         <v>0</v>
       </c>
       <c r="Z96" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA96" s="2" t="s">
         <v>438</v>
@@ -13511,8 +13566,8 @@
         <v>0</v>
       </c>
       <c r="Z97" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>1700</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1250</v>
       </c>
       <c r="AA97" s="2" t="s">
         <v>418</v>
@@ -13608,8 +13663,8 @@
         <v>0</v>
       </c>
       <c r="Z98" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>1700</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1250</v>
       </c>
       <c r="AA98" s="2" t="s">
         <v>417</v>
@@ -13705,8 +13760,8 @@
         <v>0</v>
       </c>
       <c r="Z99" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>1700</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1250</v>
       </c>
       <c r="AA99" s="2" t="s">
         <v>420</v>
@@ -13802,8 +13857,8 @@
         <v>0</v>
       </c>
       <c r="Z100" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>1700</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1250</v>
       </c>
       <c r="AA100" s="2" t="s">
         <v>421</v>
@@ -13899,8 +13954,8 @@
         <v>0</v>
       </c>
       <c r="Z101" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>1700</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1250</v>
       </c>
       <c r="AA101" s="2" t="s">
         <v>422</v>
@@ -13980,7 +14035,7 @@
         <f>(0.341+6.93+800)/Table2[[#This Row],[DENSITY]]*1000</f>
         <v>1543.5391969407265</v>
       </c>
-      <c r="W102" s="50">
+      <c r="W102" s="218">
         <f ca="1">IF(OR($D102="Ecoinvent",$D102="Betonsortenrechner",$D102="KBOB",$T102&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
@@ -13998,8 +14053,8 @@
         <v>0</v>
       </c>
       <c r="Z102" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>1700</v>
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1250</v>
       </c>
       <c r="AA102" s="2" t="s">
         <v>426</v>
@@ -14079,11 +14134,11 @@
         <f>(0.8+4.9+758)/Table2[[#This Row],[DENSITY]]*1000</f>
         <v>1631.8376068376069</v>
       </c>
-      <c r="W103" s="50">
+      <c r="W103" s="212">
         <f ca="1">IF(OR($D103="Ecoinvent",$D103="Betonsortenrechner",$D103="KBOB",$T103&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
-      <c r="X103" s="198">
+      <c r="X103" s="199">
         <f ca="1">IF(Table2[[#This Row],[VALID_TO]]&gt;=TODAY(), 1, 0)</f>
         <v>0</v>
       </c>
@@ -14096,15 +14151,15 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z103" s="206">
-        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1700,2200)</f>
-        <v>2200</v>
+      <c r="Z103" s="213">
+        <f>IF(Table2[[#This Row],[MATERIAL]]="Solid_structural_timber",1250,1750)</f>
+        <v>1750</v>
       </c>
       <c r="AA103" s="4" t="s">
         <v>467</v>
       </c>
       <c r="AB103" s="37"/>
-      <c r="AC103" s="210">
+      <c r="AC103" s="215">
         <v>1</v>
       </c>
     </row>
@@ -15497,7 +15552,7 @@
         <f>1.1+9.68+26.7</f>
         <v>37.479999999999997</v>
       </c>
-      <c r="W118" s="158">
+      <c r="W118" s="219">
         <v>0</v>
       </c>
       <c r="X118" s="193">
@@ -15591,7 +15646,7 @@
         <f>21.5+68.6</f>
         <v>90.1</v>
       </c>
-      <c r="W119" s="50">
+      <c r="W119" s="218">
         <f ca="1">IF(OR($D119="Ecoinvent",$D119="Betonsortenrechner",$D119="KBOB",$T119&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
@@ -15686,7 +15741,7 @@
         <f>5.85+7.57</f>
         <v>13.42</v>
       </c>
-      <c r="W120" s="50">
+      <c r="W120" s="218">
         <f ca="1">IF(OR($D120="Ecoinvent",$D120="Betonsortenrechner",$D120="KBOB",$T120&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
@@ -15782,7 +15837,7 @@
         <f>21.4+6.84+2.22</f>
         <v>30.459999999999997</v>
       </c>
-      <c r="W121" s="50">
+      <c r="W121" s="212">
         <f ca="1">IF(OR($D121="Ecoinvent",$D121="Betonsortenrechner",$D121="KBOB",$T121&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>0</v>
       </c>
@@ -15799,7 +15854,7 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z121" s="208">
+      <c r="Z121" s="216">
         <f>17*Table2[[#This Row],[DENSITY]]</f>
         <v>133450</v>
       </c>
@@ -15807,7 +15862,7 @@
         <v>493</v>
       </c>
       <c r="AB121" s="37"/>
-      <c r="AC121" s="210">
+      <c r="AC121" s="215">
         <f t="shared" ref="AC121" si="2">1.2</f>
         <v>1.2</v>
       </c>
@@ -15851,7 +15906,7 @@
         <v>427</v>
       </c>
       <c r="N122" s="26" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="O122" s="26"/>
       <c r="P122" s="3"/>
@@ -15938,7 +15993,7 @@
         <v>427</v>
       </c>
       <c r="N123" s="26" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="O123" s="26"/>
       <c r="P123" s="3"/>
@@ -16023,7 +16078,7 @@
         <v>427</v>
       </c>
       <c r="N124" s="26" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="O124" s="26"/>
       <c r="P124" s="3"/>
@@ -16110,7 +16165,7 @@
         <v>427</v>
       </c>
       <c r="N125" s="26" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="O125" s="26"/>
       <c r="P125" s="3"/>
@@ -16198,7 +16253,7 @@
         <v>427</v>
       </c>
       <c r="N126" s="26" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="O126" s="26"/>
       <c r="P126" s="3"/>
@@ -16284,7 +16339,7 @@
         <v>427</v>
       </c>
       <c r="N127" s="26" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="O127" s="26"/>
       <c r="P127" s="3"/>
@@ -16368,7 +16423,7 @@
         <v>427</v>
       </c>
       <c r="N128" s="26" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="O128" s="26"/>
       <c r="P128" s="3"/>
@@ -16453,7 +16508,7 @@
         <v>427</v>
       </c>
       <c r="N129" s="26" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="O129" s="26"/>
       <c r="P129" s="3"/>
@@ -16538,7 +16593,7 @@
         <v>427</v>
       </c>
       <c r="N130" s="29" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="O130" s="29"/>
       <c r="P130" s="5"/>
@@ -16556,7 +16611,7 @@
         <f>3.59+0.0792+0.326</f>
         <v>3.9952000000000001</v>
       </c>
-      <c r="W130" s="50">
+      <c r="W130" s="212">
         <f ca="1">IF(OR($D130="Ecoinvent",$D130="Betonsortenrechner",$D130="KBOB",$T130&lt;=0,Table2[[#This Row],[VALID_TO]]&lt;=TODAY()),0,1)</f>
         <v>1</v>
       </c>
@@ -16573,13 +16628,13 @@
 0)</f>
         <v>0</v>
       </c>
-      <c r="Z130" s="209">
+      <c r="Z130" s="220">
         <f t="shared" si="3"/>
         <v>78500</v>
       </c>
       <c r="AA130" s="4"/>
-      <c r="AB130" s="21"/>
-      <c r="AC130" s="210">
+      <c r="AB130" s="37"/>
+      <c r="AC130" s="215">
         <f t="shared" si="4"/>
         <v>157</v>
       </c>
@@ -17049,7 +17104,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="62" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C9" s="62"/>
       <c r="D9" s="62">
@@ -17113,10 +17168,10 @@
         <v>399</v>
       </c>
       <c r="H1" s="204" t="s">
+        <v>520</v>
+      </c>
+      <c r="I1" s="204" t="s">
         <v>521</v>
-      </c>
-      <c r="I1" s="204" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
@@ -17145,7 +17200,7 @@
         <v>9626</v>
       </c>
       <c r="I2">
-        <v>0.55000000000000004</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -17172,7 +17227,7 @@
         <v>391</v>
       </c>
       <c r="I3">
-        <v>0.55000000000000004</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -17200,7 +17255,7 @@
         <v>335</v>
       </c>
       <c r="I4">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -17253,7 +17308,7 @@
         <v>335</v>
       </c>
       <c r="I6">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -17279,7 +17334,7 @@
         <v>335</v>
       </c>
       <c r="I7">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -17298,6 +17353,7 @@
     <col min="2" max="2" width="11.1640625" customWidth="1"/>
     <col min="3" max="3" width="27.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27.33203125" customWidth="1"/>
+    <col min="6" max="7" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -17308,16 +17364,16 @@
         <v>407</v>
       </c>
       <c r="C1" s="61" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D1" s="61" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E1" s="61" t="s">
         <v>127</v>
       </c>
       <c r="F1" s="61" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -17334,10 +17390,10 @@
         <v>5830000</v>
       </c>
       <c r="E2" s="203">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" s="203">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -17354,10 +17410,10 @@
         <v>7780000</v>
       </c>
       <c r="E3" s="56">
-        <v>9</v>
+        <v>5.5</v>
       </c>
       <c r="F3" s="56">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -17374,10 +17430,10 @@
         <v>9700000</v>
       </c>
       <c r="E4" s="56">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F4" s="56">
-        <v>2.5000000000000001E-2</v>
+        <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -17394,10 +17450,10 @@
         <v>11670000</v>
       </c>
       <c r="E5" s="56">
-        <v>11</v>
+        <v>6.5</v>
       </c>
       <c r="F5" s="56">
-        <v>2.5000000000000001E-2</v>
+        <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -17405,7 +17461,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="56" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="C6" s="56"/>
       <c r="D6" s="56">
@@ -17415,6 +17471,25 @@
         <v>30</v>
       </c>
       <c r="F6" s="62">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="62">
+        <v>6</v>
+      </c>
+      <c r="B7" s="62" t="s">
+        <v>524</v>
+      </c>
+      <c r="C7" s="62"/>
+      <c r="D7" s="62">
+        <f>D6*1.5</f>
+        <v>1500000000</v>
+      </c>
+      <c r="E7" s="62">
+        <v>30</v>
+      </c>
+      <c r="F7" s="62">
         <v>0.01</v>
       </c>
     </row>

--- a/Database/260126_Datenbankdefinition.xlsx
+++ b/Database/260126_Datenbankdefinition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonathanbieg/Documents/Master Thesis/1_Code/Python Repository/SDSD_Bieg/Database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB516A97-A7B2-5F49-9546-9C6F9CD423EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08A7B295-EF35-F44C-9023-62AF7636D597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17160" activeTab="3" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17160" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
   </bookViews>
   <sheets>
     <sheet name="products" sheetId="1" r:id="rId1"/>
@@ -2277,7 +2277,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="221">
+  <cellXfs count="224">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2759,6 +2759,15 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5188,7 +5197,9 @@
       <c r="N7" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="O7" s="25"/>
+      <c r="O7" s="221">
+        <v>2400</v>
+      </c>
       <c r="P7" s="12" t="s">
         <v>167</v>
       </c>
@@ -5269,7 +5280,9 @@
       <c r="N8" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="O8" s="25"/>
+      <c r="O8" s="221">
+        <v>2400</v>
+      </c>
       <c r="P8" s="12" t="s">
         <v>167</v>
       </c>
@@ -5350,7 +5363,9 @@
       <c r="N9" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="O9" s="25"/>
+      <c r="O9" s="221">
+        <v>2400</v>
+      </c>
       <c r="P9" s="12" t="s">
         <v>167</v>
       </c>
@@ -5431,7 +5446,9 @@
       <c r="N10" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="O10" s="25"/>
+      <c r="O10" s="221">
+        <v>2400</v>
+      </c>
       <c r="P10" s="12" t="s">
         <v>167</v>
       </c>
@@ -5512,7 +5529,9 @@
       <c r="N11" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="O11" s="25"/>
+      <c r="O11" s="221">
+        <v>2400</v>
+      </c>
       <c r="P11" s="12" t="s">
         <v>167</v>
       </c>
@@ -15908,7 +15927,9 @@
       <c r="N122" s="26" t="s">
         <v>523</v>
       </c>
-      <c r="O122" s="26"/>
+      <c r="O122" s="222">
+        <v>7850</v>
+      </c>
       <c r="P122" s="3"/>
       <c r="Q122" s="3"/>
       <c r="R122" s="3"/>
@@ -15995,7 +16016,9 @@
       <c r="N123" s="26" t="s">
         <v>523</v>
       </c>
-      <c r="O123" s="26"/>
+      <c r="O123" s="222">
+        <v>7850</v>
+      </c>
       <c r="P123" s="3"/>
       <c r="Q123" s="3"/>
       <c r="R123" s="3"/>
@@ -16080,7 +16103,9 @@
       <c r="N124" s="26" t="s">
         <v>523</v>
       </c>
-      <c r="O124" s="26"/>
+      <c r="O124" s="222">
+        <v>7850</v>
+      </c>
       <c r="P124" s="3"/>
       <c r="Q124" s="3"/>
       <c r="R124" s="3"/>
@@ -16167,7 +16192,9 @@
       <c r="N125" s="26" t="s">
         <v>523</v>
       </c>
-      <c r="O125" s="26"/>
+      <c r="O125" s="222">
+        <v>7850</v>
+      </c>
       <c r="P125" s="3"/>
       <c r="Q125" s="3"/>
       <c r="R125" s="3"/>
@@ -16255,7 +16282,9 @@
       <c r="N126" s="26" t="s">
         <v>523</v>
       </c>
-      <c r="O126" s="26"/>
+      <c r="O126" s="222">
+        <v>7850</v>
+      </c>
       <c r="P126" s="3"/>
       <c r="Q126" s="3"/>
       <c r="R126" s="3"/>
@@ -16341,7 +16370,9 @@
       <c r="N127" s="26" t="s">
         <v>523</v>
       </c>
-      <c r="O127" s="26"/>
+      <c r="O127" s="222">
+        <v>7850</v>
+      </c>
       <c r="P127" s="3"/>
       <c r="Q127" s="3"/>
       <c r="R127" s="3"/>
@@ -16425,7 +16456,9 @@
       <c r="N128" s="26" t="s">
         <v>523</v>
       </c>
-      <c r="O128" s="26"/>
+      <c r="O128" s="222">
+        <v>7850</v>
+      </c>
       <c r="P128" s="3"/>
       <c r="Q128" s="3"/>
       <c r="R128" s="3"/>
@@ -16510,7 +16543,9 @@
       <c r="N129" s="26" t="s">
         <v>523</v>
       </c>
-      <c r="O129" s="26"/>
+      <c r="O129" s="222">
+        <v>7850</v>
+      </c>
       <c r="P129" s="3"/>
       <c r="Q129" s="3"/>
       <c r="R129" s="3"/>
@@ -16595,7 +16630,9 @@
       <c r="N130" s="29" t="s">
         <v>523</v>
       </c>
-      <c r="O130" s="29"/>
+      <c r="O130" s="223">
+        <v>7850</v>
+      </c>
       <c r="P130" s="5"/>
       <c r="Q130" s="5"/>
       <c r="R130" s="5"/>
